--- a/data/PS - Estimation (version 1).xlsx
+++ b/data/PS - Estimation (version 1).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xvjm020\Documents\Personnel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D206C56-6050-43B9-A7A0-89D7D413A3EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5F237E5-471D-49FF-A1BC-285565C8140E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{9D83D047-1CAD-4BF9-942E-B289F790400E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9D83D047-1CAD-4BF9-942E-B289F790400E}"/>
   </bookViews>
   <sheets>
     <sheet name="Palmon" sheetId="2" r:id="rId1"/>
@@ -5231,11 +5231,11 @@
         <v>97</v>
       </c>
       <c r="E3" s="63">
-        <v>260</v>
-      </c>
-      <c r="F3" s="125" cm="1">
+        <v>270</v>
+      </c>
+      <c r="F3" s="125" t="str" cm="1">
         <f t="array" ref="F3">IsUpgradable(E3)</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="G3" s="127">
         <f t="shared" ref="G3:G26" si="0">INT(H3)</f>
@@ -5294,15 +5294,15 @@
       </c>
       <c r="X3" s="13" cm="1">
         <f t="array" ref="X3">LevelUpgradeCost($E3)</f>
-        <v>1235520000</v>
-      </c>
-      <c r="Y3" s="61">
+        <v>135120000</v>
+      </c>
+      <c r="Y3" s="61" t="str">
         <f>F3</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AA3" s="110">
         <f>$H3*1000+$E3</f>
-        <v>5260</v>
+        <v>5270</v>
       </c>
       <c r="AB3" s="110">
         <f>RANK($AA3,$AA$3:$AA$44)+COUNTIF($AA$3:$AA3,AA3)-1</f>
@@ -5347,11 +5347,11 @@
         <v>97</v>
       </c>
       <c r="E4" s="63">
-        <v>260</v>
-      </c>
-      <c r="F4" s="125" cm="1">
+        <v>270</v>
+      </c>
+      <c r="F4" s="125" t="str" cm="1">
         <f t="array" ref="F4">IsUpgradable(E4)</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="G4" s="127">
         <f t="shared" si="0"/>
@@ -5410,15 +5410,15 @@
       </c>
       <c r="X4" s="13" cm="1">
         <f t="array" ref="X4">LevelUpgradeCost($E4)</f>
-        <v>1235520000</v>
-      </c>
-      <c r="Y4" s="61">
+        <v>135120000</v>
+      </c>
+      <c r="Y4" s="61" t="str">
         <f t="shared" ref="Y4:Y44" si="4">F4</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AA4" s="110">
         <f t="shared" ref="AA4:AA44" si="5">$H4*1000+$E4</f>
-        <v>5260</v>
+        <v>5270</v>
       </c>
       <c r="AB4" s="63">
         <f>RANK($AA4,$AA$3:$AA$44)+COUNTIF($AA$3:$AA4,AA4)-1</f>
@@ -5465,10 +5465,10 @@
       </c>
       <c r="G5" s="127">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H5" s="201">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I5" s="123">
         <v>11</v>
@@ -5486,9 +5486,9 @@
         <f t="shared" si="1"/>
         <v>Max</v>
       </c>
-      <c r="N5" s="19" t="str">
+      <c r="N5" s="19">
         <f t="shared" si="2"/>
-        <v/>
+        <v>10</v>
       </c>
       <c r="P5" s="9">
         <f>IFERROR(CHOOSE(IF($H5&gt;=Details!$B$4,1,2),Details!$D$4,IF($H5&gt;Details!$B$4-1,IF($H5&lt;1,$H5,MOD($H5,Details!$B$4-1))*10*Details!$C$4,""))/Details!$D$4,0)</f>
@@ -5508,15 +5508,15 @@
       </c>
       <c r="T5" s="9">
         <f>IFERROR(CHOOSE(IF($H5&gt;=Details!$B$8,1,2),Details!$D$8,IF($H5&gt;Details!$B$8-1,IF($H5&lt;1,Details!$G$5,MOD($H5,Details!$B$8-1))*10*Details!$C$8,""))/Details!$D$8,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U5" s="9" cm="1">
         <f t="array" ref="U5">SUMPRODUCT(TRANSPOSE(Details!$D$4:$D$8),$P5:$T5)/Details!$D$9</f>
-        <v>0.48717948717948717</v>
+        <v>1</v>
       </c>
       <c r="V5" s="13" cm="1">
         <f t="array" ref="V5">Details!$D$9-SUMPRODUCT(TRANSPOSE(Details!$D$4:$D$8),$P5:$T5)-$I5</f>
-        <v>489</v>
+        <v>-11</v>
       </c>
       <c r="X5" s="13" cm="1">
         <f t="array" ref="X5">LevelUpgradeCost($E5)</f>
@@ -5528,15 +5528,15 @@
       </c>
       <c r="AA5" s="110">
         <f t="shared" si="5"/>
-        <v>4260</v>
+        <v>5260</v>
       </c>
       <c r="AB5" s="63">
         <f>RANK($AA5,$AA$3:$AA$44)+COUNTIF($AA$3:$AA5,AA5)-1</f>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AC5" s="61" cm="1">
         <f t="array" ref="AC5">IFERROR(_xlfn.IFS($AB5&lt;8,1,$AB5&lt;15,2,$AB5&lt;21,3),"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE5" s="63" t="s">
         <v>158</v>
@@ -5644,11 +5644,11 @@
       </c>
       <c r="AB6" s="63">
         <f>RANK($AA6,$AA$3:$AA$44)+COUNTIF($AA$3:$AA6,AA6)-1</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC6" s="61" cm="1">
         <f t="array" ref="AC6">IFERROR(_xlfn.IFS($AB6&lt;8,1,$AB6&lt;15,2,$AB6&lt;21,3),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE6" s="63" t="s">
         <v>186</v>
@@ -5682,21 +5682,21 @@
         <v>98</v>
       </c>
       <c r="E7" s="63">
-        <v>260</v>
-      </c>
-      <c r="F7" s="125" cm="1">
+        <v>270</v>
+      </c>
+      <c r="F7" s="125" t="str" cm="1">
         <f t="array" ref="F7">IsUpgradable(E7)</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="G7" s="127">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H7" s="201">
-        <v>4.0999999999999996</v>
+        <v>5</v>
       </c>
       <c r="I7" s="123">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J7" s="63">
         <v>15</v>
@@ -5705,15 +5705,15 @@
         <v>15</v>
       </c>
       <c r="L7" s="7">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="M7" s="7" t="str">
         <f t="shared" si="1"/>
         <v>Max</v>
       </c>
-      <c r="N7" s="19" t="str">
+      <c r="N7" s="19">
         <f t="shared" si="2"/>
-        <v/>
+        <v>10</v>
       </c>
       <c r="P7" s="9">
         <f>IFERROR(CHOOSE(IF($H7&gt;=Details!$B$4,1,2),Details!$D$4,IF($H7&gt;Details!$B$4-1,IF($H7&lt;1,$H7,MOD($H7,Details!$B$4-1))*10*Details!$C$4,""))/Details!$D$4,0)</f>
@@ -5733,31 +5733,31 @@
       </c>
       <c r="T7" s="9">
         <f>IFERROR(CHOOSE(IF($H7&gt;=Details!$B$8,1,2),Details!$D$8,IF($H7&gt;Details!$B$8-1,IF($H7&lt;1,Details!$G$5,MOD($H7,Details!$B$8-1))*10*Details!$C$8,""))/Details!$D$8,0)</f>
-        <v>0.19999999999999929</v>
+        <v>1</v>
       </c>
       <c r="U7" s="9" cm="1">
         <f t="array" ref="U7">SUMPRODUCT(TRANSPOSE(Details!$D$4:$D$8),$P7:$T7)/Details!$D$9</f>
-        <v>0.58974358974358942</v>
+        <v>1</v>
       </c>
       <c r="V7" s="13" cm="1">
         <f t="array" ref="V7">Details!$D$9-SUMPRODUCT(TRANSPOSE(Details!$D$4:$D$8),$P7:$T7)-$I7</f>
-        <v>383.00000000000034</v>
+        <v>0</v>
       </c>
       <c r="X7" s="13" cm="1">
         <f t="array" ref="X7">LevelUpgradeCost($E7)</f>
-        <v>1235520000</v>
-      </c>
-      <c r="Y7" s="61">
+        <v>135120000</v>
+      </c>
+      <c r="Y7" s="61" t="str">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AA7" s="110">
         <f t="shared" si="5"/>
-        <v>4360</v>
+        <v>5270</v>
       </c>
       <c r="AB7" s="63">
         <f>RANK($AA7,$AA$3:$AA$44)+COUNTIF($AA$3:$AA7,AA7)-1</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AC7" s="61" cm="1">
         <f t="array" ref="AC7">IFERROR(_xlfn.IFS($AB7&lt;8,1,$AB7&lt;15,2,$AB7&lt;21,3),"")</f>
@@ -6544,7 +6544,7 @@
       </c>
       <c r="AB14" s="63">
         <f>RANK($AA14,$AA$3:$AA$44)+COUNTIF($AA$3:$AA14,AA14)-1</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AC14" s="61" cm="1">
         <f t="array" ref="AC14">IFERROR(_xlfn.IFS($AB14&lt;8,1,$AB14&lt;15,2,$AB14&lt;21,3),"")</f>
@@ -8009,7 +8009,7 @@
       </c>
       <c r="AB27" s="63">
         <f>RANK($AA27,$AA$3:$AA$44)+COUNTIF($AA$3:$AA27,AA27)-1</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC27" s="61" cm="1">
         <f t="array" ref="AC27">IFERROR(_xlfn.IFS($AB27&lt;8,1,$AB27&lt;15,2,$AB27&lt;21,3),"")</f>
@@ -8156,7 +8156,7 @@
         <v>98</v>
       </c>
       <c r="E29" s="63">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="F29" s="125" cm="1">
         <f t="array" ref="F29">IsUpgradable(E29)</f>
@@ -8219,7 +8219,7 @@
       </c>
       <c r="X29" s="13" cm="1">
         <f t="array" ref="X29">LevelUpgradeCost($E29)</f>
-        <v>4721120000</v>
+        <v>4667020000</v>
       </c>
       <c r="Y29" s="61">
         <f t="shared" ref="Y29" si="10">F29</f>
@@ -8227,7 +8227,7 @@
       </c>
       <c r="AA29" s="110">
         <f t="shared" si="5"/>
-        <v>3382</v>
+        <v>3386</v>
       </c>
       <c r="AB29" s="63">
         <f>RANK($AA29,$AA$3:$AA$44)+COUNTIF($AA$3:$AA29,AA29)-1</f>
@@ -8692,11 +8692,11 @@
         <v>97</v>
       </c>
       <c r="E34" s="64">
-        <v>260</v>
-      </c>
-      <c r="F34" s="126" cm="1">
+        <v>270</v>
+      </c>
+      <c r="F34" s="126" t="str" cm="1">
         <f t="array" ref="F34">IsUpgradable(E34)</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="G34" s="129">
         <f t="shared" si="11"/>
@@ -8757,16 +8757,16 @@
       <c r="W34" s="141"/>
       <c r="X34" s="22" cm="1">
         <f t="array" ref="X34">LevelUpgradeCost($E34)</f>
-        <v>1235520000</v>
-      </c>
-      <c r="Y34" s="62">
+        <v>135120000</v>
+      </c>
+      <c r="Y34" s="62" t="str">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="Z34" s="141"/>
       <c r="AA34" s="112">
         <f t="shared" si="5"/>
-        <v>5260</v>
+        <v>5270</v>
       </c>
       <c r="AB34" s="64">
         <f>RANK($AA34,$AA$3:$AA$44)+COUNTIF($AA$3:$AA34,AA34)-1</f>
@@ -9963,14 +9963,14 @@
       <c r="D46" s="142"/>
       <c r="E46" s="1">
         <f>COUNTIF(E3:E44,"&gt;0")-COUNTIF(E3:E44,"="&amp;HallLevel*10)</f>
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F46" s="142"/>
       <c r="G46" s="142"/>
       <c r="I46" s="5"/>
       <c r="X46" s="5">
         <f>SUMPRODUCT(X3:X44,Y3:Y44)</f>
-        <v>95528193700</v>
+        <v>90532013700</v>
       </c>
     </row>
     <row r="47" spans="1:37" ht="12" customHeight="1" x14ac:dyDescent="0.2">
@@ -10105,7 +10105,7 @@
       </c>
       <c r="Q56" s="1">
         <f t="shared" ref="Q56:Q58" si="18">SUMIF($C$3:$C$44,"=" &amp; $P56,$E$3:$E$44)</f>
-        <v>1992</v>
+        <v>2026</v>
       </c>
       <c r="R56" s="1">
         <f t="shared" ref="R56:R58" si="19">COUNTIFS($C$3:$C$44,"=" &amp; $P56,$E$3:$E$44,"&gt;0")</f>
@@ -10113,7 +10113,7 @@
       </c>
       <c r="S56" s="1">
         <f t="shared" ref="S56:S58" si="20">Q56/R56</f>
-        <v>221.33333333333334</v>
+        <v>225.11111111111111</v>
       </c>
       <c r="X56"/>
     </row>
@@ -10131,7 +10131,7 @@
       </c>
       <c r="Q57" s="1">
         <f t="shared" si="18"/>
-        <v>1870</v>
+        <v>1880</v>
       </c>
       <c r="R57" s="1">
         <f t="shared" si="19"/>
@@ -10139,7 +10139,7 @@
       </c>
       <c r="S57" s="1">
         <f t="shared" si="20"/>
-        <v>233.75</v>
+        <v>235</v>
       </c>
       <c r="X57"/>
     </row>
@@ -10619,7 +10619,7 @@
     <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="str" cm="1">
         <f t="array" ref="A3">_xlfn.CONCAT(_xlfn.LAMBDA(_xlpm.cell,_xlpm.cell &amp; ",")(Palmon!B3:'Palmon'!AJ3))</f>
-        <v>Bufonobi,Water,Attack,260,1,5,5,0,30,20,20,Max,10,,1,1,1,1,1,1,0,,1235520000,1,,5260,1,1,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRXczs_Bjhslhr7Mf2HENU6MTyGpz0RJEMjNA&amp;s, , ,,,Shadowkaeru,</v>
+        <v>Bufonobi,Water,Attack,270,,5,5,0,30,20,20,Max,10,,1,1,1,1,1,1,0,,135120000,,,5270,1,1,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRXczs_Bjhslhr7Mf2HENU6MTyGpz0RJEMjNA&amp;s, , ,,,Shadowkaeru,</v>
       </c>
     </row>
     <row r="4" spans="1:35" x14ac:dyDescent="0.25">
@@ -10917,11 +10917,11 @@
       </c>
       <c r="D2">
         <f>Palmon!E3</f>
-        <v>260</v>
-      </c>
-      <c r="E2">
+        <v>270</v>
+      </c>
+      <c r="E2" t="str">
         <f>Palmon!F3</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="F2">
         <f>Palmon!G3</f>
@@ -10993,11 +10993,11 @@
       </c>
       <c r="W2">
         <f>Palmon!X3</f>
-        <v>1235520000</v>
-      </c>
-      <c r="X2">
+        <v>135120000</v>
+      </c>
+      <c r="X2" t="str">
         <f>Palmon!Y3</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="Y2">
         <f>Palmon!Z3</f>
@@ -11005,7 +11005,7 @@
       </c>
       <c r="Z2">
         <f>Palmon!AA3</f>
-        <v>5260</v>
+        <v>5270</v>
       </c>
       <c r="AA2">
         <f>Palmon!AB3</f>
@@ -11063,11 +11063,11 @@
       </c>
       <c r="D3">
         <f>Palmon!E4</f>
-        <v>260</v>
-      </c>
-      <c r="E3">
+        <v>270</v>
+      </c>
+      <c r="E3" t="str">
         <f>Palmon!F4</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="F3">
         <f>Palmon!G4</f>
@@ -11139,11 +11139,11 @@
       </c>
       <c r="W3">
         <f>Palmon!X4</f>
-        <v>1235520000</v>
-      </c>
-      <c r="X3">
+        <v>135120000</v>
+      </c>
+      <c r="X3" t="str">
         <f>Palmon!Y4</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="Y3">
         <f>Palmon!Z4</f>
@@ -11151,7 +11151,7 @@
       </c>
       <c r="Z3">
         <f>Palmon!AA4</f>
-        <v>5260</v>
+        <v>5270</v>
       </c>
       <c r="AA3">
         <f>Palmon!AB4</f>
@@ -11217,11 +11217,11 @@
       </c>
       <c r="F4">
         <f>Palmon!G5</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G4">
         <f>Palmon!H5</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H4">
         <f>Palmon!I5</f>
@@ -11243,9 +11243,9 @@
         <f>Palmon!M5</f>
         <v>Max</v>
       </c>
-      <c r="M4" t="str">
+      <c r="M4">
         <f>Palmon!N5</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="N4">
         <f>Palmon!O5</f>
@@ -11269,15 +11269,15 @@
       </c>
       <c r="S4">
         <f>Palmon!T5</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4">
         <f>Palmon!U5</f>
-        <v>0.48717948717948717</v>
+        <v>1</v>
       </c>
       <c r="U4">
         <f>Palmon!V5</f>
-        <v>489</v>
+        <v>-11</v>
       </c>
       <c r="V4">
         <f>Palmon!W5</f>
@@ -11297,15 +11297,15 @@
       </c>
       <c r="Z4">
         <f>Palmon!AA5</f>
-        <v>4260</v>
+        <v>5260</v>
       </c>
       <c r="AA4">
         <f>Palmon!AB5</f>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AB4">
         <f>Palmon!AC5</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC4">
         <f>Palmon!AD5</f>
@@ -11447,11 +11447,11 @@
       </c>
       <c r="AA5">
         <f>Palmon!AB6</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB5">
         <f>Palmon!AC6</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC5">
         <f>Palmon!AD6</f>
@@ -11501,23 +11501,23 @@
       </c>
       <c r="D6">
         <f>Palmon!E7</f>
-        <v>260</v>
-      </c>
-      <c r="E6">
+        <v>270</v>
+      </c>
+      <c r="E6" t="str">
         <f>Palmon!F7</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="F6">
         <f>Palmon!G7</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G6">
         <f>Palmon!H7</f>
-        <v>4.0999999999999996</v>
+        <v>5</v>
       </c>
       <c r="H6">
         <f>Palmon!I7</f>
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I6">
         <f>Palmon!J7</f>
@@ -11529,15 +11529,15 @@
       </c>
       <c r="K6">
         <f>Palmon!L7</f>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="L6" t="str">
         <f>Palmon!M7</f>
         <v>Max</v>
       </c>
-      <c r="M6" t="str">
+      <c r="M6">
         <f>Palmon!N7</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="N6">
         <f>Palmon!O7</f>
@@ -11561,15 +11561,15 @@
       </c>
       <c r="S6">
         <f>Palmon!T7</f>
-        <v>0.19999999999999929</v>
+        <v>1</v>
       </c>
       <c r="T6">
         <f>Palmon!U7</f>
-        <v>0.58974358974358942</v>
+        <v>1</v>
       </c>
       <c r="U6">
         <f>Palmon!V7</f>
-        <v>383.00000000000034</v>
+        <v>0</v>
       </c>
       <c r="V6">
         <f>Palmon!W7</f>
@@ -11577,11 +11577,11 @@
       </c>
       <c r="W6">
         <f>Palmon!X7</f>
-        <v>1235520000</v>
-      </c>
-      <c r="X6">
+        <v>135120000</v>
+      </c>
+      <c r="X6" t="str">
         <f>Palmon!Y7</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="Y6">
         <f>Palmon!Z7</f>
@@ -11589,11 +11589,11 @@
       </c>
       <c r="Z6">
         <f>Palmon!AA7</f>
-        <v>4360</v>
+        <v>5270</v>
       </c>
       <c r="AA6">
         <f>Palmon!AB7</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AB6">
         <f>Palmon!AC7</f>
@@ -12615,7 +12615,7 @@
       </c>
       <c r="AA13">
         <f>Palmon!AB14</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AB13">
         <f>Palmon!AC14</f>
@@ -14513,7 +14513,7 @@
       </c>
       <c r="AA26">
         <f>Palmon!AB27</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB26">
         <f>Palmon!AC27</f>
@@ -14713,7 +14713,7 @@
       </c>
       <c r="D28">
         <f>Palmon!E29</f>
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E28">
         <f>Palmon!F29</f>
@@ -14789,7 +14789,7 @@
       </c>
       <c r="W28">
         <f>Palmon!X29</f>
-        <v>4721120000</v>
+        <v>4667020000</v>
       </c>
       <c r="X28">
         <f>Palmon!Y29</f>
@@ -14801,7 +14801,7 @@
       </c>
       <c r="Z28">
         <f>Palmon!AA29</f>
-        <v>3382</v>
+        <v>3386</v>
       </c>
       <c r="AA28">
         <f>Palmon!AB29</f>
@@ -15443,11 +15443,11 @@
       </c>
       <c r="D33">
         <f>Palmon!E34</f>
-        <v>260</v>
-      </c>
-      <c r="E33">
+        <v>270</v>
+      </c>
+      <c r="E33" t="str">
         <f>Palmon!F34</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="F33">
         <f>Palmon!G34</f>
@@ -15519,11 +15519,11 @@
       </c>
       <c r="W33">
         <f>Palmon!X34</f>
-        <v>1235520000</v>
-      </c>
-      <c r="X33">
+        <v>135120000</v>
+      </c>
+      <c r="X33" t="str">
         <f>Palmon!Y34</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="Y33">
         <f>Palmon!Z34</f>
@@ -15531,7 +15531,7 @@
       </c>
       <c r="Z33">
         <f>Palmon!AA34</f>
-        <v>5260</v>
+        <v>5270</v>
       </c>
       <c r="AA33">
         <f>Palmon!AB34</f>
@@ -17736,10 +17736,10 @@
         <v>290</v>
       </c>
       <c r="O17" s="33">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="P17" s="47">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="Q17" s="40"/>
       <c r="R17" s="1"/>
@@ -17747,7 +17747,7 @@
         <v>Fire</v>
       </c>
       <c r="V17" s="195">
-        <v>244.28571428571428</v>
+        <v>245.71428571428572</v>
       </c>
       <c r="W17" s="40" cm="1">
         <f t="array" ref="W17">COUNTA(_xlfn._xlws.FILTER(C4:C43,C4:C43=$U17,""))</f>
@@ -17799,7 +17799,7 @@
         <v>Water</v>
       </c>
       <c r="V18" s="195">
-        <v>235.71428571428572</v>
+        <v>240</v>
       </c>
       <c r="W18" s="40" cm="1">
         <f t="array" ref="W18">COUNTA(_xlfn._xlws.FILTER(C5:C44,C5:C44=$U18,""))</f>
@@ -17822,11 +17822,11 @@
       <c r="F19" s="33" t="str">
         <v/>
       </c>
-      <c r="G19" s="33">
-        <v>383.00000000000034</v>
-      </c>
-      <c r="H19" s="33" t="str">
-        <v/>
+      <c r="G19" s="33" t="str">
+        <v/>
+      </c>
+      <c r="H19" s="33">
+        <v>0</v>
       </c>
       <c r="I19" s="33"/>
       <c r="J19" s="40"/>
@@ -17874,11 +17874,11 @@
       <c r="F20" s="33" t="str">
         <v/>
       </c>
-      <c r="G20" s="33">
-        <v>489</v>
-      </c>
-      <c r="H20" s="33" t="str">
-        <v/>
+      <c r="G20" s="33" t="str">
+        <v/>
+      </c>
+      <c r="H20" s="33">
+        <v>0</v>
       </c>
       <c r="I20" s="33"/>
       <c r="J20" s="40"/>
@@ -17901,7 +17901,7 @@
       <c r="R20" s="1"/>
       <c r="V20" s="200">
         <f>AVERAGE(V16:V19)</f>
-        <v>234.04761904761904</v>
+        <v>235.47619047619048</v>
       </c>
       <c r="W20" s="199">
         <f>SUM(W16:W19)</f>
@@ -18190,10 +18190,10 @@
         <v>3</v>
       </c>
       <c r="O27" s="33">
+        <v>1</v>
+      </c>
+      <c r="P27" s="33">
         <v>2</v>
-      </c>
-      <c r="P27" s="33">
-        <v>1</v>
       </c>
       <c r="Q27" s="47">
         <v>7</v>
@@ -18235,10 +18235,10 @@
         <v>1</v>
       </c>
       <c r="O28" s="33">
+        <v>1</v>
+      </c>
+      <c r="P28" s="33">
         <v>2</v>
-      </c>
-      <c r="P28" s="33">
-        <v>1</v>
       </c>
       <c r="Q28" s="47">
         <v>8</v>
@@ -18325,10 +18325,10 @@
         <v>5</v>
       </c>
       <c r="O30" s="86">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P30" s="86">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q30" s="87">
         <v>28</v>
@@ -18526,10 +18526,10 @@
         <v>Fire</v>
       </c>
       <c r="M35" s="39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N35" s="33">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O35" s="40">
         <v>2</v>
@@ -18592,10 +18592,10 @@
         <v>Wood</v>
       </c>
       <c r="M37" s="39">
-        <v>3</v>
-      </c>
-      <c r="N37" s="33" t="str">
-        <v/>
+        <v>2</v>
+      </c>
+      <c r="N37" s="33">
+        <v>1</v>
       </c>
       <c r="O37" s="40" t="str">
         <v/>
@@ -18732,7 +18732,7 @@
         <v>Bufonobi</v>
       </c>
       <c r="M42" s="74" t="str">
-        <v>Hoofrit</v>
+        <v>Ghillant</v>
       </c>
       <c r="N42" s="75" t="str">
         <v>Blazeal</v>
@@ -18743,7 +18743,7 @@
         <v>Bufonobi</v>
       </c>
       <c r="Q42" s="1" t="str">
-        <v>Hoofrit</v>
+        <v>Ghillant</v>
       </c>
       <c r="R42" s="1"/>
       <c r="T42"/>
@@ -18794,7 +18794,7 @@
       <c r="I44" s="33"/>
       <c r="J44" s="40"/>
       <c r="L44" s="76" t="str">
-        <v>Fleurizard</v>
+        <v>Gnashley</v>
       </c>
       <c r="M44" s="77" t="str">
         <v>Pipistrigoi</v>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="O44" s="1"/>
       <c r="P44" s="1" t="str">
-        <v>Fleurizard</v>
+        <v>Gnashley</v>
       </c>
       <c r="Q44" s="1" t="str">
         <v>Pipistrigoi</v>
@@ -18849,7 +18849,7 @@
     </row>
     <row r="46" spans="2:23" x14ac:dyDescent="0.25">
       <c r="L46" s="76" t="str">
-        <v>Oleana</v>
+        <v>Hoofrit</v>
       </c>
       <c r="M46" s="77" t="str">
         <v>Magmolin</v>
@@ -18859,7 +18859,7 @@
       </c>
       <c r="O46" s="1"/>
       <c r="P46" s="1" t="str">
-        <v>Oleana</v>
+        <v>Hoofrit</v>
       </c>
       <c r="Q46" s="1" t="str">
         <v>Magmolin</v>
@@ -18872,7 +18872,7 @@
     </row>
     <row r="47" spans="2:23" x14ac:dyDescent="0.25">
       <c r="L47" s="76" t="str">
-        <v>Gnashley</v>
+        <v>Fleurizard</v>
       </c>
       <c r="M47" s="77" t="str">
         <v>Spookaboo</v>
@@ -18882,7 +18882,7 @@
       </c>
       <c r="O47" s="1"/>
       <c r="P47" s="1" t="str">
-        <v>Gnashley</v>
+        <v>Fleurizard</v>
       </c>
       <c r="Q47" s="1" t="str">
         <v>Spookaboo</v>
@@ -18895,7 +18895,7 @@
     </row>
     <row r="48" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L48" s="81" t="str">
-        <v>Ghillant</v>
+        <v>Oleana</v>
       </c>
       <c r="M48" s="82" t="str">
         <v>Barkplug</v>
@@ -18905,7 +18905,7 @@
       </c>
       <c r="O48" s="1"/>
       <c r="P48" s="1" t="str">
-        <v>Ghillant</v>
+        <v>Oleana</v>
       </c>
       <c r="Q48" s="1" t="str">
         <v>Barkplug</v>
@@ -19225,7 +19225,7 @@
     </row>
     <row r="61" spans="7:20" s="1" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="G61" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H61" s="1" t="str">
         <v/>
@@ -19234,13 +19234,13 @@
         <v>Fleurizard</v>
       </c>
       <c r="M61" s="1">
+        <v>6</v>
+      </c>
+      <c r="N61" s="1" t="str">
+        <v/>
+      </c>
+      <c r="P61" s="1">
         <v>3</v>
-      </c>
-      <c r="N61" s="1" t="str">
-        <v/>
-      </c>
-      <c r="P61" s="1">
-        <v>2</v>
       </c>
       <c r="Q61" s="1" t="str">
         <v/>
@@ -19274,7 +19274,7 @@
         <v/>
       </c>
       <c r="H63" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L63" s="1" t="str">
         <v>Ghillant</v>
@@ -19283,7 +19283,7 @@
         <v/>
       </c>
       <c r="N63" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P63" s="1" t="str">
         <v/>
@@ -19297,7 +19297,7 @@
         <v/>
       </c>
       <c r="H64" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L64" s="1" t="str">
         <v>Gnashley</v>
@@ -19306,7 +19306,7 @@
         <v/>
       </c>
       <c r="N64" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P64" s="1" t="str">
         <v/>
@@ -19317,7 +19317,7 @@
     </row>
     <row r="65" spans="7:20" s="1" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="G65" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H65" s="1" t="str">
         <v/>
@@ -19326,13 +19326,13 @@
         <v>Hoofrit</v>
       </c>
       <c r="M65" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N65" s="1" t="str">
         <v/>
       </c>
       <c r="P65" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q65" s="1" t="str">
         <v/>
@@ -19478,7 +19478,7 @@
     </row>
     <row r="72" spans="7:20" s="1" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="G72" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H72" s="1" t="str">
         <v/>
@@ -19487,13 +19487,13 @@
         <v>Oleana</v>
       </c>
       <c r="M72" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N72" s="1" t="str">
         <v/>
       </c>
       <c r="P72" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q72" s="1" t="str">
         <v/>
@@ -43019,7 +43019,7 @@
       </c>
       <c r="F3" t="str">
         <f>Palmon!B3 &amp; "," &amp; Palmon!C3 &amp; "," &amp; Palmon!D3 &amp; "," &amp; Palmon!E3 &amp; "," &amp; Palmon!G3 &amp; "," &amp; SUBSTITUTE(Palmon!H3,",",".") &amp; "," &amp; Palmon!I3 &amp; "," &amp; SUBSTITUTE(Palmon!P3,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q3,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R3,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S3,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T3,",",".") &amp; "," &amp; Palmon!J3 &amp; "," &amp; Palmon!K3 &amp; "," &amp; Palmon!L3 &amp; "," &amp; Palmon!M3 &amp; "," &amp; Palmon!N3 &amp; "," &amp; SUBSTITUTE(Palmon!U3,",",".") &amp; "," &amp; Palmon!V3 &amp; "," &amp; Palmon!X3 &amp; "," &amp; Palmon!Y3 &amp; "," &amp; Palmon!AA3 &amp; "," &amp; Palmon!AB3 &amp; "," &amp; Palmon!AC3 &amp; "," &amp; Palmon!AE3 &amp; "," &amp; Palmon!AF3 &amp; "," &amp; Palmon!AI3 &amp; "," &amp; Palmon!AJ3</f>
-        <v>Bufonobi,Water,Attack,260,5,5,0,1,1,1,1,1,30,20,20,Max,10,1,0,1235520000,1,5260,1,1,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRXczs_Bjhslhr7Mf2HENU6MTyGpz0RJEMjNA&amp;s, ,,Shadowkaeru</v>
+        <v>Bufonobi,Water,Attack,270,5,5,0,1,1,1,1,1,30,20,20,Max,10,1,0,135120000,,5270,1,1,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRXczs_Bjhslhr7Mf2HENU6MTyGpz0RJEMjNA&amp;s, ,,Shadowkaeru</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -43045,7 +43045,7 @@
       </c>
       <c r="F4" t="str">
         <f>Palmon!B4 &amp; "," &amp; Palmon!C4 &amp; "," &amp; Palmon!D4 &amp; "," &amp; Palmon!E4 &amp; "," &amp; Palmon!G4 &amp; "," &amp; SUBSTITUTE(Palmon!H4,",",".") &amp; "," &amp; Palmon!I4 &amp; "," &amp; SUBSTITUTE(Palmon!P4,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q4,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R4,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S4,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T4,",",".") &amp; "," &amp; Palmon!J4 &amp; "," &amp; Palmon!K4 &amp; "," &amp; Palmon!L4 &amp; "," &amp; Palmon!M4 &amp; "," &amp; Palmon!N4 &amp; "," &amp; SUBSTITUTE(Palmon!U4,",",".") &amp; "," &amp; Palmon!V4 &amp; "," &amp; Palmon!X4 &amp; "," &amp; Palmon!Y4 &amp; "," &amp; Palmon!AA4 &amp; "," &amp; Palmon!AB4 &amp; "," &amp; Palmon!AC4 &amp; "," &amp; Palmon!AE4 &amp; "," &amp; Palmon!AF4 &amp; "," &amp; Palmon!AI4 &amp; "," &amp; Palmon!AJ4</f>
-        <v>Vulpyrean,Fire,Attack,260,5,5,0,1,1,1,1,1,20,20,20,Max,10,1,0,1235520000,1,5260,2,1,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSDZWuq2tiKYc0zKRxpHXrLSMZ1GsY_6wEIYw&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRGF27Z8fOuiwM1qjDFQVY262gS_QKIJamMNg&amp;s,,</v>
+        <v>Vulpyrean,Fire,Attack,270,5,5,0,1,1,1,1,1,20,20,20,Max,10,1,0,135120000,,5270,2,1,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSDZWuq2tiKYc0zKRxpHXrLSMZ1GsY_6wEIYw&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRGF27Z8fOuiwM1qjDFQVY262gS_QKIJamMNg&amp;s,,</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -43071,7 +43071,7 @@
       </c>
       <c r="F5" t="str">
         <f>Palmon!B5 &amp; "," &amp; Palmon!C5 &amp; "," &amp; Palmon!D5 &amp; "," &amp; Palmon!E5 &amp; "," &amp; Palmon!G5 &amp; "," &amp; SUBSTITUTE(Palmon!H5,",",".") &amp; "," &amp; Palmon!I5 &amp; "," &amp; SUBSTITUTE(Palmon!P5,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q5,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R5,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S5,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T5,",",".") &amp; "," &amp; Palmon!J5 &amp; "," &amp; Palmon!K5 &amp; "," &amp; Palmon!L5 &amp; "," &amp; Palmon!M5 &amp; "," &amp; Palmon!N5 &amp; "," &amp; SUBSTITUTE(Palmon!U5,",",".") &amp; "," &amp; Palmon!V5 &amp; "," &amp; Palmon!X5 &amp; "," &amp; Palmon!Y5 &amp; "," &amp; Palmon!AA5 &amp; "," &amp; Palmon!AB5 &amp; "," &amp; Palmon!AC5 &amp; "," &amp; Palmon!AE5 &amp; "," &amp; Palmon!AF5 &amp; "," &amp; Palmon!AI5 &amp; "," &amp; Palmon!AJ5</f>
-        <v>Hoofrit,Fire,Attack,260,4,4,11,1,1,1,1,0,15,15,15,Max,,0.487179487179487,489,1235520000,1,4260,8,2,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRwfHFWjB1bN67FJNyjjWvBJwviWJ3Tada0Yg&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSkOv6mOI5FaIAjcVgErYDwVaivkH3WdUQIzw&amp;s,Flaries,</v>
+        <v>Hoofrit,Fire,Attack,260,5,5,11,1,1,1,1,1,15,15,15,Max,10,1,-11,1235520000,1,5260,5,1,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRwfHFWjB1bN67FJNyjjWvBJwviWJ3Tada0Yg&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSkOv6mOI5FaIAjcVgErYDwVaivkH3WdUQIzw&amp;s,Flaries,</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -43097,7 +43097,7 @@
       </c>
       <c r="F6" t="str">
         <f>Palmon!B6 &amp; "," &amp; Palmon!C6 &amp; "," &amp; Palmon!D6 &amp; "," &amp; Palmon!E6 &amp; "," &amp; Palmon!G6 &amp; "," &amp; SUBSTITUTE(Palmon!H6,",",".") &amp; "," &amp; Palmon!I6 &amp; "," &amp; SUBSTITUTE(Palmon!P6,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q6,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R6,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S6,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T6,",",".") &amp; "," &amp; Palmon!J6 &amp; "," &amp; Palmon!K6 &amp; "," &amp; Palmon!L6 &amp; "," &amp; Palmon!M6 &amp; "," &amp; Palmon!N6 &amp; "," &amp; SUBSTITUTE(Palmon!U6,",",".") &amp; "," &amp; Palmon!V6 &amp; "," &amp; Palmon!X6 &amp; "," &amp; Palmon!Y6 &amp; "," &amp; Palmon!AA6 &amp; "," &amp; Palmon!AB6 &amp; "," &amp; Palmon!AC6 &amp; "," &amp; Palmon!AE6 &amp; "," &amp; Palmon!AF6 &amp; "," &amp; Palmon!AI6 &amp; "," &amp; Palmon!AJ6</f>
-        <v>Ghillant,Wood,Defend,250,4,4.1,0,1,1,1,1,0.199999999999999,5,5,5,Max,,0.589743589743589,400,2123020000,1,4350,7,1,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQOwDXppnwkCtCXXAqUiiNMhf6T-lane54jPg&amp;s, ,Chefeuillier,</v>
+        <v>Ghillant,Wood,Defend,250,4,4.1,0,1,1,1,1,0.199999999999999,5,5,5,Max,,0.589743589743589,400,2123020000,1,4350,8,2,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQOwDXppnwkCtCXXAqUiiNMhf6T-lane54jPg&amp;s, ,Chefeuillier,</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -43123,7 +43123,7 @@
       </c>
       <c r="F7" t="str">
         <f>Palmon!B7 &amp; "," &amp; Palmon!C7 &amp; "," &amp; Palmon!D7 &amp; "," &amp; Palmon!E7 &amp; "," &amp; Palmon!G7 &amp; "," &amp; SUBSTITUTE(Palmon!H7,",",".") &amp; "," &amp; Palmon!I7 &amp; "," &amp; SUBSTITUTE(Palmon!P7,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q7,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R7,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S7,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T7,",",".") &amp; "," &amp; Palmon!J7 &amp; "," &amp; Palmon!K7 &amp; "," &amp; Palmon!L7 &amp; "," &amp; Palmon!M7 &amp; "," &amp; Palmon!N7 &amp; "," &amp; SUBSTITUTE(Palmon!U7,",",".") &amp; "," &amp; Palmon!V7 &amp; "," &amp; Palmon!X7 &amp; "," &amp; Palmon!Y7 &amp; "," &amp; Palmon!AA7 &amp; "," &amp; Palmon!AB7 &amp; "," &amp; Palmon!AC7 &amp; "," &amp; Palmon!AE7 &amp; "," &amp; Palmon!AF7 &amp; "," &amp; Palmon!AI7 &amp; "," &amp; Palmon!AJ7</f>
-        <v>Gnashley,Water,Defend,260,4,4.1,17,1,1,1,1,0.199999999999999,15,15,15,Max,,0.589743589743589,383,1235520000,1,4360,6,1,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQtrOr7ePo-_tg085QaHk6NorM32ywE44672A&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTII6bAUVzdPfr_45Db3bGwDuIVxhe-n4dSSgHRGJaEpg&amp;s,Gnashfin,</v>
+        <v>Gnashley,Water,Defend,270,5,5,0,1,1,1,1,1,15,15,30,Max,10,1,0,135120000,,5270,3,1,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQtrOr7ePo-_tg085QaHk6NorM32ywE44672A&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTII6bAUVzdPfr_45Db3bGwDuIVxhe-n4dSSgHRGJaEpg&amp;s,Gnashfin,</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -43305,7 +43305,7 @@
       </c>
       <c r="F14" t="str">
         <f>Palmon!B14 &amp; "," &amp; Palmon!C14 &amp; "," &amp; Palmon!D14 &amp; "," &amp; Palmon!E14 &amp; "," &amp; Palmon!G14 &amp; "," &amp; SUBSTITUTE(Palmon!H14,",",".") &amp; "," &amp; Palmon!I14 &amp; "," &amp; SUBSTITUTE(Palmon!P14,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q14,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R14,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S14,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T14,",",".") &amp; "," &amp; Palmon!J14 &amp; "," &amp; Palmon!K14 &amp; "," &amp; Palmon!L14 &amp; "," &amp; Palmon!M14 &amp; "," &amp; Palmon!N14 &amp; "," &amp; SUBSTITUTE(Palmon!U14,",",".") &amp; "," &amp; Palmon!V14 &amp; "," &amp; Palmon!X14 &amp; "," &amp; Palmon!Y14 &amp; "," &amp; Palmon!AA14 &amp; "," &amp; Palmon!AB14 &amp; "," &amp; Palmon!AC14 &amp; "," &amp; Palmon!AE14 &amp; "," &amp; Palmon!AF14 &amp; "," &amp; Palmon!AI14 &amp; "," &amp; Palmon!AJ14</f>
-        <v>Fleurizard,Wood,Attack,260,5,5,0,1,1,1,1,1,1,1,1,Max,10,1,0,1235520000,1,5260,3,1,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQCf63iS9oq-SMn3DO74UTS2j_zSrzNVTRMOQ&amp;s, ,,</v>
+        <v>Fleurizard,Wood,Attack,260,5,5,0,1,1,1,1,1,1,1,1,Max,10,1,0,1235520000,1,5260,6,1,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQCf63iS9oq-SMn3DO74UTS2j_zSrzNVTRMOQ&amp;s, ,,</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -43643,7 +43643,7 @@
       </c>
       <c r="F27" t="str">
         <f>Palmon!B27 &amp; "," &amp; Palmon!C27 &amp; "," &amp; Palmon!D27 &amp; "," &amp; Palmon!E27 &amp; "," &amp; Palmon!G27 &amp; "," &amp; SUBSTITUTE(Palmon!H27,",",".") &amp; "," &amp; Palmon!I27 &amp; "," &amp; SUBSTITUTE(Palmon!P27,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q27,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R27,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S27,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T27,",",".") &amp; "," &amp; Palmon!J27 &amp; "," &amp; Palmon!K27 &amp; "," &amp; Palmon!L27 &amp; "," &amp; Palmon!M27 &amp; "," &amp; Palmon!N27 &amp; "," &amp; SUBSTITUTE(Palmon!U27,",",".") &amp; "," &amp; Palmon!V27 &amp; "," &amp; Palmon!X27 &amp; "," &amp; Palmon!Y27 &amp; "," &amp; Palmon!AA27 &amp; "," &amp; Palmon!AB27 &amp; "," &amp; Palmon!AC27 &amp; "," &amp; Palmon!AE27 &amp; "," &amp; Palmon!AF27 &amp; "," &amp; Palmon!AI27 &amp; "," &amp; Palmon!AJ27</f>
-        <v>Oleana,Wood,Attack,260,4,4.3,128,1,1,1,1,0.6,1,1,1,Max,,0.794871794871795,72,0000000000002,1235520000,1,4560,5,1,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQ02wmDjsAMofj1ObwwNW6Vhl_QQ-LUodGIKA&amp;s, ,,</v>
+        <v>Oleana,Wood,Attack,260,4,4.3,128,1,1,1,1,0.6,1,1,1,Max,,0.794871794871795,72,0000000000002,1235520000,1,4560,7,1,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQ02wmDjsAMofj1ObwwNW6Vhl_QQ-LUodGIKA&amp;s, ,,</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -43695,7 +43695,7 @@
       </c>
       <c r="F29" t="str">
         <f>Palmon!B29 &amp; "," &amp; Palmon!C29 &amp; "," &amp; Palmon!D29 &amp; "," &amp; Palmon!E29 &amp; "," &amp; Palmon!G29 &amp; "," &amp; SUBSTITUTE(Palmon!H29,",",".") &amp; "," &amp; Palmon!I29 &amp; "," &amp; SUBSTITUTE(Palmon!P29,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q29,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R29,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S29,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T29,",",".") &amp; "," &amp; Palmon!J29 &amp; "," &amp; Palmon!K29 &amp; "," &amp; Palmon!L29 &amp; "," &amp; Palmon!M29 &amp; "," &amp; Palmon!N29 &amp; "," &amp; SUBSTITUTE(Palmon!U29,",",".") &amp; "," &amp; Palmon!V29 &amp; "," &amp; Palmon!X29 &amp; "," &amp; Palmon!Y29 &amp; "," &amp; Palmon!AA29 &amp; "," &amp; Palmon!AB29 &amp; "," &amp; Palmon!AC29 &amp; "," &amp; Palmon!AE29 &amp; "," &amp; Palmon!AF29 &amp; "," &amp; Palmon!AI29 &amp; "," &amp; Palmon!AJ29</f>
-        <v>Kungpaw,Water,Defend,182,3,3.2,45,1,1,1,0.4,0,1,1,1,,,0.302564102564103,635,4721120000,1,3382,11,2,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRV1HdRcNPUS4HjDBZ2YOXgaMW_I8FgZEP5xg&amp;s,,,</v>
+        <v>Kungpaw,Water,Defend,186,3,3.2,45,1,1,1,0.4,0,1,1,1,,,0.302564102564103,635,4667020000,1,3386,11,2,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRV1HdRcNPUS4HjDBZ2YOXgaMW_I8FgZEP5xg&amp;s,,,</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -43809,7 +43809,7 @@
       </c>
       <c r="F34" t="str">
         <f>Palmon!B34 &amp; "," &amp; Palmon!C34 &amp; "," &amp; Palmon!D34 &amp; "," &amp; Palmon!E34 &amp; "," &amp; Palmon!G34 &amp; "," &amp; SUBSTITUTE(Palmon!H34,",",".") &amp; "," &amp; Palmon!I34 &amp; "," &amp; SUBSTITUTE(Palmon!P34,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q34,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R34,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S34,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T34,",",".") &amp; "," &amp; Palmon!J34 &amp; "," &amp; Palmon!K34 &amp; "," &amp; Palmon!L34 &amp; "," &amp; Palmon!M34 &amp; "," &amp; Palmon!N34 &amp; "," &amp; SUBSTITUTE(Palmon!U34,",",".") &amp; "," &amp; Palmon!V34 &amp; "," &amp; Palmon!X34 &amp; "," &amp; Palmon!Y34 &amp; "," &amp; Palmon!AA34 &amp; "," &amp; Palmon!AB34 &amp; "," &amp; Palmon!AC34 &amp; "," &amp; Palmon!AE34 &amp; "," &amp; Palmon!AF34 &amp; "," &amp; Palmon!AI34 &amp; "," &amp; Palmon!AJ34</f>
-        <v>Glacewing,Water,Attack,260,5,5,0,1,1,1,1,1,30,30,30,Max,10,1,0,1235520000,1,5260,4,1,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTrE4qGrnpy2BMETqUKNyATj-OrXMdX4IeXcQ&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSRbCy1ARx2qd0P1rLvdoRvfNqa4pUV20r12A&amp;s,Cryovern,</v>
+        <v>Glacewing,Water,Attack,270,5,5,0,1,1,1,1,1,30,30,30,Max,10,1,0,135120000,,5270,4,1,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTrE4qGrnpy2BMETqUKNyATj-OrXMdX4IeXcQ&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSRbCy1ARx2qd0P1rLvdoRvfNqa4pUV20r12A&amp;s,Cryovern,</v>
       </c>
     </row>
     <row r="35" spans="3:6" x14ac:dyDescent="0.25">

--- a/data/PS - Estimation (version 1).xlsx
+++ b/data/PS - Estimation (version 1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xvjm020\Documents\Personnel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9D278E3-5386-4859-A505-38CFE5B68AE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64FDED73-3ED4-411D-899D-2E7501FF5A41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9D83D047-1CAD-4BF9-942E-B289F790400E}"/>
   </bookViews>
@@ -2739,26 +2739,6 @@
   <dxfs count="72">
     <dxf>
       <font>
-        <color theme="4"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="4"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <color theme="0"/>
       </font>
       <fill>
@@ -3217,6 +3197,26 @@
           <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="4"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="4"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -10534,7 +10534,7 @@
     <mergeCell ref="X1:Y1"/>
     <mergeCell ref="P1:V1"/>
   </mergeCells>
-  <conditionalFormatting sqref="B51:C51 B57:C57 C59:C61 B62:C81 B3:C48">
+  <conditionalFormatting sqref="B3:C48 B51:C51 B57:C57 C59:C61 B62:C81">
     <cfRule type="expression" dxfId="69" priority="108">
       <formula>$C3="Fire"</formula>
     </cfRule>
@@ -10548,7 +10548,7 @@
       <formula>$C3="Wood"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D57:D81 D3:D53">
+  <conditionalFormatting sqref="D3:D53 D57:D81">
     <cfRule type="cellIs" dxfId="65" priority="76" operator="equal">
       <formula>"Attack"</formula>
     </cfRule>
@@ -10609,11 +10609,41 @@
       </iconSet>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AB8:AB29">
+    <cfRule type="expression" dxfId="59" priority="251">
+      <formula>VLOOKUP($B57,PalmonList,3,FALSE)="Attack"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="58" priority="252">
+      <formula>VLOOKUP($B57,PalmonList,3,FALSE)&lt;&gt;"Attack"</formula>
+    </cfRule>
+    <cfRule type="iconSet" priority="253">
+      <iconSet iconSet="3Flags">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="num" val="8"/>
+        <cfvo type="num" val="15"/>
+      </iconSet>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB30:AB37">
+    <cfRule type="expression" dxfId="57" priority="254">
+      <formula>VLOOKUP($B76,PalmonList,3,FALSE)="Attack"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="56" priority="255">
+      <formula>VLOOKUP($B76,PalmonList,3,FALSE)&lt;&gt;"Attack"</formula>
+    </cfRule>
+    <cfRule type="iconSet" priority="256">
+      <iconSet iconSet="3Flags">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="num" val="8"/>
+        <cfvo type="num" val="15"/>
+      </iconSet>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AB38:AB45">
-    <cfRule type="expression" dxfId="59" priority="242">
+    <cfRule type="expression" dxfId="55" priority="242">
       <formula>VLOOKUP($B81,PalmonList,3,FALSE)="Attack"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="58" priority="243">
+    <cfRule type="expression" dxfId="54" priority="243">
       <formula>VLOOKUP($B81,PalmonList,3,FALSE)&lt;&gt;"Attack"</formula>
     </cfRule>
     <cfRule type="iconSet" priority="244">
@@ -10630,36 +10660,6 @@
         <cfvo type="percent" val="0"/>
         <cfvo type="num" val="2"/>
         <cfvo type="num" val="3"/>
-      </iconSet>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AB8:AB29">
-    <cfRule type="expression" dxfId="3" priority="251">
-      <formula>VLOOKUP($B57,PalmonList,3,FALSE)="Attack"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="252">
-      <formula>VLOOKUP($B57,PalmonList,3,FALSE)&lt;&gt;"Attack"</formula>
-    </cfRule>
-    <cfRule type="iconSet" priority="253">
-      <iconSet iconSet="3Flags">
-        <cfvo type="percent" val="0"/>
-        <cfvo type="num" val="8"/>
-        <cfvo type="num" val="15"/>
-      </iconSet>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AB30:AB37">
-    <cfRule type="expression" dxfId="1" priority="254">
-      <formula>VLOOKUP($B76,PalmonList,3,FALSE)="Attack"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="255">
-      <formula>VLOOKUP($B76,PalmonList,3,FALSE)&lt;&gt;"Attack"</formula>
-    </cfRule>
-    <cfRule type="iconSet" priority="256">
-      <iconSet iconSet="3Flags">
-        <cfvo type="percent" val="0"/>
-        <cfvo type="num" val="8"/>
-        <cfvo type="num" val="15"/>
       </iconSet>
     </cfRule>
   </conditionalFormatting>
@@ -10937,7 +10937,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F30CDCB-18C3-423D-800C-A25763793463}">
-  <dimension ref="A1:AJ43"/>
+  <dimension ref="A1:AJ45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.25">
@@ -15906,1314 +15906,1606 @@
     </row>
     <row r="35" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A35" t="str">
+        <f>Palmon!B36</f>
+        <v>Plunderjaw</v>
+      </c>
+      <c r="B35" t="str">
+        <f>Palmon!C36</f>
+        <v>Water</v>
+      </c>
+      <c r="C35" t="str">
+        <f>Palmon!D36</f>
+        <v>Attack</v>
+      </c>
+      <c r="D35">
+        <f>Palmon!E36</f>
+        <v>0</v>
+      </c>
+      <c r="E35" t="str">
+        <f>Palmon!F36</f>
+        <v/>
+      </c>
+      <c r="F35">
+        <f>Palmon!G36</f>
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <f>Palmon!H36</f>
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <f>Palmon!I36</f>
+        <v>2</v>
+      </c>
+      <c r="I35" t="str">
+        <f>Palmon!J36</f>
+        <v/>
+      </c>
+      <c r="J35">
+        <f>Palmon!K36</f>
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <f>Palmon!L36</f>
+        <v>0</v>
+      </c>
+      <c r="L35" t="str">
+        <f>Palmon!M36</f>
+        <v/>
+      </c>
+      <c r="M35" t="str">
+        <f>Palmon!N36</f>
+        <v/>
+      </c>
+      <c r="N35">
+        <f>Palmon!O36</f>
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <f>Palmon!P36</f>
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <f>Palmon!Q36</f>
+        <v>0</v>
+      </c>
+      <c r="Q35">
+        <f>Palmon!R36</f>
+        <v>0</v>
+      </c>
+      <c r="R35">
+        <f>Palmon!S36</f>
+        <v>0</v>
+      </c>
+      <c r="S35">
+        <f>Palmon!T36</f>
+        <v>0</v>
+      </c>
+      <c r="T35">
+        <f>Palmon!U36</f>
+        <v>0</v>
+      </c>
+      <c r="U35">
+        <f>Palmon!V36</f>
+        <v>973</v>
+      </c>
+      <c r="V35">
+        <f>Palmon!W36</f>
+        <v>0</v>
+      </c>
+      <c r="W35">
+        <f>Palmon!X36</f>
+        <v>5044093700</v>
+      </c>
+      <c r="X35" t="str">
+        <f>Palmon!Y36</f>
+        <v/>
+      </c>
+      <c r="Y35">
+        <f>Palmon!Z36</f>
+        <v>0</v>
+      </c>
+      <c r="Z35">
+        <f>Palmon!AA36</f>
+        <v>0</v>
+      </c>
+      <c r="AA35">
+        <f>Palmon!AB36</f>
+        <v>36</v>
+      </c>
+      <c r="AB35" t="str">
+        <f>Palmon!AC36</f>
+        <v/>
+      </c>
+      <c r="AC35">
+        <f>Palmon!AD36</f>
+        <v>0</v>
+      </c>
+      <c r="AD35" t="str">
+        <f>Palmon!AE36</f>
+        <v>https://scontent-cdg4-2.xx.fbcdn.net/v/t39.30808-6/649210457_122193691484516338_487581885207006414_n.jpg?_nc_cat=109&amp;ccb=1-7&amp;_nc_sid=13d280&amp;_nc_ohc=wC2lV9slkY0Q7kNvwFsmsEi&amp;_nc_oc=AdoKFb_1lsq4UKznFnmvtUqFji4Fy3cRlYhvboqzO_RsdrIGc0H1ylJ_YUjH-ZC78Mo&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-2.xx&amp;_nc_gid=Djk5o2l4ZrQNgbZ5SKGinA&amp;_nc_ss=7a30f&amp;oh=00_AfyKhBvM3HYsSpbWT_gcFpYi9I2AfF0V35uyBreinYCQwQ&amp;oe=69C8204C</v>
+      </c>
+      <c r="AE35">
+        <f>Palmon!AF36</f>
+        <v>0</v>
+      </c>
+      <c r="AF35">
+        <f>Palmon!AG36</f>
+        <v>0</v>
+      </c>
+      <c r="AG35">
+        <f>Palmon!AH36</f>
+        <v>0</v>
+      </c>
+      <c r="AH35">
+        <f>Palmon!AI36</f>
+        <v>0</v>
+      </c>
+      <c r="AI35">
+        <f>Palmon!AJ36</f>
+        <v>0</v>
+      </c>
+      <c r="AJ35">
+        <f>Palmon!AK36</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A36" t="str">
+        <f>Palmon!B37</f>
+        <v>Dreadmaw</v>
+      </c>
+      <c r="B36" t="str">
+        <f>Palmon!C37</f>
+        <v>Water</v>
+      </c>
+      <c r="C36" t="str">
+        <f>Palmon!D37</f>
+        <v>Attack</v>
+      </c>
+      <c r="D36">
+        <f>Palmon!E37</f>
+        <v>0</v>
+      </c>
+      <c r="E36" t="str">
+        <f>Palmon!F37</f>
+        <v/>
+      </c>
+      <c r="F36">
+        <f>Palmon!G37</f>
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <f>Palmon!H37</f>
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <f>Palmon!I37</f>
+        <v>0</v>
+      </c>
+      <c r="I36" t="str">
+        <f>Palmon!J37</f>
+        <v/>
+      </c>
+      <c r="J36">
+        <f>Palmon!K37</f>
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <f>Palmon!L37</f>
+        <v>0</v>
+      </c>
+      <c r="L36" t="str">
+        <f>Palmon!M37</f>
+        <v/>
+      </c>
+      <c r="M36" t="str">
+        <f>Palmon!N37</f>
+        <v/>
+      </c>
+      <c r="N36">
+        <f>Palmon!O37</f>
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <f>Palmon!P37</f>
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <f>Palmon!Q37</f>
+        <v>0</v>
+      </c>
+      <c r="Q36">
+        <f>Palmon!R37</f>
+        <v>0</v>
+      </c>
+      <c r="R36">
+        <f>Palmon!S37</f>
+        <v>0</v>
+      </c>
+      <c r="S36">
+        <f>Palmon!T37</f>
+        <v>0</v>
+      </c>
+      <c r="T36">
+        <f>Palmon!U37</f>
+        <v>0</v>
+      </c>
+      <c r="U36">
+        <f>Palmon!V37</f>
+        <v>975</v>
+      </c>
+      <c r="V36">
+        <f>Palmon!W37</f>
+        <v>0</v>
+      </c>
+      <c r="W36">
+        <f>Palmon!X37</f>
+        <v>5044093700</v>
+      </c>
+      <c r="X36" t="str">
+        <f>Palmon!Y37</f>
+        <v/>
+      </c>
+      <c r="Y36">
+        <f>Palmon!Z37</f>
+        <v>0</v>
+      </c>
+      <c r="Z36">
+        <f>Palmon!AA37</f>
+        <v>0</v>
+      </c>
+      <c r="AA36">
+        <f>Palmon!AB37</f>
+        <v>37</v>
+      </c>
+      <c r="AB36" t="str">
+        <f>Palmon!AC37</f>
+        <v/>
+      </c>
+      <c r="AC36">
+        <f>Palmon!AD37</f>
+        <v>0</v>
+      </c>
+      <c r="AD36" t="str">
+        <f>Palmon!AE37</f>
+        <v>https://scontent-cdg4-2.xx.fbcdn.net/v/t39.30808-6/649210457_122193691484516338_487581885207006414_n.jpg?_nc_cat=109&amp;ccb=1-7&amp;_nc_sid=13d280&amp;_nc_ohc=wC2lV9slkY0Q7kNvwFsmsEi&amp;_nc_oc=AdoKFb_1lsq4UKznFnmvtUqFji4Fy3cRlYhvboqzO_RsdrIGc0H1ylJ_YUjH-ZC78Mo&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-2.xx&amp;_nc_gid=Djk5o2l4ZrQNgbZ5SKGinA&amp;_nc_ss=7a30f&amp;oh=00_AfyKhBvM3HYsSpbWT_gcFpYi9I2AfF0V35uyBreinYCQwQ&amp;oe=69C8204C</v>
+      </c>
+      <c r="AE36">
+        <f>Palmon!AF37</f>
+        <v>0</v>
+      </c>
+      <c r="AF36">
+        <f>Palmon!AG37</f>
+        <v>0</v>
+      </c>
+      <c r="AG36">
+        <f>Palmon!AH37</f>
+        <v>0</v>
+      </c>
+      <c r="AH36" t="str">
+        <f>Palmon!AI37</f>
+        <v>Dreadmaw</v>
+      </c>
+      <c r="AI36">
+        <f>Palmon!AJ37</f>
+        <v>0</v>
+      </c>
+      <c r="AJ36">
+        <f>Palmon!AK37</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A37" t="str">
         <f>Palmon!B38</f>
         <v>Woozard</v>
       </c>
-      <c r="B35" t="str">
+      <c r="B37" t="str">
         <f>Palmon!C38</f>
         <v>Wood</v>
       </c>
-      <c r="C35" t="str">
+      <c r="C37" t="str">
         <f>Palmon!D38</f>
         <v>Attack</v>
       </c>
-      <c r="D35">
+      <c r="D37">
         <f>Palmon!E38</f>
         <v>1</v>
       </c>
-      <c r="E35">
+      <c r="E37">
         <f>Palmon!F38</f>
         <v>1</v>
       </c>
-      <c r="F35">
+      <c r="F37">
         <f>Palmon!G38</f>
         <v>0</v>
       </c>
-      <c r="G35">
+      <c r="G37">
         <f>Palmon!H38</f>
         <v>0</v>
       </c>
-      <c r="H35">
+      <c r="H37">
         <f>Palmon!I38</f>
         <v>0</v>
       </c>
-      <c r="I35">
+      <c r="I37">
         <f>Palmon!J38</f>
         <v>1</v>
       </c>
-      <c r="J35">
+      <c r="J37">
         <f>Palmon!K38</f>
         <v>1</v>
       </c>
-      <c r="K35">
+      <c r="K37">
         <f>Palmon!L38</f>
         <v>1</v>
       </c>
-      <c r="L35" t="str">
+      <c r="L37" t="str">
         <f>Palmon!M38</f>
         <v/>
       </c>
-      <c r="M35" t="str">
+      <c r="M37" t="str">
         <f>Palmon!N38</f>
         <v/>
       </c>
-      <c r="N35">
+      <c r="N37">
         <f>Palmon!O38</f>
         <v>0</v>
       </c>
-      <c r="O35">
+      <c r="O37">
         <f>Palmon!P38</f>
         <v>0</v>
       </c>
-      <c r="P35">
+      <c r="P37">
         <f>Palmon!Q38</f>
         <v>0</v>
       </c>
-      <c r="Q35">
+      <c r="Q37">
         <f>Palmon!R38</f>
         <v>0</v>
       </c>
-      <c r="R35">
+      <c r="R37">
         <f>Palmon!S38</f>
         <v>0</v>
       </c>
-      <c r="S35">
+      <c r="S37">
         <f>Palmon!T38</f>
         <v>0</v>
       </c>
-      <c r="T35">
+      <c r="T37">
         <f>Palmon!U38</f>
         <v>0</v>
       </c>
-      <c r="U35">
+      <c r="U37">
         <f>Palmon!V38</f>
         <v>975</v>
       </c>
-      <c r="V35">
+      <c r="V37">
         <f>Palmon!W38</f>
         <v>0</v>
       </c>
-      <c r="W35">
+      <c r="W37">
         <f>Palmon!X38</f>
         <v>5044093700</v>
       </c>
-      <c r="X35">
+      <c r="X37">
         <f>Palmon!Y38</f>
         <v>1</v>
       </c>
-      <c r="Y35">
+      <c r="Y37">
         <f>Palmon!Z38</f>
         <v>0</v>
       </c>
-      <c r="Z35">
+      <c r="Z37">
         <f>Palmon!AA38</f>
         <v>1</v>
       </c>
-      <c r="AA35">
+      <c r="AA37">
         <f>Palmon!AB38</f>
         <v>32</v>
       </c>
-      <c r="AB35" t="str">
+      <c r="AB37" t="str">
         <f>Palmon!AC38</f>
         <v/>
       </c>
-      <c r="AC35">
+      <c r="AC37">
         <f>Palmon!AD38</f>
         <v>0</v>
       </c>
-      <c r="AD35" t="str">
+      <c r="AD37" t="str">
         <f>Palmon!AE38</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQCf63iS9oq-SMn3DO74UTS2j_zSrzNVTRMOQ&amp;s</v>
       </c>
-      <c r="AE35" t="str">
+      <c r="AE37" t="str">
         <f>Palmon!AF38</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AF35" t="str">
+      <c r="AF37" t="str">
         <f>Palmon!AG38</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AG35">
+      <c r="AG37">
         <f>Palmon!AH38</f>
         <v>0</v>
       </c>
-      <c r="AH35" t="str">
+      <c r="AH37" t="str">
         <f>Palmon!AI38</f>
         <v>Fleurizard</v>
       </c>
-      <c r="AI35">
+      <c r="AI37">
         <f>Palmon!AJ38</f>
         <v>0</v>
       </c>
-      <c r="AJ35">
+      <c r="AJ37">
         <f>Palmon!AK38</f>
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A36" t="str">
+    <row r="38" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A38" t="str">
         <f>Palmon!B39</f>
         <v>Mystiray</v>
       </c>
-      <c r="B36" t="str">
+      <c r="B38" t="str">
         <f>Palmon!C39</f>
         <v>Electricity</v>
       </c>
-      <c r="C36" t="str">
+      <c r="C38" t="str">
         <f>Palmon!D39</f>
         <v>Attack</v>
       </c>
-      <c r="D36">
+      <c r="D38">
         <f>Palmon!E39</f>
         <v>0</v>
       </c>
-      <c r="E36" t="str">
+      <c r="E38" t="str">
         <f>Palmon!F39</f>
         <v/>
       </c>
-      <c r="F36">
+      <c r="F38">
         <f>Palmon!G39</f>
         <v>0</v>
       </c>
-      <c r="G36">
+      <c r="G38">
         <f>Palmon!H39</f>
         <v>0</v>
       </c>
-      <c r="H36">
+      <c r="H38">
         <f>Palmon!I39</f>
         <v>0</v>
       </c>
-      <c r="I36" t="str">
+      <c r="I38" t="str">
         <f>Palmon!J39</f>
         <v/>
       </c>
-      <c r="J36">
+      <c r="J38">
         <f>Palmon!K39</f>
         <v>0</v>
       </c>
-      <c r="K36">
+      <c r="K38">
         <f>Palmon!L39</f>
         <v>0</v>
       </c>
-      <c r="L36" t="str">
+      <c r="L38" t="str">
         <f>Palmon!M39</f>
         <v/>
       </c>
-      <c r="M36" t="str">
+      <c r="M38" t="str">
         <f>Palmon!N39</f>
         <v/>
       </c>
-      <c r="N36">
+      <c r="N38">
         <f>Palmon!O39</f>
         <v>0</v>
       </c>
-      <c r="O36">
+      <c r="O38">
         <f>Palmon!P39</f>
         <v>0</v>
       </c>
-      <c r="P36">
+      <c r="P38">
         <f>Palmon!Q39</f>
         <v>0</v>
       </c>
-      <c r="Q36">
+      <c r="Q38">
         <f>Palmon!R39</f>
         <v>0</v>
       </c>
-      <c r="R36">
+      <c r="R38">
         <f>Palmon!S39</f>
         <v>0</v>
       </c>
-      <c r="S36">
+      <c r="S38">
         <f>Palmon!T39</f>
         <v>0</v>
       </c>
-      <c r="T36">
+      <c r="T38">
         <f>Palmon!U39</f>
         <v>0</v>
       </c>
-      <c r="U36">
+      <c r="U38">
         <f>Palmon!V39</f>
         <v>975</v>
       </c>
-      <c r="V36">
+      <c r="V38">
         <f>Palmon!W39</f>
         <v>0</v>
       </c>
-      <c r="W36">
+      <c r="W38">
         <f>Palmon!X39</f>
         <v>5044093700</v>
       </c>
-      <c r="X36" t="str">
+      <c r="X38" t="str">
         <f>Palmon!Y39</f>
         <v/>
       </c>
-      <c r="Y36">
+      <c r="Y38">
         <f>Palmon!Z39</f>
         <v>0</v>
       </c>
-      <c r="Z36">
+      <c r="Z38">
         <f>Palmon!AA39</f>
         <v>0</v>
       </c>
-      <c r="AA36">
+      <c r="AA38">
         <f>Palmon!AB39</f>
         <v>38</v>
       </c>
-      <c r="AB36" t="str">
+      <c r="AB38" t="str">
         <f>Palmon!AC39</f>
         <v/>
       </c>
-      <c r="AC36">
+      <c r="AC38">
         <f>Palmon!AD39</f>
         <v>0</v>
       </c>
-      <c r="AD36">
+      <c r="AD38">
         <f>Palmon!AE39</f>
         <v>0</v>
       </c>
-      <c r="AE36" t="str">
+      <c r="AE38" t="str">
         <f>Palmon!AF39</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AF36" t="str">
+      <c r="AF38" t="str">
         <f>Palmon!AG39</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AG36">
+      <c r="AG38">
         <f>Palmon!AH39</f>
         <v>0</v>
       </c>
-      <c r="AH36">
+      <c r="AH38">
         <f>Palmon!AI39</f>
         <v>0</v>
       </c>
-      <c r="AI36">
+      <c r="AI38">
         <f>Palmon!AJ39</f>
         <v>0</v>
       </c>
-      <c r="AJ36">
+      <c r="AJ38">
         <f>Palmon!AK39</f>
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A37" t="str">
+    <row r="39" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A39" t="str">
         <f>Palmon!B40</f>
         <v>Predalynx</v>
       </c>
-      <c r="B37" t="str">
+      <c r="B39" t="str">
         <f>Palmon!C40</f>
         <v>Wood</v>
       </c>
-      <c r="C37" t="str">
+      <c r="C39" t="str">
         <f>Palmon!D40</f>
         <v>Attack</v>
       </c>
-      <c r="D37">
+      <c r="D39">
         <f>Palmon!E40</f>
         <v>0</v>
       </c>
-      <c r="E37" t="str">
+      <c r="E39" t="str">
         <f>Palmon!F40</f>
         <v/>
       </c>
-      <c r="F37">
+      <c r="F39">
         <f>Palmon!G40</f>
         <v>0</v>
       </c>
-      <c r="G37">
+      <c r="G39">
         <f>Palmon!H40</f>
         <v>0</v>
       </c>
-      <c r="H37">
+      <c r="H39">
         <f>Palmon!I40</f>
         <v>0</v>
       </c>
-      <c r="I37" t="str">
+      <c r="I39" t="str">
         <f>Palmon!J40</f>
         <v/>
       </c>
-      <c r="J37">
+      <c r="J39">
         <f>Palmon!K40</f>
         <v>0</v>
       </c>
-      <c r="K37">
+      <c r="K39">
         <f>Palmon!L40</f>
         <v>0</v>
       </c>
-      <c r="L37" t="str">
+      <c r="L39" t="str">
         <f>Palmon!M40</f>
         <v/>
       </c>
-      <c r="M37" t="str">
+      <c r="M39" t="str">
         <f>Palmon!N40</f>
         <v/>
       </c>
-      <c r="N37">
+      <c r="N39">
         <f>Palmon!O40</f>
         <v>0</v>
       </c>
-      <c r="O37">
+      <c r="O39">
         <f>Palmon!P40</f>
         <v>0</v>
       </c>
-      <c r="P37">
+      <c r="P39">
         <f>Palmon!Q40</f>
         <v>0</v>
       </c>
-      <c r="Q37">
+      <c r="Q39">
         <f>Palmon!R40</f>
         <v>0</v>
       </c>
-      <c r="R37">
+      <c r="R39">
         <f>Palmon!S40</f>
         <v>0</v>
       </c>
-      <c r="S37">
+      <c r="S39">
         <f>Palmon!T40</f>
         <v>0</v>
       </c>
-      <c r="T37">
+      <c r="T39">
         <f>Palmon!U40</f>
         <v>0</v>
       </c>
-      <c r="U37">
+      <c r="U39">
         <f>Palmon!V40</f>
         <v>975</v>
       </c>
-      <c r="V37">
+      <c r="V39">
         <f>Palmon!W40</f>
         <v>0</v>
       </c>
-      <c r="W37">
+      <c r="W39">
         <f>Palmon!X40</f>
         <v>5044093700</v>
       </c>
-      <c r="X37" t="str">
+      <c r="X39" t="str">
         <f>Palmon!Y40</f>
         <v/>
       </c>
-      <c r="Y37">
+      <c r="Y39">
         <f>Palmon!Z40</f>
         <v>0</v>
       </c>
-      <c r="Z37">
+      <c r="Z39">
         <f>Palmon!AA40</f>
         <v>0</v>
       </c>
-      <c r="AA37">
+      <c r="AA39">
         <f>Palmon!AB40</f>
         <v>39</v>
       </c>
-      <c r="AB37" t="str">
+      <c r="AB39" t="str">
         <f>Palmon!AC40</f>
         <v/>
       </c>
-      <c r="AC37">
+      <c r="AC39">
         <f>Palmon!AD40</f>
         <v>0</v>
       </c>
-      <c r="AD37">
+      <c r="AD39">
         <f>Palmon!AE40</f>
         <v>0</v>
       </c>
-      <c r="AE37" t="str">
+      <c r="AE39" t="str">
         <f>Palmon!AF40</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AF37" t="str">
+      <c r="AF39" t="str">
         <f>Palmon!AG40</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AG37">
+      <c r="AG39">
         <f>Palmon!AH40</f>
         <v>0</v>
       </c>
-      <c r="AH37">
+      <c r="AH39">
         <f>Palmon!AI40</f>
         <v>0</v>
       </c>
-      <c r="AI37">
+      <c r="AI39">
         <f>Palmon!AJ40</f>
         <v>0</v>
       </c>
-      <c r="AJ37">
+      <c r="AJ39">
         <f>Palmon!AK40</f>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A38" t="str">
+    <row r="40" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A40" t="str">
         <f>Palmon!B41</f>
         <v>Solhorn</v>
       </c>
-      <c r="B38" t="str">
+      <c r="B40" t="str">
         <f>Palmon!C41</f>
         <v>Fire</v>
       </c>
-      <c r="C38" t="str">
+      <c r="C40" t="str">
         <f>Palmon!D41</f>
         <v>Attack</v>
       </c>
-      <c r="D38">
+      <c r="D40">
         <f>Palmon!E41</f>
         <v>0</v>
       </c>
-      <c r="E38" t="str">
+      <c r="E40" t="str">
         <f>Palmon!F41</f>
         <v/>
       </c>
-      <c r="F38">
+      <c r="F40">
         <f>Palmon!G41</f>
         <v>0</v>
       </c>
-      <c r="G38">
+      <c r="G40">
         <f>Palmon!H41</f>
         <v>0</v>
       </c>
-      <c r="H38">
+      <c r="H40">
         <f>Palmon!I41</f>
         <v>0</v>
       </c>
-      <c r="I38" t="str">
+      <c r="I40" t="str">
         <f>Palmon!J41</f>
         <v/>
       </c>
-      <c r="J38">
+      <c r="J40">
         <f>Palmon!K41</f>
         <v>0</v>
       </c>
-      <c r="K38">
+      <c r="K40">
         <f>Palmon!L41</f>
         <v>0</v>
       </c>
-      <c r="L38" t="str">
+      <c r="L40" t="str">
         <f>Palmon!M41</f>
         <v/>
       </c>
-      <c r="M38" t="str">
+      <c r="M40" t="str">
         <f>Palmon!N41</f>
         <v/>
       </c>
-      <c r="N38">
+      <c r="N40">
         <f>Palmon!O41</f>
         <v>0</v>
       </c>
-      <c r="O38">
+      <c r="O40">
         <f>Palmon!P41</f>
         <v>0</v>
       </c>
-      <c r="P38">
+      <c r="P40">
         <f>Palmon!Q41</f>
         <v>0</v>
       </c>
-      <c r="Q38">
+      <c r="Q40">
         <f>Palmon!R41</f>
         <v>0</v>
       </c>
-      <c r="R38">
+      <c r="R40">
         <f>Palmon!S41</f>
         <v>0</v>
       </c>
-      <c r="S38">
+      <c r="S40">
         <f>Palmon!T41</f>
         <v>0</v>
       </c>
-      <c r="T38">
+      <c r="T40">
         <f>Palmon!U41</f>
         <v>0</v>
       </c>
-      <c r="U38">
+      <c r="U40">
         <f>Palmon!V41</f>
         <v>975</v>
       </c>
-      <c r="V38">
+      <c r="V40">
         <f>Palmon!W41</f>
         <v>0</v>
       </c>
-      <c r="W38">
+      <c r="W40">
         <f>Palmon!X41</f>
         <v>5044093700</v>
       </c>
-      <c r="X38" t="str">
+      <c r="X40" t="str">
         <f>Palmon!Y41</f>
         <v/>
       </c>
-      <c r="Y38">
+      <c r="Y40">
         <f>Palmon!Z41</f>
         <v>0</v>
       </c>
-      <c r="Z38">
+      <c r="Z40">
         <f>Palmon!AA41</f>
         <v>0</v>
       </c>
-      <c r="AA38">
+      <c r="AA40">
         <f>Palmon!AB41</f>
         <v>40</v>
       </c>
-      <c r="AB38" t="str">
+      <c r="AB40" t="str">
         <f>Palmon!AC41</f>
         <v/>
       </c>
-      <c r="AC38">
+      <c r="AC40">
         <f>Palmon!AD41</f>
         <v>0</v>
       </c>
-      <c r="AD38">
+      <c r="AD40">
         <f>Palmon!AE41</f>
         <v>0</v>
       </c>
-      <c r="AE38" t="str">
+      <c r="AE40" t="str">
         <f>Palmon!AF41</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AF38" t="str">
+      <c r="AF40" t="str">
         <f>Palmon!AG41</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AG38">
+      <c r="AG40">
         <f>Palmon!AH41</f>
         <v>0</v>
       </c>
-      <c r="AH38">
+      <c r="AH40">
         <f>Palmon!AI41</f>
         <v>0</v>
       </c>
-      <c r="AI38">
+      <c r="AI40">
         <f>Palmon!AJ41</f>
         <v>0</v>
       </c>
-      <c r="AJ38">
+      <c r="AJ40">
         <f>Palmon!AK41</f>
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A39" t="str">
+    <row r="41" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A41" t="str">
         <f>Palmon!B42</f>
         <v>Leviadolph</v>
       </c>
-      <c r="B39" t="str">
+      <c r="B41" t="str">
         <f>Palmon!C42</f>
         <v>Water</v>
       </c>
-      <c r="C39" t="str">
+      <c r="C41" t="str">
         <f>Palmon!D42</f>
         <v>Attack</v>
       </c>
-      <c r="D39">
+      <c r="D41">
         <f>Palmon!E42</f>
         <v>0</v>
       </c>
-      <c r="E39" t="str">
+      <c r="E41" t="str">
         <f>Palmon!F42</f>
         <v/>
       </c>
-      <c r="F39">
+      <c r="F41">
         <f>Palmon!G42</f>
         <v>0</v>
       </c>
-      <c r="G39">
+      <c r="G41">
         <f>Palmon!H42</f>
         <v>0</v>
       </c>
-      <c r="H39">
+      <c r="H41">
         <f>Palmon!I42</f>
         <v>0</v>
       </c>
-      <c r="I39" t="str">
+      <c r="I41" t="str">
         <f>Palmon!J42</f>
         <v/>
       </c>
-      <c r="J39">
+      <c r="J41">
         <f>Palmon!K42</f>
         <v>0</v>
       </c>
-      <c r="K39">
+      <c r="K41">
         <f>Palmon!L42</f>
         <v>0</v>
       </c>
-      <c r="L39" t="str">
+      <c r="L41" t="str">
         <f>Palmon!M42</f>
         <v/>
       </c>
-      <c r="M39" t="str">
+      <c r="M41" t="str">
         <f>Palmon!N42</f>
         <v/>
       </c>
-      <c r="N39">
+      <c r="N41">
         <f>Palmon!O42</f>
         <v>0</v>
       </c>
-      <c r="O39">
+      <c r="O41">
         <f>Palmon!P42</f>
         <v>0</v>
       </c>
-      <c r="P39">
+      <c r="P41">
         <f>Palmon!Q42</f>
         <v>0</v>
       </c>
-      <c r="Q39">
+      <c r="Q41">
         <f>Palmon!R42</f>
         <v>0</v>
       </c>
-      <c r="R39">
+      <c r="R41">
         <f>Palmon!S42</f>
         <v>0</v>
       </c>
-      <c r="S39">
+      <c r="S41">
         <f>Palmon!T42</f>
         <v>0</v>
       </c>
-      <c r="T39">
+      <c r="T41">
         <f>Palmon!U42</f>
         <v>0</v>
       </c>
-      <c r="U39">
+      <c r="U41">
         <f>Palmon!V42</f>
         <v>975</v>
       </c>
-      <c r="V39">
+      <c r="V41">
         <f>Palmon!W42</f>
         <v>0</v>
       </c>
-      <c r="W39">
+      <c r="W41">
         <f>Palmon!X42</f>
         <v>5044093700</v>
       </c>
-      <c r="X39" t="str">
+      <c r="X41" t="str">
         <f>Palmon!Y42</f>
         <v/>
       </c>
-      <c r="Y39">
+      <c r="Y41">
         <f>Palmon!Z42</f>
         <v>0</v>
       </c>
-      <c r="Z39">
+      <c r="Z41">
         <f>Palmon!AA42</f>
         <v>0</v>
       </c>
-      <c r="AA39">
+      <c r="AA41">
         <f>Palmon!AB42</f>
         <v>41</v>
       </c>
-      <c r="AB39" t="str">
+      <c r="AB41" t="str">
         <f>Palmon!AC42</f>
         <v/>
       </c>
-      <c r="AC39">
+      <c r="AC41">
         <f>Palmon!AD42</f>
         <v>0</v>
       </c>
-      <c r="AD39">
+      <c r="AD41">
         <f>Palmon!AE42</f>
         <v>0</v>
       </c>
-      <c r="AE39" t="str">
+      <c r="AE41" t="str">
         <f>Palmon!AF42</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AF39" t="str">
+      <c r="AF41" t="str">
         <f>Palmon!AG42</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AG39">
+      <c r="AG41">
         <f>Palmon!AH42</f>
         <v>0</v>
       </c>
-      <c r="AH39">
+      <c r="AH41">
         <f>Palmon!AI42</f>
         <v>0</v>
       </c>
-      <c r="AI39">
+      <c r="AI41">
         <f>Palmon!AJ42</f>
         <v>0</v>
       </c>
-      <c r="AJ39">
+      <c r="AJ41">
         <f>Palmon!AK42</f>
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A40" t="str">
+    <row r="42" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A42" t="str">
         <f>Palmon!B43</f>
         <v>Voltfang</v>
       </c>
-      <c r="B40" t="str">
+      <c r="B42" t="str">
         <f>Palmon!C43</f>
         <v>Electricity</v>
       </c>
-      <c r="C40" t="str">
+      <c r="C42" t="str">
         <f>Palmon!D43</f>
         <v>Attack</v>
       </c>
-      <c r="D40">
+      <c r="D42">
         <f>Palmon!E43</f>
         <v>0</v>
       </c>
-      <c r="E40" t="str">
+      <c r="E42" t="str">
         <f>Palmon!F43</f>
         <v/>
       </c>
-      <c r="F40">
+      <c r="F42">
         <f>Palmon!G43</f>
         <v>0</v>
       </c>
-      <c r="G40">
+      <c r="G42">
         <f>Palmon!H43</f>
         <v>0</v>
       </c>
-      <c r="H40">
+      <c r="H42">
         <f>Palmon!I43</f>
         <v>0</v>
       </c>
-      <c r="I40" t="str">
+      <c r="I42" t="str">
         <f>Palmon!J43</f>
         <v/>
       </c>
-      <c r="J40">
+      <c r="J42">
         <f>Palmon!K43</f>
         <v>0</v>
       </c>
-      <c r="K40">
+      <c r="K42">
         <f>Palmon!L43</f>
         <v>0</v>
       </c>
-      <c r="L40" t="str">
+      <c r="L42" t="str">
         <f>Palmon!M43</f>
         <v/>
       </c>
-      <c r="M40" t="str">
+      <c r="M42" t="str">
         <f>Palmon!N43</f>
         <v/>
       </c>
-      <c r="N40">
+      <c r="N42">
         <f>Palmon!O43</f>
         <v>0</v>
       </c>
-      <c r="O40">
+      <c r="O42">
         <f>Palmon!P43</f>
         <v>0</v>
       </c>
-      <c r="P40">
+      <c r="P42">
         <f>Palmon!Q43</f>
         <v>0</v>
       </c>
-      <c r="Q40">
+      <c r="Q42">
         <f>Palmon!R43</f>
         <v>0</v>
       </c>
-      <c r="R40">
+      <c r="R42">
         <f>Palmon!S43</f>
         <v>0</v>
       </c>
-      <c r="S40">
+      <c r="S42">
         <f>Palmon!T43</f>
         <v>0</v>
       </c>
-      <c r="T40">
+      <c r="T42">
         <f>Palmon!U43</f>
         <v>0</v>
       </c>
-      <c r="U40">
+      <c r="U42">
         <f>Palmon!V43</f>
         <v>975</v>
       </c>
-      <c r="V40">
+      <c r="V42">
         <f>Palmon!W43</f>
         <v>0</v>
       </c>
-      <c r="W40">
+      <c r="W42">
         <f>Palmon!X43</f>
         <v>5044093700</v>
       </c>
-      <c r="X40" t="str">
+      <c r="X42" t="str">
         <f>Palmon!Y43</f>
         <v/>
       </c>
-      <c r="Y40">
+      <c r="Y42">
         <f>Palmon!Z43</f>
         <v>0</v>
       </c>
-      <c r="Z40">
+      <c r="Z42">
         <f>Palmon!AA43</f>
         <v>0</v>
       </c>
-      <c r="AA40">
+      <c r="AA42">
         <f>Palmon!AB43</f>
         <v>42</v>
       </c>
-      <c r="AB40" t="str">
+      <c r="AB42" t="str">
         <f>Palmon!AC43</f>
         <v/>
       </c>
-      <c r="AC40">
+      <c r="AC42">
         <f>Palmon!AD43</f>
         <v>0</v>
       </c>
-      <c r="AD40">
+      <c r="AD42">
         <f>Palmon!AE43</f>
         <v>0</v>
       </c>
-      <c r="AE40" t="str">
+      <c r="AE42" t="str">
         <f>Palmon!AF43</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AF40" t="str">
+      <c r="AF42" t="str">
         <f>Palmon!AG43</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AG40">
+      <c r="AG42">
         <f>Palmon!AH43</f>
         <v>0</v>
       </c>
-      <c r="AH40">
+      <c r="AH42">
         <f>Palmon!AI43</f>
         <v>0</v>
       </c>
-      <c r="AI40">
+      <c r="AI42">
         <f>Palmon!AJ43</f>
         <v>0</v>
       </c>
-      <c r="AJ40">
+      <c r="AJ42">
         <f>Palmon!AK43</f>
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A41" t="str">
+    <row r="43" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A43" t="str">
         <f>Palmon!B44</f>
         <v>Leafgarde</v>
       </c>
-      <c r="B41" t="str">
+      <c r="B43" t="str">
         <f>Palmon!C44</f>
         <v>Wood</v>
       </c>
-      <c r="C41" t="str">
+      <c r="C43" t="str">
         <f>Palmon!D44</f>
         <v>Attack</v>
       </c>
-      <c r="D41">
+      <c r="D43">
         <f>Palmon!E44</f>
         <v>0</v>
       </c>
-      <c r="E41" t="str">
+      <c r="E43" t="str">
         <f>Palmon!F44</f>
         <v/>
       </c>
-      <c r="F41">
+      <c r="F43">
         <f>Palmon!G44</f>
         <v>0</v>
       </c>
-      <c r="G41">
+      <c r="G43">
         <f>Palmon!H44</f>
         <v>0</v>
       </c>
-      <c r="H41">
+      <c r="H43">
         <f>Palmon!I44</f>
         <v>0</v>
       </c>
-      <c r="I41" t="str">
+      <c r="I43" t="str">
         <f>Palmon!J44</f>
         <v/>
       </c>
-      <c r="J41">
+      <c r="J43">
         <f>Palmon!K44</f>
         <v>0</v>
       </c>
-      <c r="K41">
+      <c r="K43">
         <f>Palmon!L44</f>
         <v>0</v>
       </c>
-      <c r="L41" t="str">
+      <c r="L43" t="str">
         <f>Palmon!M44</f>
         <v/>
       </c>
-      <c r="M41" t="str">
+      <c r="M43" t="str">
         <f>Palmon!N44</f>
         <v/>
       </c>
-      <c r="N41">
+      <c r="N43">
         <f>Palmon!O44</f>
         <v>0</v>
       </c>
-      <c r="O41">
+      <c r="O43">
         <f>Palmon!P44</f>
         <v>0</v>
       </c>
-      <c r="P41">
+      <c r="P43">
         <f>Palmon!Q44</f>
         <v>0</v>
       </c>
-      <c r="Q41">
+      <c r="Q43">
         <f>Palmon!R44</f>
         <v>0</v>
       </c>
-      <c r="R41">
+      <c r="R43">
         <f>Palmon!S44</f>
         <v>0</v>
       </c>
-      <c r="S41">
+      <c r="S43">
         <f>Palmon!T44</f>
         <v>0</v>
       </c>
-      <c r="T41">
+      <c r="T43">
         <f>Palmon!U44</f>
         <v>0</v>
       </c>
-      <c r="U41">
+      <c r="U43">
         <f>Palmon!V44</f>
         <v>975</v>
       </c>
-      <c r="V41">
+      <c r="V43">
         <f>Palmon!W44</f>
         <v>0</v>
       </c>
-      <c r="W41">
+      <c r="W43">
         <f>Palmon!X44</f>
         <v>5044093700</v>
       </c>
-      <c r="X41" t="str">
+      <c r="X43" t="str">
         <f>Palmon!Y44</f>
         <v/>
       </c>
-      <c r="Y41">
+      <c r="Y43">
         <f>Palmon!Z44</f>
         <v>0</v>
       </c>
-      <c r="Z41">
+      <c r="Z43">
         <f>Palmon!AA44</f>
         <v>0</v>
       </c>
-      <c r="AA41">
+      <c r="AA43">
         <f>Palmon!AB44</f>
         <v>43</v>
       </c>
-      <c r="AB41" t="str">
+      <c r="AB43" t="str">
         <f>Palmon!AC44</f>
         <v/>
       </c>
-      <c r="AC41">
+      <c r="AC43">
         <f>Palmon!AD44</f>
         <v>0</v>
       </c>
-      <c r="AD41">
+      <c r="AD43">
         <f>Palmon!AE44</f>
         <v>0</v>
       </c>
-      <c r="AE41" t="str">
+      <c r="AE43" t="str">
         <f>Palmon!AF44</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AF41" t="str">
+      <c r="AF43" t="str">
         <f>Palmon!AG44</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AG41">
+      <c r="AG43">
         <f>Palmon!AH44</f>
         <v>0</v>
       </c>
-      <c r="AH41">
+      <c r="AH43">
         <f>Palmon!AI44</f>
         <v>0</v>
       </c>
-      <c r="AI41">
+      <c r="AI43">
         <f>Palmon!AJ44</f>
         <v>0</v>
       </c>
-      <c r="AJ41">
+      <c r="AJ43">
         <f>Palmon!AK44</f>
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A42" t="str">
+    <row r="44" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A44" t="str">
         <f>Palmon!B45</f>
         <v>Inferdrake</v>
       </c>
-      <c r="B42" t="str">
+      <c r="B44" t="str">
         <f>Palmon!C45</f>
         <v>Fire</v>
       </c>
-      <c r="C42" t="str">
+      <c r="C44" t="str">
         <f>Palmon!D45</f>
         <v>Attack</v>
       </c>
-      <c r="D42">
+      <c r="D44">
         <f>Palmon!E45</f>
         <v>0</v>
       </c>
-      <c r="E42" t="str">
+      <c r="E44" t="str">
         <f>Palmon!F45</f>
         <v/>
       </c>
-      <c r="F42">
+      <c r="F44">
         <f>Palmon!G45</f>
         <v>0</v>
       </c>
-      <c r="G42">
+      <c r="G44">
         <f>Palmon!H45</f>
         <v>0</v>
       </c>
-      <c r="H42">
+      <c r="H44">
         <f>Palmon!I45</f>
         <v>0</v>
       </c>
-      <c r="I42" t="str">
+      <c r="I44" t="str">
         <f>Palmon!J45</f>
         <v/>
       </c>
-      <c r="J42">
+      <c r="J44">
         <f>Palmon!K45</f>
         <v>0</v>
       </c>
-      <c r="K42">
+      <c r="K44">
         <f>Palmon!L45</f>
         <v>0</v>
       </c>
-      <c r="L42" t="str">
+      <c r="L44" t="str">
         <f>Palmon!M45</f>
         <v/>
       </c>
-      <c r="M42" t="str">
+      <c r="M44" t="str">
         <f>Palmon!N45</f>
         <v/>
       </c>
-      <c r="N42">
+      <c r="N44">
         <f>Palmon!O45</f>
         <v>0</v>
       </c>
-      <c r="O42">
+      <c r="O44">
         <f>Palmon!P45</f>
         <v>0</v>
       </c>
-      <c r="P42">
+      <c r="P44">
         <f>Palmon!Q45</f>
         <v>0</v>
       </c>
-      <c r="Q42">
+      <c r="Q44">
         <f>Palmon!R45</f>
         <v>0</v>
       </c>
-      <c r="R42">
+      <c r="R44">
         <f>Palmon!S45</f>
         <v>0</v>
       </c>
-      <c r="S42">
+      <c r="S44">
         <f>Palmon!T45</f>
         <v>0</v>
       </c>
-      <c r="T42">
+      <c r="T44">
         <f>Palmon!U45</f>
         <v>0</v>
       </c>
-      <c r="U42">
+      <c r="U44">
         <f>Palmon!V45</f>
         <v>975</v>
       </c>
-      <c r="V42">
+      <c r="V44">
         <f>Palmon!W45</f>
         <v>0</v>
       </c>
-      <c r="W42">
+      <c r="W44">
         <f>Palmon!X45</f>
         <v>5044093700</v>
       </c>
-      <c r="X42" t="str">
+      <c r="X44" t="str">
         <f>Palmon!Y45</f>
         <v/>
       </c>
-      <c r="Y42">
+      <c r="Y44">
         <f>Palmon!Z45</f>
         <v>0</v>
       </c>
-      <c r="Z42">
+      <c r="Z44">
         <f>Palmon!AA45</f>
         <v>0</v>
       </c>
-      <c r="AA42">
+      <c r="AA44">
         <f>Palmon!AB45</f>
         <v>44</v>
       </c>
-      <c r="AB42" t="str">
+      <c r="AB44" t="str">
         <f>Palmon!AC45</f>
         <v/>
       </c>
-      <c r="AC42">
+      <c r="AC44">
         <f>Palmon!AD45</f>
         <v>0</v>
       </c>
-      <c r="AD42">
+      <c r="AD44">
         <f>Palmon!AE45</f>
         <v>0</v>
       </c>
-      <c r="AE42" t="str">
+      <c r="AE44" t="str">
         <f>Palmon!AF45</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AF42" t="str">
+      <c r="AF44" t="str">
         <f>Palmon!AG45</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AG42">
+      <c r="AG44">
         <f>Palmon!AH45</f>
         <v>0</v>
       </c>
-      <c r="AH42">
+      <c r="AH44">
         <f>Palmon!AI45</f>
         <v>0</v>
       </c>
-      <c r="AI42">
+      <c r="AI44">
         <f>Palmon!AJ45</f>
         <v>0</v>
       </c>
-      <c r="AJ42">
+      <c r="AJ44">
         <f>Palmon!AK45</f>
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A43" t="str">
+    <row r="45" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A45" t="str">
         <f>Palmon!B46</f>
         <v>Revontulet</v>
       </c>
-      <c r="B43" t="str">
+      <c r="B45" t="str">
         <f>Palmon!C46</f>
         <v>Fire</v>
       </c>
-      <c r="C43" t="str">
+      <c r="C45" t="str">
         <f>Palmon!D46</f>
         <v>Attack</v>
       </c>
-      <c r="D43">
+      <c r="D45">
         <f>Palmon!E46</f>
         <v>160</v>
       </c>
-      <c r="E43">
+      <c r="E45">
         <f>Palmon!F46</f>
         <v>1</v>
       </c>
-      <c r="F43">
+      <c r="F45">
         <f>Palmon!G46</f>
         <v>2</v>
       </c>
-      <c r="G43">
+      <c r="G45">
         <f>Palmon!H46</f>
         <v>2.2999999999999998</v>
       </c>
-      <c r="H43">
+      <c r="H45">
         <f>Palmon!I46</f>
         <v>0</v>
       </c>
-      <c r="I43">
+      <c r="I45">
         <f>Palmon!J46</f>
         <v>1</v>
       </c>
-      <c r="J43">
+      <c r="J45">
         <f>Palmon!K46</f>
         <v>1</v>
       </c>
-      <c r="K43">
+      <c r="K45">
         <f>Palmon!L46</f>
         <v>1</v>
       </c>
-      <c r="L43" t="str">
+      <c r="L45" t="str">
         <f>Palmon!M46</f>
         <v/>
       </c>
-      <c r="M43" t="str">
+      <c r="M45" t="str">
         <f>Palmon!N46</f>
         <v/>
       </c>
-      <c r="N43">
+      <c r="N45">
         <f>Palmon!O46</f>
         <v>0</v>
       </c>
-      <c r="O43">
+      <c r="O45">
         <f>Palmon!P46</f>
         <v>1</v>
       </c>
-      <c r="P43">
+      <c r="P45">
         <f>Palmon!Q46</f>
         <v>1</v>
       </c>
-      <c r="Q43">
+      <c r="Q45">
         <f>Palmon!R46</f>
         <v>0.59999999999999964</v>
       </c>
-      <c r="R43">
+      <c r="R45">
         <f>Palmon!S46</f>
         <v>0</v>
       </c>
-      <c r="S43">
+      <c r="S45">
         <f>Palmon!T46</f>
         <v>0</v>
       </c>
-      <c r="T43">
+      <c r="T45">
         <f>Palmon!U46</f>
         <v>0.13846153846153844</v>
       </c>
-      <c r="U43">
+      <c r="U45">
         <f>Palmon!V46</f>
         <v>840</v>
       </c>
-      <c r="V43">
+      <c r="V45">
         <f>Palmon!W46</f>
         <v>0</v>
       </c>
-      <c r="W43">
+      <c r="W45">
         <f>Palmon!X46</f>
         <v>4919220000</v>
       </c>
-      <c r="X43">
+      <c r="X45">
         <f>Palmon!Y46</f>
         <v>1</v>
       </c>
-      <c r="Y43">
+      <c r="Y45">
         <f>Palmon!Z46</f>
         <v>0</v>
       </c>
-      <c r="Z43">
+      <c r="Z45">
         <f>Palmon!AA46</f>
         <v>2460</v>
       </c>
-      <c r="AA43">
+      <c r="AA45">
         <f>Palmon!AB46</f>
         <v>20</v>
       </c>
-      <c r="AB43">
+      <c r="AB45">
         <f>Palmon!AC46</f>
         <v>3</v>
       </c>
-      <c r="AC43">
+      <c r="AC45">
         <f>Palmon!AD46</f>
         <v>0</v>
       </c>
-      <c r="AD43">
+      <c r="AD45">
         <f>Palmon!AE46</f>
         <v>0</v>
       </c>
-      <c r="AE43" t="str">
+      <c r="AE45" t="str">
         <f>Palmon!AF46</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AF43" t="str">
+      <c r="AF45" t="str">
         <f>Palmon!AG46</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AG43">
+      <c r="AG45">
         <f>Palmon!AH46</f>
         <v>0</v>
       </c>
-      <c r="AH43" t="str">
+      <c r="AH45" t="str">
         <f>Palmon!AI46</f>
         <v>Vulpyrean</v>
       </c>
-      <c r="AI43" t="str">
+      <c r="AI45" t="str">
         <f>Palmon!AJ46</f>
         <v>Camouflynx</v>
       </c>
-      <c r="AJ43">
+      <c r="AJ45">
         <f>Palmon!AK46</f>
         <v>0</v>
       </c>
@@ -20003,58 +20295,58 @@
     <mergeCell ref="M22:S22"/>
   </mergeCells>
   <conditionalFormatting sqref="B6:D45">
-    <cfRule type="expression" dxfId="57" priority="43">
+    <cfRule type="expression" dxfId="53" priority="43">
       <formula>$C6="Fire"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="56" priority="44">
+    <cfRule type="expression" dxfId="52" priority="44">
       <formula>$C6="Water"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="55" priority="45">
+    <cfRule type="expression" dxfId="51" priority="45">
       <formula>$C6="Electricity"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="54" priority="46">
+    <cfRule type="expression" dxfId="50" priority="46">
       <formula>$C6="Wood"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L16:L19 U16:U19">
-    <cfRule type="expression" dxfId="53" priority="39">
+    <cfRule type="expression" dxfId="49" priority="39">
       <formula>$L16="Fire"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="52" priority="40">
+    <cfRule type="expression" dxfId="48" priority="40">
       <formula>$L16="Water"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="51" priority="41">
+    <cfRule type="expression" dxfId="47" priority="41">
       <formula>$L16="Electricity"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="42">
+    <cfRule type="expression" dxfId="46" priority="42">
       <formula>$L16="Wood"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L26:L29">
-    <cfRule type="expression" dxfId="49" priority="35">
+    <cfRule type="expression" dxfId="45" priority="35">
       <formula>$L26="Fire"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="36">
+    <cfRule type="expression" dxfId="44" priority="36">
       <formula>$L26="Water"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="47" priority="37">
+    <cfRule type="expression" dxfId="43" priority="37">
       <formula>$L26="Electricity"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="38">
+    <cfRule type="expression" dxfId="42" priority="38">
       <formula>$L26="Wood"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L34:L37">
-    <cfRule type="expression" dxfId="45" priority="31">
+    <cfRule type="expression" dxfId="41" priority="31">
       <formula>$L34="Fire"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="32">
+    <cfRule type="expression" dxfId="40" priority="32">
       <formula>$L34="Water"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="43" priority="33">
+    <cfRule type="expression" dxfId="39" priority="33">
       <formula>$L34="Electricity"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="34">
+    <cfRule type="expression" dxfId="38" priority="34">
       <formula>$L34="Wood"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20068,16 +20360,16 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L42:N48">
-    <cfRule type="expression" dxfId="41" priority="17">
+    <cfRule type="expression" dxfId="37" priority="17">
       <formula>VLOOKUP(L42,PalmonList,2,FALSE)="Wood"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="18">
+    <cfRule type="expression" dxfId="36" priority="18">
       <formula>VLOOKUP(L42,PalmonList,2,FALSE)="Fire"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="39" priority="19">
+    <cfRule type="expression" dxfId="35" priority="19">
       <formula>VLOOKUP(L42,PalmonList,2,FALSE)="Electricity"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="20">
+    <cfRule type="expression" dxfId="34" priority="20">
       <formula>VLOOKUP(L42,PalmonList,2,FALSE)="Water"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20091,16 +20383,16 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q34:Q37">
-    <cfRule type="expression" dxfId="37" priority="5">
+    <cfRule type="expression" dxfId="33" priority="5">
       <formula>$L34="Fire"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="6">
+    <cfRule type="expression" dxfId="32" priority="6">
       <formula>$L34="Water"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="35" priority="7">
+    <cfRule type="expression" dxfId="31" priority="7">
       <formula>$L34="Electricity"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="8">
+    <cfRule type="expression" dxfId="30" priority="8">
       <formula>$L34="Wood"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -32729,10 +33021,10 @@
     <mergeCell ref="Z8:AD8"/>
   </mergeCells>
   <conditionalFormatting sqref="U3:U41">
-    <cfRule type="expression" dxfId="33" priority="5">
+    <cfRule type="expression" dxfId="29" priority="5">
       <formula>AND($U4="",$U3&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="6" operator="notEqual">
+    <cfRule type="cellIs" dxfId="28" priority="6" operator="notEqual">
       <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
@@ -33247,100 +33539,100 @@
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <conditionalFormatting sqref="B2:B4">
-    <cfRule type="expression" dxfId="31" priority="25">
+    <cfRule type="expression" dxfId="27" priority="25">
       <formula>$C2="Fire"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="26">
+    <cfRule type="expression" dxfId="26" priority="26">
       <formula>$C2="Water"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="27">
+    <cfRule type="expression" dxfId="25" priority="27">
       <formula>$C2="Electricity"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="28">
+    <cfRule type="expression" dxfId="24" priority="28">
       <formula>$C2="Wood"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E4">
-    <cfRule type="expression" dxfId="27" priority="21">
+    <cfRule type="expression" dxfId="23" priority="21">
       <formula>$C2="Fire"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="22">
+    <cfRule type="expression" dxfId="22" priority="22">
       <formula>$C2="Water"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="23">
+    <cfRule type="expression" dxfId="21" priority="23">
       <formula>$C2="Electricity"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="24">
+    <cfRule type="expression" dxfId="20" priority="24">
       <formula>$C2="Wood"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J4">
-    <cfRule type="expression" dxfId="23" priority="17">
+    <cfRule type="expression" dxfId="19" priority="17">
       <formula>$C2="Fire"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="18">
+    <cfRule type="expression" dxfId="18" priority="18">
       <formula>$C2="Water"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="19">
+    <cfRule type="expression" dxfId="17" priority="19">
       <formula>$C2="Electricity"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="20">
+    <cfRule type="expression" dxfId="16" priority="20">
       <formula>$C2="Wood"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:P3 Q2:Q7 K4 L4:P7">
-    <cfRule type="expression" dxfId="19" priority="13">
+    <cfRule type="expression" dxfId="15" priority="13">
       <formula>$C2="Fire"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="14">
+    <cfRule type="expression" dxfId="14" priority="14">
       <formula>$C2="Water"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="15">
+    <cfRule type="expression" dxfId="13" priority="15">
       <formula>$C2="Electricity"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="16">
+    <cfRule type="expression" dxfId="12" priority="16">
       <formula>$C2="Wood"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T2:X2">
-    <cfRule type="expression" dxfId="15" priority="9">
+    <cfRule type="expression" dxfId="11" priority="9">
       <formula>$C2="Fire"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="10">
+    <cfRule type="expression" dxfId="10" priority="10">
       <formula>$C2="Water"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="11">
+    <cfRule type="expression" dxfId="9" priority="11">
       <formula>$C2="Electricity"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="12">
+    <cfRule type="expression" dxfId="8" priority="12">
       <formula>$C2="Wood"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2">
-    <cfRule type="expression" dxfId="11" priority="5">
+    <cfRule type="expression" dxfId="7" priority="5">
       <formula>$C2="Fire"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="6">
+    <cfRule type="expression" dxfId="6" priority="6">
       <formula>$C2="Water"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="7">
+    <cfRule type="expression" dxfId="5" priority="7">
       <formula>$C2="Electricity"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="8">
+    <cfRule type="expression" dxfId="4" priority="8">
       <formula>$C2="Wood"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD2">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>$C2="Fire"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="2">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>$C2="Water"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="3">
+    <cfRule type="expression" dxfId="1" priority="3">
       <formula>$C2="Electricity"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="4">
+    <cfRule type="expression" dxfId="0" priority="4">
       <formula>$C2="Wood"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/data/PS - Estimation (version 1).xlsx
+++ b/data/PS - Estimation (version 1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xvjm020\Documents\Personnel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64FDED73-3ED4-411D-899D-2E7501FF5A41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90202AC0-F7FA-4303-A088-E70EC687C02C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9D83D047-1CAD-4BF9-942E-B289F790400E}"/>
   </bookViews>
@@ -2777,6 +2777,74 @@
       </font>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCC6600"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCC6600"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFCC6600"/>
         </patternFill>
       </fill>
@@ -2792,6 +2860,16 @@
       <fill>
         <patternFill>
           <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2835,31 +2913,7 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFCC6600"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2874,12 +2928,9 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFCC6600"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2887,13 +2938,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2908,12 +2952,9 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFCC6600"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2925,53 +2966,12 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <color theme="0"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFCC6600"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5453,10 +5453,10 @@
       </c>
       <c r="G5" s="127">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H5" s="198">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I5" s="123">
         <v>11</v>
@@ -5474,9 +5474,9 @@
         <f t="shared" si="1"/>
         <v>Max</v>
       </c>
-      <c r="N5" s="19">
+      <c r="N5" s="19" t="str">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v/>
       </c>
       <c r="P5" s="9">
         <f>IFERROR(CHOOSE(IF($H5&gt;=Details!$B$4,1,2),Details!$D$4,IF($H5&gt;Details!$B$4-1,IF($H5&lt;1,$H5,MOD($H5,Details!$B$4-1))*10*Details!$C$4,""))/Details!$D$4,0)</f>
@@ -5496,15 +5496,15 @@
       </c>
       <c r="T5" s="9">
         <f>IFERROR(CHOOSE(IF($H5&gt;=Details!$B$8,1,2),Details!$D$8,IF($H5&gt;Details!$B$8-1,IF($H5&lt;1,Details!$G$5,MOD($H5,Details!$B$8-1))*10*Details!$C$8,""))/Details!$D$8,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U5" s="9" cm="1">
         <f t="array" ref="U5">SUMPRODUCT(TRANSPOSE(Details!$D$4:$D$8),$P5:$T5)/Details!$D$9</f>
-        <v>1</v>
+        <v>0.48717948717948717</v>
       </c>
       <c r="V5" s="13" cm="1">
         <f t="array" ref="V5">Details!$D$9-SUMPRODUCT(TRANSPOSE(Details!$D$4:$D$8),$P5:$T5)-$I5</f>
-        <v>-11</v>
+        <v>489</v>
       </c>
       <c r="X5" s="13" cm="1">
         <f t="array" ref="X5">LevelUpgradeCost($E5)</f>
@@ -5516,15 +5516,15 @@
       </c>
       <c r="AA5" s="110">
         <f t="shared" si="5"/>
-        <v>5260</v>
+        <v>4260</v>
       </c>
       <c r="AB5" s="63">
         <f>RANK($AA5,$AA$3:$AA$46)+COUNTIF($AA$3:$AA5,AA5)-1</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC5" s="61" cm="1">
         <f t="array" ref="AC5">IFERROR(_xlfn.IFS($AB5&lt;8,1,$AB5&lt;15,2,$AB5&lt;21,3),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE5" s="63" t="s">
         <v>158</v>
@@ -5632,11 +5632,11 @@
       </c>
       <c r="AB6" s="63">
         <f>RANK($AA6,$AA$3:$AA$46)+COUNTIF($AA$3:$AA6,AA6)-1</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC6" s="61" cm="1">
         <f t="array" ref="AC6">IFERROR(_xlfn.IFS($AB6&lt;8,1,$AB6&lt;15,2,$AB6&lt;21,3),"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE6" s="63" t="s">
         <v>186</v>
@@ -6532,7 +6532,7 @@
       </c>
       <c r="AB14" s="63">
         <f>RANK($AA14,$AA$3:$AA$46)+COUNTIF($AA$3:$AA14,AA14)-1</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC14" s="61" cm="1">
         <f t="array" ref="AC14">IFERROR(_xlfn.IFS($AB14&lt;8,1,$AB14&lt;15,2,$AB14&lt;21,3),"")</f>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="AB27" s="63">
         <f>RANK($AA27,$AA$3:$AA$46)+COUNTIF($AA$3:$AA27,AA27)-1</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC27" s="61" cm="1">
         <f t="array" ref="AC27">IFERROR(_xlfn.IFS($AB27&lt;8,1,$AB27&lt;15,2,$AB27&lt;21,3),"")</f>
@@ -8471,7 +8471,7 @@
         <v>97</v>
       </c>
       <c r="E32" s="63">
-        <v>10</v>
+        <v>140</v>
       </c>
       <c r="F32" s="125" cm="1">
         <f t="array" ref="F32">IsUpgradable(E32)</f>
@@ -8535,7 +8535,7 @@
       </c>
       <c r="X32" s="13" cm="1">
         <f t="array" ref="X32">LevelUpgradeCost($E32)</f>
-        <v>5044089200</v>
+        <v>4999220000</v>
       </c>
       <c r="Y32" s="61">
         <f t="shared" si="4"/>
@@ -8543,7 +8543,7 @@
       </c>
       <c r="AA32" s="110">
         <f t="shared" si="5"/>
-        <v>10</v>
+        <v>140</v>
       </c>
       <c r="AB32" s="63">
         <f>RANK($AA32,$AA$3:$AA$46)+COUNTIF($AA$3:$AA32,AA32)-1</f>
@@ -10154,7 +10154,7 @@
       <c r="I48" s="5"/>
       <c r="X48" s="5">
         <f>SUMPRODUCT(X3:X46,Y3:Y46)</f>
-        <v>95576102900</v>
+        <v>95531233700</v>
       </c>
     </row>
     <row r="49" spans="2:24" ht="12" customHeight="1" x14ac:dyDescent="0.2">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="Q60" s="1">
         <f t="shared" si="22"/>
-        <v>1350</v>
+        <v>1480</v>
       </c>
       <c r="R60" s="1">
         <f t="shared" si="23"/>
@@ -10349,7 +10349,7 @@
       </c>
       <c r="S60" s="1">
         <f t="shared" si="24"/>
-        <v>192.85714285714286</v>
+        <v>211.42857142857142</v>
       </c>
       <c r="X60"/>
     </row>
@@ -11401,11 +11401,11 @@
       </c>
       <c r="F4">
         <f>Palmon!G5</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G4">
         <f>Palmon!H5</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H4">
         <f>Palmon!I5</f>
@@ -11427,9 +11427,9 @@
         <f>Palmon!M5</f>
         <v>Max</v>
       </c>
-      <c r="M4">
+      <c r="M4" t="str">
         <f>Palmon!N5</f>
-        <v>10</v>
+        <v/>
       </c>
       <c r="N4">
         <f>Palmon!O5</f>
@@ -11453,15 +11453,15 @@
       </c>
       <c r="S4">
         <f>Palmon!T5</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4">
         <f>Palmon!U5</f>
-        <v>1</v>
+        <v>0.48717948717948717</v>
       </c>
       <c r="U4">
         <f>Palmon!V5</f>
-        <v>-11</v>
+        <v>489</v>
       </c>
       <c r="V4">
         <f>Palmon!W5</f>
@@ -11481,15 +11481,15 @@
       </c>
       <c r="Z4">
         <f>Palmon!AA5</f>
-        <v>5260</v>
+        <v>4260</v>
       </c>
       <c r="AA4">
         <f>Palmon!AB5</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AB4">
         <f>Palmon!AC5</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC4">
         <f>Palmon!AD5</f>
@@ -11631,11 +11631,11 @@
       </c>
       <c r="AA5">
         <f>Palmon!AB6</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB5">
         <f>Palmon!AC6</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC5">
         <f>Palmon!AD6</f>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="AA13">
         <f>Palmon!AB14</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB13">
         <f>Palmon!AC14</f>
@@ -14697,7 +14697,7 @@
       </c>
       <c r="AA26">
         <f>Palmon!AB27</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB26">
         <f>Palmon!AC27</f>
@@ -15335,7 +15335,7 @@
       </c>
       <c r="D31">
         <f>Palmon!E32</f>
-        <v>10</v>
+        <v>140</v>
       </c>
       <c r="E31">
         <f>Palmon!F32</f>
@@ -15411,7 +15411,7 @@
       </c>
       <c r="W31">
         <f>Palmon!X32</f>
-        <v>5044089200</v>
+        <v>4999220000</v>
       </c>
       <c r="X31">
         <f>Palmon!Y32</f>
@@ -15423,7 +15423,7 @@
       </c>
       <c r="Z31">
         <f>Palmon!AA32</f>
-        <v>10</v>
+        <v>140</v>
       </c>
       <c r="AA31">
         <f>Palmon!AB32</f>
@@ -18212,10 +18212,10 @@
         <v>290</v>
       </c>
       <c r="O17" s="33">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="P17" s="47">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="Q17" s="40"/>
       <c r="R17" s="1"/>
@@ -18350,11 +18350,11 @@
       <c r="F20" s="33" t="str">
         <v/>
       </c>
-      <c r="G20" s="33" t="str">
-        <v/>
-      </c>
-      <c r="H20" s="33">
-        <v>0</v>
+      <c r="G20" s="33">
+        <v>489</v>
+      </c>
+      <c r="H20" s="33" t="str">
+        <v/>
       </c>
       <c r="I20" s="33"/>
       <c r="J20" s="40"/>
@@ -18666,10 +18666,10 @@
         <v>3</v>
       </c>
       <c r="O27" s="33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P27" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q27" s="47">
         <v>7</v>
@@ -18801,10 +18801,10 @@
         <v>5</v>
       </c>
       <c r="O30" s="86">
+        <v>5</v>
+      </c>
+      <c r="P30" s="86">
         <v>4</v>
-      </c>
-      <c r="P30" s="86">
-        <v>5</v>
       </c>
       <c r="Q30" s="87">
         <v>28</v>
@@ -19002,10 +19002,10 @@
         <v>Fire</v>
       </c>
       <c r="M35" s="39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N35" s="33">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O35" s="40">
         <v>2</v>
@@ -19068,10 +19068,10 @@
         <v>Wood</v>
       </c>
       <c r="M37" s="39">
-        <v>2</v>
-      </c>
-      <c r="N37" s="33">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="N37" s="33" t="str">
+        <v/>
       </c>
       <c r="O37" s="40" t="str">
         <v/>
@@ -19208,7 +19208,7 @@
         <v>Bufonobi</v>
       </c>
       <c r="M42" s="74" t="str">
-        <v>Ghillant</v>
+        <v>Hoofrit</v>
       </c>
       <c r="N42" s="75" t="str">
         <v>Blazeal</v>
@@ -19219,7 +19219,7 @@
         <v>Bufonobi</v>
       </c>
       <c r="Q42" s="1" t="str">
-        <v>Ghillant</v>
+        <v>Hoofrit</v>
       </c>
       <c r="R42" s="1"/>
       <c r="T42"/>
@@ -19325,7 +19325,7 @@
     </row>
     <row r="46" spans="2:23" x14ac:dyDescent="0.25">
       <c r="L46" s="76" t="str">
-        <v>Hoofrit</v>
+        <v>Fleurizard</v>
       </c>
       <c r="M46" s="77" t="str">
         <v>Magmolin</v>
@@ -19335,7 +19335,7 @@
       </c>
       <c r="O46" s="1"/>
       <c r="P46" s="1" t="str">
-        <v>Hoofrit</v>
+        <v>Fleurizard</v>
       </c>
       <c r="Q46" s="1" t="str">
         <v>Magmolin</v>
@@ -19348,7 +19348,7 @@
     </row>
     <row r="47" spans="2:23" x14ac:dyDescent="0.25">
       <c r="L47" s="76" t="str">
-        <v>Fleurizard</v>
+        <v>Oleana</v>
       </c>
       <c r="M47" s="77" t="str">
         <v>Spookaboo</v>
@@ -19358,7 +19358,7 @@
       </c>
       <c r="O47" s="1"/>
       <c r="P47" s="1" t="str">
-        <v>Fleurizard</v>
+        <v>Oleana</v>
       </c>
       <c r="Q47" s="1" t="str">
         <v>Spookaboo</v>
@@ -19371,7 +19371,7 @@
     </row>
     <row r="48" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L48" s="81" t="str">
-        <v>Oleana</v>
+        <v>Ghillant</v>
       </c>
       <c r="M48" s="82" t="str">
         <v>Barkplug</v>
@@ -19381,7 +19381,7 @@
       </c>
       <c r="O48" s="1"/>
       <c r="P48" s="1" t="str">
-        <v>Oleana</v>
+        <v>Ghillant</v>
       </c>
       <c r="Q48" s="1" t="str">
         <v>Barkplug</v>
@@ -19701,7 +19701,7 @@
     </row>
     <row r="61" spans="7:20" s="1" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="G61" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H61" s="1" t="str">
         <v/>
@@ -19710,13 +19710,13 @@
         <v>Fleurizard</v>
       </c>
       <c r="M61" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N61" s="1" t="str">
         <v/>
       </c>
       <c r="P61" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q61" s="1" t="str">
         <v/>
@@ -19750,7 +19750,7 @@
         <v/>
       </c>
       <c r="H63" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L63" s="1" t="str">
         <v>Ghillant</v>
@@ -19759,7 +19759,7 @@
         <v/>
       </c>
       <c r="N63" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P63" s="1" t="str">
         <v/>
@@ -19793,7 +19793,7 @@
     </row>
     <row r="65" spans="7:20" s="1" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="G65" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H65" s="1" t="str">
         <v/>
@@ -19802,13 +19802,13 @@
         <v>Hoofrit</v>
       </c>
       <c r="M65" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N65" s="1" t="str">
         <v/>
       </c>
       <c r="P65" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q65" s="1" t="str">
         <v/>
@@ -19954,7 +19954,7 @@
     </row>
     <row r="72" spans="7:20" s="1" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="G72" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H72" s="1" t="str">
         <v/>
@@ -19963,13 +19963,13 @@
         <v>Oleana</v>
       </c>
       <c r="M72" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N72" s="1" t="str">
         <v/>
       </c>
       <c r="P72" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q72" s="1" t="str">
         <v/>
@@ -33038,6 +33038,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA7308F7-EA56-45FF-9245-DD8052CA9BFA}">
   <dimension ref="A1:AD12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="10" max="16" width="6.5703125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="253" t="s">
@@ -33170,25 +33173,25 @@
       <c r="I3" s="248" t="s">
         <v>249</v>
       </c>
-      <c r="J3" s="237">
+      <c r="J3" s="4">
         <v>1</v>
       </c>
       <c r="K3" s="246">
         <v>0</v>
       </c>
-      <c r="L3" s="237">
-        <v>0</v>
-      </c>
-      <c r="M3" s="237">
-        <v>0</v>
-      </c>
-      <c r="N3" s="237">
-        <v>0</v>
-      </c>
-      <c r="O3" s="237">
-        <v>0</v>
-      </c>
-      <c r="P3" s="237">
+      <c r="L3" s="4">
+        <v>0</v>
+      </c>
+      <c r="M3" s="4">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0</v>
+      </c>
+      <c r="O3" s="4">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
         <v>0</v>
       </c>
       <c r="Q3" s="237" t="s">
@@ -33236,25 +33239,25 @@
       <c r="I4" s="248" t="s">
         <v>50</v>
       </c>
-      <c r="J4" s="237">
-        <v>1</v>
+      <c r="J4" s="4">
+        <v>42</v>
       </c>
       <c r="K4" s="246">
         <v>0</v>
       </c>
-      <c r="L4" s="237">
-        <v>0</v>
-      </c>
-      <c r="M4" s="237">
-        <v>0</v>
-      </c>
-      <c r="N4" s="237">
-        <v>0</v>
-      </c>
-      <c r="O4" s="237">
-        <v>0</v>
-      </c>
-      <c r="P4" s="237">
+      <c r="L4" s="4">
+        <v>0</v>
+      </c>
+      <c r="M4" s="4">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0</v>
+      </c>
+      <c r="O4" s="4">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
         <v>0</v>
       </c>
       <c r="Q4" s="237" t="s">
@@ -33302,25 +33305,25 @@
       <c r="I5" s="248" t="s">
         <v>61</v>
       </c>
-      <c r="J5" s="237">
-        <v>1</v>
+      <c r="J5" s="4">
+        <v>50</v>
       </c>
       <c r="K5" s="246">
         <v>0</v>
       </c>
-      <c r="L5" s="237">
-        <v>0</v>
-      </c>
-      <c r="M5" s="237">
-        <v>0</v>
-      </c>
-      <c r="N5" s="237">
-        <v>0</v>
-      </c>
-      <c r="O5" s="237">
-        <v>0</v>
-      </c>
-      <c r="P5" s="237">
+      <c r="L5" s="4">
+        <v>0</v>
+      </c>
+      <c r="M5" s="4">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0</v>
+      </c>
+      <c r="O5" s="4">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
         <v>0</v>
       </c>
       <c r="Q5" s="237" t="s">
@@ -33362,25 +33365,25 @@
       <c r="I6" s="248" t="s">
         <v>53</v>
       </c>
-      <c r="J6" s="237">
+      <c r="J6" s="4">
         <v>120</v>
       </c>
       <c r="K6" s="246">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="L6" s="237">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="L6" s="4">
         <v>5</v>
       </c>
-      <c r="M6" s="237">
-        <v>0</v>
-      </c>
-      <c r="N6" s="237">
-        <v>0</v>
-      </c>
-      <c r="O6" s="237">
-        <v>0</v>
-      </c>
-      <c r="P6" s="237">
+      <c r="M6" s="4">
+        <v>3</v>
+      </c>
+      <c r="N6" s="4">
+        <v>0</v>
+      </c>
+      <c r="O6" s="4">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
         <v>0</v>
       </c>
       <c r="Q6" s="237" t="s">
@@ -33419,25 +33422,25 @@
       <c r="I7" s="248" t="s">
         <v>55</v>
       </c>
-      <c r="J7" s="237">
+      <c r="J7" s="4">
         <v>1</v>
       </c>
       <c r="K7" s="246">
         <v>0</v>
       </c>
-      <c r="L7" s="237">
-        <v>0</v>
-      </c>
-      <c r="M7" s="237">
-        <v>0</v>
-      </c>
-      <c r="N7" s="237">
-        <v>0</v>
-      </c>
-      <c r="O7" s="237">
-        <v>0</v>
-      </c>
-      <c r="P7" s="237">
+      <c r="L7" s="4">
+        <v>0</v>
+      </c>
+      <c r="M7" s="4">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4">
+        <v>0</v>
+      </c>
+      <c r="O7" s="4">
+        <v>0</v>
+      </c>
+      <c r="P7" s="4">
         <v>0</v>
       </c>
       <c r="Q7" s="237" t="s">
@@ -33539,100 +33542,100 @@
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <conditionalFormatting sqref="B2:B4">
-    <cfRule type="expression" dxfId="27" priority="25">
+    <cfRule type="expression" dxfId="27" priority="36">
+      <formula>$C2="Wood"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="26" priority="35">
+      <formula>$C2="Electricity"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="25" priority="34">
+      <formula>$C2="Water"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="33">
       <formula>$C2="Fire"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="26">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E4">
+    <cfRule type="expression" dxfId="23" priority="31">
+      <formula>$C2="Electricity"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="30">
       <formula>$C2="Water"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="27">
-      <formula>$C2="Electricity"</formula>
+    <cfRule type="expression" dxfId="21" priority="29">
+      <formula>$C2="Fire"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="28">
+    <cfRule type="expression" dxfId="20" priority="32">
       <formula>$C2="Wood"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E4">
-    <cfRule type="expression" dxfId="23" priority="21">
+  <conditionalFormatting sqref="J2:P4">
+    <cfRule type="expression" dxfId="19" priority="2">
+      <formula>$C2="Water"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="3">
+      <formula>$C2="Electricity"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="4">
+      <formula>$C2="Wood"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="1">
       <formula>$C2="Fire"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="22">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q2:Q7">
+    <cfRule type="expression" dxfId="15" priority="21">
+      <formula>$C2="Fire"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="22">
       <formula>$C2="Water"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="23">
+    <cfRule type="expression" dxfId="13" priority="23">
       <formula>$C2="Electricity"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="24">
-      <formula>$C2="Wood"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J4">
-    <cfRule type="expression" dxfId="19" priority="17">
-      <formula>$C2="Fire"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="18" priority="18">
-      <formula>$C2="Water"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="17" priority="19">
-      <formula>$C2="Electricity"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="16" priority="20">
-      <formula>$C2="Wood"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:P3 Q2:Q7 K4 L4:P7">
-    <cfRule type="expression" dxfId="15" priority="13">
-      <formula>$C2="Fire"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="14" priority="14">
-      <formula>$C2="Water"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="13" priority="15">
-      <formula>$C2="Electricity"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="12" priority="16">
+    <cfRule type="expression" dxfId="12" priority="24">
       <formula>$C2="Wood"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T2:X2">
-    <cfRule type="expression" dxfId="11" priority="9">
+    <cfRule type="expression" dxfId="11" priority="20">
+      <formula>$C2="Wood"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="18">
+      <formula>$C2="Water"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="9" priority="17">
       <formula>$C2="Fire"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="10">
-      <formula>$C2="Water"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="9" priority="11">
+    <cfRule type="expression" dxfId="8" priority="19">
       <formula>$C2="Electricity"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="8" priority="12">
-      <formula>$C2="Wood"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2">
-    <cfRule type="expression" dxfId="7" priority="5">
-      <formula>$C2="Fire"</formula>
+    <cfRule type="expression" dxfId="7" priority="16">
+      <formula>$C2="Wood"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="6">
+    <cfRule type="expression" dxfId="6" priority="15">
+      <formula>$C2="Electricity"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="14">
       <formula>$C2="Water"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="7">
-      <formula>$C2="Electricity"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="8">
-      <formula>$C2="Wood"</formula>
+    <cfRule type="expression" dxfId="4" priority="13">
+      <formula>$C2="Fire"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD2">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="3" priority="9">
       <formula>$C2="Fire"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="2" priority="10">
       <formula>$C2="Water"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="3">
+    <cfRule type="expression" dxfId="1" priority="11">
       <formula>$C2="Electricity"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="4">
+    <cfRule type="expression" dxfId="0" priority="12">
       <formula>$C2="Wood"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -43560,7 +43563,7 @@
       </c>
       <c r="F5" t="str">
         <f>Palmon!B5 &amp; "," &amp; Palmon!C5 &amp; "," &amp; Palmon!D5 &amp; "," &amp; Palmon!E5 &amp; "," &amp; Palmon!G5 &amp; "," &amp; SUBSTITUTE(Palmon!H5,",",".") &amp; "," &amp; Palmon!I5 &amp; "," &amp; SUBSTITUTE(Palmon!P5,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q5,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R5,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S5,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T5,",",".") &amp; "," &amp; Palmon!J5 &amp; "," &amp; Palmon!K5 &amp; "," &amp; Palmon!L5 &amp; "," &amp; Palmon!M5 &amp; "," &amp; Palmon!N5 &amp; "," &amp; SUBSTITUTE(Palmon!U5,",",".") &amp; "," &amp; Palmon!V5 &amp; "," &amp; Palmon!X5 &amp; "," &amp; Palmon!Y5 &amp; "," &amp; Palmon!AA5 &amp; "," &amp; Palmon!AB5 &amp; "," &amp; Palmon!AC5 &amp; "," &amp; Palmon!AE5 &amp; "," &amp; Palmon!AF5 &amp; "," &amp; Palmon!AI5 &amp; "," &amp; Palmon!AJ5</f>
-        <v>Hoofrit,Fire,Attack,260,5,5,11,1,1,1,1,1,15,15,15,Max,10,1,-11,1235520000,1,5260,5,1,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRwfHFWjB1bN67FJNyjjWvBJwviWJ3Tada0Yg&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSkOv6mOI5FaIAjcVgErYDwVaivkH3WdUQIzw&amp;s,Flaries,</v>
+        <v>Hoofrit,Fire,Attack,260,4,4,11,1,1,1,1,0,15,15,15,Max,,0.487179487179487,489,1235520000,1,4260,8,2,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRwfHFWjB1bN67FJNyjjWvBJwviWJ3Tada0Yg&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSkOv6mOI5FaIAjcVgErYDwVaivkH3WdUQIzw&amp;s,Flaries,</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -43586,7 +43589,7 @@
       </c>
       <c r="F6" t="str">
         <f>Palmon!B6 &amp; "," &amp; Palmon!C6 &amp; "," &amp; Palmon!D6 &amp; "," &amp; Palmon!E6 &amp; "," &amp; Palmon!G6 &amp; "," &amp; SUBSTITUTE(Palmon!H6,",",".") &amp; "," &amp; Palmon!I6 &amp; "," &amp; SUBSTITUTE(Palmon!P6,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q6,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R6,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S6,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T6,",",".") &amp; "," &amp; Palmon!J6 &amp; "," &amp; Palmon!K6 &amp; "," &amp; Palmon!L6 &amp; "," &amp; Palmon!M6 &amp; "," &amp; Palmon!N6 &amp; "," &amp; SUBSTITUTE(Palmon!U6,",",".") &amp; "," &amp; Palmon!V6 &amp; "," &amp; Palmon!X6 &amp; "," &amp; Palmon!Y6 &amp; "," &amp; Palmon!AA6 &amp; "," &amp; Palmon!AB6 &amp; "," &amp; Palmon!AC6 &amp; "," &amp; Palmon!AE6 &amp; "," &amp; Palmon!AF6 &amp; "," &amp; Palmon!AI6 &amp; "," &amp; Palmon!AJ6</f>
-        <v>Ghillant,Wood,Defend,250,4,4.1,0,1,1,1,1,0.199999999999999,5,5,5,Max,,0.589743589743589,400,2123020000,1,4350,8,2,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQOwDXppnwkCtCXXAqUiiNMhf6T-lane54jPg&amp;s, ,Chefeuillier,</v>
+        <v>Ghillant,Wood,Defend,250,4,4.1,0,1,1,1,1,0.199999999999999,5,5,5,Max,,0.589743589743589,400,2123020000,1,4350,7,1,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQOwDXppnwkCtCXXAqUiiNMhf6T-lane54jPg&amp;s, ,Chefeuillier,</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -43794,7 +43797,7 @@
       </c>
       <c r="F14" t="str">
         <f>Palmon!B14 &amp; "," &amp; Palmon!C14 &amp; "," &amp; Palmon!D14 &amp; "," &amp; Palmon!E14 &amp; "," &amp; Palmon!G14 &amp; "," &amp; SUBSTITUTE(Palmon!H14,",",".") &amp; "," &amp; Palmon!I14 &amp; "," &amp; SUBSTITUTE(Palmon!P14,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q14,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R14,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S14,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T14,",",".") &amp; "," &amp; Palmon!J14 &amp; "," &amp; Palmon!K14 &amp; "," &amp; Palmon!L14 &amp; "," &amp; Palmon!M14 &amp; "," &amp; Palmon!N14 &amp; "," &amp; SUBSTITUTE(Palmon!U14,",",".") &amp; "," &amp; Palmon!V14 &amp; "," &amp; Palmon!X14 &amp; "," &amp; Palmon!Y14 &amp; "," &amp; Palmon!AA14 &amp; "," &amp; Palmon!AB14 &amp; "," &amp; Palmon!AC14 &amp; "," &amp; Palmon!AE14 &amp; "," &amp; Palmon!AF14 &amp; "," &amp; Palmon!AI14 &amp; "," &amp; Palmon!AJ14</f>
-        <v>Fleurizard,Wood,Attack,260,5,5,0,1,1,1,1,1,1,1,1,Max,10,1,0,1235520000,1,5260,6,1,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQCf63iS9oq-SMn3DO74UTS2j_zSrzNVTRMOQ&amp;s, ,,</v>
+        <v>Fleurizard,Wood,Attack,260,5,5,0,1,1,1,1,1,1,1,1,Max,10,1,0,1235520000,1,5260,5,1,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQCf63iS9oq-SMn3DO74UTS2j_zSrzNVTRMOQ&amp;s, ,,</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -44132,7 +44135,7 @@
       </c>
       <c r="F27" t="str">
         <f>Palmon!B27 &amp; "," &amp; Palmon!C27 &amp; "," &amp; Palmon!D27 &amp; "," &amp; Palmon!E27 &amp; "," &amp; Palmon!G27 &amp; "," &amp; SUBSTITUTE(Palmon!H27,",",".") &amp; "," &amp; Palmon!I27 &amp; "," &amp; SUBSTITUTE(Palmon!P27,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q27,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R27,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S27,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T27,",",".") &amp; "," &amp; Palmon!J27 &amp; "," &amp; Palmon!K27 &amp; "," &amp; Palmon!L27 &amp; "," &amp; Palmon!M27 &amp; "," &amp; Palmon!N27 &amp; "," &amp; SUBSTITUTE(Palmon!U27,",",".") &amp; "," &amp; Palmon!V27 &amp; "," &amp; Palmon!X27 &amp; "," &amp; Palmon!Y27 &amp; "," &amp; Palmon!AA27 &amp; "," &amp; Palmon!AB27 &amp; "," &amp; Palmon!AC27 &amp; "," &amp; Palmon!AE27 &amp; "," &amp; Palmon!AF27 &amp; "," &amp; Palmon!AI27 &amp; "," &amp; Palmon!AJ27</f>
-        <v>Oleana,Wood,Attack,260,4,4.3,128,1,1,1,1,0.6,1,1,1,Max,,0.794871794871795,72,0000000000002,1235520000,1,4560,7,1,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQ02wmDjsAMofj1ObwwNW6Vhl_QQ-LUodGIKA&amp;s, ,,</v>
+        <v>Oleana,Wood,Attack,260,4,4.3,128,1,1,1,1,0.6,1,1,1,Max,,0.794871794871795,72,0000000000002,1235520000,1,4560,6,1,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQ02wmDjsAMofj1ObwwNW6Vhl_QQ-LUodGIKA&amp;s, ,,</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -44262,7 +44265,7 @@
       </c>
       <c r="F32" t="str">
         <f>Palmon!B32 &amp; "," &amp; Palmon!C32 &amp; "," &amp; Palmon!D32 &amp; "," &amp; Palmon!E32 &amp; "," &amp; Palmon!G32 &amp; "," &amp; SUBSTITUTE(Palmon!H32,",",".") &amp; "," &amp; Palmon!I32 &amp; "," &amp; SUBSTITUTE(Palmon!P32,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q32,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R32,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S32,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T32,",",".") &amp; "," &amp; Palmon!J32 &amp; "," &amp; Palmon!K32 &amp; "," &amp; Palmon!L32 &amp; "," &amp; Palmon!M32 &amp; "," &amp; Palmon!N32 &amp; "," &amp; SUBSTITUTE(Palmon!U32,",",".") &amp; "," &amp; Palmon!V32 &amp; "," &amp; Palmon!X32 &amp; "," &amp; Palmon!Y32 &amp; "," &amp; Palmon!AA32 &amp; "," &amp; Palmon!AB32 &amp; "," &amp; Palmon!AC32 &amp; "," &amp; Palmon!AE32 &amp; "," &amp; Palmon!AF32 &amp; "," &amp; Palmon!AI32 &amp; "," &amp; Palmon!AJ32</f>
-        <v>Thundertooth,Electricity,Attack,10,0,0,250,0,0,0,0,0,1,1,1,,,0,725,5044089200,1,10,31,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRNSg29kZ5t51s7m9SpGygJKsQow67zLt08qg&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQoXkXemCK02vmhKICXcvjchtQ-qvcAc5zyrA&amp;s,Thundermane,</v>
+        <v>Thundertooth,Electricity,Attack,140,0,0,250,0,0,0,0,0,1,1,1,,,0,725,4999220000,1,140,31,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRNSg29kZ5t51s7m9SpGygJKsQow67zLt08qg&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQoXkXemCK02vmhKICXcvjchtQ-qvcAc5zyrA&amp;s,Thundermane,</v>
       </c>
     </row>
     <row r="33" spans="3:6" x14ac:dyDescent="0.25">

--- a/data/PS - Estimation (version 1).xlsx
+++ b/data/PS - Estimation (version 1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xvjm020\Documents\Personnel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90202AC0-F7FA-4303-A088-E70EC687C02C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B79F1D30-8A5D-4856-830E-830A00D6E767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9D83D047-1CAD-4BF9-942E-B289F790400E}"/>
   </bookViews>
@@ -2777,30 +2777,6 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFCC6600"/>
         </patternFill>
       </fill>
@@ -2809,16 +2785,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2835,7 +2801,7 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFCC6600"/>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2879,6 +2845,30 @@
       </font>
       <fill>
         <patternFill>
+          <bgColor rgb="FFCC6600"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
@@ -2913,7 +2903,31 @@
       </font>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFCC6600"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2928,9 +2942,12 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
       <fill>
         <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor rgb="FFCC6600"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2942,26 +2959,9 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2971,7 +2971,7 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFCC6600"/>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5445,11 +5445,11 @@
         <v>97</v>
       </c>
       <c r="E5" s="63">
-        <v>260</v>
-      </c>
-      <c r="F5" s="125" cm="1">
+        <v>270</v>
+      </c>
+      <c r="F5" s="125" t="str" cm="1">
         <f t="array" ref="F5">IsUpgradable(E5)</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="G5" s="127">
         <f t="shared" si="0"/>
@@ -5508,19 +5508,19 @@
       </c>
       <c r="X5" s="13" cm="1">
         <f t="array" ref="X5">LevelUpgradeCost($E5)</f>
-        <v>1235520000</v>
-      </c>
-      <c r="Y5" s="61">
+        <v>135120000</v>
+      </c>
+      <c r="Y5" s="61" t="str">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AA5" s="110">
         <f t="shared" si="5"/>
-        <v>4260</v>
+        <v>4270</v>
       </c>
       <c r="AB5" s="63">
         <f>RANK($AA5,$AA$3:$AA$46)+COUNTIF($AA$3:$AA5,AA5)-1</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC5" s="61" cm="1">
         <f t="array" ref="AC5">IFERROR(_xlfn.IFS($AB5&lt;8,1,$AB5&lt;15,2,$AB5&lt;21,3),"")</f>
@@ -5632,11 +5632,11 @@
       </c>
       <c r="AB6" s="63">
         <f>RANK($AA6,$AA$3:$AA$46)+COUNTIF($AA$3:$AA6,AA6)-1</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC6" s="61" cm="1">
         <f t="array" ref="AC6">IFERROR(_xlfn.IFS($AB6&lt;8,1,$AB6&lt;15,2,$AB6&lt;21,3),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE6" s="63" t="s">
         <v>186</v>
@@ -5857,7 +5857,7 @@
       </c>
       <c r="AB8" s="63">
         <f>RANK($AA8,$AA$3:$AA$46)+COUNTIF($AA$3:$AA8,AA8)-1</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AC8" s="61" cm="1">
         <f t="array" ref="AC8">IFERROR(_xlfn.IFS($AB8&lt;8,1,$AB8&lt;15,2,$AB8&lt;21,3),"")</f>
@@ -6082,11 +6082,11 @@
       </c>
       <c r="AB10" s="63">
         <f>RANK($AA10,$AA$3:$AA$46)+COUNTIF($AA$3:$AA10,AA10)-1</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC10" s="61" cm="1">
         <f t="array" ref="AC10">IFERROR(_xlfn.IFS($AB10&lt;8,1,$AB10&lt;15,2,$AB10&lt;21,3),"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE10" s="63" t="s">
         <v>190</v>
@@ -6127,10 +6127,10 @@
       </c>
       <c r="G11" s="127">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H11" s="198">
-        <v>2.2999999999999998</v>
+        <v>4</v>
       </c>
       <c r="I11" s="123">
         <v>14</v>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="M11" s="7" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Max</v>
       </c>
       <c r="N11" s="19" t="str">
         <f t="shared" si="2"/>
@@ -6162,11 +6162,11 @@
       </c>
       <c r="R11" s="9">
         <f>IFERROR(CHOOSE(IF($H11&gt;=Details!$B$6,1,2),Details!$D$6,IF($H11&gt;Details!$B$6-1,IF($H11&lt;1,Details!$G$5,MOD($H11,Details!$B$6-1))*10*Details!$C$6,""))/Details!$D$6,0)</f>
-        <v>0.59999999999999964</v>
+        <v>1</v>
       </c>
       <c r="S11" s="9">
         <f>IFERROR(CHOOSE(IF($H11&gt;=Details!$B$7,1,2),Details!$D$7,IF($H11&gt;Details!$B$7-1,IF($H11&lt;1,Details!$G$5,MOD($H11,Details!$B$7-1))*10*Details!$C$7,""))/Details!$D$7,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T11" s="9">
         <f>IFERROR(CHOOSE(IF($H11&gt;=Details!$B$8,1,2),Details!$D$8,IF($H11&gt;Details!$B$8-1,IF($H11&lt;1,Details!$G$5,MOD($H11,Details!$B$8-1))*10*Details!$C$8,""))/Details!$D$8,0)</f>
@@ -6174,11 +6174,11 @@
       </c>
       <c r="U11" s="9" cm="1">
         <f t="array" ref="U11">SUMPRODUCT(TRANSPOSE(Details!$D$4:$D$8),$P11:$T11)/Details!$D$9</f>
-        <v>0.13846153846153844</v>
+        <v>0.48717948717948717</v>
       </c>
       <c r="V11" s="13" cm="1">
         <f t="array" ref="V11">Details!$D$9-SUMPRODUCT(TRANSPOSE(Details!$D$4:$D$8),$P11:$T11)-$I11</f>
-        <v>826</v>
+        <v>486</v>
       </c>
       <c r="X11" s="13" cm="1">
         <f t="array" ref="X11">LevelUpgradeCost($E11)</f>
@@ -6190,15 +6190,15 @@
       </c>
       <c r="AA11" s="110">
         <f t="shared" si="5"/>
-        <v>2530</v>
+        <v>4230</v>
       </c>
       <c r="AB11" s="63">
         <f>RANK($AA11,$AA$3:$AA$46)+COUNTIF($AA$3:$AA11,AA11)-1</f>
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AC11" s="61" cm="1">
         <f t="array" ref="AC11">IFERROR(_xlfn.IFS($AB11&lt;8,1,$AB11&lt;15,2,$AB11&lt;21,3),"")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE11" s="63" t="s">
         <v>170</v>
@@ -6344,11 +6344,11 @@
         <v>97</v>
       </c>
       <c r="E13" s="63">
-        <v>260</v>
-      </c>
-      <c r="F13" s="125" cm="1">
+        <v>270</v>
+      </c>
+      <c r="F13" s="125" t="str" cm="1">
         <f t="array" ref="F13">IsUpgradable(E13)</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="G13" s="127">
         <f t="shared" si="0"/>
@@ -6407,19 +6407,19 @@
       </c>
       <c r="X13" s="13" cm="1">
         <f t="array" ref="X13">LevelUpgradeCost($E13)</f>
-        <v>1235520000</v>
-      </c>
-      <c r="Y13" s="61">
+        <v>135120000</v>
+      </c>
+      <c r="Y13" s="61" t="str">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AA13" s="110">
         <f t="shared" si="5"/>
-        <v>4260</v>
+        <v>4270</v>
       </c>
       <c r="AB13" s="63">
         <f>RANK($AA13,$AA$3:$AA$46)+COUNTIF($AA$3:$AA13,AA13)-1</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC13" s="61" cm="1">
         <f t="array" ref="AC13">IFERROR(_xlfn.IFS($AB13&lt;8,1,$AB13&lt;15,2,$AB13&lt;21,3),"")</f>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="AB18" s="63">
         <f>RANK($AA18,$AA$3:$AA$46)+COUNTIF($AA$3:$AA18,AA18)-1</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AC18" s="61" cm="1">
         <f t="array" ref="AC18">IFERROR(_xlfn.IFS($AB18&lt;8,1,$AB18&lt;15,2,$AB18&lt;21,3),"")</f>
@@ -7017,18 +7017,18 @@
         <v>97</v>
       </c>
       <c r="E19" s="63">
-        <v>260</v>
-      </c>
-      <c r="F19" s="125" cm="1">
+        <v>270</v>
+      </c>
+      <c r="F19" s="125" t="str" cm="1">
         <f t="array" ref="F19">IsUpgradable(E19)</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="G19" s="127">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="H19" s="198">
-        <v>4</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="I19" s="123">
         <v>13</v>
@@ -7068,35 +7068,35 @@
       </c>
       <c r="T19" s="9">
         <f>IFERROR(CHOOSE(IF($H19&gt;=Details!$B$8,1,2),Details!$D$8,IF($H19&gt;Details!$B$8-1,IF($H19&lt;1,Details!$G$5,MOD($H19,Details!$B$8-1))*10*Details!$C$8,""))/Details!$D$8,0)</f>
-        <v>0</v>
+        <v>0.19999999999999929</v>
       </c>
       <c r="U19" s="9" cm="1">
         <f t="array" ref="U19">SUMPRODUCT(TRANSPOSE(Details!$D$4:$D$8),$P19:$T19)/Details!$D$9</f>
-        <v>0.48717948717948717</v>
+        <v>0.58974358974358942</v>
       </c>
       <c r="V19" s="13" cm="1">
         <f t="array" ref="V19">Details!$D$9-SUMPRODUCT(TRANSPOSE(Details!$D$4:$D$8),$P19:$T19)-$I19</f>
-        <v>487</v>
+        <v>387.00000000000034</v>
       </c>
       <c r="X19" s="13" cm="1">
         <f t="array" ref="X19">LevelUpgradeCost($E19)</f>
-        <v>1235520000</v>
-      </c>
-      <c r="Y19" s="61">
+        <v>135120000</v>
+      </c>
+      <c r="Y19" s="61" t="str">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AA19" s="110">
         <f t="shared" si="5"/>
-        <v>4260</v>
+        <v>4370</v>
       </c>
       <c r="AB19" s="63">
         <f>RANK($AA19,$AA$3:$AA$46)+COUNTIF($AA$3:$AA19,AA19)-1</f>
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC19" s="61" cm="1">
         <f t="array" ref="AC19">IFERROR(_xlfn.IFS($AB19&lt;8,1,$AB19&lt;15,2,$AB19&lt;21,3),"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD19" s="1"/>
       <c r="AE19" s="121" t="s">
@@ -7884,7 +7884,7 @@
       </c>
       <c r="AB26" s="63">
         <f>RANK($AA26,$AA$3:$AA$46)+COUNTIF($AA$3:$AA26,AA26)-1</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AC26" s="61" cm="1">
         <f t="array" ref="AC26">IFERROR(_xlfn.IFS($AB26&lt;8,1,$AB26&lt;15,2,$AB26&lt;21,3),"")</f>
@@ -7930,10 +7930,10 @@
       </c>
       <c r="G27" s="127">
         <f>INT(H27)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H27" s="199">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="I27" s="156">
         <v>128</v>
@@ -7951,9 +7951,9 @@
         <f t="shared" ref="M27:M33" si="7">IF($G27&gt;3,"Max","")</f>
         <v>Max</v>
       </c>
-      <c r="N27" s="19" t="str">
+      <c r="N27" s="19">
         <f t="shared" ref="N27:N33" si="8">IF(H27=5,10,"")</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="P27" s="9">
         <f>IFERROR(CHOOSE(IF($H27&gt;=Details!$B$4,1,2),Details!$D$4,IF($H27&gt;Details!$B$4-1,IF($H27&lt;1,$H27,MOD($H27,Details!$B$4-1))*10*Details!$C$4,""))/Details!$D$4,0)</f>
@@ -7973,15 +7973,15 @@
       </c>
       <c r="T27" s="9">
         <f>IFERROR(CHOOSE(IF($H27&gt;=Details!$B$8,1,2),Details!$D$8,IF($H27&gt;Details!$B$8-1,IF($H27&lt;1,Details!$G$5,MOD($H27,Details!$B$8-1))*10*Details!$C$8,""))/Details!$D$8,0)</f>
-        <v>0.59999999999999964</v>
+        <v>1</v>
       </c>
       <c r="U27" s="9" cm="1">
         <f t="array" ref="U27">SUMPRODUCT(TRANSPOSE(Details!$D$4:$D$8),$P27:$T27)/Details!$D$9</f>
-        <v>0.7948717948717946</v>
+        <v>1</v>
       </c>
       <c r="V27" s="13" cm="1">
         <f t="array" ref="V27">Details!$D$9-SUMPRODUCT(TRANSPOSE(Details!$D$4:$D$8),$P27:$T27)-$I27</f>
-        <v>72.000000000000227</v>
+        <v>-128</v>
       </c>
       <c r="X27" s="13" cm="1">
         <f t="array" ref="X27">LevelUpgradeCost($E27)</f>
@@ -7993,7 +7993,7 @@
       </c>
       <c r="AA27" s="110">
         <f t="shared" si="5"/>
-        <v>4560</v>
+        <v>5260</v>
       </c>
       <c r="AB27" s="63">
         <f>RANK($AA27,$AA$3:$AA$46)+COUNTIF($AA$3:$AA27,AA27)-1</f>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="AB28" s="63">
         <f>RANK($AA28,$AA$3:$AA$46)+COUNTIF($AA$3:$AA28,AA28)-1</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AC28" s="61" cm="1">
         <f t="array" ref="AC28">IFERROR(_xlfn.IFS($AB28&lt;8,1,$AB28&lt;15,2,$AB28&lt;21,3),"")</f>
@@ -8155,7 +8155,7 @@
         <v>3</v>
       </c>
       <c r="H29" s="198">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I29" s="123">
         <v>45</v>
@@ -8191,7 +8191,7 @@
       </c>
       <c r="S29" s="9">
         <f>IFERROR(CHOOSE(IF($H29&gt;=Details!$B$7,1,2),Details!$D$7,IF($H29&gt;Details!$B$7-1,IF($H29&lt;1,Details!$G$5,MOD($H29,Details!$B$7-1))*10*Details!$C$7,""))/Details!$D$7,0)</f>
-        <v>0.40000000000000036</v>
+        <v>0.59999999999999964</v>
       </c>
       <c r="T29" s="9">
         <f>IFERROR(CHOOSE(IF($H29&gt;=Details!$B$8,1,2),Details!$D$8,IF($H29&gt;Details!$B$8-1,IF($H29&lt;1,Details!$G$5,MOD($H29,Details!$B$8-1))*10*Details!$C$8,""))/Details!$D$8,0)</f>
@@ -8199,11 +8199,11 @@
       </c>
       <c r="U29" s="9" cm="1">
         <f t="array" ref="U29">SUMPRODUCT(TRANSPOSE(Details!$D$4:$D$8),$P29:$T29)/Details!$D$9</f>
-        <v>0.30256410256410265</v>
+        <v>0.36410256410256397</v>
       </c>
       <c r="V29" s="13" cm="1">
         <f t="array" ref="V29">Details!$D$9-SUMPRODUCT(TRANSPOSE(Details!$D$4:$D$8),$P29:$T29)-$I29</f>
-        <v>634.99999999999989</v>
+        <v>575.00000000000011</v>
       </c>
       <c r="X29" s="13" cm="1">
         <f t="array" ref="X29">LevelUpgradeCost($E29)</f>
@@ -8215,11 +8215,11 @@
       </c>
       <c r="AA29" s="110">
         <f t="shared" si="5"/>
-        <v>3386</v>
+        <v>3486</v>
       </c>
       <c r="AB29" s="63">
         <f>RANK($AA29,$AA$3:$AA$46)+COUNTIF($AA$3:$AA29,AA29)-1</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AC29" s="61" cm="1">
         <f t="array" ref="AC29">IFERROR(_xlfn.IFS($AB29&lt;8,1,$AB29&lt;15,2,$AB29&lt;21,3),"")</f>
@@ -10147,14 +10147,14 @@
       <c r="D48" s="142"/>
       <c r="E48" s="1">
         <f>COUNTIF(E3:E46,"&gt;0")-COUNTIF(E3:E46,"="&amp;HallLevel*10)</f>
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F48" s="142"/>
       <c r="G48" s="142"/>
       <c r="I48" s="5"/>
       <c r="X48" s="5">
         <f>SUMPRODUCT(X3:X46,Y3:Y46)</f>
-        <v>95531233700</v>
+        <v>91824673700</v>
       </c>
     </row>
     <row r="49" spans="2:24" ht="12" customHeight="1" x14ac:dyDescent="0.2">
@@ -10289,7 +10289,7 @@
       </c>
       <c r="Q58" s="1">
         <f t="shared" ref="Q58:Q60" si="22">SUMIF($C$3:$C$46,"=" &amp; $P58,$E$3:$E$46)</f>
-        <v>2026</v>
+        <v>2036</v>
       </c>
       <c r="R58" s="1">
         <f t="shared" ref="R58:R60" si="23">COUNTIFS($C$3:$C$46,"=" &amp; $P58,$E$3:$E$46,"&gt;0")</f>
@@ -10297,7 +10297,7 @@
       </c>
       <c r="S58" s="1">
         <f t="shared" ref="S58:S60" si="24">Q58/R58</f>
-        <v>225.11111111111111</v>
+        <v>226.22222222222223</v>
       </c>
       <c r="X58"/>
     </row>
@@ -10315,7 +10315,7 @@
       </c>
       <c r="Q59" s="1">
         <f t="shared" si="22"/>
-        <v>1880</v>
+        <v>1900</v>
       </c>
       <c r="R59" s="1">
         <f t="shared" si="23"/>
@@ -10323,7 +10323,7 @@
       </c>
       <c r="S59" s="1">
         <f t="shared" si="24"/>
-        <v>235</v>
+        <v>237.5</v>
       </c>
       <c r="X59"/>
     </row>
@@ -11393,11 +11393,11 @@
       </c>
       <c r="D4">
         <f>Palmon!E5</f>
-        <v>260</v>
-      </c>
-      <c r="E4">
+        <v>270</v>
+      </c>
+      <c r="E4" t="str">
         <f>Palmon!F5</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="F4">
         <f>Palmon!G5</f>
@@ -11469,11 +11469,11 @@
       </c>
       <c r="W4">
         <f>Palmon!X5</f>
-        <v>1235520000</v>
-      </c>
-      <c r="X4">
+        <v>135120000</v>
+      </c>
+      <c r="X4" t="str">
         <f>Palmon!Y5</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="Y4">
         <f>Palmon!Z5</f>
@@ -11481,11 +11481,11 @@
       </c>
       <c r="Z4">
         <f>Palmon!AA5</f>
-        <v>4260</v>
+        <v>4270</v>
       </c>
       <c r="AA4">
         <f>Palmon!AB5</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB4">
         <f>Palmon!AC5</f>
@@ -11631,11 +11631,11 @@
       </c>
       <c r="AA5">
         <f>Palmon!AB6</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB5">
         <f>Palmon!AC6</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC5">
         <f>Palmon!AD6</f>
@@ -11923,7 +11923,7 @@
       </c>
       <c r="AA7">
         <f>Palmon!AB8</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AB7">
         <f>Palmon!AC8</f>
@@ -12215,11 +12215,11 @@
       </c>
       <c r="AA9">
         <f>Palmon!AB10</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB9">
         <f>Palmon!AC10</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC9">
         <f>Palmon!AD10</f>
@@ -12277,11 +12277,11 @@
       </c>
       <c r="F10">
         <f>Palmon!G11</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G10">
         <f>Palmon!H11</f>
-        <v>2.2999999999999998</v>
+        <v>4</v>
       </c>
       <c r="H10">
         <f>Palmon!I11</f>
@@ -12301,7 +12301,7 @@
       </c>
       <c r="L10" t="str">
         <f>Palmon!M11</f>
-        <v/>
+        <v>Max</v>
       </c>
       <c r="M10" t="str">
         <f>Palmon!N11</f>
@@ -12321,11 +12321,11 @@
       </c>
       <c r="Q10">
         <f>Palmon!R11</f>
-        <v>0.59999999999999964</v>
+        <v>1</v>
       </c>
       <c r="R10">
         <f>Palmon!S11</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10">
         <f>Palmon!T11</f>
@@ -12333,11 +12333,11 @@
       </c>
       <c r="T10">
         <f>Palmon!U11</f>
-        <v>0.13846153846153844</v>
+        <v>0.48717948717948717</v>
       </c>
       <c r="U10">
         <f>Palmon!V11</f>
-        <v>826</v>
+        <v>486</v>
       </c>
       <c r="V10">
         <f>Palmon!W11</f>
@@ -12357,15 +12357,15 @@
       </c>
       <c r="Z10">
         <f>Palmon!AA11</f>
-        <v>2530</v>
+        <v>4230</v>
       </c>
       <c r="AA10">
         <f>Palmon!AB11</f>
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AB10">
         <f>Palmon!AC11</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC10">
         <f>Palmon!AD11</f>
@@ -12561,11 +12561,11 @@
       </c>
       <c r="D12">
         <f>Palmon!E13</f>
-        <v>260</v>
-      </c>
-      <c r="E12">
+        <v>270</v>
+      </c>
+      <c r="E12" t="str">
         <f>Palmon!F13</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="F12">
         <f>Palmon!G13</f>
@@ -12637,11 +12637,11 @@
       </c>
       <c r="W12">
         <f>Palmon!X13</f>
-        <v>1235520000</v>
-      </c>
-      <c r="X12">
+        <v>135120000</v>
+      </c>
+      <c r="X12" t="str">
         <f>Palmon!Y13</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="Y12">
         <f>Palmon!Z13</f>
@@ -12649,11 +12649,11 @@
       </c>
       <c r="Z12">
         <f>Palmon!AA13</f>
-        <v>4260</v>
+        <v>4270</v>
       </c>
       <c r="AA12">
         <f>Palmon!AB13</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB12">
         <f>Palmon!AC13</f>
@@ -13383,7 +13383,7 @@
       </c>
       <c r="AA17">
         <f>Palmon!AB18</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB17">
         <f>Palmon!AC18</f>
@@ -13437,11 +13437,11 @@
       </c>
       <c r="D18">
         <f>Palmon!E19</f>
-        <v>260</v>
-      </c>
-      <c r="E18">
+        <v>270</v>
+      </c>
+      <c r="E18" t="str">
         <f>Palmon!F19</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="F18">
         <f>Palmon!G19</f>
@@ -13449,7 +13449,7 @@
       </c>
       <c r="G18">
         <f>Palmon!H19</f>
-        <v>4</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="H18">
         <f>Palmon!I19</f>
@@ -13497,15 +13497,15 @@
       </c>
       <c r="S18">
         <f>Palmon!T19</f>
-        <v>0</v>
+        <v>0.19999999999999929</v>
       </c>
       <c r="T18">
         <f>Palmon!U19</f>
-        <v>0.48717948717948717</v>
+        <v>0.58974358974358942</v>
       </c>
       <c r="U18">
         <f>Palmon!V19</f>
-        <v>487</v>
+        <v>387.00000000000034</v>
       </c>
       <c r="V18">
         <f>Palmon!W19</f>
@@ -13513,11 +13513,11 @@
       </c>
       <c r="W18">
         <f>Palmon!X19</f>
-        <v>1235520000</v>
-      </c>
-      <c r="X18">
+        <v>135120000</v>
+      </c>
+      <c r="X18" t="str">
         <f>Palmon!Y19</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="Y18">
         <f>Palmon!Z19</f>
@@ -13525,15 +13525,15 @@
       </c>
       <c r="Z18">
         <f>Palmon!AA19</f>
-        <v>4260</v>
+        <v>4370</v>
       </c>
       <c r="AA18">
         <f>Palmon!AB19</f>
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB18">
         <f>Palmon!AC19</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC18">
         <f>Palmon!AD19</f>
@@ -14551,7 +14551,7 @@
       </c>
       <c r="AA25">
         <f>Palmon!AB26</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB25">
         <f>Palmon!AC26</f>
@@ -14613,11 +14613,11 @@
       </c>
       <c r="F26">
         <f>Palmon!G27</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G26">
         <f>Palmon!H27</f>
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="H26">
         <f>Palmon!I27</f>
@@ -14639,9 +14639,9 @@
         <f>Palmon!M27</f>
         <v>Max</v>
       </c>
-      <c r="M26" t="str">
+      <c r="M26">
         <f>Palmon!N27</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="N26">
         <f>Palmon!O27</f>
@@ -14665,15 +14665,15 @@
       </c>
       <c r="S26">
         <f>Palmon!T27</f>
-        <v>0.59999999999999964</v>
+        <v>1</v>
       </c>
       <c r="T26">
         <f>Palmon!U27</f>
-        <v>0.7948717948717946</v>
+        <v>1</v>
       </c>
       <c r="U26">
         <f>Palmon!V27</f>
-        <v>72.000000000000227</v>
+        <v>-128</v>
       </c>
       <c r="V26">
         <f>Palmon!W27</f>
@@ -14693,7 +14693,7 @@
       </c>
       <c r="Z26">
         <f>Palmon!AA27</f>
-        <v>4560</v>
+        <v>5260</v>
       </c>
       <c r="AA26">
         <f>Palmon!AB27</f>
@@ -14843,7 +14843,7 @@
       </c>
       <c r="AA27">
         <f>Palmon!AB28</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AB27">
         <f>Palmon!AC28</f>
@@ -14909,7 +14909,7 @@
       </c>
       <c r="G28">
         <f>Palmon!H29</f>
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="H28">
         <f>Palmon!I29</f>
@@ -14953,7 +14953,7 @@
       </c>
       <c r="R28">
         <f>Palmon!S29</f>
-        <v>0.40000000000000036</v>
+        <v>0.59999999999999964</v>
       </c>
       <c r="S28">
         <f>Palmon!T29</f>
@@ -14961,11 +14961,11 @@
       </c>
       <c r="T28">
         <f>Palmon!U29</f>
-        <v>0.30256410256410265</v>
+        <v>0.36410256410256397</v>
       </c>
       <c r="U28">
         <f>Palmon!V29</f>
-        <v>634.99999999999989</v>
+        <v>575.00000000000011</v>
       </c>
       <c r="V28">
         <f>Palmon!W29</f>
@@ -14985,11 +14985,11 @@
       </c>
       <c r="Z28">
         <f>Palmon!AA29</f>
-        <v>3386</v>
+        <v>3486</v>
       </c>
       <c r="AA28">
         <f>Palmon!AB29</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AB28">
         <f>Palmon!AC29</f>
@@ -17708,14 +17708,14 @@
       <c r="D6" s="47" t="str">
         <v>Defend</v>
       </c>
-      <c r="E6" s="39">
-        <v>26.000000000000028</v>
+      <c r="E6" s="39" t="str">
+        <v/>
       </c>
       <c r="F6" s="33" t="str">
         <v/>
       </c>
-      <c r="G6" s="33" t="str">
-        <v/>
+      <c r="G6" s="33">
+        <v>486</v>
       </c>
       <c r="H6" s="33" t="str">
         <v/>
@@ -18159,11 +18159,11 @@
       <c r="N16" s="33">
         <v>300</v>
       </c>
-      <c r="O16" s="33" t="str">
-        <v/>
+      <c r="O16" s="33">
+        <v>486</v>
       </c>
       <c r="P16" s="47">
-        <v>300</v>
+        <v>486</v>
       </c>
       <c r="Q16" s="40"/>
       <c r="R16" s="1"/>
@@ -18223,7 +18223,7 @@
         <v>Fire</v>
       </c>
       <c r="V17" s="192">
-        <v>245.71428571428572</v>
+        <v>248.57142857142858</v>
       </c>
       <c r="W17" s="40" cm="1">
         <f t="array" ref="W17">COUNTA(_xlfn._xlws.FILTER(C4:C43,C4:C43=$U17,""))</f>
@@ -18261,7 +18261,7 @@
         <v>100</v>
       </c>
       <c r="N18" s="33">
-        <v>134.99999999999989</v>
+        <v>75.000000000000114</v>
       </c>
       <c r="O18" s="33">
         <v>500</v>
@@ -18275,7 +18275,7 @@
         <v>Water</v>
       </c>
       <c r="V18" s="192">
-        <v>240</v>
+        <v>241.42857142857142</v>
       </c>
       <c r="W18" s="40" cm="1">
         <f t="array" ref="W18">COUNTA(_xlfn._xlws.FILTER(C5:C44,C5:C44=$U18,""))</f>
@@ -18377,7 +18377,7 @@
       <c r="R20" s="1"/>
       <c r="V20" s="197">
         <f>AVERAGE(V16:V19)</f>
-        <v>235.47619047619048</v>
+        <v>236.54761904761907</v>
       </c>
       <c r="W20" s="196">
         <f>SUM(W16:W19)</f>
@@ -18398,7 +18398,7 @@
         <v/>
       </c>
       <c r="F21" s="33">
-        <v>134.99999999999989</v>
+        <v>75.000000000000114</v>
       </c>
       <c r="G21" s="33" t="str">
         <v/>
@@ -18615,13 +18615,13 @@
         <v>Electricity</v>
       </c>
       <c r="M26" s="39">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N26" s="33">
         <v>1</v>
       </c>
-      <c r="O26" s="33" t="str">
-        <v/>
+      <c r="O26" s="33">
+        <v>1</v>
       </c>
       <c r="P26" s="33" t="str">
         <v/>
@@ -18648,11 +18648,11 @@
       <c r="F27" s="33" t="str">
         <v/>
       </c>
-      <c r="G27" s="33">
-        <v>72.000000000000227</v>
-      </c>
-      <c r="H27" s="33" t="str">
-        <v/>
+      <c r="G27" s="33" t="str">
+        <v/>
+      </c>
+      <c r="H27" s="33">
+        <v>0</v>
       </c>
       <c r="I27" s="33"/>
       <c r="J27" s="40"/>
@@ -18694,7 +18694,7 @@
         <v/>
       </c>
       <c r="G28" s="33">
-        <v>487</v>
+        <v>387.00000000000034</v>
       </c>
       <c r="H28" s="33" t="str">
         <v/>
@@ -18756,10 +18756,10 @@
         <v/>
       </c>
       <c r="O29" s="33">
+        <v>1</v>
+      </c>
+      <c r="P29" s="33">
         <v>2</v>
-      </c>
-      <c r="P29" s="33">
-        <v>1</v>
       </c>
       <c r="Q29" s="47">
         <v>7</v>
@@ -18795,7 +18795,7 @@
         <v>Total</v>
       </c>
       <c r="M30" s="85">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N30" s="86">
         <v>5</v>
@@ -18804,7 +18804,7 @@
         <v>5</v>
       </c>
       <c r="P30" s="86">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q30" s="87">
         <v>28</v>
@@ -19002,10 +19002,10 @@
         <v>Fire</v>
       </c>
       <c r="M35" s="39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N35" s="33">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O35" s="40">
         <v>2</v>
@@ -19068,10 +19068,10 @@
         <v>Wood</v>
       </c>
       <c r="M37" s="39">
-        <v>3</v>
-      </c>
-      <c r="N37" s="33" t="str">
-        <v/>
+        <v>2</v>
+      </c>
+      <c r="N37" s="33">
+        <v>1</v>
       </c>
       <c r="O37" s="40" t="str">
         <v/>
@@ -19208,10 +19208,10 @@
         <v>Bufonobi</v>
       </c>
       <c r="M42" s="74" t="str">
-        <v>Hoofrit</v>
+        <v>Ghillant</v>
       </c>
       <c r="N42" s="75" t="str">
-        <v>Blazeal</v>
+        <v>Barkplug</v>
       </c>
       <c r="O42" s="1"/>
       <c r="P42" s="1" t="str" cm="1">
@@ -19219,7 +19219,7 @@
         <v>Bufonobi</v>
       </c>
       <c r="Q42" s="1" t="str">
-        <v>Hoofrit</v>
+        <v>Ghillant</v>
       </c>
       <c r="R42" s="1"/>
       <c r="T42"/>
@@ -19241,17 +19241,17 @@
         <v>Vulpyrean</v>
       </c>
       <c r="M43" s="77" t="str">
-        <v>Lucidina</v>
+        <v>Hoofrit</v>
       </c>
       <c r="N43" s="78" t="str">
-        <v>Mantleray</v>
+        <v>Blazeal</v>
       </c>
       <c r="O43" s="1"/>
       <c r="P43" s="1" t="str">
         <v>Vulpyrean</v>
       </c>
       <c r="Q43" s="1" t="str">
-        <v>Lucidina</v>
+        <v>Hoofrit</v>
       </c>
       <c r="R43" s="1"/>
       <c r="T43"/>
@@ -19273,17 +19273,17 @@
         <v>Gnashley</v>
       </c>
       <c r="M44" s="77" t="str">
-        <v>Pipistrigoi</v>
+        <v>Lucidina</v>
       </c>
       <c r="N44" s="78" t="str">
-        <v>Abuzzinian</v>
+        <v>Mantleray</v>
       </c>
       <c r="O44" s="1"/>
       <c r="P44" s="1" t="str">
         <v>Gnashley</v>
       </c>
       <c r="Q44" s="1" t="str">
-        <v>Pipistrigoi</v>
+        <v>Lucidina</v>
       </c>
       <c r="R44" s="1"/>
       <c r="T44"/>
@@ -19305,7 +19305,7 @@
         <v>Glacewing</v>
       </c>
       <c r="M45" s="77" t="str">
-        <v>Kungpaw</v>
+        <v>Abuzzinian</v>
       </c>
       <c r="N45" s="78" t="str">
         <v>Escarffier</v>
@@ -19315,7 +19315,7 @@
         <v>Glacewing</v>
       </c>
       <c r="Q45" s="1" t="str">
-        <v>Kungpaw</v>
+        <v>Abuzzinian</v>
       </c>
       <c r="R45" s="1"/>
       <c r="T45"/>
@@ -19328,7 +19328,7 @@
         <v>Fleurizard</v>
       </c>
       <c r="M46" s="77" t="str">
-        <v>Magmolin</v>
+        <v>Kungpaw</v>
       </c>
       <c r="N46" s="78" t="str">
         <v>Ninjump</v>
@@ -19338,7 +19338,7 @@
         <v>Fleurizard</v>
       </c>
       <c r="Q46" s="1" t="str">
-        <v>Magmolin</v>
+        <v>Kungpaw</v>
       </c>
       <c r="R46" s="1"/>
       <c r="T46"/>
@@ -19351,7 +19351,7 @@
         <v>Oleana</v>
       </c>
       <c r="M47" s="77" t="str">
-        <v>Spookaboo</v>
+        <v>Magmolin</v>
       </c>
       <c r="N47" s="78" t="str">
         <v>Revontulet</v>
@@ -19361,7 +19361,7 @@
         <v>Oleana</v>
       </c>
       <c r="Q47" s="1" t="str">
-        <v>Spookaboo</v>
+        <v>Magmolin</v>
       </c>
       <c r="R47" s="1"/>
       <c r="T47"/>
@@ -19371,20 +19371,20 @@
     </row>
     <row r="48" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L48" s="81" t="str">
-        <v>Ghillant</v>
+        <v>Pipistrigoi</v>
       </c>
       <c r="M48" s="82" t="str">
-        <v>Barkplug</v>
+        <v>Spookaboo</v>
       </c>
       <c r="N48" s="83" t="str">
         <v>Limudroid</v>
       </c>
       <c r="O48" s="1"/>
       <c r="P48" s="1" t="str">
-        <v>Ghillant</v>
+        <v>Pipistrigoi</v>
       </c>
       <c r="Q48" s="1" t="str">
-        <v>Barkplug</v>
+        <v>Spookaboo</v>
       </c>
       <c r="R48" s="1"/>
       <c r="T48"/>
@@ -19451,7 +19451,7 @@
         <v/>
       </c>
       <c r="H52" s="1">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="L52" s="1" t="str">
         <v>Abuzzinian</v>
@@ -19460,7 +19460,7 @@
         <v/>
       </c>
       <c r="N52" s="1">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="P52" s="1" t="str" cm="1">
         <f t="array" ref="P52:P78">_xlfn.LAMBDA(_xlpm.row,IFERROR(_xlfn.RANK.EQ(_xlpm.row,M$52:M$78,1),""))(M$52:M$78)</f>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="Q52" s="1" cm="1">
         <f t="array" ref="Q52:Q78">_xlfn.LAMBDA(_xlpm.row,IFERROR(_xlfn.RANK.EQ(_xlpm.row,N$52:N$78,1),""))(N$52:N$78)</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S52" s="1" t="str" cm="1">
         <f t="array" ref="S52:S58">_xlfn.CHOOSECOLS(_xlfn._xlws.FILTER(L52:Q78,P52:P78&lt;=7),1)</f>
@@ -19513,7 +19513,7 @@
         <v/>
       </c>
       <c r="H54" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L54" s="1" t="str">
         <v>Barkplug</v>
@@ -19522,13 +19522,13 @@
         <v/>
       </c>
       <c r="N54" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P54" s="1" t="str">
         <v/>
       </c>
       <c r="Q54" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S54" s="1" t="str">
         <v>Hoofrit</v>
@@ -19568,7 +19568,7 @@
     </row>
     <row r="56" spans="7:20" s="1" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="G56" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H56" s="1" t="str">
         <v/>
@@ -19577,7 +19577,7 @@
         <v>Blazeal</v>
       </c>
       <c r="M56" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N56" s="1" t="str">
         <v/>
@@ -19750,7 +19750,7 @@
         <v/>
       </c>
       <c r="H63" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L63" s="1" t="str">
         <v>Ghillant</v>
@@ -19759,7 +19759,7 @@
         <v/>
       </c>
       <c r="N63" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P63" s="1" t="str">
         <v/>
@@ -19793,7 +19793,7 @@
     </row>
     <row r="65" spans="7:20" s="1" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="G65" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H65" s="1" t="str">
         <v/>
@@ -19802,13 +19802,13 @@
         <v>Hoofrit</v>
       </c>
       <c r="M65" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N65" s="1" t="str">
         <v/>
       </c>
       <c r="P65" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q65" s="1" t="str">
         <v/>
@@ -19819,7 +19819,7 @@
         <v/>
       </c>
       <c r="H66" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L66" s="1" t="str">
         <v>Kungpaw</v>
@@ -19828,13 +19828,13 @@
         <v/>
       </c>
       <c r="N66" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P66" s="1" t="str">
         <v/>
       </c>
       <c r="Q66" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67" spans="7:20" s="1" customFormat="1" ht="12" x14ac:dyDescent="0.2">
@@ -19862,7 +19862,7 @@
     </row>
     <row r="68" spans="7:20" s="1" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="G68" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H68" s="1" t="str">
         <v/>
@@ -19871,13 +19871,13 @@
         <v>Lucidina</v>
       </c>
       <c r="M68" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N68" s="1" t="str">
         <v/>
       </c>
       <c r="P68" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q68" s="1" t="str">
         <v/>
@@ -19888,7 +19888,7 @@
         <v/>
       </c>
       <c r="H69" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L69" s="1" t="str">
         <v>Magmolin</v>
@@ -19897,18 +19897,18 @@
         <v/>
       </c>
       <c r="N69" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P69" s="1" t="str">
         <v/>
       </c>
       <c r="Q69" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="7:20" s="1" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="G70" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H70" s="1" t="str">
         <v/>
@@ -19917,7 +19917,7 @@
         <v>Mantleray</v>
       </c>
       <c r="M70" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N70" s="1" t="str">
         <v/>
@@ -19977,7 +19977,7 @@
     </row>
     <row r="73" spans="7:20" s="1" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="G73" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H73" s="1" t="str">
         <v/>
@@ -19986,13 +19986,13 @@
         <v>Pipistrigoi</v>
       </c>
       <c r="M73" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="N73" s="1" t="str">
         <v/>
       </c>
       <c r="P73" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q73" s="1" t="str">
         <v/>
@@ -20046,7 +20046,7 @@
     </row>
     <row r="76" spans="7:20" s="1" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="G76" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H76" s="1" t="str">
         <v/>
@@ -20055,7 +20055,7 @@
         <v>Spookaboo</v>
       </c>
       <c r="M76" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N76" s="1" t="str">
         <v/>
@@ -33366,7 +33366,7 @@
         <v>53</v>
       </c>
       <c r="J6" s="4">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="K6" s="246">
         <v>2.2000000000000002</v>
@@ -33542,45 +33542,45 @@
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <conditionalFormatting sqref="B2:B4">
-    <cfRule type="expression" dxfId="27" priority="36">
-      <formula>$C2="Wood"</formula>
+    <cfRule type="expression" dxfId="27" priority="33">
+      <formula>$C2="Fire"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="35">
+    <cfRule type="expression" dxfId="26" priority="34">
+      <formula>$C2="Water"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="25" priority="35">
       <formula>$C2="Electricity"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="34">
-      <formula>$C2="Water"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="24" priority="33">
-      <formula>$C2="Fire"</formula>
+    <cfRule type="expression" dxfId="24" priority="36">
+      <formula>$C2="Wood"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E4">
-    <cfRule type="expression" dxfId="23" priority="31">
-      <formula>$C2="Electricity"</formula>
+    <cfRule type="expression" dxfId="23" priority="29">
+      <formula>$C2="Fire"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="30">
       <formula>$C2="Water"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="29">
-      <formula>$C2="Fire"</formula>
+    <cfRule type="expression" dxfId="21" priority="31">
+      <formula>$C2="Electricity"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="32">
       <formula>$C2="Wood"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:P4">
-    <cfRule type="expression" dxfId="19" priority="2">
+    <cfRule type="expression" dxfId="19" priority="1">
+      <formula>$C2="Fire"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="2">
       <formula>$C2="Water"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="3">
+    <cfRule type="expression" dxfId="17" priority="3">
       <formula>$C2="Electricity"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="4">
+    <cfRule type="expression" dxfId="16" priority="4">
       <formula>$C2="Wood"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="16" priority="1">
-      <formula>$C2="Fire"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q7">
@@ -33598,31 +33598,31 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T2:X2">
-    <cfRule type="expression" dxfId="11" priority="20">
-      <formula>$C2="Wood"</formula>
+    <cfRule type="expression" dxfId="11" priority="17">
+      <formula>$C2="Fire"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="10" priority="18">
       <formula>$C2="Water"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="17">
-      <formula>$C2="Fire"</formula>
+    <cfRule type="expression" dxfId="9" priority="19">
+      <formula>$C2="Electricity"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="19">
-      <formula>$C2="Electricity"</formula>
+    <cfRule type="expression" dxfId="8" priority="20">
+      <formula>$C2="Wood"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2">
-    <cfRule type="expression" dxfId="7" priority="16">
-      <formula>$C2="Wood"</formula>
+    <cfRule type="expression" dxfId="7" priority="13">
+      <formula>$C2="Fire"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="15">
+    <cfRule type="expression" dxfId="6" priority="14">
+      <formula>$C2="Water"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="15">
       <formula>$C2="Electricity"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="14">
-      <formula>$C2="Water"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="13">
-      <formula>$C2="Fire"</formula>
+    <cfRule type="expression" dxfId="4" priority="16">
+      <formula>$C2="Wood"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD2">
@@ -43563,7 +43563,7 @@
       </c>
       <c r="F5" t="str">
         <f>Palmon!B5 &amp; "," &amp; Palmon!C5 &amp; "," &amp; Palmon!D5 &amp; "," &amp; Palmon!E5 &amp; "," &amp; Palmon!G5 &amp; "," &amp; SUBSTITUTE(Palmon!H5,",",".") &amp; "," &amp; Palmon!I5 &amp; "," &amp; SUBSTITUTE(Palmon!P5,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q5,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R5,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S5,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T5,",",".") &amp; "," &amp; Palmon!J5 &amp; "," &amp; Palmon!K5 &amp; "," &amp; Palmon!L5 &amp; "," &amp; Palmon!M5 &amp; "," &amp; Palmon!N5 &amp; "," &amp; SUBSTITUTE(Palmon!U5,",",".") &amp; "," &amp; Palmon!V5 &amp; "," &amp; Palmon!X5 &amp; "," &amp; Palmon!Y5 &amp; "," &amp; Palmon!AA5 &amp; "," &amp; Palmon!AB5 &amp; "," &amp; Palmon!AC5 &amp; "," &amp; Palmon!AE5 &amp; "," &amp; Palmon!AF5 &amp; "," &amp; Palmon!AI5 &amp; "," &amp; Palmon!AJ5</f>
-        <v>Hoofrit,Fire,Attack,260,4,4,11,1,1,1,1,0,15,15,15,Max,,0.487179487179487,489,1235520000,1,4260,8,2,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRwfHFWjB1bN67FJNyjjWvBJwviWJ3Tada0Yg&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSkOv6mOI5FaIAjcVgErYDwVaivkH3WdUQIzw&amp;s,Flaries,</v>
+        <v>Hoofrit,Fire,Attack,270,4,4,11,1,1,1,1,0,15,15,15,Max,,0.487179487179487,489,135120000,,4270,9,2,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRwfHFWjB1bN67FJNyjjWvBJwviWJ3Tada0Yg&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSkOv6mOI5FaIAjcVgErYDwVaivkH3WdUQIzw&amp;s,Flaries,</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -43589,7 +43589,7 @@
       </c>
       <c r="F6" t="str">
         <f>Palmon!B6 &amp; "," &amp; Palmon!C6 &amp; "," &amp; Palmon!D6 &amp; "," &amp; Palmon!E6 &amp; "," &amp; Palmon!G6 &amp; "," &amp; SUBSTITUTE(Palmon!H6,",",".") &amp; "," &amp; Palmon!I6 &amp; "," &amp; SUBSTITUTE(Palmon!P6,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q6,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R6,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S6,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T6,",",".") &amp; "," &amp; Palmon!J6 &amp; "," &amp; Palmon!K6 &amp; "," &amp; Palmon!L6 &amp; "," &amp; Palmon!M6 &amp; "," &amp; Palmon!N6 &amp; "," &amp; SUBSTITUTE(Palmon!U6,",",".") &amp; "," &amp; Palmon!V6 &amp; "," &amp; Palmon!X6 &amp; "," &amp; Palmon!Y6 &amp; "," &amp; Palmon!AA6 &amp; "," &amp; Palmon!AB6 &amp; "," &amp; Palmon!AC6 &amp; "," &amp; Palmon!AE6 &amp; "," &amp; Palmon!AF6 &amp; "," &amp; Palmon!AI6 &amp; "," &amp; Palmon!AJ6</f>
-        <v>Ghillant,Wood,Defend,250,4,4.1,0,1,1,1,1,0.199999999999999,5,5,5,Max,,0.589743589743589,400,2123020000,1,4350,7,1,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQOwDXppnwkCtCXXAqUiiNMhf6T-lane54jPg&amp;s, ,Chefeuillier,</v>
+        <v>Ghillant,Wood,Defend,250,4,4.1,0,1,1,1,1,0.199999999999999,5,5,5,Max,,0.589743589743589,400,2123020000,1,4350,8,2,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQOwDXppnwkCtCXXAqUiiNMhf6T-lane54jPg&amp;s, ,Chefeuillier,</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -43641,7 +43641,7 @@
       </c>
       <c r="F8" t="str">
         <f>Palmon!B8 &amp; "," &amp; Palmon!C8 &amp; "," &amp; Palmon!D8 &amp; "," &amp; Palmon!E8 &amp; "," &amp; Palmon!G8 &amp; "," &amp; SUBSTITUTE(Palmon!H8,",",".") &amp; "," &amp; Palmon!I8 &amp; "," &amp; SUBSTITUTE(Palmon!P8,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q8,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R8,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S8,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T8,",",".") &amp; "," &amp; Palmon!J8 &amp; "," &amp; Palmon!K8 &amp; "," &amp; Palmon!L8 &amp; "," &amp; Palmon!M8 &amp; "," &amp; Palmon!N8 &amp; "," &amp; SUBSTITUTE(Palmon!U8,",",".") &amp; "," &amp; Palmon!V8 &amp; "," &amp; Palmon!X8 &amp; "," &amp; Palmon!Y8 &amp; "," &amp; Palmon!AA8 &amp; "," &amp; Palmon!AB8 &amp; "," &amp; Palmon!AC8 &amp; "," &amp; Palmon!AE8 &amp; "," &amp; Palmon!AF8 &amp; "," &amp; Palmon!AI8 &amp; "," &amp; Palmon!AJ8</f>
-        <v>Magmolin,Fire,Defend,240,3,3.1,61,1,1,1,0.2,0,10,5,15,,,0.241025641025641,679,2831420000,1,3340,12,2,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRebc6KbOAxblleg_L3rr2K13bt-Yyzq1bAaw&amp;s, ,Obsidrake,</v>
+        <v>Magmolin,Fire,Defend,240,3,3.1,61,1,1,1,0.2,0,10,5,15,,,0.241025641025641,679,2831420000,1,3340,13,2,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRebc6KbOAxblleg_L3rr2K13bt-Yyzq1bAaw&amp;s, ,Obsidrake,</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -43693,7 +43693,7 @@
       </c>
       <c r="F10" t="str">
         <f>Palmon!B10 &amp; "," &amp; Palmon!C10 &amp; "," &amp; Palmon!D10 &amp; "," &amp; Palmon!E10 &amp; "," &amp; Palmon!G10 &amp; "," &amp; SUBSTITUTE(Palmon!H10,",",".") &amp; "," &amp; Palmon!I10 &amp; "," &amp; SUBSTITUTE(Palmon!P10,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q10,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R10,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S10,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T10,",",".") &amp; "," &amp; Palmon!J10 &amp; "," &amp; Palmon!K10 &amp; "," &amp; Palmon!L10 &amp; "," &amp; Palmon!M10 &amp; "," &amp; Palmon!N10 &amp; "," &amp; SUBSTITUTE(Palmon!U10,",",".") &amp; "," &amp; Palmon!V10 &amp; "," &amp; Palmon!X10 &amp; "," &amp; Palmon!Y10 &amp; "," &amp; Palmon!AA10 &amp; "," &amp; Palmon!AB10 &amp; "," &amp; Palmon!AC10 &amp; "," &amp; Palmon!AE10 &amp; "," &amp; Palmon!AF10 &amp; "," &amp; Palmon!AI10 &amp; "," &amp; Palmon!AJ10</f>
-        <v>Barkplug,Electricity,Defend,250,3,3,0,1,1,1,0,0,14,5,10,,,0.179487179487179,800,2123020000,1,3250,14,2,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSf59xsunrPEuFvdtBi-IRVMcrdBfW_vNshLA&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRUDpuK5BvjXDFqgMZvlxYadsaFFQDKOQrNCAHymiAy_w&amp;s,Wattweiler,</v>
+        <v>Barkplug,Electricity,Defend,250,3,3,0,1,1,1,0,0,14,5,10,,,0.179487179487179,800,2123020000,1,3250,15,3,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSf59xsunrPEuFvdtBi-IRVMcrdBfW_vNshLA&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRUDpuK5BvjXDFqgMZvlxYadsaFFQDKOQrNCAHymiAy_w&amp;s,Wattweiler,</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -43719,7 +43719,7 @@
       </c>
       <c r="F11" t="str">
         <f>Palmon!B11 &amp; "," &amp; Palmon!C11 &amp; "," &amp; Palmon!D11 &amp; "," &amp; Palmon!E11 &amp; "," &amp; Palmon!G11 &amp; "," &amp; SUBSTITUTE(Palmon!H11,",",".") &amp; "," &amp; Palmon!I11 &amp; "," &amp; SUBSTITUTE(Palmon!P11,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q11,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R11,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S11,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T11,",",".") &amp; "," &amp; Palmon!J11 &amp; "," &amp; Palmon!K11 &amp; "," &amp; Palmon!L11 &amp; "," &amp; Palmon!M11 &amp; "," &amp; Palmon!N11 &amp; "," &amp; SUBSTITUTE(Palmon!U11,",",".") &amp; "," &amp; Palmon!V11 &amp; "," &amp; Palmon!X11 &amp; "," &amp; Palmon!Y11 &amp; "," &amp; Palmon!AA11 &amp; "," &amp; Palmon!AB11 &amp; "," &amp; Palmon!AC11 &amp; "," &amp; Palmon!AE11 &amp; "," &amp; Palmon!AF11 &amp; "," &amp; Palmon!AI11 &amp; "," &amp; Palmon!AJ11</f>
-        <v>Abuzzinian,Electricity,Defend,230,2,2.3,14,1,1,0.6,0,0,1,1,1,,,0.138461538461538,826,3390620000,1,2530,17,3,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcT-r6BZKxjf-kMlCmzHjhnUHjvmCaOn5DxiYw&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcR23XO-FCNYoHOIhLnxge8AzFmdP8mD1D-mzQ&amp;s,Servolt,</v>
+        <v>Abuzzinian,Electricity,Defend,230,4,4,14,1,1,1,1,0,1,1,1,Max,,0.487179487179487,486,3390620000,1,4230,11,2,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcT-r6BZKxjf-kMlCmzHjhnUHjvmCaOn5DxiYw&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcR23XO-FCNYoHOIhLnxge8AzFmdP8mD1D-mzQ&amp;s,Servolt,</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -43771,7 +43771,7 @@
       </c>
       <c r="F13" t="str">
         <f>Palmon!B13 &amp; "," &amp; Palmon!C13 &amp; "," &amp; Palmon!D13 &amp; "," &amp; Palmon!E13 &amp; "," &amp; Palmon!G13 &amp; "," &amp; SUBSTITUTE(Palmon!H13,",",".") &amp; "," &amp; Palmon!I13 &amp; "," &amp; SUBSTITUTE(Palmon!P13,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q13,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R13,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S13,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T13,",",".") &amp; "," &amp; Palmon!J13 &amp; "," &amp; Palmon!K13 &amp; "," &amp; Palmon!L13 &amp; "," &amp; Palmon!M13 &amp; "," &amp; Palmon!N13 &amp; "," &amp; SUBSTITUTE(Palmon!U13,",",".") &amp; "," &amp; Palmon!V13 &amp; "," &amp; Palmon!X13 &amp; "," &amp; Palmon!Y13 &amp; "," &amp; Palmon!AA13 &amp; "," &amp; Palmon!AB13 &amp; "," &amp; Palmon!AC13 &amp; "," &amp; Palmon!AE13 &amp; "," &amp; Palmon!AF13 &amp; "," &amp; Palmon!AI13 &amp; "," &amp; Palmon!AJ13</f>
-        <v>Lucidina,Water,Attack,260,4,4,0,1,1,1,1,0,5,5,15,Max,,0.487179487179487,500,1235520000,1,4260,9,2,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcR9A_xtftnwTH1zCnLIOcgmJKNZtFnB-e8QOw&amp;s, ,Oneirina,</v>
+        <v>Lucidina,Water,Attack,270,4,4,0,1,1,1,1,0,5,5,15,Max,,0.487179487179487,500,135120000,,4270,10,2,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcR9A_xtftnwTH1zCnLIOcgmJKNZtFnB-e8QOw&amp;s, ,Oneirina,</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -43901,7 +43901,7 @@
       </c>
       <c r="F18" t="str">
         <f>Palmon!B18 &amp; "," &amp; Palmon!C18 &amp; "," &amp; Palmon!D18 &amp; "," &amp; Palmon!E18 &amp; "," &amp; Palmon!G18 &amp; "," &amp; SUBSTITUTE(Palmon!H18,",",".") &amp; "," &amp; Palmon!I18 &amp; "," &amp; SUBSTITUTE(Palmon!P18,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q18,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R18,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S18,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T18,",",".") &amp; "," &amp; Palmon!J18 &amp; "," &amp; Palmon!K18 &amp; "," &amp; Palmon!L18 &amp; "," &amp; Palmon!M18 &amp; "," &amp; Palmon!N18 &amp; "," &amp; SUBSTITUTE(Palmon!U18,",",".") &amp; "," &amp; Palmon!V18 &amp; "," &amp; Palmon!X18 &amp; "," &amp; Palmon!Y18 &amp; "," &amp; Palmon!AA18 &amp; "," &amp; Palmon!AB18 &amp; "," &amp; Palmon!AC18 &amp; "," &amp; Palmon!AE18 &amp; "," &amp; Palmon!AF18 &amp; "," &amp; Palmon!AI18 &amp; "," &amp; Palmon!AJ18</f>
-        <v>Blazeal,Fire,Attack,250,3,3,10,1,1,1,0,0,15,10,15,,,0.179487179487179,790,2123020000,1,3250,15,3,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRsDMtJC3uCFkue3lLpIZqf7OpQgR7XoKOS8g&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTc2Arfa7L5NJadx_WdnWjGTYRLP6bgvNMsDUbraRNI&amp;s,Wildfuror,</v>
+        <v>Blazeal,Fire,Attack,250,3,3,10,1,1,1,0,0,15,10,15,,,0.179487179487179,790,2123020000,1,3250,16,3,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRsDMtJC3uCFkue3lLpIZqf7OpQgR7XoKOS8g&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTc2Arfa7L5NJadx_WdnWjGTYRLP6bgvNMsDUbraRNI&amp;s,Wildfuror,</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -43927,7 +43927,7 @@
       </c>
       <c r="F19" t="str">
         <f>Palmon!B19 &amp; "," &amp; Palmon!C19 &amp; "," &amp; Palmon!D19 &amp; "," &amp; Palmon!E19 &amp; "," &amp; Palmon!G19 &amp; "," &amp; SUBSTITUTE(Palmon!H19,",",".") &amp; "," &amp; Palmon!I19 &amp; "," &amp; SUBSTITUTE(Palmon!P19,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q19,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R19,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S19,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T19,",",".") &amp; "," &amp; Palmon!J19 &amp; "," &amp; Palmon!K19 &amp; "," &amp; Palmon!L19 &amp; "," &amp; Palmon!M19 &amp; "," &amp; Palmon!N19 &amp; "," &amp; SUBSTITUTE(Palmon!U19,",",".") &amp; "," &amp; Palmon!V19 &amp; "," &amp; Palmon!X19 &amp; "," &amp; Palmon!Y19 &amp; "," &amp; Palmon!AA19 &amp; "," &amp; Palmon!AB19 &amp; "," &amp; Palmon!AC19 &amp; "," &amp; Palmon!AE19 &amp; "," &amp; Palmon!AF19 &amp; "," &amp; Palmon!AI19 &amp; "," &amp; Palmon!AJ19</f>
-        <v>Pipistrigoi,Fire,Attack,260,4,4,13,1,1,1,1,0,15,15,15,Max,,0.487179487179487,487,1235520000,1,4260,10,2,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSSdARGNHB_mPJlsb0v4ULv5HaXw2movjzNTNSrkzsi&amp;s, ,Azurostrigoi,</v>
+        <v>Pipistrigoi,Fire,Attack,270,4,4.1,13,1,1,1,1,0.199999999999999,15,15,15,Max,,0.589743589743589,387,135120000,,4370,7,1,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSSdARGNHB_mPJlsb0v4ULv5HaXw2movjzNTNSrkzsi&amp;s, ,Azurostrigoi,</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -44109,7 +44109,7 @@
       </c>
       <c r="F26" t="str">
         <f>Palmon!B26 &amp; "," &amp; Palmon!C26 &amp; "," &amp; Palmon!D26 &amp; "," &amp; Palmon!E26 &amp; "," &amp; Palmon!G26 &amp; "," &amp; SUBSTITUTE(Palmon!H26,",",".") &amp; "," &amp; Palmon!I26 &amp; "," &amp; SUBSTITUTE(Palmon!P26,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q26,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R26,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S26,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T26,",",".") &amp; "," &amp; Palmon!J26 &amp; "," &amp; Palmon!K26 &amp; "," &amp; Palmon!L26 &amp; "," &amp; Palmon!M26 &amp; "," &amp; Palmon!N26 &amp; "," &amp; SUBSTITUTE(Palmon!U26,",",".") &amp; "," &amp; Palmon!V26 &amp; "," &amp; Palmon!X26 &amp; "," &amp; Palmon!Y26 &amp; "," &amp; Palmon!AA26 &amp; "," &amp; Palmon!AB26 &amp; "," &amp; Palmon!AC26 &amp; "," &amp; Palmon!AE26 &amp; "," &amp; Palmon!AF26 &amp; "," &amp; Palmon!AI26 &amp; "," &amp; Palmon!AJ26</f>
-        <v>Mantleray,Electricity,Attack,210,2,2.4,3,1,1,0.8,0,0,4,1,1,,,0.158974358974359,817,4161420000,1,2610,16,3,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSWhzppoZXwh-zBnWIY3GFkIp0x0kc0hAzG0A&amp;s, ,Sorceray,</v>
+        <v>Mantleray,Electricity,Attack,210,2,2.4,3,1,1,0.8,0,0,4,1,1,,,0.158974358974359,817,4161420000,1,2610,17,3,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSWhzppoZXwh-zBnWIY3GFkIp0x0kc0hAzG0A&amp;s, ,Sorceray,</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -44135,7 +44135,7 @@
       </c>
       <c r="F27" t="str">
         <f>Palmon!B27 &amp; "," &amp; Palmon!C27 &amp; "," &amp; Palmon!D27 &amp; "," &amp; Palmon!E27 &amp; "," &amp; Palmon!G27 &amp; "," &amp; SUBSTITUTE(Palmon!H27,",",".") &amp; "," &amp; Palmon!I27 &amp; "," &amp; SUBSTITUTE(Palmon!P27,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q27,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R27,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S27,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T27,",",".") &amp; "," &amp; Palmon!J27 &amp; "," &amp; Palmon!K27 &amp; "," &amp; Palmon!L27 &amp; "," &amp; Palmon!M27 &amp; "," &amp; Palmon!N27 &amp; "," &amp; SUBSTITUTE(Palmon!U27,",",".") &amp; "," &amp; Palmon!V27 &amp; "," &amp; Palmon!X27 &amp; "," &amp; Palmon!Y27 &amp; "," &amp; Palmon!AA27 &amp; "," &amp; Palmon!AB27 &amp; "," &amp; Palmon!AC27 &amp; "," &amp; Palmon!AE27 &amp; "," &amp; Palmon!AF27 &amp; "," &amp; Palmon!AI27 &amp; "," &amp; Palmon!AJ27</f>
-        <v>Oleana,Wood,Attack,260,4,4.3,128,1,1,1,1,0.6,1,1,1,Max,,0.794871794871795,72,0000000000002,1235520000,1,4560,6,1,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQ02wmDjsAMofj1ObwwNW6Vhl_QQ-LUodGIKA&amp;s, ,,</v>
+        <v>Oleana,Wood,Attack,260,5,5,128,1,1,1,1,1,1,1,1,Max,10,1,-128,1235520000,1,5260,6,1,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQ02wmDjsAMofj1ObwwNW6Vhl_QQ-LUodGIKA&amp;s, ,,</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -44161,7 +44161,7 @@
       </c>
       <c r="F28" t="str">
         <f>Palmon!B28 &amp; "," &amp; Palmon!C28 &amp; "," &amp; Palmon!D28 &amp; "," &amp; Palmon!E28 &amp; "," &amp; Palmon!G28 &amp; "," &amp; SUBSTITUTE(Palmon!H28,",",".") &amp; "," &amp; Palmon!I28 &amp; "," &amp; SUBSTITUTE(Palmon!P28,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q28,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R28,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S28,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T28,",",".") &amp; "," &amp; Palmon!J28 &amp; "," &amp; Palmon!K28 &amp; "," &amp; Palmon!L28 &amp; "," &amp; Palmon!M28 &amp; "," &amp; Palmon!N28 &amp; "," &amp; SUBSTITUTE(Palmon!U28,",",".") &amp; "," &amp; Palmon!V28 &amp; "," &amp; Palmon!X28 &amp; "," &amp; Palmon!Y28 &amp; "," &amp; Palmon!AA28 &amp; "," &amp; Palmon!AB28 &amp; "," &amp; Palmon!AC28 &amp; "," &amp; Palmon!AE28 &amp; "," &amp; Palmon!AF28 &amp; "," &amp; Palmon!AI28 &amp; "," &amp; Palmon!AJ28</f>
-        <v>Spookaboo,Fire,Attack,210,3,3.1,10,1,1,1,0.2,0,1,1,1,,,0.241025641025641,730,4161420000,1,3310,13,2,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcT29K673YTBvt_EofrppvnWB4sgt43DEq1pTw&amp;s, ,,</v>
+        <v>Spookaboo,Fire,Attack,210,3,3.1,10,1,1,1,0.2,0,1,1,1,,,0.241025641025641,730,4161420000,1,3310,14,2,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcT29K673YTBvt_EofrppvnWB4sgt43DEq1pTw&amp;s, ,,</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -44187,7 +44187,7 @@
       </c>
       <c r="F29" t="str">
         <f>Palmon!B29 &amp; "," &amp; Palmon!C29 &amp; "," &amp; Palmon!D29 &amp; "," &amp; Palmon!E29 &amp; "," &amp; Palmon!G29 &amp; "," &amp; SUBSTITUTE(Palmon!H29,",",".") &amp; "," &amp; Palmon!I29 &amp; "," &amp; SUBSTITUTE(Palmon!P29,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q29,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R29,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S29,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T29,",",".") &amp; "," &amp; Palmon!J29 &amp; "," &amp; Palmon!K29 &amp; "," &amp; Palmon!L29 &amp; "," &amp; Palmon!M29 &amp; "," &amp; Palmon!N29 &amp; "," &amp; SUBSTITUTE(Palmon!U29,",",".") &amp; "," &amp; Palmon!V29 &amp; "," &amp; Palmon!X29 &amp; "," &amp; Palmon!Y29 &amp; "," &amp; Palmon!AA29 &amp; "," &amp; Palmon!AB29 &amp; "," &amp; Palmon!AC29 &amp; "," &amp; Palmon!AE29 &amp; "," &amp; Palmon!AF29 &amp; "," &amp; Palmon!AI29 &amp; "," &amp; Palmon!AJ29</f>
-        <v>Kungpaw,Water,Defend,186,3,3.2,45,1,1,1,0.4,0,1,1,1,,,0.302564102564103,635,4667020000,1,3386,11,2,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRV1HdRcNPUS4HjDBZ2YOXgaMW_I8FgZEP5xg&amp;s,,,</v>
+        <v>Kungpaw,Water,Defend,186,3,3.3,45,1,1,1,0.6,0,1,1,1,,,0.364102564102564,575,4667020000,1,3486,12,2,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRV1HdRcNPUS4HjDBZ2YOXgaMW_I8FgZEP5xg&amp;s,,,</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">

--- a/data/PS - Estimation (version 1).xlsx
+++ b/data/PS - Estimation (version 1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xvjm020\Documents\Personnel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B79F1D30-8A5D-4856-830E-830A00D6E767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCEB0D13-115A-465C-9E7F-8550311C9454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9D83D047-1CAD-4BF9-942E-B289F790400E}"/>
   </bookViews>
@@ -5970,7 +5970,7 @@
       </c>
       <c r="AB9" s="63">
         <f>RANK($AA9,$AA$3:$AA$46)+COUNTIF($AA$3:$AA9,AA9)-1</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AC9" s="61" t="str" cm="1">
         <f t="array" ref="AC9">IFERROR(_xlfn.IFS($AB9&lt;8,1,$AB9&lt;15,2,$AB9&lt;21,3),"")</f>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="AB12" s="63">
         <f>RANK($AA12,$AA$3:$AA$46)+COUNTIF($AA$3:$AA12,AA12)-1</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AC12" s="61" cm="1">
         <f t="array" ref="AC12">IFERROR(_xlfn.IFS($AB12&lt;8,1,$AB12&lt;15,2,$AB12&lt;21,3),"")</f>
@@ -6643,7 +6643,7 @@
       </c>
       <c r="AB15" s="63">
         <f>RANK($AA15,$AA$3:$AA$46)+COUNTIF($AA$3:$AA15,AA15)-1</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AC15" s="61" t="str" cm="1">
         <f t="array" ref="AC15">IFERROR(_xlfn.IFS($AB15&lt;8,1,$AB15&lt;15,2,$AB15&lt;21,3),"")</f>
@@ -6689,13 +6689,13 @@
       </c>
       <c r="G16" s="127">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H16" s="198">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I16" s="123">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J16" s="63">
         <v>1</v>
@@ -6724,7 +6724,7 @@
       </c>
       <c r="R16" s="9">
         <f>IFERROR(CHOOSE(IF($H16&gt;=Details!$B$6,1,2),Details!$D$6,IF($H16&gt;Details!$B$6-1,IF($H16&lt;1,Details!$G$5,MOD($H16,Details!$B$6-1))*10*Details!$C$6,""))/Details!$D$6,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" s="9">
         <f>IFERROR(CHOOSE(IF($H16&gt;=Details!$B$7,1,2),Details!$D$7,IF($H16&gt;Details!$B$7-1,IF($H16&lt;1,Details!$G$5,MOD($H16,Details!$B$7-1))*10*Details!$C$7,""))/Details!$D$7,0)</f>
@@ -6736,11 +6736,11 @@
       </c>
       <c r="U16" s="9" cm="1">
         <f t="array" ref="U16">SUMPRODUCT(TRANSPOSE(Details!$D$4:$D$8),$P16:$T16)/Details!$D$9</f>
-        <v>7.6923076923076927E-2</v>
+        <v>0.17948717948717949</v>
       </c>
       <c r="V16" s="13" cm="1">
         <f t="array" ref="V16">Details!$D$9-SUMPRODUCT(TRANSPOSE(Details!$D$4:$D$8),$P16:$T16)-$I16</f>
-        <v>887</v>
+        <v>800</v>
       </c>
       <c r="X16" s="13" cm="1">
         <f t="array" ref="X16">LevelUpgradeCost($E16)</f>
@@ -6752,15 +6752,15 @@
       </c>
       <c r="AA16" s="110">
         <f t="shared" si="5"/>
-        <v>2210</v>
+        <v>3210</v>
       </c>
       <c r="AB16" s="63">
         <f>RANK($AA16,$AA$3:$AA$46)+COUNTIF($AA$3:$AA16,AA16)-1</f>
-        <v>27</v>
-      </c>
-      <c r="AC16" s="61" t="str" cm="1">
+        <v>17</v>
+      </c>
+      <c r="AC16" s="61" cm="1">
         <f t="array" ref="AC16">IFERROR(_xlfn.IFS($AB16&lt;8,1,$AB16&lt;15,2,$AB16&lt;21,3),"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AE16" s="63" t="s">
         <v>171</v>
@@ -6807,7 +6807,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="I17" s="123">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J17" s="63">
         <v>5</v>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="V17" s="13" cm="1">
         <f t="array" ref="V17">Details!$D$9-SUMPRODUCT(TRANSPOSE(Details!$D$4:$D$8),$P17:$T17)-$I17</f>
-        <v>852</v>
+        <v>860</v>
       </c>
       <c r="X17" s="13" cm="1">
         <f t="array" ref="X17">LevelUpgradeCost($E17)</f>
@@ -6868,7 +6868,7 @@
       </c>
       <c r="AB17" s="63">
         <f>RANK($AA17,$AA$3:$AA$46)+COUNTIF($AA$3:$AA17,AA17)-1</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AC17" s="61" t="str" cm="1">
         <f t="array" ref="AC17">IFERROR(_xlfn.IFS($AB17&lt;8,1,$AB17&lt;15,2,$AB17&lt;21,3),"")</f>
@@ -7324,7 +7324,7 @@
       </c>
       <c r="AB21" s="63">
         <f>RANK($AA21,$AA$3:$AA$46)+COUNTIF($AA$3:$AA21,AA21)-1</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AC21" s="61" t="str" cm="1">
         <f t="array" ref="AC21">IFERROR(_xlfn.IFS($AB21&lt;8,1,$AB21&lt;15,2,$AB21&lt;21,3),"")</f>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="AB22" s="63">
         <f>RANK($AA22,$AA$3:$AA$46)+COUNTIF($AA$3:$AA22,AA22)-1</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AC22" s="61" cm="1">
         <f t="array" ref="AC22">IFERROR(_xlfn.IFS($AB22&lt;8,1,$AB22&lt;15,2,$AB22&lt;21,3),"")</f>
@@ -7550,7 +7550,7 @@
       </c>
       <c r="AB23" s="63">
         <f>RANK($AA23,$AA$3:$AA$46)+COUNTIF($AA$3:$AA23,AA23)-1</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AC23" s="61" t="str" cm="1">
         <f t="array" ref="AC23">IFERROR(_xlfn.IFS($AB23&lt;8,1,$AB23&lt;15,2,$AB23&lt;21,3),"")</f>
@@ -7884,7 +7884,7 @@
       </c>
       <c r="AB26" s="63">
         <f>RANK($AA26,$AA$3:$AA$46)+COUNTIF($AA$3:$AA26,AA26)-1</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AC26" s="61" cm="1">
         <f t="array" ref="AC26">IFERROR(_xlfn.IFS($AB26&lt;8,1,$AB26&lt;15,2,$AB26&lt;21,3),"")</f>
@@ -8327,7 +8327,7 @@
       </c>
       <c r="AB30" s="153">
         <f>RANK($AA30,$AA$3:$AA$46)+COUNTIF($AA$3:$AA30,AA30)-1</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AC30" s="160" t="str" cm="1">
         <f t="array" ref="AC30">IFERROR(_xlfn.IFS($AB30&lt;8,1,$AB30&lt;15,2,$AB30&lt;21,3),"")</f>
@@ -9977,11 +9977,11 @@
       </c>
       <c r="AB46" s="64">
         <f>RANK($AA46,$AA$3:$AA$46)+COUNTIF($AA$3:$AA46,AA46)-1</f>
-        <v>20</v>
-      </c>
-      <c r="AC46" s="62" cm="1">
+        <v>21</v>
+      </c>
+      <c r="AC46" s="62" t="str" cm="1">
         <f t="array" ref="AC46">IFERROR(_xlfn.IFS($AB46&lt;8,1,$AB46&lt;15,2,$AB46&lt;21,3),"")</f>
-        <v>3</v>
+        <v/>
       </c>
       <c r="AE46" s="64"/>
       <c r="AF46" s="70" t="str">
@@ -12069,7 +12069,7 @@
       </c>
       <c r="AA8">
         <f>Palmon!AB9</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB8" t="str">
         <f>Palmon!AC9</f>
@@ -12507,7 +12507,7 @@
       </c>
       <c r="AA11">
         <f>Palmon!AB12</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AB11">
         <f>Palmon!AC12</f>
@@ -12945,7 +12945,7 @@
       </c>
       <c r="AA14">
         <f>Palmon!AB15</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB14" t="str">
         <f>Palmon!AC15</f>
@@ -13007,15 +13007,15 @@
       </c>
       <c r="F15">
         <f>Palmon!G16</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15">
         <f>Palmon!H16</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15">
         <f>Palmon!I16</f>
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I15">
         <f>Palmon!J16</f>
@@ -13051,7 +13051,7 @@
       </c>
       <c r="Q15">
         <f>Palmon!R16</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15">
         <f>Palmon!S16</f>
@@ -13063,11 +13063,11 @@
       </c>
       <c r="T15">
         <f>Palmon!U16</f>
-        <v>7.6923076923076927E-2</v>
+        <v>0.17948717948717949</v>
       </c>
       <c r="U15">
         <f>Palmon!V16</f>
-        <v>887</v>
+        <v>800</v>
       </c>
       <c r="V15">
         <f>Palmon!W16</f>
@@ -13087,15 +13087,15 @@
       </c>
       <c r="Z15">
         <f>Palmon!AA16</f>
-        <v>2210</v>
+        <v>3210</v>
       </c>
       <c r="AA15">
         <f>Palmon!AB16</f>
-        <v>27</v>
-      </c>
-      <c r="AB15" t="str">
+        <v>17</v>
+      </c>
+      <c r="AB15">
         <f>Palmon!AC16</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AC15">
         <f>Palmon!AD16</f>
@@ -13161,7 +13161,7 @@
       </c>
       <c r="H16">
         <f>Palmon!I17</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I16">
         <f>Palmon!J17</f>
@@ -13213,7 +13213,7 @@
       </c>
       <c r="U16">
         <f>Palmon!V17</f>
-        <v>852</v>
+        <v>860</v>
       </c>
       <c r="V16">
         <f>Palmon!W17</f>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="AA16">
         <f>Palmon!AB17</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB16" t="str">
         <f>Palmon!AC17</f>
@@ -13821,7 +13821,7 @@
       </c>
       <c r="AA20">
         <f>Palmon!AB21</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AB20" t="str">
         <f>Palmon!AC21</f>
@@ -13967,7 +13967,7 @@
       </c>
       <c r="AA21">
         <f>Palmon!AB22</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AB21">
         <f>Palmon!AC22</f>
@@ -14113,7 +14113,7 @@
       </c>
       <c r="AA22">
         <f>Palmon!AB23</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AB22" t="str">
         <f>Palmon!AC23</f>
@@ -14551,7 +14551,7 @@
       </c>
       <c r="AA25">
         <f>Palmon!AB26</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AB25">
         <f>Palmon!AC26</f>
@@ -15135,7 +15135,7 @@
       </c>
       <c r="AA29">
         <f>Palmon!AB30</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AB29" t="str">
         <f>Palmon!AC30</f>
@@ -17471,11 +17471,11 @@
       </c>
       <c r="AA45">
         <f>Palmon!AB46</f>
-        <v>20</v>
-      </c>
-      <c r="AB45">
+        <v>21</v>
+      </c>
+      <c r="AB45" t="str">
         <f>Palmon!AC46</f>
-        <v>3</v>
+        <v/>
       </c>
       <c r="AC45">
         <f>Palmon!AD46</f>
@@ -17855,11 +17855,11 @@
       <c r="D9" s="47" t="str">
         <v>Attack</v>
       </c>
-      <c r="E9" s="39">
-        <v>87</v>
-      </c>
-      <c r="F9" s="33" t="str">
-        <v/>
+      <c r="E9" s="39" t="str">
+        <v/>
+      </c>
+      <c r="F9" s="33">
+        <v>300</v>
       </c>
       <c r="G9" s="33" t="str">
         <v/>
@@ -18137,7 +18137,7 @@
         <v>Defend</v>
       </c>
       <c r="E16" s="39">
-        <v>51.999999999999972</v>
+        <v>59.999999999999972</v>
       </c>
       <c r="F16" s="33" t="str">
         <v/>
@@ -18154,7 +18154,7 @@
         <v>Electricity</v>
       </c>
       <c r="M16" s="39">
-        <v>87</v>
+        <v>59.999999999999972</v>
       </c>
       <c r="N16" s="33">
         <v>300</v>
@@ -18615,10 +18615,10 @@
         <v>Electricity</v>
       </c>
       <c r="M26" s="39">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N26" s="33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O26" s="33">
         <v>1</v>
@@ -18795,10 +18795,10 @@
         <v>Total</v>
       </c>
       <c r="M30" s="85">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N30" s="86">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O30" s="86">
         <v>5</v>
@@ -18961,7 +18961,7 @@
         <v>1</v>
       </c>
       <c r="O34" s="40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P34" s="1"/>
       <c r="Q34" s="216" t="str">
@@ -19107,7 +19107,7 @@
         <v>7</v>
       </c>
       <c r="O38" s="88">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P38" s="1"/>
       <c r="Q38" s="218" t="str">
@@ -19276,7 +19276,7 @@
         <v>Lucidina</v>
       </c>
       <c r="N44" s="78" t="str">
-        <v>Mantleray</v>
+        <v>Battereina</v>
       </c>
       <c r="O44" s="1"/>
       <c r="P44" s="1" t="str">
@@ -19308,7 +19308,7 @@
         <v>Abuzzinian</v>
       </c>
       <c r="N45" s="78" t="str">
-        <v>Escarffier</v>
+        <v>Mantleray</v>
       </c>
       <c r="O45" s="1"/>
       <c r="P45" s="1" t="str">
@@ -19331,7 +19331,7 @@
         <v>Kungpaw</v>
       </c>
       <c r="N46" s="78" t="str">
-        <v>Ninjump</v>
+        <v>Escarffier</v>
       </c>
       <c r="O46" s="1"/>
       <c r="P46" s="1" t="str">
@@ -19354,7 +19354,7 @@
         <v>Magmolin</v>
       </c>
       <c r="N47" s="78" t="str">
-        <v>Revontulet</v>
+        <v>Ninjump</v>
       </c>
       <c r="O47" s="1"/>
       <c r="P47" s="1" t="str">
@@ -19377,7 +19377,7 @@
         <v>Spookaboo</v>
       </c>
       <c r="N48" s="83" t="str">
-        <v>Limudroid</v>
+        <v>Revontulet</v>
       </c>
       <c r="O48" s="1"/>
       <c r="P48" s="1" t="str">
@@ -19481,7 +19481,7 @@
     </row>
     <row r="53" spans="7:20" s="1" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="G53" s="1">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H53" s="1" t="str">
         <v/>
@@ -19490,13 +19490,13 @@
         <v>Baboom</v>
       </c>
       <c r="M53" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N53" s="1" t="str">
         <v/>
       </c>
       <c r="P53" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q53" s="1" t="str">
         <v/>
@@ -19539,7 +19539,7 @@
     </row>
     <row r="55" spans="7:20" s="1" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="G55" s="1">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H55" s="1" t="str">
         <v/>
@@ -19548,13 +19548,13 @@
         <v>Battereina</v>
       </c>
       <c r="M55" s="1">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="N55" s="1" t="str">
         <v/>
       </c>
       <c r="P55" s="1">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="Q55" s="1" t="str">
         <v/>
@@ -19629,7 +19629,7 @@
         <v/>
       </c>
       <c r="H58" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L58" s="1" t="str">
         <v>Dolphriend</v>
@@ -19638,7 +19638,7 @@
         <v/>
       </c>
       <c r="N58" s="1">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P58" s="1" t="str">
         <v/>
@@ -19658,7 +19658,7 @@
         <v/>
       </c>
       <c r="H59" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L59" s="1" t="str">
         <v>Escarffier</v>
@@ -19667,7 +19667,7 @@
         <v/>
       </c>
       <c r="N59" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P59" s="1" t="str">
         <v/>
@@ -19727,7 +19727,7 @@
         <v/>
       </c>
       <c r="H62" s="1">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L62" s="1" t="str">
         <v>Fulgairy</v>
@@ -19736,7 +19736,7 @@
         <v/>
       </c>
       <c r="N62" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P62" s="1" t="str">
         <v/>
@@ -19839,7 +19839,7 @@
     </row>
     <row r="67" spans="7:20" s="1" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="G67" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H67" s="1" t="str">
         <v/>
@@ -19848,13 +19848,13 @@
         <v>Limudroid</v>
       </c>
       <c r="M67" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N67" s="1" t="str">
         <v/>
       </c>
       <c r="P67" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q67" s="1" t="str">
         <v/>
@@ -19908,7 +19908,7 @@
     </row>
     <row r="70" spans="7:20" s="1" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="G70" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H70" s="1" t="str">
         <v/>
@@ -19917,13 +19917,13 @@
         <v>Mantleray</v>
       </c>
       <c r="M70" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N70" s="1" t="str">
         <v/>
       </c>
       <c r="P70" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q70" s="1" t="str">
         <v/>
@@ -19931,7 +19931,7 @@
     </row>
     <row r="71" spans="7:20" s="1" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="G71" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H71" s="1" t="str">
         <v/>
@@ -19940,13 +19940,13 @@
         <v>Ninjump</v>
       </c>
       <c r="M71" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N71" s="1" t="str">
         <v/>
       </c>
       <c r="P71" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q71" s="1" t="str">
         <v/>
@@ -20072,7 +20072,7 @@
         <v/>
       </c>
       <c r="H77" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L77" s="1" t="str">
         <v>Statchew</v>
@@ -20081,7 +20081,7 @@
         <v/>
       </c>
       <c r="N77" s="1">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P77" s="1" t="str">
         <v/>
@@ -20092,7 +20092,7 @@
     </row>
     <row r="78" spans="7:20" s="1" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="G78" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H78" s="1" t="str">
         <v/>
@@ -20101,13 +20101,13 @@
         <v>Surveilynx</v>
       </c>
       <c r="M78" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N78" s="1" t="str">
         <v/>
       </c>
       <c r="P78" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q78" s="1" t="str">
         <v/>
@@ -33240,7 +33240,7 @@
         <v>50</v>
       </c>
       <c r="J4" s="4">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="K4" s="246">
         <v>0</v>
@@ -33366,7 +33366,7 @@
         <v>53</v>
       </c>
       <c r="J6" s="4">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="K6" s="246">
         <v>2.2000000000000002</v>
@@ -43667,7 +43667,7 @@
       </c>
       <c r="F9" t="str">
         <f>Palmon!B9 &amp; "," &amp; Palmon!C9 &amp; "," &amp; Palmon!D9 &amp; "," &amp; Palmon!E9 &amp; "," &amp; Palmon!G9 &amp; "," &amp; SUBSTITUTE(Palmon!H9,",",".") &amp; "," &amp; Palmon!I9 &amp; "," &amp; SUBSTITUTE(Palmon!P9,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q9,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R9,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S9,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T9,",",".") &amp; "," &amp; Palmon!J9 &amp; "," &amp; Palmon!K9 &amp; "," &amp; Palmon!L9 &amp; "," &amp; Palmon!M9 &amp; "," &amp; Palmon!N9 &amp; "," &amp; SUBSTITUTE(Palmon!U9,",",".") &amp; "," &amp; Palmon!V9 &amp; "," &amp; Palmon!X9 &amp; "," &amp; Palmon!Y9 &amp; "," &amp; Palmon!AA9 &amp; "," &amp; Palmon!AB9 &amp; "," &amp; Palmon!AC9 &amp; "," &amp; Palmon!AE9 &amp; "," &amp; Palmon!AF9 &amp; "," &amp; Palmon!AI9 &amp; "," &amp; Palmon!AJ9</f>
-        <v>Limudroid,Electricity,Attack,230,2,2.2,4,1,1,0.4,0,0,1,1,5,,,0.117948717948718,856,3390620000,1,2430,21,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQzaI21taP2V17MKjiPAeulm4V9qfST4umPdg&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRMlruQNUenhVk-fAEq9d3Wi8zw--0GbkLGJrX1CuQ1&amp;s,Bunodroid,</v>
+        <v>Limudroid,Electricity,Attack,230,2,2.2,4,1,1,0.4,0,0,1,1,5,,,0.117948717948718,856,3390620000,1,2430,22,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQzaI21taP2V17MKjiPAeulm4V9qfST4umPdg&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRMlruQNUenhVk-fAEq9d3Wi8zw--0GbkLGJrX1CuQ1&amp;s,Bunodroid,</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -43745,7 +43745,7 @@
       </c>
       <c r="F12" t="str">
         <f>Palmon!B12 &amp; "," &amp; Palmon!C12 &amp; "," &amp; Palmon!D12 &amp; "," &amp; Palmon!E12 &amp; "," &amp; Palmon!G12 &amp; "," &amp; SUBSTITUTE(Palmon!H12,",",".") &amp; "," &amp; Palmon!I12 &amp; "," &amp; SUBSTITUTE(Palmon!P12,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q12,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R12,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S12,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T12,",",".") &amp; "," &amp; Palmon!J12 &amp; "," &amp; Palmon!K12 &amp; "," &amp; Palmon!L12 &amp; "," &amp; Palmon!M12 &amp; "," &amp; Palmon!N12 &amp; "," &amp; SUBSTITUTE(Palmon!U12,",",".") &amp; "," &amp; Palmon!V12 &amp; "," &amp; Palmon!X12 &amp; "," &amp; Palmon!Y12 &amp; "," &amp; Palmon!AA12 &amp; "," &amp; Palmon!AB12 &amp; "," &amp; Palmon!AC12 &amp; "," &amp; Palmon!AE12 &amp; "," &amp; Palmon!AF12 &amp; "," &amp; Palmon!AI12 &amp; "," &amp; Palmon!AJ12</f>
-        <v>Escarffier,Fire,Defend,230,2,2.3,8,1,1,0.6,0,0,5,5,5,,,0.138461538461538,832,3390620000,1,2530,18,3,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcST2CrUIPAlFNBLPgZn0Tu93KelabHVVAbNLQ&amp;s, ,Essaucier,</v>
+        <v>Escarffier,Fire,Defend,230,2,2.3,8,1,1,0.6,0,0,5,5,5,,,0.138461538461538,832,3390620000,1,2530,19,3,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcST2CrUIPAlFNBLPgZn0Tu93KelabHVVAbNLQ&amp;s, ,Essaucier,</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -43823,7 +43823,7 @@
       </c>
       <c r="F15" t="str">
         <f>Palmon!B15 &amp; "," &amp; Palmon!C15 &amp; "," &amp; Palmon!D15 &amp; "," &amp; Palmon!E15 &amp; "," &amp; Palmon!G15 &amp; "," &amp; SUBSTITUTE(Palmon!H15,",",".") &amp; "," &amp; Palmon!I15 &amp; "," &amp; SUBSTITUTE(Palmon!P15,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q15,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R15,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S15,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T15,",",".") &amp; "," &amp; Palmon!J15 &amp; "," &amp; Palmon!K15 &amp; "," &amp; Palmon!L15 &amp; "," &amp; Palmon!M15 &amp; "," &amp; Palmon!N15 &amp; "," &amp; SUBSTITUTE(Palmon!U15,",",".") &amp; "," &amp; Palmon!V15 &amp; "," &amp; Palmon!X15 &amp; "," &amp; Palmon!Y15 &amp; "," &amp; Palmon!AA15 &amp; "," &amp; Palmon!AB15 &amp; "," &amp; Palmon!AC15 &amp; "," &amp; Palmon!AE15 &amp; "," &amp; Palmon!AF15 &amp; "," &amp; Palmon!AI15 &amp; "," &amp; Palmon!AJ15</f>
-        <v>Statchew,Wood,Defend,230,2,2.2,10,1,1,0.4,0,0,15,5,9,,,0.117948717948718,850,3390620000,1,2430,22,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSC1rp-0lIuUyVvSi8kN_vJnr_Ln4mF4lh4zg&amp;s, ,Anubeast,</v>
+        <v>Statchew,Wood,Defend,230,2,2.2,10,1,1,0.4,0,0,15,5,9,,,0.117948717948718,850,3390620000,1,2430,23,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSC1rp-0lIuUyVvSi8kN_vJnr_Ln4mF4lh4zg&amp;s, ,Anubeast,</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -43849,7 +43849,7 @@
       </c>
       <c r="F16" t="str">
         <f>Palmon!B16 &amp; "," &amp; Palmon!C16 &amp; "," &amp; Palmon!D16 &amp; "," &amp; Palmon!E16 &amp; "," &amp; Palmon!G16 &amp; "," &amp; SUBSTITUTE(Palmon!H16,",",".") &amp; "," &amp; Palmon!I16 &amp; "," &amp; SUBSTITUTE(Palmon!P16,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q16,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R16,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S16,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T16,",",".") &amp; "," &amp; Palmon!J16 &amp; "," &amp; Palmon!K16 &amp; "," &amp; Palmon!L16 &amp; "," &amp; Palmon!M16 &amp; "," &amp; Palmon!N16 &amp; "," &amp; SUBSTITUTE(Palmon!U16,",",".") &amp; "," &amp; Palmon!V16 &amp; "," &amp; Palmon!X16 &amp; "," &amp; Palmon!Y16 &amp; "," &amp; Palmon!AA16 &amp; "," &amp; Palmon!AB16 &amp; "," &amp; Palmon!AC16 &amp; "," &amp; Palmon!AE16 &amp; "," &amp; Palmon!AF16 &amp; "," &amp; Palmon!AI16 &amp; "," &amp; Palmon!AJ16</f>
-        <v>Battereina,Electricity,Attack,210,2,2,13,1,1,0,0,0,1,1,1,,,0.0769230769230769,887,4161420000,1,2210,27,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQaumzt62POzCPWE5kNVnUA5j6pKVetbogSOJqvW2HU&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTun-SMpIMKagR2SMRlAysEcjxhO7sD6Nq3IQ&amp;s,Ampereina,</v>
+        <v>Battereina,Electricity,Attack,210,3,3,0,1,1,1,0,0,1,1,1,,,0.179487179487179,800,4161420000,1,3210,17,3,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQaumzt62POzCPWE5kNVnUA5j6pKVetbogSOJqvW2HU&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTun-SMpIMKagR2SMRlAysEcjxhO7sD6Nq3IQ&amp;s,Ampereina,</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -43875,7 +43875,7 @@
       </c>
       <c r="F17" t="str">
         <f>Palmon!B17 &amp; "," &amp; Palmon!C17 &amp; "," &amp; Palmon!D17 &amp; "," &amp; Palmon!E17 &amp; "," &amp; Palmon!G17 &amp; "," &amp; SUBSTITUTE(Palmon!H17,",",".") &amp; "," &amp; Palmon!I17 &amp; "," &amp; SUBSTITUTE(Palmon!P17,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q17,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R17,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S17,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T17,",",".") &amp; "," &amp; Palmon!J17 &amp; "," &amp; Palmon!K17 &amp; "," &amp; Palmon!L17 &amp; "," &amp; Palmon!M17 &amp; "," &amp; Palmon!N17 &amp; "," &amp; SUBSTITUTE(Palmon!U17,",",".") &amp; "," &amp; Palmon!V17 &amp; "," &amp; Palmon!X17 &amp; "," &amp; Palmon!Y17 &amp; "," &amp; Palmon!AA17 &amp; "," &amp; Palmon!AB17 &amp; "," &amp; Palmon!AC17 &amp; "," &amp; Palmon!AE17 &amp; "," &amp; Palmon!AF17 &amp; "," &amp; Palmon!AI17 &amp; "," &amp; Palmon!AJ17</f>
-        <v>Fulgairy,Electricity,Defend,210,2,2.2,8,1,1,0.4,0,0,5,5,10,,,0.117948717948718,852,4161420000,1,2410,23,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRvhKm8Syu_29_yraif6I_ybijQhVUhvDmMNg&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSNLJe_mmX76tcOcm93Zzrq-x4btMmg4l1csw&amp;s,Keraunosaur,</v>
+        <v>Fulgairy,Electricity,Defend,210,2,2.2,0,1,1,0.4,0,0,5,5,10,,,0.117948717948718,860,4161420000,1,2410,24,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRvhKm8Syu_29_yraif6I_ybijQhVUhvDmMNg&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSNLJe_mmX76tcOcm93Zzrq-x4btMmg4l1csw&amp;s,Keraunosaur,</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -43979,7 +43979,7 @@
       </c>
       <c r="F21" t="str">
         <f>Palmon!B21 &amp; "," &amp; Palmon!C21 &amp; "," &amp; Palmon!D21 &amp; "," &amp; Palmon!E21 &amp; "," &amp; Palmon!G21 &amp; "," &amp; SUBSTITUTE(Palmon!H21,",",".") &amp; "," &amp; Palmon!I21 &amp; "," &amp; SUBSTITUTE(Palmon!P21,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q21,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R21,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S21,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T21,",",".") &amp; "," &amp; Palmon!J21 &amp; "," &amp; Palmon!K21 &amp; "," &amp; Palmon!L21 &amp; "," &amp; Palmon!M21 &amp; "," &amp; Palmon!N21 &amp; "," &amp; SUBSTITUTE(Palmon!U21,",",".") &amp; "," &amp; Palmon!V21 &amp; "," &amp; Palmon!X21 &amp; "," &amp; Palmon!Y21 &amp; "," &amp; Palmon!AA21 &amp; "," &amp; Palmon!AB21 &amp; "," &amp; Palmon!AC21 &amp; "," &amp; Palmon!AE21 &amp; "," &amp; Palmon!AF21 &amp; "," &amp; Palmon!AI21 &amp; "," &amp; Palmon!AJ21</f>
-        <v>Dolphriend,Water,Defend,210,2,2.2,1,1,1,0.4,0,0,1,1,1,,,0.117948717948718,859,4161420000,1,2410,24,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQ5ThIRML8-S9czd3JEMxpMlnMn9UAMwdeiBw&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTQp9fQrKVHd_zzyuSxM8QSOjlZsRbJ0lwxrg&amp;s,Adolphonis,</v>
+        <v>Dolphriend,Water,Defend,210,2,2.2,1,1,1,0.4,0,0,1,1,1,,,0.117948717948718,859,4161420000,1,2410,25,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQ5ThIRML8-S9czd3JEMxpMlnMn9UAMwdeiBw&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTQp9fQrKVHd_zzyuSxM8QSOjlZsRbJ0lwxrg&amp;s,Adolphonis,</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -44005,7 +44005,7 @@
       </c>
       <c r="F22" t="str">
         <f>Palmon!B22 &amp; "," &amp; Palmon!C22 &amp; "," &amp; Palmon!D22 &amp; "," &amp; Palmon!E22 &amp; "," &amp; Palmon!G22 &amp; "," &amp; SUBSTITUTE(Palmon!H22,",",".") &amp; "," &amp; Palmon!I22 &amp; "," &amp; SUBSTITUTE(Palmon!P22,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q22,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R22,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S22,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T22,",",".") &amp; "," &amp; Palmon!J22 &amp; "," &amp; Palmon!K22 &amp; "," &amp; Palmon!L22 &amp; "," &amp; Palmon!M22 &amp; "," &amp; Palmon!N22 &amp; "," &amp; SUBSTITUTE(Palmon!U22,",",".") &amp; "," &amp; Palmon!V22 &amp; "," &amp; Palmon!X22 &amp; "," &amp; Palmon!Y22 &amp; "," &amp; Palmon!AA22 &amp; "," &amp; Palmon!AB22 &amp; "," &amp; Palmon!AC22 &amp; "," &amp; Palmon!AE22 &amp; "," &amp; Palmon!AF22 &amp; "," &amp; Palmon!AI22 &amp; "," &amp; Palmon!AJ22</f>
-        <v>Ninjump,Water,Attack,160,2,2.3,10,1,1,0.6,0,0,1,1,1,,,0.138461538461538,830,4919220000,1,2460,19,3,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQlW5YoM4c6bArAuIb7UxI-VfUI9GmBp85Qig&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRXczs_Bjhslhr7Mf2HENU6MTyGpz0RJEMjNA&amp;s,Bufonobi,Shadowkaeru</v>
+        <v>Ninjump,Water,Attack,160,2,2.3,10,1,1,0.6,0,0,1,1,1,,,0.138461538461538,830,4919220000,1,2460,20,3,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQlW5YoM4c6bArAuIb7UxI-VfUI9GmBp85Qig&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRXczs_Bjhslhr7Mf2HENU6MTyGpz0RJEMjNA&amp;s,Bufonobi,Shadowkaeru</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -44031,7 +44031,7 @@
       </c>
       <c r="F23" t="str">
         <f>Palmon!B23 &amp; "," &amp; Palmon!C23 &amp; "," &amp; Palmon!D23 &amp; "," &amp; Palmon!E23 &amp; "," &amp; Palmon!G23 &amp; "," &amp; SUBSTITUTE(Palmon!H23,",",".") &amp; "," &amp; Palmon!I23 &amp; "," &amp; SUBSTITUTE(Palmon!P23,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q23,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R23,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S23,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T23,",",".") &amp; "," &amp; Palmon!J23 &amp; "," &amp; Palmon!K23 &amp; "," &amp; Palmon!L23 &amp; "," &amp; Palmon!M23 &amp; "," &amp; Palmon!N23 &amp; "," &amp; SUBSTITUTE(Palmon!U23,",",".") &amp; "," &amp; Palmon!V23 &amp; "," &amp; Palmon!X23 &amp; "," &amp; Palmon!Y23 &amp; "," &amp; Palmon!AA23 &amp; "," &amp; Palmon!AB23 &amp; "," &amp; Palmon!AC23 &amp; "," &amp; Palmon!AE23 &amp; "," &amp; Palmon!AF23 &amp; "," &amp; Palmon!AI23 &amp; "," &amp; Palmon!AJ23</f>
-        <v>Surveilynx,Wood,Attack,220,2,2,0,1,1,0,0,0,10,10,10,,,0.0769230769230769,900,3826220000,1,2220,26,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcS2Z4TkKenIldVD1AQ7o1ftBU6pG9zKRz-FKA&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQt6lIf0Em_f_DT0VurOVsujswJCEmGOpJk4N6txfed&amp;s,Camouflynx,</v>
+        <v>Surveilynx,Wood,Attack,220,2,2,0,1,1,0,0,0,10,10,10,,,0.0769230769230769,900,3826220000,1,2220,27,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcS2Z4TkKenIldVD1AQ7o1ftBU6pG9zKRz-FKA&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQt6lIf0Em_f_DT0VurOVsujswJCEmGOpJk4N6txfed&amp;s,Camouflynx,</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -44109,7 +44109,7 @@
       </c>
       <c r="F26" t="str">
         <f>Palmon!B26 &amp; "," &amp; Palmon!C26 &amp; "," &amp; Palmon!D26 &amp; "," &amp; Palmon!E26 &amp; "," &amp; Palmon!G26 &amp; "," &amp; SUBSTITUTE(Palmon!H26,",",".") &amp; "," &amp; Palmon!I26 &amp; "," &amp; SUBSTITUTE(Palmon!P26,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q26,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R26,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S26,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T26,",",".") &amp; "," &amp; Palmon!J26 &amp; "," &amp; Palmon!K26 &amp; "," &amp; Palmon!L26 &amp; "," &amp; Palmon!M26 &amp; "," &amp; Palmon!N26 &amp; "," &amp; SUBSTITUTE(Palmon!U26,",",".") &amp; "," &amp; Palmon!V26 &amp; "," &amp; Palmon!X26 &amp; "," &amp; Palmon!Y26 &amp; "," &amp; Palmon!AA26 &amp; "," &amp; Palmon!AB26 &amp; "," &amp; Palmon!AC26 &amp; "," &amp; Palmon!AE26 &amp; "," &amp; Palmon!AF26 &amp; "," &amp; Palmon!AI26 &amp; "," &amp; Palmon!AJ26</f>
-        <v>Mantleray,Electricity,Attack,210,2,2.4,3,1,1,0.8,0,0,4,1,1,,,0.158974358974359,817,4161420000,1,2610,17,3,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSWhzppoZXwh-zBnWIY3GFkIp0x0kc0hAzG0A&amp;s, ,Sorceray,</v>
+        <v>Mantleray,Electricity,Attack,210,2,2.4,3,1,1,0.8,0,0,4,1,1,,,0.158974358974359,817,4161420000,1,2610,18,3,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSWhzppoZXwh-zBnWIY3GFkIp0x0kc0hAzG0A&amp;s, ,Sorceray,</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -44213,7 +44213,7 @@
       </c>
       <c r="F30" t="str">
         <f>Palmon!B30 &amp; "," &amp; Palmon!C30 &amp; "," &amp; Palmon!D30 &amp; "," &amp; Palmon!E30 &amp; "," &amp; Palmon!G30 &amp; "," &amp; SUBSTITUTE(Palmon!H30,",",".") &amp; "," &amp; Palmon!I30 &amp; "," &amp; SUBSTITUTE(Palmon!P30,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q30,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R30,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S30,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T30,",",".") &amp; "," &amp; Palmon!J30 &amp; "," &amp; Palmon!K30 &amp; "," &amp; Palmon!L30 &amp; "," &amp; Palmon!M30 &amp; "," &amp; Palmon!N30 &amp; "," &amp; SUBSTITUTE(Palmon!U30,",",".") &amp; "," &amp; Palmon!V30 &amp; "," &amp; Palmon!X30 &amp; "," &amp; Palmon!Y30 &amp; "," &amp; Palmon!AA30 &amp; "," &amp; Palmon!AB30 &amp; "," &amp; Palmon!AC30 &amp; "," &amp; Palmon!AE30 &amp; "," &amp; Palmon!AF30 &amp; "," &amp; Palmon!AI30 &amp; "," &amp; Palmon!AJ30</f>
-        <v>Baboom,Wood,Attack,210,2,2.1,10,1,1,0.2,0,0,5,1,1,,,0.0974358974358975,870,4161420000,1,2310,25,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRh7P3oaH_Kq0fni1aOxe3TmDgHULu_Z-UWUg&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSQA67-vNrm701vphmHvRKGkJTx2O2gyTi00Q&amp;s,Rumbkey,</v>
+        <v>Baboom,Wood,Attack,210,2,2.1,10,1,1,0.2,0,0,5,1,1,,,0.0974358974358975,870,4161420000,1,2310,26,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRh7P3oaH_Kq0fni1aOxe3TmDgHULu_Z-UWUg&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSQA67-vNrm701vphmHvRKGkJTx2O2gyTi00Q&amp;s,Rumbkey,</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -44463,7 +44463,7 @@
       </c>
       <c r="F43" t="str">
         <f>Palmon!B46 &amp; "," &amp; Palmon!C46 &amp; "," &amp; Palmon!D46 &amp; "," &amp; Palmon!E46 &amp; "," &amp; Palmon!G46 &amp; "," &amp; SUBSTITUTE(Palmon!H46,",",".") &amp; "," &amp; Palmon!I46 &amp; "," &amp; SUBSTITUTE(Palmon!P46,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q46,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R46,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S46,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T46,",",".") &amp; "," &amp; Palmon!J46 &amp; "," &amp; Palmon!K46 &amp; "," &amp; Palmon!L46 &amp; "," &amp; Palmon!M46 &amp; "," &amp; Palmon!N46 &amp; "," &amp; SUBSTITUTE(Palmon!U46,",",".") &amp; "," &amp; Palmon!V46 &amp; "," &amp; Palmon!X46 &amp; "," &amp; Palmon!Y46 &amp; "," &amp; Palmon!AA46 &amp; "," &amp; Palmon!AB46 &amp; "," &amp; Palmon!AC46 &amp; "," &amp; Palmon!AE46 &amp; "," &amp; Palmon!AF46 &amp; "," &amp; Palmon!AI46 &amp; "," &amp; Palmon!AJ46</f>
-        <v>Revontulet,Fire,Attack,160,2,2.3,0,1,1,0.6,0,0,1,1,1,,,0.138461538461538,840,4919220000,1,2460,20,3,, ,Vulpyrean,Camouflynx</v>
+        <v>Revontulet,Fire,Attack,160,2,2.3,0,1,1,0.6,0,0,1,1,1,,,0.138461538461538,840,4919220000,1,2460,21,,, ,Vulpyrean,Camouflynx</v>
       </c>
     </row>
     <row r="44" spans="3:6" x14ac:dyDescent="0.25">

--- a/data/PS - Estimation (version 1).xlsx
+++ b/data/PS - Estimation (version 1).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xvjm020\Documents\Personnel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCEB0D13-115A-465C-9E7F-8550311C9454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96F11454-2024-4F51-A845-290D98F2F678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9D83D047-1CAD-4BF9-942E-B289F790400E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{9D83D047-1CAD-4BF9-942E-B289F790400E}"/>
   </bookViews>
   <sheets>
     <sheet name="Palmon" sheetId="2" r:id="rId1"/>
@@ -103,7 +103,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="266">
   <si>
     <t>I</t>
   </si>
@@ -688,9 +688,6 @@
   </si>
   <si>
     <t>URL Mutation</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>Vulpyrean</t>
@@ -4362,8 +4359,8 @@
           <xdr:rowOff>114300</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>10</xdr:col>
-          <xdr:colOff>323850</xdr:colOff>
+          <xdr:col>31</xdr:col>
+          <xdr:colOff>476250</xdr:colOff>
           <xdr:row>148</xdr:row>
           <xdr:rowOff>9525</xdr:rowOff>
         </xdr:to>
@@ -5046,21 +5043,21 @@
     <col min="1" max="1" width="2.85546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.42578125" style="1" customWidth="1"/>
-    <col min="4" max="6" width="11.42578125" style="1" customWidth="1" outlineLevel="1"/>
-    <col min="7" max="14" width="6.28515625" style="1" customWidth="1" outlineLevel="1"/>
-    <col min="15" max="15" width="1.28515625" style="1" customWidth="1"/>
-    <col min="16" max="17" width="11.42578125" style="1" customWidth="1" outlineLevel="1"/>
-    <col min="18" max="18" width="8" style="1" customWidth="1" outlineLevel="1"/>
-    <col min="19" max="20" width="5.7109375" style="1" customWidth="1" outlineLevel="1"/>
-    <col min="21" max="21" width="10.28515625" style="1" customWidth="1" outlineLevel="1"/>
-    <col min="22" max="22" width="5.7109375" style="1" customWidth="1" outlineLevel="1"/>
-    <col min="23" max="23" width="1.42578125" style="1" customWidth="1"/>
-    <col min="24" max="24" width="13" style="1" customWidth="1" outlineLevel="1"/>
-    <col min="25" max="25" width="11.5703125" style="1" customWidth="1" outlineLevel="1"/>
-    <col min="26" max="26" width="0.85546875" style="1" customWidth="1" outlineLevel="1"/>
-    <col min="27" max="28" width="6.28515625" style="1" customWidth="1" outlineLevel="1"/>
-    <col min="29" max="29" width="12.5703125" style="1" customWidth="1" outlineLevel="1"/>
-    <col min="30" max="30" width="0.85546875" style="1" customWidth="1"/>
+    <col min="4" max="6" width="11.42578125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="14" width="6.28515625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="15" max="15" width="1.28515625" style="1" customWidth="1" collapsed="1"/>
+    <col min="16" max="17" width="11.42578125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="18" max="18" width="8" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="19" max="20" width="5.7109375" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="21" max="21" width="10.28515625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="22" max="22" width="5.7109375" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="23" max="23" width="1.42578125" style="1" customWidth="1" collapsed="1"/>
+    <col min="24" max="24" width="13" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="25" max="25" width="11.5703125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="26" max="26" width="0.85546875" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="27" max="28" width="6.28515625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="29" max="29" width="12.5703125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="30" max="30" width="0.85546875" style="1" customWidth="1" collapsed="1"/>
     <col min="31" max="33" width="11.42578125" style="1"/>
     <col min="34" max="34" width="0.85546875" style="1" customWidth="1"/>
     <col min="35" max="16384" width="11.42578125" style="1"/>
@@ -5312,9 +5309,7 @@
         <f>" "</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AI3" s="170" t="s">
-        <v>195</v>
-      </c>
+      <c r="AI3" s="170"/>
       <c r="AJ3" s="166" t="s">
         <v>112</v>
       </c>
@@ -5326,7 +5321,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C4" s="19" t="s">
         <v>50</v>
@@ -5537,7 +5532,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AI5" s="63" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AJ5" s="7"/>
       <c r="AK5" s="19"/>
@@ -5762,7 +5757,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AI7" s="63" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AJ7" s="7"/>
       <c r="AK7" s="19"/>
@@ -5875,7 +5870,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AI8" s="63" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AJ8" s="7"/>
       <c r="AK8" s="19"/>
@@ -5987,7 +5982,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AI9" s="63" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AJ9" s="7"/>
       <c r="AK9" s="19"/>
@@ -6099,7 +6094,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AI10" s="63" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AJ10" s="7"/>
       <c r="AK10" s="19"/>
@@ -6211,7 +6206,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AI11" s="63" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AJ11" s="7"/>
       <c r="AK11" s="19"/>
@@ -6324,7 +6319,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AI12" s="63" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AJ12" s="7"/>
       <c r="AK12" s="19"/>
@@ -6448,7 +6443,7 @@
         <v>1</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C14" s="19" t="s">
         <v>55</v>
@@ -6661,7 +6656,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AI15" s="63" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AJ15" s="7"/>
       <c r="AK15" s="19"/>
@@ -6773,7 +6768,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AI16" s="63" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AJ16" s="7"/>
       <c r="AK16" s="19"/>
@@ -6885,7 +6880,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AI17" s="63" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AJ17" s="7"/>
       <c r="AK17" s="19"/>
@@ -6997,7 +6992,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AI18" s="63" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AJ18" s="7"/>
       <c r="AK18" s="19"/>
@@ -7111,7 +7106,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AI19" s="121" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AJ19" s="117"/>
       <c r="AK19" s="212"/>
@@ -7229,7 +7224,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AI20" s="63" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AJ20" s="7"/>
       <c r="AK20" s="19"/>
@@ -7677,7 +7672,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AI24" s="63" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AJ24" s="7"/>
       <c r="AK24" s="19"/>
@@ -7789,7 +7784,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AI25" s="63" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AJ25" s="7"/>
       <c r="AK25" s="19"/>
@@ -7902,7 +7897,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AI26" s="63" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AJ26" s="7"/>
       <c r="AK26" s="19"/>
@@ -8135,7 +8130,7 @@
         <v/>
       </c>
       <c r="B29" s="31" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C29" s="19" t="s">
         <v>53</v>
@@ -8226,7 +8221,7 @@
         <v>2</v>
       </c>
       <c r="AE29" s="63" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AF29" s="7"/>
       <c r="AG29" s="19" t="str">
@@ -8344,7 +8339,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AI30" s="64" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AJ30" s="70"/>
       <c r="AK30" s="20"/>
@@ -8451,7 +8446,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AI31" s="174" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AJ31" s="178"/>
       <c r="AK31" s="172"/>
@@ -8564,7 +8559,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AI32" s="63" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AJ32" s="7"/>
       <c r="AK32" s="19"/>
@@ -8575,7 +8570,7 @@
         <v/>
       </c>
       <c r="B33" s="31" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C33" s="19" t="s">
         <v>55</v>
@@ -8890,12 +8885,12 @@
     </row>
     <row r="36" spans="1:37" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B36" s="161" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C36" s="162" t="s">
         <v>53</v>
       </c>
-      <c r="D36" s="163" t="s">
+      <c r="D36" s="152" t="s">
         <v>97</v>
       </c>
       <c r="E36" s="63"/>
@@ -8974,7 +8969,7 @@
         <v/>
       </c>
       <c r="AE36" s="170" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="AF36" s="166"/>
       <c r="AG36" s="167"/>
@@ -8984,12 +8979,12 @@
     </row>
     <row r="37" spans="1:37" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B37" s="161" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C37" s="162" t="s">
         <v>53</v>
       </c>
-      <c r="D37" s="163" t="s">
+      <c r="D37" s="152" t="s">
         <v>97</v>
       </c>
       <c r="E37" s="63"/>
@@ -9066,12 +9061,12 @@
         <v/>
       </c>
       <c r="AE37" s="170" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="AF37" s="166"/>
       <c r="AG37" s="167"/>
       <c r="AI37" s="170" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AJ37" s="166"/>
       <c r="AK37" s="167"/>
@@ -9181,7 +9176,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AI38" s="63" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AJ38" s="7"/>
       <c r="AK38" s="19"/>
@@ -9993,11 +9988,9 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AI46" s="64" t="s">
-        <v>196</v>
-      </c>
-      <c r="AJ46" s="70" t="s">
-        <v>187</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="AJ46" s="70"/>
       <c r="AK46" s="20"/>
     </row>
     <row r="47" spans="1:37" ht="12" customHeight="1" x14ac:dyDescent="0.2">
@@ -10248,7 +10241,7 @@
         <v>9985660300</v>
       </c>
       <c r="D56" s="208" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E56" s="61">
         <f>C56-E55</f>
@@ -10279,7 +10272,7 @@
     </row>
     <row r="58" spans="2:24" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B58" s="253" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C58" s="254"/>
       <c r="D58" s="142"/>
@@ -10303,7 +10296,7 @@
     </row>
     <row r="59" spans="2:24" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="240" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C59" s="60">
         <v>400000</v>
@@ -10329,7 +10322,7 @@
     </row>
     <row r="60" spans="2:24" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="204" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C60" s="13">
         <v>300</v>
@@ -10355,7 +10348,7 @@
     </row>
     <row r="61" spans="2:24" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B61" s="241" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C61" s="22">
         <v>975</v>
@@ -10548,7 +10541,7 @@
       <formula>$C3="Wood"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D3:D53 D57:D81">
+  <conditionalFormatting sqref="D57:D81 D3:D53">
     <cfRule type="cellIs" dxfId="65" priority="76" operator="equal">
       <formula>"Attack"</formula>
     </cfRule>
@@ -10696,8 +10689,8 @@
                     <xdr:rowOff>114300</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>10</xdr:col>
-                    <xdr:colOff>323850</xdr:colOff>
+                    <xdr:col>31</xdr:col>
+                    <xdr:colOff>476250</xdr:colOff>
                     <xdr:row>148</xdr:row>
                     <xdr:rowOff>9525</xdr:rowOff>
                   </to>
@@ -10791,7 +10784,7 @@
   <sheetData>
     <row r="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="2" spans="1:35" x14ac:dyDescent="0.25">
@@ -11220,11 +11213,11 @@
         <v>0</v>
       </c>
       <c r="AH2" t="str">
-        <f>Palmon!AI3</f>
-        <v/>
+        <f>IF(Palmon!AI3=0,"Non",Palmon!AI3)</f>
+        <v>Non</v>
       </c>
       <c r="AI2" t="str">
-        <f>Palmon!AJ3</f>
+        <f>IF(Palmon!AJ3=0,"Non",Palmon!AJ3)</f>
         <v>Shadowkaeru</v>
       </c>
       <c r="AJ2">
@@ -11365,13 +11358,13 @@
         <f>Palmon!AH4</f>
         <v>0</v>
       </c>
-      <c r="AH3">
-        <f>Palmon!AI4</f>
-        <v>0</v>
-      </c>
-      <c r="AI3">
-        <f>Palmon!AJ4</f>
-        <v>0</v>
+      <c r="AH3" t="str">
+        <f>IF(Palmon!AI4=0,"Non",Palmon!AI4)</f>
+        <v>Non</v>
+      </c>
+      <c r="AI3" t="str">
+        <f>IF(Palmon!AJ4=0,"Non",Palmon!AJ4)</f>
+        <v>Non</v>
       </c>
       <c r="AJ3">
         <f>Palmon!AK4</f>
@@ -11512,12 +11505,12 @@
         <v>0</v>
       </c>
       <c r="AH4" t="str">
-        <f>Palmon!AI5</f>
+        <f>IF(Palmon!AI5=0,"Non",Palmon!AI5)</f>
         <v>Flaries</v>
       </c>
-      <c r="AI4">
-        <f>Palmon!AJ5</f>
-        <v>0</v>
+      <c r="AI4" t="str">
+        <f>IF(Palmon!AJ5=0,"Non",Palmon!AJ5)</f>
+        <v>Non</v>
       </c>
       <c r="AJ4">
         <f>Palmon!AK5</f>
@@ -11658,12 +11651,12 @@
         <v>0</v>
       </c>
       <c r="AH5" t="str">
-        <f>Palmon!AI6</f>
+        <f>IF(Palmon!AI6=0,"Non",Palmon!AI6)</f>
         <v>Chefeuillier</v>
       </c>
-      <c r="AI5">
-        <f>Palmon!AJ6</f>
-        <v>0</v>
+      <c r="AI5" t="str">
+        <f>IF(Palmon!AJ6=0,"Non",Palmon!AJ6)</f>
+        <v>Non</v>
       </c>
       <c r="AJ5">
         <f>Palmon!AK6</f>
@@ -11804,12 +11797,12 @@
         <v>0</v>
       </c>
       <c r="AH6" t="str">
-        <f>Palmon!AI7</f>
+        <f>IF(Palmon!AI7=0,"Non",Palmon!AI7)</f>
         <v>Gnashfin</v>
       </c>
-      <c r="AI6">
-        <f>Palmon!AJ7</f>
-        <v>0</v>
+      <c r="AI6" t="str">
+        <f>IF(Palmon!AJ7=0,"Non",Palmon!AJ7)</f>
+        <v>Non</v>
       </c>
       <c r="AJ6">
         <f>Palmon!AK7</f>
@@ -11950,12 +11943,12 @@
         <v>0</v>
       </c>
       <c r="AH7" t="str">
-        <f>Palmon!AI8</f>
+        <f>IF(Palmon!AI8=0,"Non",Palmon!AI8)</f>
         <v>Obsidrake</v>
       </c>
-      <c r="AI7">
-        <f>Palmon!AJ8</f>
-        <v>0</v>
+      <c r="AI7" t="str">
+        <f>IF(Palmon!AJ8=0,"Non",Palmon!AJ8)</f>
+        <v>Non</v>
       </c>
       <c r="AJ7">
         <f>Palmon!AK8</f>
@@ -12096,12 +12089,12 @@
         <v>0</v>
       </c>
       <c r="AH8" t="str">
-        <f>Palmon!AI9</f>
+        <f>IF(Palmon!AI9=0,"Non",Palmon!AI9)</f>
         <v>Bunodroid</v>
       </c>
-      <c r="AI8">
-        <f>Palmon!AJ9</f>
-        <v>0</v>
+      <c r="AI8" t="str">
+        <f>IF(Palmon!AJ9=0,"Non",Palmon!AJ9)</f>
+        <v>Non</v>
       </c>
       <c r="AJ8">
         <f>Palmon!AK9</f>
@@ -12242,12 +12235,12 @@
         <v>0</v>
       </c>
       <c r="AH9" t="str">
-        <f>Palmon!AI10</f>
+        <f>IF(Palmon!AI10=0,"Non",Palmon!AI10)</f>
         <v>Wattweiler</v>
       </c>
-      <c r="AI9">
-        <f>Palmon!AJ10</f>
-        <v>0</v>
+      <c r="AI9" t="str">
+        <f>IF(Palmon!AJ10=0,"Non",Palmon!AJ10)</f>
+        <v>Non</v>
       </c>
       <c r="AJ9">
         <f>Palmon!AK10</f>
@@ -12388,12 +12381,12 @@
         <v>0</v>
       </c>
       <c r="AH10" t="str">
-        <f>Palmon!AI11</f>
+        <f>IF(Palmon!AI11=0,"Non",Palmon!AI11)</f>
         <v>Servolt</v>
       </c>
-      <c r="AI10">
-        <f>Palmon!AJ11</f>
-        <v>0</v>
+      <c r="AI10" t="str">
+        <f>IF(Palmon!AJ11=0,"Non",Palmon!AJ11)</f>
+        <v>Non</v>
       </c>
       <c r="AJ10">
         <f>Palmon!AK11</f>
@@ -12534,12 +12527,12 @@
         <v>0</v>
       </c>
       <c r="AH11" t="str">
-        <f>Palmon!AI12</f>
+        <f>IF(Palmon!AI12=0,"Non",Palmon!AI12)</f>
         <v>Essaucier</v>
       </c>
-      <c r="AI11">
-        <f>Palmon!AJ12</f>
-        <v>0</v>
+      <c r="AI11" t="str">
+        <f>IF(Palmon!AJ12=0,"Non",Palmon!AJ12)</f>
+        <v>Non</v>
       </c>
       <c r="AJ11">
         <f>Palmon!AK12</f>
@@ -12680,12 +12673,12 @@
         <v>0</v>
       </c>
       <c r="AH12" t="str">
-        <f>Palmon!AI13</f>
+        <f>IF(Palmon!AI13=0,"Non",Palmon!AI13)</f>
         <v>Oneirina</v>
       </c>
-      <c r="AI12">
-        <f>Palmon!AJ13</f>
-        <v>0</v>
+      <c r="AI12" t="str">
+        <f>IF(Palmon!AJ13=0,"Non",Palmon!AJ13)</f>
+        <v>Non</v>
       </c>
       <c r="AJ12">
         <f>Palmon!AK13</f>
@@ -12825,13 +12818,13 @@
         <f>Palmon!AH14</f>
         <v>0</v>
       </c>
-      <c r="AH13">
-        <f>Palmon!AI14</f>
-        <v>0</v>
-      </c>
-      <c r="AI13">
-        <f>Palmon!AJ14</f>
-        <v>0</v>
+      <c r="AH13" t="str">
+        <f>IF(Palmon!AI14=0,"Non",Palmon!AI14)</f>
+        <v>Non</v>
+      </c>
+      <c r="AI13" t="str">
+        <f>IF(Palmon!AJ14=0,"Non",Palmon!AJ14)</f>
+        <v>Non</v>
       </c>
       <c r="AJ13">
         <f>Palmon!AK14</f>
@@ -12972,12 +12965,12 @@
         <v>0</v>
       </c>
       <c r="AH14" t="str">
-        <f>Palmon!AI15</f>
+        <f>IF(Palmon!AI15=0,"Non",Palmon!AI15)</f>
         <v>Anubeast</v>
       </c>
-      <c r="AI14">
-        <f>Palmon!AJ15</f>
-        <v>0</v>
+      <c r="AI14" t="str">
+        <f>IF(Palmon!AJ15=0,"Non",Palmon!AJ15)</f>
+        <v>Non</v>
       </c>
       <c r="AJ14">
         <f>Palmon!AK15</f>
@@ -13118,12 +13111,12 @@
         <v>0</v>
       </c>
       <c r="AH15" t="str">
-        <f>Palmon!AI16</f>
+        <f>IF(Palmon!AI16=0,"Non",Palmon!AI16)</f>
         <v>Ampereina</v>
       </c>
-      <c r="AI15">
-        <f>Palmon!AJ16</f>
-        <v>0</v>
+      <c r="AI15" t="str">
+        <f>IF(Palmon!AJ16=0,"Non",Palmon!AJ16)</f>
+        <v>Non</v>
       </c>
       <c r="AJ15">
         <f>Palmon!AK16</f>
@@ -13264,12 +13257,12 @@
         <v>0</v>
       </c>
       <c r="AH16" t="str">
-        <f>Palmon!AI17</f>
+        <f>IF(Palmon!AI17=0,"Non",Palmon!AI17)</f>
         <v>Keraunosaur</v>
       </c>
-      <c r="AI16">
-        <f>Palmon!AJ17</f>
-        <v>0</v>
+      <c r="AI16" t="str">
+        <f>IF(Palmon!AJ17=0,"Non",Palmon!AJ17)</f>
+        <v>Non</v>
       </c>
       <c r="AJ16">
         <f>Palmon!AK17</f>
@@ -13410,12 +13403,12 @@
         <v>0</v>
       </c>
       <c r="AH17" t="str">
-        <f>Palmon!AI18</f>
+        <f>IF(Palmon!AI18=0,"Non",Palmon!AI18)</f>
         <v>Wildfuror</v>
       </c>
-      <c r="AI17">
-        <f>Palmon!AJ18</f>
-        <v>0</v>
+      <c r="AI17" t="str">
+        <f>IF(Palmon!AJ18=0,"Non",Palmon!AJ18)</f>
+        <v>Non</v>
       </c>
       <c r="AJ17">
         <f>Palmon!AK18</f>
@@ -13556,12 +13549,12 @@
         <v>0</v>
       </c>
       <c r="AH18" t="str">
-        <f>Palmon!AI19</f>
+        <f>IF(Palmon!AI19=0,"Non",Palmon!AI19)</f>
         <v>Azurostrigoi</v>
       </c>
-      <c r="AI18">
-        <f>Palmon!AJ19</f>
-        <v>0</v>
+      <c r="AI18" t="str">
+        <f>IF(Palmon!AJ19=0,"Non",Palmon!AJ19)</f>
+        <v>Non</v>
       </c>
       <c r="AJ18">
         <f>Palmon!AK19</f>
@@ -13702,12 +13695,12 @@
         <v>0</v>
       </c>
       <c r="AH19" t="str">
-        <f>Palmon!AI20</f>
+        <f>IF(Palmon!AI20=0,"Non",Palmon!AI20)</f>
         <v>Finnabelle</v>
       </c>
-      <c r="AI19">
-        <f>Palmon!AJ20</f>
-        <v>0</v>
+      <c r="AI19" t="str">
+        <f>IF(Palmon!AJ20=0,"Non",Palmon!AJ20)</f>
+        <v>Non</v>
       </c>
       <c r="AJ19">
         <f>Palmon!AK20</f>
@@ -13848,12 +13841,12 @@
         <v>0</v>
       </c>
       <c r="AH20" t="str">
-        <f>Palmon!AI21</f>
+        <f>IF(Palmon!AI21=0,"Non",Palmon!AI21)</f>
         <v>Adolphonis</v>
       </c>
-      <c r="AI20">
-        <f>Palmon!AJ21</f>
-        <v>0</v>
+      <c r="AI20" t="str">
+        <f>IF(Palmon!AJ21=0,"Non",Palmon!AJ21)</f>
+        <v>Non</v>
       </c>
       <c r="AJ20">
         <f>Palmon!AK21</f>
@@ -13994,11 +13987,11 @@
         <v>0</v>
       </c>
       <c r="AH21" t="str">
-        <f>Palmon!AI22</f>
+        <f>IF(Palmon!AI22=0,"Non",Palmon!AI22)</f>
         <v>Bufonobi</v>
       </c>
       <c r="AI21" t="str">
-        <f>Palmon!AJ22</f>
+        <f>IF(Palmon!AJ22=0,"Non",Palmon!AJ22)</f>
         <v>Shadowkaeru</v>
       </c>
       <c r="AJ21">
@@ -14140,12 +14133,12 @@
         <v>0</v>
       </c>
       <c r="AH22" t="str">
-        <f>Palmon!AI23</f>
+        <f>IF(Palmon!AI23=0,"Non",Palmon!AI23)</f>
         <v>Camouflynx</v>
       </c>
-      <c r="AI22">
-        <f>Palmon!AJ23</f>
-        <v>0</v>
+      <c r="AI22" t="str">
+        <f>IF(Palmon!AJ23=0,"Non",Palmon!AJ23)</f>
+        <v>Non</v>
       </c>
       <c r="AJ22">
         <f>Palmon!AK23</f>
@@ -14286,12 +14279,12 @@
         <v>0</v>
       </c>
       <c r="AH23" t="str">
-        <f>Palmon!AI24</f>
+        <f>IF(Palmon!AI24=0,"Non",Palmon!AI24)</f>
         <v>Silvaurus</v>
       </c>
-      <c r="AI23">
-        <f>Palmon!AJ24</f>
-        <v>0</v>
+      <c r="AI23" t="str">
+        <f>IF(Palmon!AJ24=0,"Non",Palmon!AJ24)</f>
+        <v>Non</v>
       </c>
       <c r="AJ23">
         <f>Palmon!AK24</f>
@@ -14432,12 +14425,12 @@
         <v>0</v>
       </c>
       <c r="AH24" t="str">
-        <f>Palmon!AI25</f>
+        <f>IF(Palmon!AI25=0,"Non",Palmon!AI25)</f>
         <v>Lionarch</v>
       </c>
-      <c r="AI24">
-        <f>Palmon!AJ25</f>
-        <v>0</v>
+      <c r="AI24" t="str">
+        <f>IF(Palmon!AJ25=0,"Non",Palmon!AJ25)</f>
+        <v>Non</v>
       </c>
       <c r="AJ24">
         <f>Palmon!AK25</f>
@@ -14578,12 +14571,12 @@
         <v>0</v>
       </c>
       <c r="AH25" t="str">
-        <f>Palmon!AI26</f>
+        <f>IF(Palmon!AI26=0,"Non",Palmon!AI26)</f>
         <v>Sorceray</v>
       </c>
-      <c r="AI25">
-        <f>Palmon!AJ26</f>
-        <v>0</v>
+      <c r="AI25" t="str">
+        <f>IF(Palmon!AJ26=0,"Non",Palmon!AJ26)</f>
+        <v>Non</v>
       </c>
       <c r="AJ25">
         <f>Palmon!AK26</f>
@@ -14723,13 +14716,13 @@
         <f>Palmon!AH27</f>
         <v>0</v>
       </c>
-      <c r="AH26">
-        <f>Palmon!AI27</f>
-        <v>0</v>
-      </c>
-      <c r="AI26">
-        <f>Palmon!AJ27</f>
-        <v>0</v>
+      <c r="AH26" t="str">
+        <f>IF(Palmon!AI27=0,"Non",Palmon!AI27)</f>
+        <v>Non</v>
+      </c>
+      <c r="AI26" t="str">
+        <f>IF(Palmon!AJ27=0,"Non",Palmon!AJ27)</f>
+        <v>Non</v>
       </c>
       <c r="AJ26">
         <f>Palmon!AK27</f>
@@ -14869,13 +14862,13 @@
         <f>Palmon!AH28</f>
         <v>0</v>
       </c>
-      <c r="AH27">
-        <f>Palmon!AI28</f>
-        <v>0</v>
-      </c>
-      <c r="AI27">
-        <f>Palmon!AJ28</f>
-        <v>0</v>
+      <c r="AH27" t="str">
+        <f>IF(Palmon!AI28=0,"Non",Palmon!AI28)</f>
+        <v>Non</v>
+      </c>
+      <c r="AI27" t="str">
+        <f>IF(Palmon!AJ28=0,"Non",Palmon!AJ28)</f>
+        <v>Non</v>
       </c>
       <c r="AJ27">
         <f>Palmon!AK28</f>
@@ -15015,13 +15008,13 @@
         <f>Palmon!AH29</f>
         <v>0</v>
       </c>
-      <c r="AH28">
-        <f>Palmon!AI29</f>
-        <v>0</v>
-      </c>
-      <c r="AI28">
-        <f>Palmon!AJ29</f>
-        <v>0</v>
+      <c r="AH28" t="str">
+        <f>IF(Palmon!AI29=0,"Non",Palmon!AI29)</f>
+        <v>Non</v>
+      </c>
+      <c r="AI28" t="str">
+        <f>IF(Palmon!AJ29=0,"Non",Palmon!AJ29)</f>
+        <v>Non</v>
       </c>
       <c r="AJ28">
         <f>Palmon!AK29</f>
@@ -15162,12 +15155,12 @@
         <v>0</v>
       </c>
       <c r="AH29" t="str">
-        <f>Palmon!AI30</f>
+        <f>IF(Palmon!AI30=0,"Non",Palmon!AI30)</f>
         <v>Rumbkey</v>
       </c>
-      <c r="AI29">
-        <f>Palmon!AJ30</f>
-        <v>0</v>
+      <c r="AI29" t="str">
+        <f>IF(Palmon!AJ30=0,"Non",Palmon!AJ30)</f>
+        <v>Non</v>
       </c>
       <c r="AJ29">
         <f>Palmon!AK30</f>
@@ -15308,12 +15301,12 @@
         <v>0</v>
       </c>
       <c r="AH30" t="str">
-        <f>Palmon!AI31</f>
+        <f>IF(Palmon!AI31=0,"Non",Palmon!AI31)</f>
         <v>Embergeist</v>
       </c>
-      <c r="AI30">
-        <f>Palmon!AJ31</f>
-        <v>0</v>
+      <c r="AI30" t="str">
+        <f>IF(Palmon!AJ31=0,"Non",Palmon!AJ31)</f>
+        <v>Non</v>
       </c>
       <c r="AJ30">
         <f>Palmon!AK31</f>
@@ -15454,12 +15447,12 @@
         <v>0</v>
       </c>
       <c r="AH31" t="str">
-        <f>Palmon!AI32</f>
+        <f>IF(Palmon!AI32=0,"Non",Palmon!AI32)</f>
         <v>Thundermane</v>
       </c>
-      <c r="AI31">
-        <f>Palmon!AJ32</f>
-        <v>0</v>
+      <c r="AI31" t="str">
+        <f>IF(Palmon!AJ32=0,"Non",Palmon!AJ32)</f>
+        <v>Non</v>
       </c>
       <c r="AJ31">
         <f>Palmon!AK32</f>
@@ -15600,12 +15593,12 @@
         <v>0</v>
       </c>
       <c r="AH32" t="str">
-        <f>Palmon!AI33</f>
+        <f>IF(Palmon!AI33=0,"Non",Palmon!AI33)</f>
         <v>Prismalith</v>
       </c>
-      <c r="AI32">
-        <f>Palmon!AJ33</f>
-        <v>0</v>
+      <c r="AI32" t="str">
+        <f>IF(Palmon!AJ33=0,"Non",Palmon!AJ33)</f>
+        <v>Non</v>
       </c>
       <c r="AJ32">
         <f>Palmon!AK33</f>
@@ -15746,12 +15739,12 @@
         <v>0</v>
       </c>
       <c r="AH33" t="str">
-        <f>Palmon!AI34</f>
+        <f>IF(Palmon!AI34=0,"Non",Palmon!AI34)</f>
         <v>Cryovern</v>
       </c>
-      <c r="AI33">
-        <f>Palmon!AJ34</f>
-        <v>0</v>
+      <c r="AI33" t="str">
+        <f>IF(Palmon!AJ34=0,"Non",Palmon!AJ34)</f>
+        <v>Non</v>
       </c>
       <c r="AJ33">
         <f>Palmon!AK34</f>
@@ -15891,13 +15884,13 @@
         <f>Palmon!AH35</f>
         <v>0</v>
       </c>
-      <c r="AH34">
-        <f>Palmon!AI35</f>
-        <v>0</v>
-      </c>
-      <c r="AI34">
-        <f>Palmon!AJ35</f>
-        <v>0</v>
+      <c r="AH34" t="str">
+        <f>IF(Palmon!AI35=0,"Non",Palmon!AI35)</f>
+        <v>Non</v>
+      </c>
+      <c r="AI34" t="str">
+        <f>IF(Palmon!AJ35=0,"Non",Palmon!AJ35)</f>
+        <v>Non</v>
       </c>
       <c r="AJ34">
         <f>Palmon!AK35</f>
@@ -16037,13 +16030,13 @@
         <f>Palmon!AH36</f>
         <v>0</v>
       </c>
-      <c r="AH35">
-        <f>Palmon!AI36</f>
-        <v>0</v>
-      </c>
-      <c r="AI35">
-        <f>Palmon!AJ36</f>
-        <v>0</v>
+      <c r="AH35" t="str">
+        <f>IF(Palmon!AI36=0,"Non",Palmon!AI36)</f>
+        <v>Non</v>
+      </c>
+      <c r="AI35" t="str">
+        <f>IF(Palmon!AJ36=0,"Non",Palmon!AJ36)</f>
+        <v>Non</v>
       </c>
       <c r="AJ35">
         <f>Palmon!AK36</f>
@@ -16184,12 +16177,12 @@
         <v>0</v>
       </c>
       <c r="AH36" t="str">
-        <f>Palmon!AI37</f>
+        <f>IF(Palmon!AI37=0,"Non",Palmon!AI37)</f>
         <v>Dreadmaw</v>
       </c>
-      <c r="AI36">
-        <f>Palmon!AJ37</f>
-        <v>0</v>
+      <c r="AI36" t="str">
+        <f>IF(Palmon!AJ37=0,"Non",Palmon!AJ37)</f>
+        <v>Non</v>
       </c>
       <c r="AJ36">
         <f>Palmon!AK37</f>
@@ -16330,12 +16323,12 @@
         <v>0</v>
       </c>
       <c r="AH37" t="str">
-        <f>Palmon!AI38</f>
+        <f>IF(Palmon!AI38=0,"Non",Palmon!AI38)</f>
         <v>Fleurizard</v>
       </c>
-      <c r="AI37">
-        <f>Palmon!AJ38</f>
-        <v>0</v>
+      <c r="AI37" t="str">
+        <f>IF(Palmon!AJ38=0,"Non",Palmon!AJ38)</f>
+        <v>Non</v>
       </c>
       <c r="AJ37">
         <f>Palmon!AK38</f>
@@ -16475,13 +16468,13 @@
         <f>Palmon!AH39</f>
         <v>0</v>
       </c>
-      <c r="AH38">
-        <f>Palmon!AI39</f>
-        <v>0</v>
-      </c>
-      <c r="AI38">
-        <f>Palmon!AJ39</f>
-        <v>0</v>
+      <c r="AH38" t="str">
+        <f>IF(Palmon!AI39=0,"Non",Palmon!AI39)</f>
+        <v>Non</v>
+      </c>
+      <c r="AI38" t="str">
+        <f>IF(Palmon!AJ39=0,"Non",Palmon!AJ39)</f>
+        <v>Non</v>
       </c>
       <c r="AJ38">
         <f>Palmon!AK39</f>
@@ -16621,13 +16614,13 @@
         <f>Palmon!AH40</f>
         <v>0</v>
       </c>
-      <c r="AH39">
-        <f>Palmon!AI40</f>
-        <v>0</v>
-      </c>
-      <c r="AI39">
-        <f>Palmon!AJ40</f>
-        <v>0</v>
+      <c r="AH39" t="str">
+        <f>IF(Palmon!AI40=0,"Non",Palmon!AI40)</f>
+        <v>Non</v>
+      </c>
+      <c r="AI39" t="str">
+        <f>IF(Palmon!AJ40=0,"Non",Palmon!AJ40)</f>
+        <v>Non</v>
       </c>
       <c r="AJ39">
         <f>Palmon!AK40</f>
@@ -16767,13 +16760,13 @@
         <f>Palmon!AH41</f>
         <v>0</v>
       </c>
-      <c r="AH40">
-        <f>Palmon!AI41</f>
-        <v>0</v>
-      </c>
-      <c r="AI40">
-        <f>Palmon!AJ41</f>
-        <v>0</v>
+      <c r="AH40" t="str">
+        <f>IF(Palmon!AI41=0,"Non",Palmon!AI41)</f>
+        <v>Non</v>
+      </c>
+      <c r="AI40" t="str">
+        <f>IF(Palmon!AJ41=0,"Non",Palmon!AJ41)</f>
+        <v>Non</v>
       </c>
       <c r="AJ40">
         <f>Palmon!AK41</f>
@@ -16913,13 +16906,13 @@
         <f>Palmon!AH42</f>
         <v>0</v>
       </c>
-      <c r="AH41">
-        <f>Palmon!AI42</f>
-        <v>0</v>
-      </c>
-      <c r="AI41">
-        <f>Palmon!AJ42</f>
-        <v>0</v>
+      <c r="AH41" t="str">
+        <f>IF(Palmon!AI42=0,"Non",Palmon!AI42)</f>
+        <v>Non</v>
+      </c>
+      <c r="AI41" t="str">
+        <f>IF(Palmon!AJ42=0,"Non",Palmon!AJ42)</f>
+        <v>Non</v>
       </c>
       <c r="AJ41">
         <f>Palmon!AK42</f>
@@ -17059,13 +17052,13 @@
         <f>Palmon!AH43</f>
         <v>0</v>
       </c>
-      <c r="AH42">
-        <f>Palmon!AI43</f>
-        <v>0</v>
-      </c>
-      <c r="AI42">
-        <f>Palmon!AJ43</f>
-        <v>0</v>
+      <c r="AH42" t="str">
+        <f>IF(Palmon!AI43=0,"Non",Palmon!AI43)</f>
+        <v>Non</v>
+      </c>
+      <c r="AI42" t="str">
+        <f>IF(Palmon!AJ43=0,"Non",Palmon!AJ43)</f>
+        <v>Non</v>
       </c>
       <c r="AJ42">
         <f>Palmon!AK43</f>
@@ -17205,13 +17198,13 @@
         <f>Palmon!AH44</f>
         <v>0</v>
       </c>
-      <c r="AH43">
-        <f>Palmon!AI44</f>
-        <v>0</v>
-      </c>
-      <c r="AI43">
-        <f>Palmon!AJ44</f>
-        <v>0</v>
+      <c r="AH43" t="str">
+        <f>IF(Palmon!AI44=0,"Non",Palmon!AI44)</f>
+        <v>Non</v>
+      </c>
+      <c r="AI43" t="str">
+        <f>IF(Palmon!AJ44=0,"Non",Palmon!AJ44)</f>
+        <v>Non</v>
       </c>
       <c r="AJ43">
         <f>Palmon!AK44</f>
@@ -17351,13 +17344,13 @@
         <f>Palmon!AH45</f>
         <v>0</v>
       </c>
-      <c r="AH44">
-        <f>Palmon!AI45</f>
-        <v>0</v>
-      </c>
-      <c r="AI44">
-        <f>Palmon!AJ45</f>
-        <v>0</v>
+      <c r="AH44" t="str">
+        <f>IF(Palmon!AI45=0,"Non",Palmon!AI45)</f>
+        <v>Non</v>
+      </c>
+      <c r="AI44" t="str">
+        <f>IF(Palmon!AJ45=0,"Non",Palmon!AJ45)</f>
+        <v>Non</v>
       </c>
       <c r="AJ44">
         <f>Palmon!AK45</f>
@@ -17498,12 +17491,12 @@
         <v>0</v>
       </c>
       <c r="AH45" t="str">
-        <f>Palmon!AI46</f>
+        <f>IF(Palmon!AI46=0,"Non",Palmon!AI46)</f>
         <v>Vulpyrean</v>
       </c>
       <c r="AI45" t="str">
-        <f>Palmon!AJ46</f>
-        <v>Camouflynx</v>
+        <f>IF(Palmon!AJ46=0,"Non",Palmon!AJ46)</f>
+        <v>Non</v>
       </c>
       <c r="AJ45">
         <f>Palmon!AK46</f>
@@ -19404,17 +19397,17 @@
     <row r="50" spans="7:20" x14ac:dyDescent="0.25">
       <c r="L50" s="1"/>
       <c r="M50" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="N50" s="1"/>
       <c r="O50" s="1"/>
       <c r="P50" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Q50" s="1"/>
       <c r="R50" s="1"/>
       <c r="S50" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="51" spans="7:20" s="1" customFormat="1" ht="12" x14ac:dyDescent="0.2">
@@ -22110,10 +22103,10 @@
         <v>102</v>
       </c>
       <c r="Z18" s="238" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AA18" s="238" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="19" spans="1:29" x14ac:dyDescent="0.2">
@@ -22269,10 +22262,10 @@
         <v>403200</v>
       </c>
       <c r="AB20" s="238" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AC20" s="238" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="21" spans="1:29" x14ac:dyDescent="0.2">
@@ -22948,13 +22941,13 @@
       </c>
       <c r="X30" s="236"/>
       <c r="Y30" s="236" t="s">
+        <v>199</v>
+      </c>
+      <c r="Z30" s="236" t="s">
         <v>200</v>
       </c>
-      <c r="Z30" s="236" t="s">
+      <c r="AA30" s="236" t="s">
         <v>201</v>
-      </c>
-      <c r="AA30" s="236" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="31" spans="1:29" x14ac:dyDescent="0.2">
@@ -23020,7 +23013,7 @@
         <v>Surveilynx</v>
       </c>
       <c r="X31" s="236" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Y31" s="236">
         <v>1</v>
@@ -32132,7 +32125,7 @@
         <v>113400000</v>
       </c>
       <c r="K269" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="270" spans="1:11" x14ac:dyDescent="0.2">
@@ -32167,7 +32160,7 @@
         <v>115800000</v>
       </c>
       <c r="K270" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="271" spans="1:11" x14ac:dyDescent="0.2">
@@ -33044,16 +33037,16 @@
   <sheetData>
     <row r="1" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="253" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B1" s="254"/>
       <c r="D1" s="292" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E1" s="293"/>
       <c r="F1" s="293"/>
       <c r="H1" s="292" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I1" s="293"/>
       <c r="J1" s="293"/>
@@ -33065,17 +33058,17 @@
       <c r="P1" s="293"/>
       <c r="Q1" s="293"/>
       <c r="Z1" s="253" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AA1" s="254"/>
       <c r="AC1" s="253" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AD1" s="254"/>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="240" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B2" s="60">
         <v>400000</v>
@@ -33087,7 +33080,7 @@
         <v>20</v>
       </c>
       <c r="F2" s="222" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H2" s="223" t="s">
         <v>78</v>
@@ -33102,46 +33095,46 @@
         <v>17</v>
       </c>
       <c r="L2" s="222" t="s">
+        <v>241</v>
+      </c>
+      <c r="M2" s="222" t="s">
         <v>242</v>
       </c>
-      <c r="M2" s="222" t="s">
+      <c r="N2" s="222" t="s">
         <v>243</v>
       </c>
-      <c r="N2" s="222" t="s">
+      <c r="O2" s="222" t="s">
         <v>244</v>
       </c>
-      <c r="O2" s="222" t="s">
+      <c r="P2" s="222" t="s">
         <v>245</v>
-      </c>
-      <c r="P2" s="222" t="s">
-        <v>246</v>
       </c>
       <c r="Q2" s="222" t="s">
         <v>144</v>
       </c>
       <c r="S2" s="223" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="T2" s="222" t="s">
+        <v>241</v>
+      </c>
+      <c r="U2" s="222" t="s">
         <v>242</v>
       </c>
-      <c r="U2" s="222" t="s">
+      <c r="V2" s="222" t="s">
         <v>243</v>
       </c>
-      <c r="V2" s="222" t="s">
+      <c r="W2" s="222" t="s">
         <v>244</v>
       </c>
-      <c r="W2" s="222" t="s">
+      <c r="X2" s="222" t="s">
         <v>245</v>
-      </c>
-      <c r="X2" s="222" t="s">
-        <v>246</v>
       </c>
       <c r="Z2" s="223" t="s">
         <v>79</v>
       </c>
       <c r="AA2" s="222" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AC2" s="223" t="s">
         <v>79</v>
@@ -33152,7 +33145,7 @@
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="204" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B3" s="13">
         <v>300</v>
@@ -33168,10 +33161,10 @@
         <v>1000</v>
       </c>
       <c r="H3" s="245" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="I3" s="248" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="J3" s="4">
         <v>1</v>
@@ -33195,7 +33188,7 @@
         <v>0</v>
       </c>
       <c r="Q3" s="237" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="S3" s="225">
         <v>1</v>
@@ -33218,7 +33211,7 @@
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="204" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B4" s="13">
         <v>975</v>
@@ -33234,7 +33227,7 @@
         <v>2000</v>
       </c>
       <c r="H4" s="245" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I4" s="248" t="s">
         <v>50</v>
@@ -33261,7 +33254,7 @@
         <v>0</v>
       </c>
       <c r="Q4" s="237" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="S4" s="225">
         <v>2</v>
@@ -33284,7 +33277,7 @@
     </row>
     <row r="5" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="241" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B5" s="22">
         <v>9985660300</v>
@@ -33300,7 +33293,7 @@
         <v>4000</v>
       </c>
       <c r="H5" s="245" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I5" s="248" t="s">
         <v>61</v>
@@ -33327,7 +33320,7 @@
         <v>0</v>
       </c>
       <c r="Q5" s="237" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="S5" s="225">
         <v>3</v>
@@ -33360,7 +33353,7 @@
         <v>5000</v>
       </c>
       <c r="H6" s="245" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I6" s="248" t="s">
         <v>53</v>
@@ -33387,7 +33380,7 @@
         <v>0</v>
       </c>
       <c r="Q6" s="237" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="S6" s="225">
         <v>4</v>
@@ -33417,7 +33410,7 @@
         <v>6000</v>
       </c>
       <c r="H7" s="245" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I7" s="248" t="s">
         <v>55</v>
@@ -33444,7 +33437,7 @@
         <v>0</v>
       </c>
       <c r="Q7" s="237" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="S7" s="225">
         <v>5</v>
@@ -33661,7 +33654,7 @@
         <v>20</v>
       </c>
       <c r="C1" s="222" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -33726,7 +33719,7 @@
     </row>
     <row r="7" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="228" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B7" s="229"/>
       <c r="C7" s="229">
@@ -43453,13 +43446,13 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B1" s="244" t="s">
+        <v>232</v>
+      </c>
+      <c r="D1" s="244" t="s">
         <v>233</v>
       </c>
-      <c r="D1" s="244" t="s">
+      <c r="F1" s="244" t="s">
         <v>234</v>
-      </c>
-      <c r="F1" s="244" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -44463,7 +44456,7 @@
       </c>
       <c r="F43" t="str">
         <f>Palmon!B46 &amp; "," &amp; Palmon!C46 &amp; "," &amp; Palmon!D46 &amp; "," &amp; Palmon!E46 &amp; "," &amp; Palmon!G46 &amp; "," &amp; SUBSTITUTE(Palmon!H46,",",".") &amp; "," &amp; Palmon!I46 &amp; "," &amp; SUBSTITUTE(Palmon!P46,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q46,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R46,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S46,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T46,",",".") &amp; "," &amp; Palmon!J46 &amp; "," &amp; Palmon!K46 &amp; "," &amp; Palmon!L46 &amp; "," &amp; Palmon!M46 &amp; "," &amp; Palmon!N46 &amp; "," &amp; SUBSTITUTE(Palmon!U46,",",".") &amp; "," &amp; Palmon!V46 &amp; "," &amp; Palmon!X46 &amp; "," &amp; Palmon!Y46 &amp; "," &amp; Palmon!AA46 &amp; "," &amp; Palmon!AB46 &amp; "," &amp; Palmon!AC46 &amp; "," &amp; Palmon!AE46 &amp; "," &amp; Palmon!AF46 &amp; "," &amp; Palmon!AI46 &amp; "," &amp; Palmon!AJ46</f>
-        <v>Revontulet,Fire,Attack,160,2,2.3,0,1,1,0.6,0,0,1,1,1,,,0.138461538461538,840,4919220000,1,2460,21,,, ,Vulpyrean,Camouflynx</v>
+        <v>Revontulet,Fire,Attack,160,2,2.3,0,1,1,0.6,0,0,1,1,1,,,0.138461538461538,840,4919220000,1,2460,21,,, ,Vulpyrean,</v>
       </c>
     </row>
     <row r="44" spans="3:6" x14ac:dyDescent="0.25">

--- a/data/PS - Estimation (version 1).xlsx
+++ b/data/PS - Estimation (version 1).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xvjm020\Documents\Personnel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96F11454-2024-4F51-A845-290D98F2F678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{081AFD2A-6DAF-4D72-9D39-4455FDA3B8F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{9D83D047-1CAD-4BF9-942E-B289F790400E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9D83D047-1CAD-4BF9-942E-B289F790400E}"/>
   </bookViews>
   <sheets>
     <sheet name="Palmon" sheetId="2" r:id="rId1"/>
@@ -4359,8 +4359,8 @@
           <xdr:rowOff>114300</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>31</xdr:col>
-          <xdr:colOff>476250</xdr:colOff>
+          <xdr:col>10</xdr:col>
+          <xdr:colOff>323850</xdr:colOff>
           <xdr:row>148</xdr:row>
           <xdr:rowOff>9525</xdr:rowOff>
         </xdr:to>
@@ -5043,9 +5043,9 @@
     <col min="1" max="1" width="2.85546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.42578125" style="1" customWidth="1"/>
-    <col min="4" max="6" width="11.42578125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="7" max="14" width="6.28515625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="15" max="15" width="1.28515625" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="6" width="11.42578125" style="1" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="14" width="6.28515625" style="1" customWidth="1" outlineLevel="1"/>
+    <col min="15" max="15" width="1.28515625" style="1" customWidth="1"/>
     <col min="16" max="17" width="11.42578125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="18" max="18" width="8" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="19" max="20" width="5.7109375" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
@@ -5239,7 +5239,7 @@
         <v>20</v>
       </c>
       <c r="L3" s="7">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M3" s="7" t="str">
         <f t="shared" ref="M3:M26" si="1">IF($G3&gt;3,"Max","")</f>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="AB5" s="63">
         <f>RANK($AA5,$AA$3:$AA$46)+COUNTIF($AA$3:$AA5,AA5)-1</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC5" s="61" cm="1">
         <f t="array" ref="AC5">IFERROR(_xlfn.IFS($AB5&lt;8,1,$AB5&lt;15,2,$AB5&lt;21,3),"")</f>
@@ -5627,7 +5627,7 @@
       </c>
       <c r="AB6" s="63">
         <f>RANK($AA6,$AA$3:$AA$46)+COUNTIF($AA$3:$AA6,AA6)-1</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC6" s="61" cm="1">
         <f t="array" ref="AC6">IFERROR(_xlfn.IFS($AB6&lt;8,1,$AB6&lt;15,2,$AB6&lt;21,3),"")</f>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="AB8" s="63">
         <f>RANK($AA8,$AA$3:$AA$46)+COUNTIF($AA$3:$AA8,AA8)-1</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AC8" s="61" cm="1">
         <f t="array" ref="AC8">IFERROR(_xlfn.IFS($AB8&lt;8,1,$AB8&lt;15,2,$AB8&lt;21,3),"")</f>
@@ -5965,7 +5965,7 @@
       </c>
       <c r="AB9" s="63">
         <f>RANK($AA9,$AA$3:$AA$46)+COUNTIF($AA$3:$AA9,AA9)-1</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AC9" s="61" t="str" cm="1">
         <f t="array" ref="AC9">IFERROR(_xlfn.IFS($AB9&lt;8,1,$AB9&lt;15,2,$AB9&lt;21,3),"")</f>
@@ -6077,7 +6077,7 @@
       </c>
       <c r="AB10" s="63">
         <f>RANK($AA10,$AA$3:$AA$46)+COUNTIF($AA$3:$AA10,AA10)-1</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AC10" s="61" cm="1">
         <f t="array" ref="AC10">IFERROR(_xlfn.IFS($AB10&lt;8,1,$AB10&lt;15,2,$AB10&lt;21,3),"")</f>
@@ -6189,7 +6189,7 @@
       </c>
       <c r="AB11" s="63">
         <f>RANK($AA11,$AA$3:$AA$46)+COUNTIF($AA$3:$AA11,AA11)-1</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AC11" s="61" cm="1">
         <f t="array" ref="AC11">IFERROR(_xlfn.IFS($AB11&lt;8,1,$AB11&lt;15,2,$AB11&lt;21,3),"")</f>
@@ -6301,7 +6301,7 @@
       </c>
       <c r="AB12" s="63">
         <f>RANK($AA12,$AA$3:$AA$46)+COUNTIF($AA$3:$AA12,AA12)-1</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AC12" s="61" cm="1">
         <f t="array" ref="AC12">IFERROR(_xlfn.IFS($AB12&lt;8,1,$AB12&lt;15,2,$AB12&lt;21,3),"")</f>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="AB13" s="63">
         <f>RANK($AA13,$AA$3:$AA$46)+COUNTIF($AA$3:$AA13,AA13)-1</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AC13" s="61" cm="1">
         <f t="array" ref="AC13">IFERROR(_xlfn.IFS($AB13&lt;8,1,$AB13&lt;15,2,$AB13&lt;21,3),"")</f>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="AB15" s="63">
         <f>RANK($AA15,$AA$3:$AA$46)+COUNTIF($AA$3:$AA15,AA15)-1</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AC15" s="61" t="str" cm="1">
         <f t="array" ref="AC15">IFERROR(_xlfn.IFS($AB15&lt;8,1,$AB15&lt;15,2,$AB15&lt;21,3),"")</f>
@@ -6751,7 +6751,7 @@
       </c>
       <c r="AB16" s="63">
         <f>RANK($AA16,$AA$3:$AA$46)+COUNTIF($AA$3:$AA16,AA16)-1</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AC16" s="61" cm="1">
         <f t="array" ref="AC16">IFERROR(_xlfn.IFS($AB16&lt;8,1,$AB16&lt;15,2,$AB16&lt;21,3),"")</f>
@@ -6863,7 +6863,7 @@
       </c>
       <c r="AB17" s="63">
         <f>RANK($AA17,$AA$3:$AA$46)+COUNTIF($AA$3:$AA17,AA17)-1</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AC17" s="61" t="str" cm="1">
         <f t="array" ref="AC17">IFERROR(_xlfn.IFS($AB17&lt;8,1,$AB17&lt;15,2,$AB17&lt;21,3),"")</f>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="AB18" s="63">
         <f>RANK($AA18,$AA$3:$AA$46)+COUNTIF($AA$3:$AA18,AA18)-1</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AC18" s="61" cm="1">
         <f t="array" ref="AC18">IFERROR(_xlfn.IFS($AB18&lt;8,1,$AB18&lt;15,2,$AB18&lt;21,3),"")</f>
@@ -7087,11 +7087,11 @@
       </c>
       <c r="AB19" s="63">
         <f>RANK($AA19,$AA$3:$AA$46)+COUNTIF($AA$3:$AA19,AA19)-1</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC19" s="61" cm="1">
         <f t="array" ref="AC19">IFERROR(_xlfn.IFS($AB19&lt;8,1,$AB19&lt;15,2,$AB19&lt;21,3),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD19" s="1"/>
       <c r="AE19" s="121" t="s">
@@ -7207,7 +7207,7 @@
       </c>
       <c r="AB20" s="63">
         <f>RANK($AA20,$AA$3:$AA$46)+COUNTIF($AA$3:$AA20,AA20)-1</f>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AC20" s="61" t="str" cm="1">
         <f t="array" ref="AC20">IFERROR(_xlfn.IFS($AB20&lt;8,1,$AB20&lt;15,2,$AB20&lt;21,3),"")</f>
@@ -7319,7 +7319,7 @@
       </c>
       <c r="AB21" s="63">
         <f>RANK($AA21,$AA$3:$AA$46)+COUNTIF($AA$3:$AA21,AA21)-1</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AC21" s="61" t="str" cm="1">
         <f t="array" ref="AC21">IFERROR(_xlfn.IFS($AB21&lt;8,1,$AB21&lt;15,2,$AB21&lt;21,3),"")</f>
@@ -7431,11 +7431,11 @@
       </c>
       <c r="AB22" s="63">
         <f>RANK($AA22,$AA$3:$AA$46)+COUNTIF($AA$3:$AA22,AA22)-1</f>
-        <v>20</v>
-      </c>
-      <c r="AC22" s="61" cm="1">
+        <v>21</v>
+      </c>
+      <c r="AC22" s="61" t="str" cm="1">
         <f t="array" ref="AC22">IFERROR(_xlfn.IFS($AB22&lt;8,1,$AB22&lt;15,2,$AB22&lt;21,3),"")</f>
-        <v>3</v>
+        <v/>
       </c>
       <c r="AE22" s="63" t="s">
         <v>152</v>
@@ -7545,7 +7545,7 @@
       </c>
       <c r="AB23" s="63">
         <f>RANK($AA23,$AA$3:$AA$46)+COUNTIF($AA$3:$AA23,AA23)-1</f>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AC23" s="61" t="str" cm="1">
         <f t="array" ref="AC23">IFERROR(_xlfn.IFS($AB23&lt;8,1,$AB23&lt;15,2,$AB23&lt;21,3),"")</f>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="AB24" s="63">
         <f>RANK($AA24,$AA$3:$AA$46)+COUNTIF($AA$3:$AA24,AA24)-1</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="AC24" s="61" t="str" cm="1">
         <f t="array" ref="AC24">IFERROR(_xlfn.IFS($AB24&lt;8,1,$AB24&lt;15,2,$AB24&lt;21,3),"")</f>
@@ -7703,10 +7703,10 @@
         <v>2</v>
       </c>
       <c r="H25" s="198">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="I25" s="123">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J25" s="63">
         <v>10</v>
@@ -7735,7 +7735,7 @@
       </c>
       <c r="R25" s="9">
         <f>IFERROR(CHOOSE(IF($H25&gt;=Details!$B$6,1,2),Details!$D$6,IF($H25&gt;Details!$B$6-1,IF($H25&lt;1,Details!$G$5,MOD($H25,Details!$B$6-1))*10*Details!$C$6,""))/Details!$D$6,0)</f>
-        <v>0</v>
+        <v>0.20000000000000018</v>
       </c>
       <c r="S25" s="9">
         <f>IFERROR(CHOOSE(IF($H25&gt;=Details!$B$7,1,2),Details!$D$7,IF($H25&gt;Details!$B$7-1,IF($H25&lt;1,Details!$G$5,MOD($H25,Details!$B$7-1))*10*Details!$C$7,""))/Details!$D$7,0)</f>
@@ -7747,11 +7747,11 @@
       </c>
       <c r="U25" s="9" cm="1">
         <f t="array" ref="U25">SUMPRODUCT(TRANSPOSE(Details!$D$4:$D$8),$P25:$T25)/Details!$D$9</f>
-        <v>7.6923076923076927E-2</v>
+        <v>9.7435897435897451E-2</v>
       </c>
       <c r="V25" s="13" cm="1">
         <f t="array" ref="V25">Details!$D$9-SUMPRODUCT(TRANSPOSE(Details!$D$4:$D$8),$P25:$T25)-$I25</f>
-        <v>900</v>
+        <v>869</v>
       </c>
       <c r="X25" s="13" cm="1">
         <f t="array" ref="X25">LevelUpgradeCost($E25)</f>
@@ -7763,11 +7763,11 @@
       </c>
       <c r="AA25" s="110">
         <f t="shared" si="5"/>
-        <v>2200</v>
+        <v>2300</v>
       </c>
       <c r="AB25" s="63">
         <f>RANK($AA25,$AA$3:$AA$46)+COUNTIF($AA$3:$AA25,AA25)-1</f>
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AC25" s="61" t="str" cm="1">
         <f t="array" ref="AC25">IFERROR(_xlfn.IFS($AB25&lt;8,1,$AB25&lt;15,2,$AB25&lt;21,3),"")</f>
@@ -7879,7 +7879,7 @@
       </c>
       <c r="AB26" s="63">
         <f>RANK($AA26,$AA$3:$AA$46)+COUNTIF($AA$3:$AA26,AA26)-1</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AC26" s="61" cm="1">
         <f t="array" ref="AC26">IFERROR(_xlfn.IFS($AB26&lt;8,1,$AB26&lt;15,2,$AB26&lt;21,3),"")</f>
@@ -8103,11 +8103,11 @@
       </c>
       <c r="AB28" s="63">
         <f>RANK($AA28,$AA$3:$AA$46)+COUNTIF($AA$3:$AA28,AA28)-1</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC28" s="61" cm="1">
         <f t="array" ref="AC28">IFERROR(_xlfn.IFS($AB28&lt;8,1,$AB28&lt;15,2,$AB28&lt;21,3),"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE28" s="63" t="s">
         <v>180</v>
@@ -8139,7 +8139,7 @@
         <v>98</v>
       </c>
       <c r="E29" s="63">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="F29" s="125" cm="1">
         <f t="array" ref="F29">IsUpgradable(E29)</f>
@@ -8147,13 +8147,13 @@
       </c>
       <c r="G29" s="127">
         <f t="shared" ref="G29" si="9">INT(H29)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H29" s="198">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="I29" s="123">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="J29" s="153">
         <v>1</v>
@@ -8166,7 +8166,7 @@
       </c>
       <c r="M29" s="7" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>Max</v>
       </c>
       <c r="N29" s="19" t="str">
         <f t="shared" si="8"/>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="S29" s="9">
         <f>IFERROR(CHOOSE(IF($H29&gt;=Details!$B$7,1,2),Details!$D$7,IF($H29&gt;Details!$B$7-1,IF($H29&lt;1,Details!$G$5,MOD($H29,Details!$B$7-1))*10*Details!$C$7,""))/Details!$D$7,0)</f>
-        <v>0.59999999999999964</v>
+        <v>1</v>
       </c>
       <c r="T29" s="9">
         <f>IFERROR(CHOOSE(IF($H29&gt;=Details!$B$8,1,2),Details!$D$8,IF($H29&gt;Details!$B$8-1,IF($H29&lt;1,Details!$G$5,MOD($H29,Details!$B$8-1))*10*Details!$C$8,""))/Details!$D$8,0)</f>
@@ -8194,15 +8194,15 @@
       </c>
       <c r="U29" s="9" cm="1">
         <f t="array" ref="U29">SUMPRODUCT(TRANSPOSE(Details!$D$4:$D$8),$P29:$T29)/Details!$D$9</f>
-        <v>0.36410256410256397</v>
+        <v>0.48717948717948717</v>
       </c>
       <c r="V29" s="13" cm="1">
         <f t="array" ref="V29">Details!$D$9-SUMPRODUCT(TRANSPOSE(Details!$D$4:$D$8),$P29:$T29)-$I29</f>
-        <v>575.00000000000011</v>
+        <v>470</v>
       </c>
       <c r="X29" s="13" cm="1">
         <f t="array" ref="X29">LevelUpgradeCost($E29)</f>
-        <v>4667020000</v>
+        <v>4605720000</v>
       </c>
       <c r="Y29" s="61">
         <f t="shared" ref="Y29" si="10">F29</f>
@@ -8210,11 +8210,11 @@
       </c>
       <c r="AA29" s="110">
         <f t="shared" si="5"/>
-        <v>3486</v>
+        <v>4190</v>
       </c>
       <c r="AB29" s="63">
         <f>RANK($AA29,$AA$3:$AA$46)+COUNTIF($AA$3:$AA29,AA29)-1</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AC29" s="61" cm="1">
         <f t="array" ref="AC29">IFERROR(_xlfn.IFS($AB29&lt;8,1,$AB29&lt;15,2,$AB29&lt;21,3),"")</f>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="AB30" s="153">
         <f>RANK($AA30,$AA$3:$AA$46)+COUNTIF($AA$3:$AA30,AA30)-1</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AC30" s="160" t="str" cm="1">
         <f t="array" ref="AC30">IFERROR(_xlfn.IFS($AB30&lt;8,1,$AB30&lt;15,2,$AB30&lt;21,3),"")</f>
@@ -8474,13 +8474,13 @@
       </c>
       <c r="G32" s="127">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H32" s="198">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I32" s="123">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="J32" s="63" cm="1">
         <f t="array" ref="J32:L32">IF(E32="","",_xlfn.MAKEARRAY(1,3,_xlfn.LAMBDA(_xlpm.row,_xlpm.col,1)))</f>
@@ -8494,39 +8494,39 @@
       </c>
       <c r="M32" s="7" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="N32" s="19" t="str">
+        <v>Max</v>
+      </c>
+      <c r="N32" s="19">
         <f t="shared" si="8"/>
-        <v/>
+        <v>10</v>
       </c>
       <c r="P32" s="9">
         <f>IFERROR(CHOOSE(IF($H32&gt;=Details!$B$4,1,2),Details!$D$4,IF($H32&gt;Details!$B$4-1,IF($H32&lt;1,$H32,MOD($H32,Details!$B$4-1))*10*Details!$C$4,""))/Details!$D$4,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q32" s="9">
         <f>IFERROR(CHOOSE(IF($H32&gt;=Details!$B$5,1,2),Details!$D$5,IF($H32&gt;Details!$B$5-1,IF($H32&lt;1,Details!$G$4,MOD($H32,Details!$B$5-1))*10*Details!$C$5,""))/Details!$D$5,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" s="9">
         <f>IFERROR(CHOOSE(IF($H32&gt;=Details!$B$6,1,2),Details!$D$6,IF($H32&gt;Details!$B$6-1,IF($H32&lt;1,Details!$G$5,MOD($H32,Details!$B$6-1))*10*Details!$C$6,""))/Details!$D$6,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" s="9">
         <f>IFERROR(CHOOSE(IF($H32&gt;=Details!$B$7,1,2),Details!$D$7,IF($H32&gt;Details!$B$7-1,IF($H32&lt;1,Details!$G$5,MOD($H32,Details!$B$7-1))*10*Details!$C$7,""))/Details!$D$7,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T32" s="9">
         <f>IFERROR(CHOOSE(IF($H32&gt;=Details!$B$8,1,2),Details!$D$8,IF($H32&gt;Details!$B$8-1,IF($H32&lt;1,Details!$G$5,MOD($H32,Details!$B$8-1))*10*Details!$C$8,""))/Details!$D$8,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U32" s="9" cm="1">
         <f t="array" ref="U32">SUMPRODUCT(TRANSPOSE(Details!$D$4:$D$8),$P32:$T32)/Details!$D$9</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V32" s="13" cm="1">
         <f t="array" ref="V32">Details!$D$9-SUMPRODUCT(TRANSPOSE(Details!$D$4:$D$8),$P32:$T32)-$I32</f>
-        <v>725</v>
+        <v>0</v>
       </c>
       <c r="X32" s="13" cm="1">
         <f t="array" ref="X32">LevelUpgradeCost($E32)</f>
@@ -8538,15 +8538,15 @@
       </c>
       <c r="AA32" s="110">
         <f t="shared" si="5"/>
-        <v>140</v>
+        <v>5140</v>
       </c>
       <c r="AB32" s="63">
         <f>RANK($AA32,$AA$3:$AA$46)+COUNTIF($AA$3:$AA32,AA32)-1</f>
-        <v>31</v>
-      </c>
-      <c r="AC32" s="61" t="str" cm="1">
+        <v>7</v>
+      </c>
+      <c r="AC32" s="61" cm="1">
         <f t="array" ref="AC32">IFERROR(_xlfn.IFS($AB32&lt;8,1,$AB32&lt;15,2,$AB32&lt;21,3),"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AE32" s="63" t="s">
         <v>165</v>
@@ -9972,7 +9972,7 @@
       </c>
       <c r="AB46" s="64">
         <f>RANK($AA46,$AA$3:$AA$46)+COUNTIF($AA$3:$AA46,AA46)-1</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AC46" s="62" t="str" cm="1">
         <f t="array" ref="AC46">IFERROR(_xlfn.IFS($AB46&lt;8,1,$AB46&lt;15,2,$AB46&lt;21,3),"")</f>
@@ -10147,7 +10147,7 @@
       <c r="I48" s="5"/>
       <c r="X48" s="5">
         <f>SUMPRODUCT(X3:X46,Y3:Y46)</f>
-        <v>91824673700</v>
+        <v>91763373700</v>
       </c>
     </row>
     <row r="49" spans="2:24" ht="12" customHeight="1" x14ac:dyDescent="0.2">
@@ -10282,7 +10282,7 @@
       </c>
       <c r="Q58" s="1">
         <f t="shared" ref="Q58:Q60" si="22">SUMIF($C$3:$C$46,"=" &amp; $P58,$E$3:$E$46)</f>
-        <v>2036</v>
+        <v>2040</v>
       </c>
       <c r="R58" s="1">
         <f t="shared" ref="R58:R60" si="23">COUNTIFS($C$3:$C$46,"=" &amp; $P58,$E$3:$E$46,"&gt;0")</f>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="S58" s="1">
         <f t="shared" ref="S58:S60" si="24">Q58/R58</f>
-        <v>226.22222222222223</v>
+        <v>226.66666666666666</v>
       </c>
       <c r="X58"/>
     </row>
@@ -10689,8 +10689,8 @@
                     <xdr:rowOff>114300</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>31</xdr:col>
-                    <xdr:colOff>476250</xdr:colOff>
+                    <xdr:col>10</xdr:col>
+                    <xdr:colOff>323850</xdr:colOff>
                     <xdr:row>148</xdr:row>
                     <xdr:rowOff>9525</xdr:rowOff>
                   </to>
@@ -10796,7 +10796,7 @@
     <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="str" cm="1">
         <f t="array" ref="A3">_xlfn.CONCAT(_xlfn.LAMBDA(_xlpm.cell,_xlpm.cell &amp; ",")(Palmon!B3:'Palmon'!AJ3))</f>
-        <v>Bufonobi,Water,Attack,270,,5,5,0,30,20,20,Max,10,,1,1,1,1,1,1,0,,135120000,,,5270,1,1,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRXczs_Bjhslhr7Mf2HENU6MTyGpz0RJEMjNA&amp;s, , ,,,Shadowkaeru,</v>
+        <v>Bufonobi,Water,Attack,270,,5,5,0,30,20,30,Max,10,,1,1,1,1,1,1,0,,135120000,,,5270,1,1,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRXczs_Bjhslhr7Mf2HENU6MTyGpz0RJEMjNA&amp;s, , ,,,Shadowkaeru,</v>
       </c>
     </row>
     <row r="4" spans="1:35" x14ac:dyDescent="0.25">
@@ -11122,7 +11122,7 @@
       </c>
       <c r="K2">
         <f>Palmon!L3</f>
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="L2" t="str">
         <f>Palmon!M3</f>
@@ -11478,7 +11478,7 @@
       </c>
       <c r="AA4">
         <f>Palmon!AB5</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB4">
         <f>Palmon!AC5</f>
@@ -11624,7 +11624,7 @@
       </c>
       <c r="AA5">
         <f>Palmon!AB6</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB5">
         <f>Palmon!AC6</f>
@@ -11916,7 +11916,7 @@
       </c>
       <c r="AA7">
         <f>Palmon!AB8</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AB7">
         <f>Palmon!AC8</f>
@@ -12062,7 +12062,7 @@
       </c>
       <c r="AA8">
         <f>Palmon!AB9</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB8" t="str">
         <f>Palmon!AC9</f>
@@ -12208,7 +12208,7 @@
       </c>
       <c r="AA9">
         <f>Palmon!AB10</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB9">
         <f>Palmon!AC10</f>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AA10">
         <f>Palmon!AB11</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AB10">
         <f>Palmon!AC11</f>
@@ -12500,7 +12500,7 @@
       </c>
       <c r="AA11">
         <f>Palmon!AB12</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AB11">
         <f>Palmon!AC12</f>
@@ -12646,7 +12646,7 @@
       </c>
       <c r="AA12">
         <f>Palmon!AB13</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB12">
         <f>Palmon!AC13</f>
@@ -12938,7 +12938,7 @@
       </c>
       <c r="AA14">
         <f>Palmon!AB15</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB14" t="str">
         <f>Palmon!AC15</f>
@@ -13084,7 +13084,7 @@
       </c>
       <c r="AA15">
         <f>Palmon!AB16</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AB15">
         <f>Palmon!AC16</f>
@@ -13230,7 +13230,7 @@
       </c>
       <c r="AA16">
         <f>Palmon!AB17</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AB16" t="str">
         <f>Palmon!AC17</f>
@@ -13376,7 +13376,7 @@
       </c>
       <c r="AA17">
         <f>Palmon!AB18</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB17">
         <f>Palmon!AC18</f>
@@ -13522,11 +13522,11 @@
       </c>
       <c r="AA18">
         <f>Palmon!AB19</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB18">
         <f>Palmon!AC19</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC18">
         <f>Palmon!AD19</f>
@@ -13668,7 +13668,7 @@
       </c>
       <c r="AA19">
         <f>Palmon!AB20</f>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AB19" t="str">
         <f>Palmon!AC20</f>
@@ -13814,7 +13814,7 @@
       </c>
       <c r="AA20">
         <f>Palmon!AB21</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AB20" t="str">
         <f>Palmon!AC21</f>
@@ -13960,11 +13960,11 @@
       </c>
       <c r="AA21">
         <f>Palmon!AB22</f>
-        <v>20</v>
-      </c>
-      <c r="AB21">
+        <v>21</v>
+      </c>
+      <c r="AB21" t="str">
         <f>Palmon!AC22</f>
-        <v>3</v>
+        <v/>
       </c>
       <c r="AC21">
         <f>Palmon!AD22</f>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="AA22">
         <f>Palmon!AB23</f>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AB22" t="str">
         <f>Palmon!AC23</f>
@@ -14252,7 +14252,7 @@
       </c>
       <c r="AA23">
         <f>Palmon!AB24</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="AB23" t="str">
         <f>Palmon!AC24</f>
@@ -14318,11 +14318,11 @@
       </c>
       <c r="G24">
         <f>Palmon!H25</f>
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="H24">
         <f>Palmon!I25</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I24">
         <f>Palmon!J25</f>
@@ -14358,7 +14358,7 @@
       </c>
       <c r="Q24">
         <f>Palmon!R25</f>
-        <v>0</v>
+        <v>0.20000000000000018</v>
       </c>
       <c r="R24">
         <f>Palmon!S25</f>
@@ -14370,11 +14370,11 @@
       </c>
       <c r="T24">
         <f>Palmon!U25</f>
-        <v>7.6923076923076927E-2</v>
+        <v>9.7435897435897451E-2</v>
       </c>
       <c r="U24">
         <f>Palmon!V25</f>
-        <v>900</v>
+        <v>869</v>
       </c>
       <c r="V24">
         <f>Palmon!W25</f>
@@ -14394,11 +14394,11 @@
       </c>
       <c r="Z24">
         <f>Palmon!AA25</f>
-        <v>2200</v>
+        <v>2300</v>
       </c>
       <c r="AA24">
         <f>Palmon!AB25</f>
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AB24" t="str">
         <f>Palmon!AC25</f>
@@ -14544,7 +14544,7 @@
       </c>
       <c r="AA25">
         <f>Palmon!AB26</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AB25">
         <f>Palmon!AC26</f>
@@ -14836,11 +14836,11 @@
       </c>
       <c r="AA27">
         <f>Palmon!AB28</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB27">
         <f>Palmon!AC28</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC27">
         <f>Palmon!AD28</f>
@@ -14890,7 +14890,7 @@
       </c>
       <c r="D28">
         <f>Palmon!E29</f>
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E28">
         <f>Palmon!F29</f>
@@ -14898,15 +14898,15 @@
       </c>
       <c r="F28">
         <f>Palmon!G29</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G28">
         <f>Palmon!H29</f>
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="H28">
         <f>Palmon!I29</f>
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I28">
         <f>Palmon!J29</f>
@@ -14922,7 +14922,7 @@
       </c>
       <c r="L28" t="str">
         <f>Palmon!M29</f>
-        <v/>
+        <v>Max</v>
       </c>
       <c r="M28" t="str">
         <f>Palmon!N29</f>
@@ -14946,7 +14946,7 @@
       </c>
       <c r="R28">
         <f>Palmon!S29</f>
-        <v>0.59999999999999964</v>
+        <v>1</v>
       </c>
       <c r="S28">
         <f>Palmon!T29</f>
@@ -14954,11 +14954,11 @@
       </c>
       <c r="T28">
         <f>Palmon!U29</f>
-        <v>0.36410256410256397</v>
+        <v>0.48717948717948717</v>
       </c>
       <c r="U28">
         <f>Palmon!V29</f>
-        <v>575.00000000000011</v>
+        <v>470</v>
       </c>
       <c r="V28">
         <f>Palmon!W29</f>
@@ -14966,7 +14966,7 @@
       </c>
       <c r="W28">
         <f>Palmon!X29</f>
-        <v>4667020000</v>
+        <v>4605720000</v>
       </c>
       <c r="X28">
         <f>Palmon!Y29</f>
@@ -14978,11 +14978,11 @@
       </c>
       <c r="Z28">
         <f>Palmon!AA29</f>
-        <v>3486</v>
+        <v>4190</v>
       </c>
       <c r="AA28">
         <f>Palmon!AB29</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AB28">
         <f>Palmon!AC29</f>
@@ -15128,7 +15128,7 @@
       </c>
       <c r="AA29">
         <f>Palmon!AB30</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AB29" t="str">
         <f>Palmon!AC30</f>
@@ -15336,15 +15336,15 @@
       </c>
       <c r="F31">
         <f>Palmon!G32</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G31">
         <f>Palmon!H32</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H31">
         <f>Palmon!I32</f>
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="I31">
         <f>Palmon!J32</f>
@@ -15360,11 +15360,11 @@
       </c>
       <c r="L31" t="str">
         <f>Palmon!M32</f>
-        <v/>
-      </c>
-      <c r="M31" t="str">
+        <v>Max</v>
+      </c>
+      <c r="M31">
         <f>Palmon!N32</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="N31">
         <f>Palmon!O32</f>
@@ -15372,31 +15372,31 @@
       </c>
       <c r="O31">
         <f>Palmon!P32</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P31">
         <f>Palmon!Q32</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q31">
         <f>Palmon!R32</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31">
         <f>Palmon!S32</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31">
         <f>Palmon!T32</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T31">
         <f>Palmon!U32</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U31">
         <f>Palmon!V32</f>
-        <v>725</v>
+        <v>0</v>
       </c>
       <c r="V31">
         <f>Palmon!W32</f>
@@ -15416,15 +15416,15 @@
       </c>
       <c r="Z31">
         <f>Palmon!AA32</f>
-        <v>140</v>
+        <v>5140</v>
       </c>
       <c r="AA31">
         <f>Palmon!AB32</f>
-        <v>31</v>
-      </c>
-      <c r="AB31" t="str">
+        <v>7</v>
+      </c>
+      <c r="AB31">
         <f>Palmon!AC32</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AC31">
         <f>Palmon!AD32</f>
@@ -17464,7 +17464,7 @@
       </c>
       <c r="AA45">
         <f>Palmon!AB46</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB45" t="str">
         <f>Palmon!AC46</f>
@@ -17544,7 +17544,7 @@
     </row>
     <row r="3" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="str" cm="1">
-        <f t="array" ref="B3:H35">_xlfn.PIVOTBY(Palmon!B2:D46,IFERROR(Palmon!G2:G46+1,"To Next Step"),_xlfn.LAMBDA(_xlpm.x,IFERROR(VLOOKUP(Palmon!G2:G46+1,StepNeeds,4,FALSE)-NeedsFull*_xlpm.x-Palmon!I2:I46,""))(Palmon!U2:U46),_xleta.MAX,3,0,,0,,Palmon!G2:G46&gt;0)</f>
+        <f t="array" ref="B3:H36">_xlfn.PIVOTBY(Palmon!B2:D46,IFERROR(Palmon!G2:G46+1,"To Next Step"),_xlfn.LAMBDA(_xlpm.x,IFERROR(VLOOKUP(Palmon!G2:G46+1,StepNeeds,4,FALSE)-NeedsFull*_xlpm.x-Palmon!I2:I46,""))(Palmon!U2:U46),_xleta.MAX,3,0,,0,,Palmon!G2:G46&gt;0)</f>
         <v/>
       </c>
       <c r="C3" s="1" t="str">
@@ -18168,7 +18168,7 @@
       </c>
       <c r="W16" s="40" cm="1">
         <f t="array" ref="W16">COUNTA(_xlfn._xlws.FILTER(C3:C42,C3:C42=$U16,""))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="2:23" x14ac:dyDescent="0.25">
@@ -18251,10 +18251,10 @@
         <v>Water</v>
       </c>
       <c r="M18" s="39">
-        <v>100</v>
-      </c>
-      <c r="N18" s="33">
-        <v>75.000000000000114</v>
+        <v>87</v>
+      </c>
+      <c r="N18" s="33" t="str">
+        <v/>
       </c>
       <c r="O18" s="33">
         <v>500</v>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="W20" s="196">
         <f>SUM(W16:W19)</f>
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -18390,11 +18390,11 @@
       <c r="E21" s="39" t="str">
         <v/>
       </c>
-      <c r="F21" s="33">
-        <v>75.000000000000114</v>
-      </c>
-      <c r="G21" s="33" t="str">
-        <v/>
+      <c r="F21" s="33" t="str">
+        <v/>
+      </c>
+      <c r="G21" s="33">
+        <v>470</v>
       </c>
       <c r="H21" s="33" t="str">
         <v/>
@@ -18700,11 +18700,11 @@
       <c r="M28" s="39">
         <v>4</v>
       </c>
-      <c r="N28" s="33">
-        <v>1</v>
+      <c r="N28" s="33" t="str">
+        <v/>
       </c>
       <c r="O28" s="33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P28" s="33">
         <v>2</v>
@@ -18726,7 +18726,7 @@
         <v>Defend</v>
       </c>
       <c r="E29" s="39">
-        <v>100</v>
+        <v>68.999999999999986</v>
       </c>
       <c r="F29" s="33" t="str">
         <v/>
@@ -18791,10 +18791,10 @@
         <v>12</v>
       </c>
       <c r="N30" s="86">
+        <v>5</v>
+      </c>
+      <c r="O30" s="86">
         <v>6</v>
-      </c>
-      <c r="O30" s="86">
-        <v>5</v>
       </c>
       <c r="P30" s="86">
         <v>5</v>
@@ -18969,10 +18969,10 @@
     </row>
     <row r="35" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B35" s="36" t="str">
-        <v>Vulpyrean</v>
+        <v>Thundertooth</v>
       </c>
       <c r="C35" s="32" t="str">
-        <v>Fire</v>
+        <v>Electricity</v>
       </c>
       <c r="D35" s="47" t="str">
         <v>Attack</v>
@@ -18995,13 +18995,13 @@
         <v>Fire</v>
       </c>
       <c r="M35" s="39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N35" s="33">
         <v>3</v>
       </c>
       <c r="O35" s="40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P35" s="1"/>
       <c r="Q35" s="217" t="str">
@@ -19015,13 +19015,27 @@
       </c>
     </row>
     <row r="36" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B36" s="36"/>
-      <c r="C36" s="32"/>
-      <c r="D36" s="47"/>
-      <c r="E36" s="39"/>
-      <c r="F36" s="33"/>
-      <c r="G36" s="33"/>
-      <c r="H36" s="33"/>
+      <c r="B36" s="36" t="str">
+        <v>Vulpyrean</v>
+      </c>
+      <c r="C36" s="32" t="str">
+        <v>Fire</v>
+      </c>
+      <c r="D36" s="47" t="str">
+        <v>Attack</v>
+      </c>
+      <c r="E36" s="39" t="str">
+        <v/>
+      </c>
+      <c r="F36" s="33" t="str">
+        <v/>
+      </c>
+      <c r="G36" s="33" t="str">
+        <v/>
+      </c>
+      <c r="H36" s="33">
+        <v>0</v>
+      </c>
       <c r="I36" s="33"/>
       <c r="J36" s="40"/>
       <c r="L36" s="46" t="str">
@@ -19033,8 +19047,8 @@
       <c r="N36" s="33">
         <v>2</v>
       </c>
-      <c r="O36" s="40">
-        <v>1</v>
+      <c r="O36" s="40" t="str">
+        <v/>
       </c>
       <c r="P36" s="1"/>
       <c r="Q36" s="217" t="str">
@@ -19094,7 +19108,7 @@
         <v>Total</v>
       </c>
       <c r="M38" s="85">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N38" s="86">
         <v>7</v>
@@ -19201,10 +19215,10 @@
         <v>Bufonobi</v>
       </c>
       <c r="M42" s="74" t="str">
-        <v>Ghillant</v>
+        <v>Pipistrigoi</v>
       </c>
       <c r="N42" s="75" t="str">
-        <v>Barkplug</v>
+        <v>Spookaboo</v>
       </c>
       <c r="O42" s="1"/>
       <c r="P42" s="1" t="str" cm="1">
@@ -19212,7 +19226,7 @@
         <v>Bufonobi</v>
       </c>
       <c r="Q42" s="1" t="str">
-        <v>Ghillant</v>
+        <v>Pipistrigoi</v>
       </c>
       <c r="R42" s="1"/>
       <c r="T42"/>
@@ -19234,17 +19248,17 @@
         <v>Vulpyrean</v>
       </c>
       <c r="M43" s="77" t="str">
-        <v>Hoofrit</v>
+        <v>Ghillant</v>
       </c>
       <c r="N43" s="78" t="str">
-        <v>Blazeal</v>
+        <v>Barkplug</v>
       </c>
       <c r="O43" s="1"/>
       <c r="P43" s="1" t="str">
         <v>Vulpyrean</v>
       </c>
       <c r="Q43" s="1" t="str">
-        <v>Hoofrit</v>
+        <v>Ghillant</v>
       </c>
       <c r="R43" s="1"/>
       <c r="T43"/>
@@ -19266,17 +19280,17 @@
         <v>Gnashley</v>
       </c>
       <c r="M44" s="77" t="str">
-        <v>Lucidina</v>
+        <v>Hoofrit</v>
       </c>
       <c r="N44" s="78" t="str">
-        <v>Battereina</v>
+        <v>Blazeal</v>
       </c>
       <c r="O44" s="1"/>
       <c r="P44" s="1" t="str">
         <v>Gnashley</v>
       </c>
       <c r="Q44" s="1" t="str">
-        <v>Lucidina</v>
+        <v>Hoofrit</v>
       </c>
       <c r="R44" s="1"/>
       <c r="T44"/>
@@ -19298,17 +19312,17 @@
         <v>Glacewing</v>
       </c>
       <c r="M45" s="77" t="str">
-        <v>Abuzzinian</v>
+        <v>Lucidina</v>
       </c>
       <c r="N45" s="78" t="str">
-        <v>Mantleray</v>
+        <v>Battereina</v>
       </c>
       <c r="O45" s="1"/>
       <c r="P45" s="1" t="str">
         <v>Glacewing</v>
       </c>
       <c r="Q45" s="1" t="str">
-        <v>Abuzzinian</v>
+        <v>Lucidina</v>
       </c>
       <c r="R45" s="1"/>
       <c r="T45"/>
@@ -19321,17 +19335,17 @@
         <v>Fleurizard</v>
       </c>
       <c r="M46" s="77" t="str">
-        <v>Kungpaw</v>
+        <v>Abuzzinian</v>
       </c>
       <c r="N46" s="78" t="str">
-        <v>Escarffier</v>
+        <v>Mantleray</v>
       </c>
       <c r="O46" s="1"/>
       <c r="P46" s="1" t="str">
         <v>Fleurizard</v>
       </c>
       <c r="Q46" s="1" t="str">
-        <v>Kungpaw</v>
+        <v>Abuzzinian</v>
       </c>
       <c r="R46" s="1"/>
       <c r="T46"/>
@@ -19344,17 +19358,17 @@
         <v>Oleana</v>
       </c>
       <c r="M47" s="77" t="str">
-        <v>Magmolin</v>
+        <v>Kungpaw</v>
       </c>
       <c r="N47" s="78" t="str">
-        <v>Ninjump</v>
+        <v>Escarffier</v>
       </c>
       <c r="O47" s="1"/>
       <c r="P47" s="1" t="str">
         <v>Oleana</v>
       </c>
       <c r="Q47" s="1" t="str">
-        <v>Magmolin</v>
+        <v>Kungpaw</v>
       </c>
       <c r="R47" s="1"/>
       <c r="T47"/>
@@ -19364,20 +19378,20 @@
     </row>
     <row r="48" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L48" s="81" t="str">
-        <v>Pipistrigoi</v>
+        <v>Thundertooth</v>
       </c>
       <c r="M48" s="82" t="str">
-        <v>Spookaboo</v>
+        <v>Magmolin</v>
       </c>
       <c r="N48" s="83" t="str">
-        <v>Revontulet</v>
+        <v>Ninjump</v>
       </c>
       <c r="O48" s="1"/>
       <c r="P48" s="1" t="str">
-        <v>Pipistrigoi</v>
+        <v>Thundertooth</v>
       </c>
       <c r="Q48" s="1" t="str">
-        <v>Spookaboo</v>
+        <v>Magmolin</v>
       </c>
       <c r="R48" s="1"/>
       <c r="T48"/>
@@ -19453,7 +19467,7 @@
         <v/>
       </c>
       <c r="N52" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P52" s="1" t="str" cm="1">
         <f t="array" ref="P52:P78">_xlfn.LAMBDA(_xlpm.row,IFERROR(_xlfn.RANK.EQ(_xlpm.row,M$52:M$78,1),""))(M$52:M$78)</f>
@@ -19483,7 +19497,7 @@
         <v>Baboom</v>
       </c>
       <c r="M53" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N53" s="1" t="str">
         <v/>
@@ -19515,7 +19529,7 @@
         <v/>
       </c>
       <c r="N54" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P54" s="1" t="str">
         <v/>
@@ -19541,7 +19555,7 @@
         <v>Battereina</v>
       </c>
       <c r="M55" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N55" s="1" t="str">
         <v/>
@@ -19570,7 +19584,7 @@
         <v>Blazeal</v>
       </c>
       <c r="M56" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N56" s="1" t="str">
         <v/>
@@ -19631,7 +19645,7 @@
         <v/>
       </c>
       <c r="N58" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P58" s="1" t="str">
         <v/>
@@ -19660,7 +19674,7 @@
         <v/>
       </c>
       <c r="N59" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P59" s="1" t="str">
         <v/>
@@ -19671,7 +19685,7 @@
     </row>
     <row r="60" spans="7:20" s="1" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="G60" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H60" s="1" t="str">
         <v/>
@@ -19680,7 +19694,7 @@
         <v>Fingenue</v>
       </c>
       <c r="M60" s="1">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="N60" s="1" t="str">
         <v/>
@@ -19729,7 +19743,7 @@
         <v/>
       </c>
       <c r="N62" s="1">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P62" s="1" t="str">
         <v/>
@@ -19752,7 +19766,7 @@
         <v/>
       </c>
       <c r="N63" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P63" s="1" t="str">
         <v/>
@@ -19795,7 +19809,7 @@
         <v>Hoofrit</v>
       </c>
       <c r="M65" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N65" s="1" t="str">
         <v/>
@@ -19821,7 +19835,7 @@
         <v/>
       </c>
       <c r="N66" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P66" s="1" t="str">
         <v/>
@@ -19841,7 +19855,7 @@
         <v>Limudroid</v>
       </c>
       <c r="M67" s="1">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N67" s="1" t="str">
         <v/>
@@ -19864,7 +19878,7 @@
         <v>Lucidina</v>
       </c>
       <c r="M68" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N68" s="1" t="str">
         <v/>
@@ -19890,7 +19904,7 @@
         <v/>
       </c>
       <c r="N69" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P69" s="1" t="str">
         <v/>
@@ -19910,7 +19924,7 @@
         <v>Mantleray</v>
       </c>
       <c r="M70" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N70" s="1" t="str">
         <v/>
@@ -19933,7 +19947,7 @@
         <v>Ninjump</v>
       </c>
       <c r="M71" s="1">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N71" s="1" t="str">
         <v/>
@@ -19979,7 +19993,7 @@
         <v>Pipistrigoi</v>
       </c>
       <c r="M73" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N73" s="1" t="str">
         <v/>
@@ -19996,7 +20010,7 @@
         <v/>
       </c>
       <c r="H74" s="1">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="L74" s="1" t="str">
         <v>Regalion</v>
@@ -20005,7 +20019,7 @@
         <v/>
       </c>
       <c r="N74" s="1">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="P74" s="1" t="str">
         <v/>
@@ -20016,7 +20030,7 @@
     </row>
     <row r="75" spans="7:20" s="1" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="G75" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H75" s="1" t="str">
         <v/>
@@ -20025,7 +20039,7 @@
         <v>Salamantis</v>
       </c>
       <c r="M75" s="1">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N75" s="1" t="str">
         <v/>
@@ -20048,7 +20062,7 @@
         <v>Spookaboo</v>
       </c>
       <c r="M76" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N76" s="1" t="str">
         <v/>
@@ -20074,7 +20088,7 @@
         <v/>
       </c>
       <c r="N77" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P77" s="1" t="str">
         <v/>
@@ -20085,7 +20099,7 @@
     </row>
     <row r="78" spans="7:20" s="1" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="G78" s="1">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H78" s="1" t="str">
         <v/>
@@ -20094,7 +20108,7 @@
         <v>Surveilynx</v>
       </c>
       <c r="M78" s="1">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="N78" s="1" t="str">
         <v/>
@@ -43504,7 +43518,7 @@
       </c>
       <c r="F3" t="str">
         <f>Palmon!B3 &amp; "," &amp; Palmon!C3 &amp; "," &amp; Palmon!D3 &amp; "," &amp; Palmon!E3 &amp; "," &amp; Palmon!G3 &amp; "," &amp; SUBSTITUTE(Palmon!H3,",",".") &amp; "," &amp; Palmon!I3 &amp; "," &amp; SUBSTITUTE(Palmon!P3,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q3,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R3,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S3,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T3,",",".") &amp; "," &amp; Palmon!J3 &amp; "," &amp; Palmon!K3 &amp; "," &amp; Palmon!L3 &amp; "," &amp; Palmon!M3 &amp; "," &amp; Palmon!N3 &amp; "," &amp; SUBSTITUTE(Palmon!U3,",",".") &amp; "," &amp; Palmon!V3 &amp; "," &amp; Palmon!X3 &amp; "," &amp; Palmon!Y3 &amp; "," &amp; Palmon!AA3 &amp; "," &amp; Palmon!AB3 &amp; "," &amp; Palmon!AC3 &amp; "," &amp; Palmon!AE3 &amp; "," &amp; Palmon!AF3 &amp; "," &amp; Palmon!AI3 &amp; "," &amp; Palmon!AJ3</f>
-        <v>Bufonobi,Water,Attack,270,5,5,0,1,1,1,1,1,30,20,20,Max,10,1,0,135120000,,5270,1,1,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRXczs_Bjhslhr7Mf2HENU6MTyGpz0RJEMjNA&amp;s, ,,Shadowkaeru</v>
+        <v>Bufonobi,Water,Attack,270,5,5,0,1,1,1,1,1,30,20,30,Max,10,1,0,135120000,,5270,1,1,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRXczs_Bjhslhr7Mf2HENU6MTyGpz0RJEMjNA&amp;s, ,,Shadowkaeru</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -43556,7 +43570,7 @@
       </c>
       <c r="F5" t="str">
         <f>Palmon!B5 &amp; "," &amp; Palmon!C5 &amp; "," &amp; Palmon!D5 &amp; "," &amp; Palmon!E5 &amp; "," &amp; Palmon!G5 &amp; "," &amp; SUBSTITUTE(Palmon!H5,",",".") &amp; "," &amp; Palmon!I5 &amp; "," &amp; SUBSTITUTE(Palmon!P5,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q5,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R5,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S5,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T5,",",".") &amp; "," &amp; Palmon!J5 &amp; "," &amp; Palmon!K5 &amp; "," &amp; Palmon!L5 &amp; "," &amp; Palmon!M5 &amp; "," &amp; Palmon!N5 &amp; "," &amp; SUBSTITUTE(Palmon!U5,",",".") &amp; "," &amp; Palmon!V5 &amp; "," &amp; Palmon!X5 &amp; "," &amp; Palmon!Y5 &amp; "," &amp; Palmon!AA5 &amp; "," &amp; Palmon!AB5 &amp; "," &amp; Palmon!AC5 &amp; "," &amp; Palmon!AE5 &amp; "," &amp; Palmon!AF5 &amp; "," &amp; Palmon!AI5 &amp; "," &amp; Palmon!AJ5</f>
-        <v>Hoofrit,Fire,Attack,270,4,4,11,1,1,1,1,0,15,15,15,Max,,0.487179487179487,489,135120000,,4270,9,2,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRwfHFWjB1bN67FJNyjjWvBJwviWJ3Tada0Yg&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSkOv6mOI5FaIAjcVgErYDwVaivkH3WdUQIzw&amp;s,Flaries,</v>
+        <v>Hoofrit,Fire,Attack,270,4,4,11,1,1,1,1,0,15,15,15,Max,,0.487179487179487,489,135120000,,4270,10,2,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRwfHFWjB1bN67FJNyjjWvBJwviWJ3Tada0Yg&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSkOv6mOI5FaIAjcVgErYDwVaivkH3WdUQIzw&amp;s,Flaries,</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -43582,7 +43596,7 @@
       </c>
       <c r="F6" t="str">
         <f>Palmon!B6 &amp; "," &amp; Palmon!C6 &amp; "," &amp; Palmon!D6 &amp; "," &amp; Palmon!E6 &amp; "," &amp; Palmon!G6 &amp; "," &amp; SUBSTITUTE(Palmon!H6,",",".") &amp; "," &amp; Palmon!I6 &amp; "," &amp; SUBSTITUTE(Palmon!P6,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q6,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R6,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S6,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T6,",",".") &amp; "," &amp; Palmon!J6 &amp; "," &amp; Palmon!K6 &amp; "," &amp; Palmon!L6 &amp; "," &amp; Palmon!M6 &amp; "," &amp; Palmon!N6 &amp; "," &amp; SUBSTITUTE(Palmon!U6,",",".") &amp; "," &amp; Palmon!V6 &amp; "," &amp; Palmon!X6 &amp; "," &amp; Palmon!Y6 &amp; "," &amp; Palmon!AA6 &amp; "," &amp; Palmon!AB6 &amp; "," &amp; Palmon!AC6 &amp; "," &amp; Palmon!AE6 &amp; "," &amp; Palmon!AF6 &amp; "," &amp; Palmon!AI6 &amp; "," &amp; Palmon!AJ6</f>
-        <v>Ghillant,Wood,Defend,250,4,4.1,0,1,1,1,1,0.199999999999999,5,5,5,Max,,0.589743589743589,400,2123020000,1,4350,8,2,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQOwDXppnwkCtCXXAqUiiNMhf6T-lane54jPg&amp;s, ,Chefeuillier,</v>
+        <v>Ghillant,Wood,Defend,250,4,4.1,0,1,1,1,1,0.199999999999999,5,5,5,Max,,0.589743589743589,400,2123020000,1,4350,9,2,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQOwDXppnwkCtCXXAqUiiNMhf6T-lane54jPg&amp;s, ,Chefeuillier,</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -43634,7 +43648,7 @@
       </c>
       <c r="F8" t="str">
         <f>Palmon!B8 &amp; "," &amp; Palmon!C8 &amp; "," &amp; Palmon!D8 &amp; "," &amp; Palmon!E8 &amp; "," &amp; Palmon!G8 &amp; "," &amp; SUBSTITUTE(Palmon!H8,",",".") &amp; "," &amp; Palmon!I8 &amp; "," &amp; SUBSTITUTE(Palmon!P8,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q8,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R8,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S8,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T8,",",".") &amp; "," &amp; Palmon!J8 &amp; "," &amp; Palmon!K8 &amp; "," &amp; Palmon!L8 &amp; "," &amp; Palmon!M8 &amp; "," &amp; Palmon!N8 &amp; "," &amp; SUBSTITUTE(Palmon!U8,",",".") &amp; "," &amp; Palmon!V8 &amp; "," &amp; Palmon!X8 &amp; "," &amp; Palmon!Y8 &amp; "," &amp; Palmon!AA8 &amp; "," &amp; Palmon!AB8 &amp; "," &amp; Palmon!AC8 &amp; "," &amp; Palmon!AE8 &amp; "," &amp; Palmon!AF8 &amp; "," &amp; Palmon!AI8 &amp; "," &amp; Palmon!AJ8</f>
-        <v>Magmolin,Fire,Defend,240,3,3.1,61,1,1,1,0.2,0,10,5,15,,,0.241025641025641,679,2831420000,1,3340,13,2,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRebc6KbOAxblleg_L3rr2K13bt-Yyzq1bAaw&amp;s, ,Obsidrake,</v>
+        <v>Magmolin,Fire,Defend,240,3,3.1,61,1,1,1,0.2,0,10,5,15,,,0.241025641025641,679,2831420000,1,3340,14,2,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRebc6KbOAxblleg_L3rr2K13bt-Yyzq1bAaw&amp;s, ,Obsidrake,</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -43660,7 +43674,7 @@
       </c>
       <c r="F9" t="str">
         <f>Palmon!B9 &amp; "," &amp; Palmon!C9 &amp; "," &amp; Palmon!D9 &amp; "," &amp; Palmon!E9 &amp; "," &amp; Palmon!G9 &amp; "," &amp; SUBSTITUTE(Palmon!H9,",",".") &amp; "," &amp; Palmon!I9 &amp; "," &amp; SUBSTITUTE(Palmon!P9,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q9,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R9,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S9,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T9,",",".") &amp; "," &amp; Palmon!J9 &amp; "," &amp; Palmon!K9 &amp; "," &amp; Palmon!L9 &amp; "," &amp; Palmon!M9 &amp; "," &amp; Palmon!N9 &amp; "," &amp; SUBSTITUTE(Palmon!U9,",",".") &amp; "," &amp; Palmon!V9 &amp; "," &amp; Palmon!X9 &amp; "," &amp; Palmon!Y9 &amp; "," &amp; Palmon!AA9 &amp; "," &amp; Palmon!AB9 &amp; "," &amp; Palmon!AC9 &amp; "," &amp; Palmon!AE9 &amp; "," &amp; Palmon!AF9 &amp; "," &amp; Palmon!AI9 &amp; "," &amp; Palmon!AJ9</f>
-        <v>Limudroid,Electricity,Attack,230,2,2.2,4,1,1,0.4,0,0,1,1,5,,,0.117948717948718,856,3390620000,1,2430,22,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQzaI21taP2V17MKjiPAeulm4V9qfST4umPdg&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRMlruQNUenhVk-fAEq9d3Wi8zw--0GbkLGJrX1CuQ1&amp;s,Bunodroid,</v>
+        <v>Limudroid,Electricity,Attack,230,2,2.2,4,1,1,0.4,0,0,1,1,5,,,0.117948717948718,856,3390620000,1,2430,23,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQzaI21taP2V17MKjiPAeulm4V9qfST4umPdg&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRMlruQNUenhVk-fAEq9d3Wi8zw--0GbkLGJrX1CuQ1&amp;s,Bunodroid,</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -43686,7 +43700,7 @@
       </c>
       <c r="F10" t="str">
         <f>Palmon!B10 &amp; "," &amp; Palmon!C10 &amp; "," &amp; Palmon!D10 &amp; "," &amp; Palmon!E10 &amp; "," &amp; Palmon!G10 &amp; "," &amp; SUBSTITUTE(Palmon!H10,",",".") &amp; "," &amp; Palmon!I10 &amp; "," &amp; SUBSTITUTE(Palmon!P10,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q10,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R10,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S10,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T10,",",".") &amp; "," &amp; Palmon!J10 &amp; "," &amp; Palmon!K10 &amp; "," &amp; Palmon!L10 &amp; "," &amp; Palmon!M10 &amp; "," &amp; Palmon!N10 &amp; "," &amp; SUBSTITUTE(Palmon!U10,",",".") &amp; "," &amp; Palmon!V10 &amp; "," &amp; Palmon!X10 &amp; "," &amp; Palmon!Y10 &amp; "," &amp; Palmon!AA10 &amp; "," &amp; Palmon!AB10 &amp; "," &amp; Palmon!AC10 &amp; "," &amp; Palmon!AE10 &amp; "," &amp; Palmon!AF10 &amp; "," &amp; Palmon!AI10 &amp; "," &amp; Palmon!AJ10</f>
-        <v>Barkplug,Electricity,Defend,250,3,3,0,1,1,1,0,0,14,5,10,,,0.179487179487179,800,2123020000,1,3250,15,3,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSf59xsunrPEuFvdtBi-IRVMcrdBfW_vNshLA&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRUDpuK5BvjXDFqgMZvlxYadsaFFQDKOQrNCAHymiAy_w&amp;s,Wattweiler,</v>
+        <v>Barkplug,Electricity,Defend,250,3,3,0,1,1,1,0,0,14,5,10,,,0.179487179487179,800,2123020000,1,3250,16,3,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSf59xsunrPEuFvdtBi-IRVMcrdBfW_vNshLA&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRUDpuK5BvjXDFqgMZvlxYadsaFFQDKOQrNCAHymiAy_w&amp;s,Wattweiler,</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -43712,7 +43726,7 @@
       </c>
       <c r="F11" t="str">
         <f>Palmon!B11 &amp; "," &amp; Palmon!C11 &amp; "," &amp; Palmon!D11 &amp; "," &amp; Palmon!E11 &amp; "," &amp; Palmon!G11 &amp; "," &amp; SUBSTITUTE(Palmon!H11,",",".") &amp; "," &amp; Palmon!I11 &amp; "," &amp; SUBSTITUTE(Palmon!P11,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q11,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R11,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S11,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T11,",",".") &amp; "," &amp; Palmon!J11 &amp; "," &amp; Palmon!K11 &amp; "," &amp; Palmon!L11 &amp; "," &amp; Palmon!M11 &amp; "," &amp; Palmon!N11 &amp; "," &amp; SUBSTITUTE(Palmon!U11,",",".") &amp; "," &amp; Palmon!V11 &amp; "," &amp; Palmon!X11 &amp; "," &amp; Palmon!Y11 &amp; "," &amp; Palmon!AA11 &amp; "," &amp; Palmon!AB11 &amp; "," &amp; Palmon!AC11 &amp; "," &amp; Palmon!AE11 &amp; "," &amp; Palmon!AF11 &amp; "," &amp; Palmon!AI11 &amp; "," &amp; Palmon!AJ11</f>
-        <v>Abuzzinian,Electricity,Defend,230,4,4,14,1,1,1,1,0,1,1,1,Max,,0.487179487179487,486,3390620000,1,4230,11,2,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcT-r6BZKxjf-kMlCmzHjhnUHjvmCaOn5DxiYw&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcR23XO-FCNYoHOIhLnxge8AzFmdP8mD1D-mzQ&amp;s,Servolt,</v>
+        <v>Abuzzinian,Electricity,Defend,230,4,4,14,1,1,1,1,0,1,1,1,Max,,0.487179487179487,486,3390620000,1,4230,12,2,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcT-r6BZKxjf-kMlCmzHjhnUHjvmCaOn5DxiYw&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcR23XO-FCNYoHOIhLnxge8AzFmdP8mD1D-mzQ&amp;s,Servolt,</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -43738,7 +43752,7 @@
       </c>
       <c r="F12" t="str">
         <f>Palmon!B12 &amp; "," &amp; Palmon!C12 &amp; "," &amp; Palmon!D12 &amp; "," &amp; Palmon!E12 &amp; "," &amp; Palmon!G12 &amp; "," &amp; SUBSTITUTE(Palmon!H12,",",".") &amp; "," &amp; Palmon!I12 &amp; "," &amp; SUBSTITUTE(Palmon!P12,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q12,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R12,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S12,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T12,",",".") &amp; "," &amp; Palmon!J12 &amp; "," &amp; Palmon!K12 &amp; "," &amp; Palmon!L12 &amp; "," &amp; Palmon!M12 &amp; "," &amp; Palmon!N12 &amp; "," &amp; SUBSTITUTE(Palmon!U12,",",".") &amp; "," &amp; Palmon!V12 &amp; "," &amp; Palmon!X12 &amp; "," &amp; Palmon!Y12 &amp; "," &amp; Palmon!AA12 &amp; "," &amp; Palmon!AB12 &amp; "," &amp; Palmon!AC12 &amp; "," &amp; Palmon!AE12 &amp; "," &amp; Palmon!AF12 &amp; "," &amp; Palmon!AI12 &amp; "," &amp; Palmon!AJ12</f>
-        <v>Escarffier,Fire,Defend,230,2,2.3,8,1,1,0.6,0,0,5,5,5,,,0.138461538461538,832,3390620000,1,2530,19,3,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcST2CrUIPAlFNBLPgZn0Tu93KelabHVVAbNLQ&amp;s, ,Essaucier,</v>
+        <v>Escarffier,Fire,Defend,230,2,2.3,8,1,1,0.6,0,0,5,5,5,,,0.138461538461538,832,3390620000,1,2530,20,3,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcST2CrUIPAlFNBLPgZn0Tu93KelabHVVAbNLQ&amp;s, ,Essaucier,</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -43764,7 +43778,7 @@
       </c>
       <c r="F13" t="str">
         <f>Palmon!B13 &amp; "," &amp; Palmon!C13 &amp; "," &amp; Palmon!D13 &amp; "," &amp; Palmon!E13 &amp; "," &amp; Palmon!G13 &amp; "," &amp; SUBSTITUTE(Palmon!H13,",",".") &amp; "," &amp; Palmon!I13 &amp; "," &amp; SUBSTITUTE(Palmon!P13,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q13,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R13,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S13,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T13,",",".") &amp; "," &amp; Palmon!J13 &amp; "," &amp; Palmon!K13 &amp; "," &amp; Palmon!L13 &amp; "," &amp; Palmon!M13 &amp; "," &amp; Palmon!N13 &amp; "," &amp; SUBSTITUTE(Palmon!U13,",",".") &amp; "," &amp; Palmon!V13 &amp; "," &amp; Palmon!X13 &amp; "," &amp; Palmon!Y13 &amp; "," &amp; Palmon!AA13 &amp; "," &amp; Palmon!AB13 &amp; "," &amp; Palmon!AC13 &amp; "," &amp; Palmon!AE13 &amp; "," &amp; Palmon!AF13 &amp; "," &amp; Palmon!AI13 &amp; "," &amp; Palmon!AJ13</f>
-        <v>Lucidina,Water,Attack,270,4,4,0,1,1,1,1,0,5,5,15,Max,,0.487179487179487,500,135120000,,4270,10,2,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcR9A_xtftnwTH1zCnLIOcgmJKNZtFnB-e8QOw&amp;s, ,Oneirina,</v>
+        <v>Lucidina,Water,Attack,270,4,4,0,1,1,1,1,0,5,5,15,Max,,0.487179487179487,500,135120000,,4270,11,2,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcR9A_xtftnwTH1zCnLIOcgmJKNZtFnB-e8QOw&amp;s, ,Oneirina,</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -43816,7 +43830,7 @@
       </c>
       <c r="F15" t="str">
         <f>Palmon!B15 &amp; "," &amp; Palmon!C15 &amp; "," &amp; Palmon!D15 &amp; "," &amp; Palmon!E15 &amp; "," &amp; Palmon!G15 &amp; "," &amp; SUBSTITUTE(Palmon!H15,",",".") &amp; "," &amp; Palmon!I15 &amp; "," &amp; SUBSTITUTE(Palmon!P15,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q15,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R15,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S15,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T15,",",".") &amp; "," &amp; Palmon!J15 &amp; "," &amp; Palmon!K15 &amp; "," &amp; Palmon!L15 &amp; "," &amp; Palmon!M15 &amp; "," &amp; Palmon!N15 &amp; "," &amp; SUBSTITUTE(Palmon!U15,",",".") &amp; "," &amp; Palmon!V15 &amp; "," &amp; Palmon!X15 &amp; "," &amp; Palmon!Y15 &amp; "," &amp; Palmon!AA15 &amp; "," &amp; Palmon!AB15 &amp; "," &amp; Palmon!AC15 &amp; "," &amp; Palmon!AE15 &amp; "," &amp; Palmon!AF15 &amp; "," &amp; Palmon!AI15 &amp; "," &amp; Palmon!AJ15</f>
-        <v>Statchew,Wood,Defend,230,2,2.2,10,1,1,0.4,0,0,15,5,9,,,0.117948717948718,850,3390620000,1,2430,23,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSC1rp-0lIuUyVvSi8kN_vJnr_Ln4mF4lh4zg&amp;s, ,Anubeast,</v>
+        <v>Statchew,Wood,Defend,230,2,2.2,10,1,1,0.4,0,0,15,5,9,,,0.117948717948718,850,3390620000,1,2430,24,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSC1rp-0lIuUyVvSi8kN_vJnr_Ln4mF4lh4zg&amp;s, ,Anubeast,</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -43842,7 +43856,7 @@
       </c>
       <c r="F16" t="str">
         <f>Palmon!B16 &amp; "," &amp; Palmon!C16 &amp; "," &amp; Palmon!D16 &amp; "," &amp; Palmon!E16 &amp; "," &amp; Palmon!G16 &amp; "," &amp; SUBSTITUTE(Palmon!H16,",",".") &amp; "," &amp; Palmon!I16 &amp; "," &amp; SUBSTITUTE(Palmon!P16,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q16,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R16,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S16,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T16,",",".") &amp; "," &amp; Palmon!J16 &amp; "," &amp; Palmon!K16 &amp; "," &amp; Palmon!L16 &amp; "," &amp; Palmon!M16 &amp; "," &amp; Palmon!N16 &amp; "," &amp; SUBSTITUTE(Palmon!U16,",",".") &amp; "," &amp; Palmon!V16 &amp; "," &amp; Palmon!X16 &amp; "," &amp; Palmon!Y16 &amp; "," &amp; Palmon!AA16 &amp; "," &amp; Palmon!AB16 &amp; "," &amp; Palmon!AC16 &amp; "," &amp; Palmon!AE16 &amp; "," &amp; Palmon!AF16 &amp; "," &amp; Palmon!AI16 &amp; "," &amp; Palmon!AJ16</f>
-        <v>Battereina,Electricity,Attack,210,3,3,0,1,1,1,0,0,1,1,1,,,0.179487179487179,800,4161420000,1,3210,17,3,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQaumzt62POzCPWE5kNVnUA5j6pKVetbogSOJqvW2HU&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTun-SMpIMKagR2SMRlAysEcjxhO7sD6Nq3IQ&amp;s,Ampereina,</v>
+        <v>Battereina,Electricity,Attack,210,3,3,0,1,1,1,0,0,1,1,1,,,0.179487179487179,800,4161420000,1,3210,18,3,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQaumzt62POzCPWE5kNVnUA5j6pKVetbogSOJqvW2HU&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTun-SMpIMKagR2SMRlAysEcjxhO7sD6Nq3IQ&amp;s,Ampereina,</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -43868,7 +43882,7 @@
       </c>
       <c r="F17" t="str">
         <f>Palmon!B17 &amp; "," &amp; Palmon!C17 &amp; "," &amp; Palmon!D17 &amp; "," &amp; Palmon!E17 &amp; "," &amp; Palmon!G17 &amp; "," &amp; SUBSTITUTE(Palmon!H17,",",".") &amp; "," &amp; Palmon!I17 &amp; "," &amp; SUBSTITUTE(Palmon!P17,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q17,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R17,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S17,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T17,",",".") &amp; "," &amp; Palmon!J17 &amp; "," &amp; Palmon!K17 &amp; "," &amp; Palmon!L17 &amp; "," &amp; Palmon!M17 &amp; "," &amp; Palmon!N17 &amp; "," &amp; SUBSTITUTE(Palmon!U17,",",".") &amp; "," &amp; Palmon!V17 &amp; "," &amp; Palmon!X17 &amp; "," &amp; Palmon!Y17 &amp; "," &amp; Palmon!AA17 &amp; "," &amp; Palmon!AB17 &amp; "," &amp; Palmon!AC17 &amp; "," &amp; Palmon!AE17 &amp; "," &amp; Palmon!AF17 &amp; "," &amp; Palmon!AI17 &amp; "," &amp; Palmon!AJ17</f>
-        <v>Fulgairy,Electricity,Defend,210,2,2.2,0,1,1,0.4,0,0,5,5,10,,,0.117948717948718,860,4161420000,1,2410,24,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRvhKm8Syu_29_yraif6I_ybijQhVUhvDmMNg&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSNLJe_mmX76tcOcm93Zzrq-x4btMmg4l1csw&amp;s,Keraunosaur,</v>
+        <v>Fulgairy,Electricity,Defend,210,2,2.2,0,1,1,0.4,0,0,5,5,10,,,0.117948717948718,860,4161420000,1,2410,25,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRvhKm8Syu_29_yraif6I_ybijQhVUhvDmMNg&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSNLJe_mmX76tcOcm93Zzrq-x4btMmg4l1csw&amp;s,Keraunosaur,</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -43894,7 +43908,7 @@
       </c>
       <c r="F18" t="str">
         <f>Palmon!B18 &amp; "," &amp; Palmon!C18 &amp; "," &amp; Palmon!D18 &amp; "," &amp; Palmon!E18 &amp; "," &amp; Palmon!G18 &amp; "," &amp; SUBSTITUTE(Palmon!H18,",",".") &amp; "," &amp; Palmon!I18 &amp; "," &amp; SUBSTITUTE(Palmon!P18,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q18,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R18,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S18,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T18,",",".") &amp; "," &amp; Palmon!J18 &amp; "," &amp; Palmon!K18 &amp; "," &amp; Palmon!L18 &amp; "," &amp; Palmon!M18 &amp; "," &amp; Palmon!N18 &amp; "," &amp; SUBSTITUTE(Palmon!U18,",",".") &amp; "," &amp; Palmon!V18 &amp; "," &amp; Palmon!X18 &amp; "," &amp; Palmon!Y18 &amp; "," &amp; Palmon!AA18 &amp; "," &amp; Palmon!AB18 &amp; "," &amp; Palmon!AC18 &amp; "," &amp; Palmon!AE18 &amp; "," &amp; Palmon!AF18 &amp; "," &amp; Palmon!AI18 &amp; "," &amp; Palmon!AJ18</f>
-        <v>Blazeal,Fire,Attack,250,3,3,10,1,1,1,0,0,15,10,15,,,0.179487179487179,790,2123020000,1,3250,16,3,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRsDMtJC3uCFkue3lLpIZqf7OpQgR7XoKOS8g&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTc2Arfa7L5NJadx_WdnWjGTYRLP6bgvNMsDUbraRNI&amp;s,Wildfuror,</v>
+        <v>Blazeal,Fire,Attack,250,3,3,10,1,1,1,0,0,15,10,15,,,0.179487179487179,790,2123020000,1,3250,17,3,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRsDMtJC3uCFkue3lLpIZqf7OpQgR7XoKOS8g&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTc2Arfa7L5NJadx_WdnWjGTYRLP6bgvNMsDUbraRNI&amp;s,Wildfuror,</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -43920,7 +43934,7 @@
       </c>
       <c r="F19" t="str">
         <f>Palmon!B19 &amp; "," &amp; Palmon!C19 &amp; "," &amp; Palmon!D19 &amp; "," &amp; Palmon!E19 &amp; "," &amp; Palmon!G19 &amp; "," &amp; SUBSTITUTE(Palmon!H19,",",".") &amp; "," &amp; Palmon!I19 &amp; "," &amp; SUBSTITUTE(Palmon!P19,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q19,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R19,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S19,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T19,",",".") &amp; "," &amp; Palmon!J19 &amp; "," &amp; Palmon!K19 &amp; "," &amp; Palmon!L19 &amp; "," &amp; Palmon!M19 &amp; "," &amp; Palmon!N19 &amp; "," &amp; SUBSTITUTE(Palmon!U19,",",".") &amp; "," &amp; Palmon!V19 &amp; "," &amp; Palmon!X19 &amp; "," &amp; Palmon!Y19 &amp; "," &amp; Palmon!AA19 &amp; "," &amp; Palmon!AB19 &amp; "," &amp; Palmon!AC19 &amp; "," &amp; Palmon!AE19 &amp; "," &amp; Palmon!AF19 &amp; "," &amp; Palmon!AI19 &amp; "," &amp; Palmon!AJ19</f>
-        <v>Pipistrigoi,Fire,Attack,270,4,4.1,13,1,1,1,1,0.199999999999999,15,15,15,Max,,0.589743589743589,387,135120000,,4370,7,1,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSSdARGNHB_mPJlsb0v4ULv5HaXw2movjzNTNSrkzsi&amp;s, ,Azurostrigoi,</v>
+        <v>Pipistrigoi,Fire,Attack,270,4,4.1,13,1,1,1,1,0.199999999999999,15,15,15,Max,,0.589743589743589,387,135120000,,4370,8,2,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSSdARGNHB_mPJlsb0v4ULv5HaXw2movjzNTNSrkzsi&amp;s, ,Azurostrigoi,</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -43946,7 +43960,7 @@
       </c>
       <c r="F20" t="str">
         <f>Palmon!B20 &amp; "," &amp; Palmon!C20 &amp; "," &amp; Palmon!D20 &amp; "," &amp; Palmon!E20 &amp; "," &amp; Palmon!G20 &amp; "," &amp; SUBSTITUTE(Palmon!H20,",",".") &amp; "," &amp; Palmon!I20 &amp; "," &amp; SUBSTITUTE(Palmon!P20,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q20,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R20,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S20,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T20,",",".") &amp; "," &amp; Palmon!J20 &amp; "," &amp; Palmon!K20 &amp; "," &amp; Palmon!L20 &amp; "," &amp; Palmon!M20 &amp; "," &amp; Palmon!N20 &amp; "," &amp; SUBSTITUTE(Palmon!U20,",",".") &amp; "," &amp; Palmon!V20 &amp; "," &amp; Palmon!X20 &amp; "," &amp; Palmon!Y20 &amp; "," &amp; Palmon!AA20 &amp; "," &amp; Palmon!AB20 &amp; "," &amp; Palmon!AC20 &amp; "," &amp; Palmon!AE20 &amp; "," &amp; Palmon!AF20 &amp; "," &amp; Palmon!AI20 &amp; "," &amp; Palmon!AJ20</f>
-        <v>Fingenue,Water,Attack,200,2,2,13,1,1,0,0,0,5,1,5,,,0.0769230769230769,887,4415720000,1,2200,28,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQMvgcplGCQCmIPq5ypILKf8v4mBVwxsMgKdg&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQK8ZtDU3nBBFFGN2vhlNn2ACJuBBoGsnFHZC7On4Gb&amp;s,Finnabelle,</v>
+        <v>Fingenue,Water,Attack,200,2,2,13,1,1,0,0,0,5,1,5,,,0.0769230769230769,887,4415720000,1,2200,30,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQMvgcplGCQCmIPq5ypILKf8v4mBVwxsMgKdg&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQK8ZtDU3nBBFFGN2vhlNn2ACJuBBoGsnFHZC7On4Gb&amp;s,Finnabelle,</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -43972,7 +43986,7 @@
       </c>
       <c r="F21" t="str">
         <f>Palmon!B21 &amp; "," &amp; Palmon!C21 &amp; "," &amp; Palmon!D21 &amp; "," &amp; Palmon!E21 &amp; "," &amp; Palmon!G21 &amp; "," &amp; SUBSTITUTE(Palmon!H21,",",".") &amp; "," &amp; Palmon!I21 &amp; "," &amp; SUBSTITUTE(Palmon!P21,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q21,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R21,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S21,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T21,",",".") &amp; "," &amp; Palmon!J21 &amp; "," &amp; Palmon!K21 &amp; "," &amp; Palmon!L21 &amp; "," &amp; Palmon!M21 &amp; "," &amp; Palmon!N21 &amp; "," &amp; SUBSTITUTE(Palmon!U21,",",".") &amp; "," &amp; Palmon!V21 &amp; "," &amp; Palmon!X21 &amp; "," &amp; Palmon!Y21 &amp; "," &amp; Palmon!AA21 &amp; "," &amp; Palmon!AB21 &amp; "," &amp; Palmon!AC21 &amp; "," &amp; Palmon!AE21 &amp; "," &amp; Palmon!AF21 &amp; "," &amp; Palmon!AI21 &amp; "," &amp; Palmon!AJ21</f>
-        <v>Dolphriend,Water,Defend,210,2,2.2,1,1,1,0.4,0,0,1,1,1,,,0.117948717948718,859,4161420000,1,2410,25,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQ5ThIRML8-S9czd3JEMxpMlnMn9UAMwdeiBw&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTQp9fQrKVHd_zzyuSxM8QSOjlZsRbJ0lwxrg&amp;s,Adolphonis,</v>
+        <v>Dolphriend,Water,Defend,210,2,2.2,1,1,1,0.4,0,0,1,1,1,,,0.117948717948718,859,4161420000,1,2410,26,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQ5ThIRML8-S9czd3JEMxpMlnMn9UAMwdeiBw&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTQp9fQrKVHd_zzyuSxM8QSOjlZsRbJ0lwxrg&amp;s,Adolphonis,</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -43998,7 +44012,7 @@
       </c>
       <c r="F22" t="str">
         <f>Palmon!B22 &amp; "," &amp; Palmon!C22 &amp; "," &amp; Palmon!D22 &amp; "," &amp; Palmon!E22 &amp; "," &amp; Palmon!G22 &amp; "," &amp; SUBSTITUTE(Palmon!H22,",",".") &amp; "," &amp; Palmon!I22 &amp; "," &amp; SUBSTITUTE(Palmon!P22,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q22,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R22,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S22,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T22,",",".") &amp; "," &amp; Palmon!J22 &amp; "," &amp; Palmon!K22 &amp; "," &amp; Palmon!L22 &amp; "," &amp; Palmon!M22 &amp; "," &amp; Palmon!N22 &amp; "," &amp; SUBSTITUTE(Palmon!U22,",",".") &amp; "," &amp; Palmon!V22 &amp; "," &amp; Palmon!X22 &amp; "," &amp; Palmon!Y22 &amp; "," &amp; Palmon!AA22 &amp; "," &amp; Palmon!AB22 &amp; "," &amp; Palmon!AC22 &amp; "," &amp; Palmon!AE22 &amp; "," &amp; Palmon!AF22 &amp; "," &amp; Palmon!AI22 &amp; "," &amp; Palmon!AJ22</f>
-        <v>Ninjump,Water,Attack,160,2,2.3,10,1,1,0.6,0,0,1,1,1,,,0.138461538461538,830,4919220000,1,2460,20,3,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQlW5YoM4c6bArAuIb7UxI-VfUI9GmBp85Qig&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRXczs_Bjhslhr7Mf2HENU6MTyGpz0RJEMjNA&amp;s,Bufonobi,Shadowkaeru</v>
+        <v>Ninjump,Water,Attack,160,2,2.3,10,1,1,0.6,0,0,1,1,1,,,0.138461538461538,830,4919220000,1,2460,21,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQlW5YoM4c6bArAuIb7UxI-VfUI9GmBp85Qig&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRXczs_Bjhslhr7Mf2HENU6MTyGpz0RJEMjNA&amp;s,Bufonobi,Shadowkaeru</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -44024,7 +44038,7 @@
       </c>
       <c r="F23" t="str">
         <f>Palmon!B23 &amp; "," &amp; Palmon!C23 &amp; "," &amp; Palmon!D23 &amp; "," &amp; Palmon!E23 &amp; "," &amp; Palmon!G23 &amp; "," &amp; SUBSTITUTE(Palmon!H23,",",".") &amp; "," &amp; Palmon!I23 &amp; "," &amp; SUBSTITUTE(Palmon!P23,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q23,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R23,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S23,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T23,",",".") &amp; "," &amp; Palmon!J23 &amp; "," &amp; Palmon!K23 &amp; "," &amp; Palmon!L23 &amp; "," &amp; Palmon!M23 &amp; "," &amp; Palmon!N23 &amp; "," &amp; SUBSTITUTE(Palmon!U23,",",".") &amp; "," &amp; Palmon!V23 &amp; "," &amp; Palmon!X23 &amp; "," &amp; Palmon!Y23 &amp; "," &amp; Palmon!AA23 &amp; "," &amp; Palmon!AB23 &amp; "," &amp; Palmon!AC23 &amp; "," &amp; Palmon!AE23 &amp; "," &amp; Palmon!AF23 &amp; "," &amp; Palmon!AI23 &amp; "," &amp; Palmon!AJ23</f>
-        <v>Surveilynx,Wood,Attack,220,2,2,0,1,1,0,0,0,10,10,10,,,0.0769230769230769,900,3826220000,1,2220,27,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcS2Z4TkKenIldVD1AQ7o1ftBU6pG9zKRz-FKA&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQt6lIf0Em_f_DT0VurOVsujswJCEmGOpJk4N6txfed&amp;s,Camouflynx,</v>
+        <v>Surveilynx,Wood,Attack,220,2,2,0,1,1,0,0,0,10,10,10,,,0.0769230769230769,900,3826220000,1,2220,29,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcS2Z4TkKenIldVD1AQ7o1ftBU6pG9zKRz-FKA&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQt6lIf0Em_f_DT0VurOVsujswJCEmGOpJk4N6txfed&amp;s,Camouflynx,</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -44050,7 +44064,7 @@
       </c>
       <c r="F24" t="str">
         <f>Palmon!B24 &amp; "," &amp; Palmon!C24 &amp; "," &amp; Palmon!D24 &amp; "," &amp; Palmon!E24 &amp; "," &amp; Palmon!G24 &amp; "," &amp; SUBSTITUTE(Palmon!H24,",",".") &amp; "," &amp; Palmon!I24 &amp; "," &amp; SUBSTITUTE(Palmon!P24,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q24,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R24,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S24,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T24,",",".") &amp; "," &amp; Palmon!J24 &amp; "," &amp; Palmon!K24 &amp; "," &amp; Palmon!L24 &amp; "," &amp; Palmon!M24 &amp; "," &amp; Palmon!N24 &amp; "," &amp; SUBSTITUTE(Palmon!U24,",",".") &amp; "," &amp; Palmon!V24 &amp; "," &amp; Palmon!X24 &amp; "," &amp; Palmon!Y24 &amp; "," &amp; Palmon!AA24 &amp; "," &amp; Palmon!AB24 &amp; "," &amp; Palmon!AC24 &amp; "," &amp; Palmon!AE24 &amp; "," &amp; Palmon!AF24 &amp; "," &amp; Palmon!AI24 &amp; "," &amp; Palmon!AJ24</f>
-        <v>Salamantis,Wood,Attack,200,2,2,0,1,1,0,0,0,1,1,1,,,0.0769230769230769,900,4415720000,1,2200,29,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSPFSxpzP3XhhfdRhxvv_Oi86DkexX6yjZrRA&amp;s,,Silvaurus,</v>
+        <v>Salamantis,Wood,Attack,200,2,2,0,1,1,0,0,0,1,1,1,,,0.0769230769230769,900,4415720000,1,2200,31,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSPFSxpzP3XhhfdRhxvv_Oi86DkexX6yjZrRA&amp;s,,Silvaurus,</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -44076,7 +44090,7 @@
       </c>
       <c r="F25" t="str">
         <f>Palmon!B25 &amp; "," &amp; Palmon!C25 &amp; "," &amp; Palmon!D25 &amp; "," &amp; Palmon!E25 &amp; "," &amp; Palmon!G25 &amp; "," &amp; SUBSTITUTE(Palmon!H25,",",".") &amp; "," &amp; Palmon!I25 &amp; "," &amp; SUBSTITUTE(Palmon!P25,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q25,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R25,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S25,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T25,",",".") &amp; "," &amp; Palmon!J25 &amp; "," &amp; Palmon!K25 &amp; "," &amp; Palmon!L25 &amp; "," &amp; Palmon!M25 &amp; "," &amp; Palmon!N25 &amp; "," &amp; SUBSTITUTE(Palmon!U25,",",".") &amp; "," &amp; Palmon!V25 &amp; "," &amp; Palmon!X25 &amp; "," &amp; Palmon!Y25 &amp; "," &amp; Palmon!AA25 &amp; "," &amp; Palmon!AB25 &amp; "," &amp; Palmon!AC25 &amp; "," &amp; Palmon!AE25 &amp; "," &amp; Palmon!AF25 &amp; "," &amp; Palmon!AI25 &amp; "," &amp; Palmon!AJ25</f>
-        <v>Regalion,Water,Defend,200,2,2,0,1,1,0,0,0,10,10,10,,,0.0769230769230769,900,4415720000,1,2200,30,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcToQuTLjFC_oynclPIY9tWM7qAaMIPbmzTn2Q&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcS0uWep-9VXcdMd6qSpdASqYR42mG4SmBsCjw&amp;s,Lionarch,</v>
+        <v>Regalion,Water,Defend,200,2,2.1,11,1,1,0.2,0,0,10,10,10,,,0.0974358974358975,869,4415720000,1,2300,28,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcToQuTLjFC_oynclPIY9tWM7qAaMIPbmzTn2Q&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcS0uWep-9VXcdMd6qSpdASqYR42mG4SmBsCjw&amp;s,Lionarch,</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -44102,7 +44116,7 @@
       </c>
       <c r="F26" t="str">
         <f>Palmon!B26 &amp; "," &amp; Palmon!C26 &amp; "," &amp; Palmon!D26 &amp; "," &amp; Palmon!E26 &amp; "," &amp; Palmon!G26 &amp; "," &amp; SUBSTITUTE(Palmon!H26,",",".") &amp; "," &amp; Palmon!I26 &amp; "," &amp; SUBSTITUTE(Palmon!P26,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q26,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R26,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S26,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T26,",",".") &amp; "," &amp; Palmon!J26 &amp; "," &amp; Palmon!K26 &amp; "," &amp; Palmon!L26 &amp; "," &amp; Palmon!M26 &amp; "," &amp; Palmon!N26 &amp; "," &amp; SUBSTITUTE(Palmon!U26,",",".") &amp; "," &amp; Palmon!V26 &amp; "," &amp; Palmon!X26 &amp; "," &amp; Palmon!Y26 &amp; "," &amp; Palmon!AA26 &amp; "," &amp; Palmon!AB26 &amp; "," &amp; Palmon!AC26 &amp; "," &amp; Palmon!AE26 &amp; "," &amp; Palmon!AF26 &amp; "," &amp; Palmon!AI26 &amp; "," &amp; Palmon!AJ26</f>
-        <v>Mantleray,Electricity,Attack,210,2,2.4,3,1,1,0.8,0,0,4,1,1,,,0.158974358974359,817,4161420000,1,2610,18,3,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSWhzppoZXwh-zBnWIY3GFkIp0x0kc0hAzG0A&amp;s, ,Sorceray,</v>
+        <v>Mantleray,Electricity,Attack,210,2,2.4,3,1,1,0.8,0,0,4,1,1,,,0.158974358974359,817,4161420000,1,2610,19,3,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSWhzppoZXwh-zBnWIY3GFkIp0x0kc0hAzG0A&amp;s, ,Sorceray,</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -44154,7 +44168,7 @@
       </c>
       <c r="F28" t="str">
         <f>Palmon!B28 &amp; "," &amp; Palmon!C28 &amp; "," &amp; Palmon!D28 &amp; "," &amp; Palmon!E28 &amp; "," &amp; Palmon!G28 &amp; "," &amp; SUBSTITUTE(Palmon!H28,",",".") &amp; "," &amp; Palmon!I28 &amp; "," &amp; SUBSTITUTE(Palmon!P28,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q28,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R28,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S28,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T28,",",".") &amp; "," &amp; Palmon!J28 &amp; "," &amp; Palmon!K28 &amp; "," &amp; Palmon!L28 &amp; "," &amp; Palmon!M28 &amp; "," &amp; Palmon!N28 &amp; "," &amp; SUBSTITUTE(Palmon!U28,",",".") &amp; "," &amp; Palmon!V28 &amp; "," &amp; Palmon!X28 &amp; "," &amp; Palmon!Y28 &amp; "," &amp; Palmon!AA28 &amp; "," &amp; Palmon!AB28 &amp; "," &amp; Palmon!AC28 &amp; "," &amp; Palmon!AE28 &amp; "," &amp; Palmon!AF28 &amp; "," &amp; Palmon!AI28 &amp; "," &amp; Palmon!AJ28</f>
-        <v>Spookaboo,Fire,Attack,210,3,3.1,10,1,1,1,0.2,0,1,1,1,,,0.241025641025641,730,4161420000,1,3310,14,2,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcT29K673YTBvt_EofrppvnWB4sgt43DEq1pTw&amp;s, ,,</v>
+        <v>Spookaboo,Fire,Attack,210,3,3.1,10,1,1,1,0.2,0,1,1,1,,,0.241025641025641,730,4161420000,1,3310,15,3,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcT29K673YTBvt_EofrppvnWB4sgt43DEq1pTw&amp;s, ,,</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -44180,7 +44194,7 @@
       </c>
       <c r="F29" t="str">
         <f>Palmon!B29 &amp; "," &amp; Palmon!C29 &amp; "," &amp; Palmon!D29 &amp; "," &amp; Palmon!E29 &amp; "," &amp; Palmon!G29 &amp; "," &amp; SUBSTITUTE(Palmon!H29,",",".") &amp; "," &amp; Palmon!I29 &amp; "," &amp; SUBSTITUTE(Palmon!P29,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q29,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R29,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S29,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T29,",",".") &amp; "," &amp; Palmon!J29 &amp; "," &amp; Palmon!K29 &amp; "," &amp; Palmon!L29 &amp; "," &amp; Palmon!M29 &amp; "," &amp; Palmon!N29 &amp; "," &amp; SUBSTITUTE(Palmon!U29,",",".") &amp; "," &amp; Palmon!V29 &amp; "," &amp; Palmon!X29 &amp; "," &amp; Palmon!Y29 &amp; "," &amp; Palmon!AA29 &amp; "," &amp; Palmon!AB29 &amp; "," &amp; Palmon!AC29 &amp; "," &amp; Palmon!AE29 &amp; "," &amp; Palmon!AF29 &amp; "," &amp; Palmon!AI29 &amp; "," &amp; Palmon!AJ29</f>
-        <v>Kungpaw,Water,Defend,186,3,3.3,45,1,1,1,0.6,0,1,1,1,,,0.364102564102564,575,4667020000,1,3486,12,2,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRV1HdRcNPUS4HjDBZ2YOXgaMW_I8FgZEP5xg&amp;s,,,</v>
+        <v>Kungpaw,Water,Defend,190,4,4,30,1,1,1,1,0,1,1,1,Max,,0.487179487179487,470,4605720000,1,4190,13,2,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRV1HdRcNPUS4HjDBZ2YOXgaMW_I8FgZEP5xg&amp;s,,,</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -44206,7 +44220,7 @@
       </c>
       <c r="F30" t="str">
         <f>Palmon!B30 &amp; "," &amp; Palmon!C30 &amp; "," &amp; Palmon!D30 &amp; "," &amp; Palmon!E30 &amp; "," &amp; Palmon!G30 &amp; "," &amp; SUBSTITUTE(Palmon!H30,",",".") &amp; "," &amp; Palmon!I30 &amp; "," &amp; SUBSTITUTE(Palmon!P30,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q30,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R30,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S30,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T30,",",".") &amp; "," &amp; Palmon!J30 &amp; "," &amp; Palmon!K30 &amp; "," &amp; Palmon!L30 &amp; "," &amp; Palmon!M30 &amp; "," &amp; Palmon!N30 &amp; "," &amp; SUBSTITUTE(Palmon!U30,",",".") &amp; "," &amp; Palmon!V30 &amp; "," &amp; Palmon!X30 &amp; "," &amp; Palmon!Y30 &amp; "," &amp; Palmon!AA30 &amp; "," &amp; Palmon!AB30 &amp; "," &amp; Palmon!AC30 &amp; "," &amp; Palmon!AE30 &amp; "," &amp; Palmon!AF30 &amp; "," &amp; Palmon!AI30 &amp; "," &amp; Palmon!AJ30</f>
-        <v>Baboom,Wood,Attack,210,2,2.1,10,1,1,0.2,0,0,5,1,1,,,0.0974358974358975,870,4161420000,1,2310,26,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRh7P3oaH_Kq0fni1aOxe3TmDgHULu_Z-UWUg&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSQA67-vNrm701vphmHvRKGkJTx2O2gyTi00Q&amp;s,Rumbkey,</v>
+        <v>Baboom,Wood,Attack,210,2,2.1,10,1,1,0.2,0,0,5,1,1,,,0.0974358974358975,870,4161420000,1,2310,27,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRh7P3oaH_Kq0fni1aOxe3TmDgHULu_Z-UWUg&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSQA67-vNrm701vphmHvRKGkJTx2O2gyTi00Q&amp;s,Rumbkey,</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -44258,7 +44272,7 @@
       </c>
       <c r="F32" t="str">
         <f>Palmon!B32 &amp; "," &amp; Palmon!C32 &amp; "," &amp; Palmon!D32 &amp; "," &amp; Palmon!E32 &amp; "," &amp; Palmon!G32 &amp; "," &amp; SUBSTITUTE(Palmon!H32,",",".") &amp; "," &amp; Palmon!I32 &amp; "," &amp; SUBSTITUTE(Palmon!P32,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q32,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R32,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S32,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T32,",",".") &amp; "," &amp; Palmon!J32 &amp; "," &amp; Palmon!K32 &amp; "," &amp; Palmon!L32 &amp; "," &amp; Palmon!M32 &amp; "," &amp; Palmon!N32 &amp; "," &amp; SUBSTITUTE(Palmon!U32,",",".") &amp; "," &amp; Palmon!V32 &amp; "," &amp; Palmon!X32 &amp; "," &amp; Palmon!Y32 &amp; "," &amp; Palmon!AA32 &amp; "," &amp; Palmon!AB32 &amp; "," &amp; Palmon!AC32 &amp; "," &amp; Palmon!AE32 &amp; "," &amp; Palmon!AF32 &amp; "," &amp; Palmon!AI32 &amp; "," &amp; Palmon!AJ32</f>
-        <v>Thundertooth,Electricity,Attack,140,0,0,250,0,0,0,0,0,1,1,1,,,0,725,4999220000,1,140,31,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRNSg29kZ5t51s7m9SpGygJKsQow67zLt08qg&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQoXkXemCK02vmhKICXcvjchtQ-qvcAc5zyrA&amp;s,Thundermane,</v>
+        <v>Thundertooth,Electricity,Attack,140,5,5,0,1,1,1,1,1,1,1,1,Max,10,1,0,4999220000,1,5140,7,1,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRNSg29kZ5t51s7m9SpGygJKsQow67zLt08qg&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQoXkXemCK02vmhKICXcvjchtQ-qvcAc5zyrA&amp;s,Thundermane,</v>
       </c>
     </row>
     <row r="33" spans="3:6" x14ac:dyDescent="0.25">
@@ -44456,7 +44470,7 @@
       </c>
       <c r="F43" t="str">
         <f>Palmon!B46 &amp; "," &amp; Palmon!C46 &amp; "," &amp; Palmon!D46 &amp; "," &amp; Palmon!E46 &amp; "," &amp; Palmon!G46 &amp; "," &amp; SUBSTITUTE(Palmon!H46,",",".") &amp; "," &amp; Palmon!I46 &amp; "," &amp; SUBSTITUTE(Palmon!P46,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q46,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R46,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S46,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T46,",",".") &amp; "," &amp; Palmon!J46 &amp; "," &amp; Palmon!K46 &amp; "," &amp; Palmon!L46 &amp; "," &amp; Palmon!M46 &amp; "," &amp; Palmon!N46 &amp; "," &amp; SUBSTITUTE(Palmon!U46,",",".") &amp; "," &amp; Palmon!V46 &amp; "," &amp; Palmon!X46 &amp; "," &amp; Palmon!Y46 &amp; "," &amp; Palmon!AA46 &amp; "," &amp; Palmon!AB46 &amp; "," &amp; Palmon!AC46 &amp; "," &amp; Palmon!AE46 &amp; "," &amp; Palmon!AF46 &amp; "," &amp; Palmon!AI46 &amp; "," &amp; Palmon!AJ46</f>
-        <v>Revontulet,Fire,Attack,160,2,2.3,0,1,1,0.6,0,0,1,1,1,,,0.138461538461538,840,4919220000,1,2460,21,,, ,Vulpyrean,</v>
+        <v>Revontulet,Fire,Attack,160,2,2.3,0,1,1,0.6,0,0,1,1,1,,,0.138461538461538,840,4919220000,1,2460,22,,, ,Vulpyrean,</v>
       </c>
     </row>
     <row r="44" spans="3:6" x14ac:dyDescent="0.25">

--- a/data/PS - Estimation (version 1).xlsx
+++ b/data/PS - Estimation (version 1).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xvjm020\Documents\Personnel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{081AFD2A-6DAF-4D72-9D39-4455FDA3B8F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A9A06F0-11D1-4EC1-9551-39A6FCC1DCFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9D83D047-1CAD-4BF9-942E-B289F790400E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{9D83D047-1CAD-4BF9-942E-B289F790400E}"/>
   </bookViews>
   <sheets>
     <sheet name="Palmon" sheetId="2" r:id="rId1"/>
@@ -10541,7 +10541,7 @@
       <formula>$C3="Wood"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D57:D81 D3:D53">
+  <conditionalFormatting sqref="D3:D53 D57:D81">
     <cfRule type="cellIs" dxfId="65" priority="76" operator="equal">
       <formula>"Attack"</formula>
     </cfRule>
@@ -11197,11 +11197,11 @@
         <v>0</v>
       </c>
       <c r="AD2" t="str">
-        <f>Palmon!AE3</f>
+        <f>IF(Palmon!AE3="","",Palmon!AE3)</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRXczs_Bjhslhr7Mf2HENU6MTyGpz0RJEMjNA&amp;s</v>
       </c>
       <c r="AE2" t="str">
-        <f>Palmon!AF3</f>
+        <f>IF(Palmon!AF3="","",Palmon!AF3)</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AF2" t="str">
@@ -11343,11 +11343,11 @@
         <v>0</v>
       </c>
       <c r="AD3" t="str">
-        <f>Palmon!AE4</f>
+        <f>IF(Palmon!AE4="","",Palmon!AE4)</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSDZWuq2tiKYc0zKRxpHXrLSMZ1GsY_6wEIYw&amp;s</v>
       </c>
       <c r="AE3" t="str">
-        <f>Palmon!AF4</f>
+        <f>IF(Palmon!AF4="","",Palmon!AF4)</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRGF27Z8fOuiwM1qjDFQVY262gS_QKIJamMNg&amp;s</v>
       </c>
       <c r="AF3" t="str">
@@ -11489,11 +11489,11 @@
         <v>0</v>
       </c>
       <c r="AD4" t="str">
-        <f>Palmon!AE5</f>
+        <f>IF(Palmon!AE5="","",Palmon!AE5)</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRwfHFWjB1bN67FJNyjjWvBJwviWJ3Tada0Yg&amp;s</v>
       </c>
       <c r="AE4" t="str">
-        <f>Palmon!AF5</f>
+        <f>IF(Palmon!AF5="","",Palmon!AF5)</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSkOv6mOI5FaIAjcVgErYDwVaivkH3WdUQIzw&amp;s</v>
       </c>
       <c r="AF4" t="str">
@@ -11635,11 +11635,11 @@
         <v>0</v>
       </c>
       <c r="AD5" t="str">
-        <f>Palmon!AE6</f>
+        <f>IF(Palmon!AE6="","",Palmon!AE6)</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQOwDXppnwkCtCXXAqUiiNMhf6T-lane54jPg&amp;s</v>
       </c>
       <c r="AE5" t="str">
-        <f>Palmon!AF6</f>
+        <f>IF(Palmon!AF6="","",Palmon!AF6)</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AF5" t="str">
@@ -11781,11 +11781,11 @@
         <v>0</v>
       </c>
       <c r="AD6" t="str">
-        <f>Palmon!AE7</f>
+        <f>IF(Palmon!AE7="","",Palmon!AE7)</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQtrOr7ePo-_tg085QaHk6NorM32ywE44672A&amp;s</v>
       </c>
       <c r="AE6" t="str">
-        <f>Palmon!AF7</f>
+        <f>IF(Palmon!AF7="","",Palmon!AF7)</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTII6bAUVzdPfr_45Db3bGwDuIVxhe-n4dSSgHRGJaEpg&amp;s</v>
       </c>
       <c r="AF6" t="str">
@@ -11927,11 +11927,11 @@
         <v>0</v>
       </c>
       <c r="AD7" t="str">
-        <f>Palmon!AE8</f>
+        <f>IF(Palmon!AE8="","",Palmon!AE8)</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRebc6KbOAxblleg_L3rr2K13bt-Yyzq1bAaw&amp;s</v>
       </c>
       <c r="AE7" t="str">
-        <f>Palmon!AF8</f>
+        <f>IF(Palmon!AF8="","",Palmon!AF8)</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AF7" t="str">
@@ -12073,11 +12073,11 @@
         <v>0</v>
       </c>
       <c r="AD8" t="str">
-        <f>Palmon!AE9</f>
+        <f>IF(Palmon!AE9="","",Palmon!AE9)</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQzaI21taP2V17MKjiPAeulm4V9qfST4umPdg&amp;s</v>
       </c>
       <c r="AE8" t="str">
-        <f>Palmon!AF9</f>
+        <f>IF(Palmon!AF9="","",Palmon!AF9)</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRMlruQNUenhVk-fAEq9d3Wi8zw--0GbkLGJrX1CuQ1&amp;s</v>
       </c>
       <c r="AF8" t="str">
@@ -12219,11 +12219,11 @@
         <v>0</v>
       </c>
       <c r="AD9" t="str">
-        <f>Palmon!AE10</f>
+        <f>IF(Palmon!AE10="","",Palmon!AE10)</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSf59xsunrPEuFvdtBi-IRVMcrdBfW_vNshLA&amp;s</v>
       </c>
       <c r="AE9" t="str">
-        <f>Palmon!AF10</f>
+        <f>IF(Palmon!AF10="","",Palmon!AF10)</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRUDpuK5BvjXDFqgMZvlxYadsaFFQDKOQrNCAHymiAy_w&amp;s</v>
       </c>
       <c r="AF9" t="str">
@@ -12365,11 +12365,11 @@
         <v>0</v>
       </c>
       <c r="AD10" t="str">
-        <f>Palmon!AE11</f>
+        <f>IF(Palmon!AE11="","",Palmon!AE11)</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcT-r6BZKxjf-kMlCmzHjhnUHjvmCaOn5DxiYw&amp;s</v>
       </c>
       <c r="AE10" t="str">
-        <f>Palmon!AF11</f>
+        <f>IF(Palmon!AF11="","",Palmon!AF11)</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcR23XO-FCNYoHOIhLnxge8AzFmdP8mD1D-mzQ&amp;s</v>
       </c>
       <c r="AF10" t="str">
@@ -12511,11 +12511,11 @@
         <v>0</v>
       </c>
       <c r="AD11" t="str">
-        <f>Palmon!AE12</f>
+        <f>IF(Palmon!AE12="","",Palmon!AE12)</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcST2CrUIPAlFNBLPgZn0Tu93KelabHVVAbNLQ&amp;s</v>
       </c>
       <c r="AE11" t="str">
-        <f>Palmon!AF12</f>
+        <f>IF(Palmon!AF12="","",Palmon!AF12)</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AF11" t="str">
@@ -12657,11 +12657,11 @@
         <v>0</v>
       </c>
       <c r="AD12" t="str">
-        <f>Palmon!AE13</f>
+        <f>IF(Palmon!AE13="","",Palmon!AE13)</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcR9A_xtftnwTH1zCnLIOcgmJKNZtFnB-e8QOw&amp;s</v>
       </c>
       <c r="AE12" t="str">
-        <f>Palmon!AF13</f>
+        <f>IF(Palmon!AF13="","",Palmon!AF13)</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AF12" t="str">
@@ -12803,11 +12803,11 @@
         <v>0</v>
       </c>
       <c r="AD13" t="str">
-        <f>Palmon!AE14</f>
+        <f>IF(Palmon!AE14="","",Palmon!AE14)</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQCf63iS9oq-SMn3DO74UTS2j_zSrzNVTRMOQ&amp;s</v>
       </c>
       <c r="AE13" t="str">
-        <f>Palmon!AF14</f>
+        <f>IF(Palmon!AF14="","",Palmon!AF14)</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AF13" t="str">
@@ -12949,11 +12949,11 @@
         <v>0</v>
       </c>
       <c r="AD14" t="str">
-        <f>Palmon!AE15</f>
+        <f>IF(Palmon!AE15="","",Palmon!AE15)</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSC1rp-0lIuUyVvSi8kN_vJnr_Ln4mF4lh4zg&amp;s</v>
       </c>
       <c r="AE14" t="str">
-        <f>Palmon!AF15</f>
+        <f>IF(Palmon!AF15="","",Palmon!AF15)</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AF14" t="str">
@@ -13095,11 +13095,11 @@
         <v>0</v>
       </c>
       <c r="AD15" t="str">
-        <f>Palmon!AE16</f>
+        <f>IF(Palmon!AE16="","",Palmon!AE16)</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQaumzt62POzCPWE5kNVnUA5j6pKVetbogSOJqvW2HU&amp;s</v>
       </c>
       <c r="AE15" t="str">
-        <f>Palmon!AF16</f>
+        <f>IF(Palmon!AF16="","",Palmon!AF16)</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTun-SMpIMKagR2SMRlAysEcjxhO7sD6Nq3IQ&amp;s</v>
       </c>
       <c r="AF15" t="str">
@@ -13241,11 +13241,11 @@
         <v>0</v>
       </c>
       <c r="AD16" t="str">
-        <f>Palmon!AE17</f>
+        <f>IF(Palmon!AE17="","",Palmon!AE17)</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRvhKm8Syu_29_yraif6I_ybijQhVUhvDmMNg&amp;s</v>
       </c>
       <c r="AE16" t="str">
-        <f>Palmon!AF17</f>
+        <f>IF(Palmon!AF17="","",Palmon!AF17)</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSNLJe_mmX76tcOcm93Zzrq-x4btMmg4l1csw&amp;s</v>
       </c>
       <c r="AF16" t="str">
@@ -13387,11 +13387,11 @@
         <v>0</v>
       </c>
       <c r="AD17" t="str">
-        <f>Palmon!AE18</f>
+        <f>IF(Palmon!AE18="","",Palmon!AE18)</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRsDMtJC3uCFkue3lLpIZqf7OpQgR7XoKOS8g&amp;s</v>
       </c>
       <c r="AE17" t="str">
-        <f>Palmon!AF18</f>
+        <f>IF(Palmon!AF18="","",Palmon!AF18)</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTc2Arfa7L5NJadx_WdnWjGTYRLP6bgvNMsDUbraRNI&amp;s</v>
       </c>
       <c r="AF17" t="str">
@@ -13533,11 +13533,11 @@
         <v>0</v>
       </c>
       <c r="AD18" t="str">
-        <f>Palmon!AE19</f>
+        <f>IF(Palmon!AE19="","",Palmon!AE19)</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSSdARGNHB_mPJlsb0v4ULv5HaXw2movjzNTNSrkzsi&amp;s</v>
       </c>
       <c r="AE18" t="str">
-        <f>Palmon!AF19</f>
+        <f>IF(Palmon!AF19="","",Palmon!AF19)</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AF18" t="str">
@@ -13679,11 +13679,11 @@
         <v>0</v>
       </c>
       <c r="AD19" t="str">
-        <f>Palmon!AE20</f>
+        <f>IF(Palmon!AE20="","",Palmon!AE20)</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQMvgcplGCQCmIPq5ypILKf8v4mBVwxsMgKdg&amp;s</v>
       </c>
       <c r="AE19" t="str">
-        <f>Palmon!AF20</f>
+        <f>IF(Palmon!AF20="","",Palmon!AF20)</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQK8ZtDU3nBBFFGN2vhlNn2ACJuBBoGsnFHZC7On4Gb&amp;s</v>
       </c>
       <c r="AF19" t="str">
@@ -13825,11 +13825,11 @@
         <v>0</v>
       </c>
       <c r="AD20" t="str">
-        <f>Palmon!AE21</f>
+        <f>IF(Palmon!AE21="","",Palmon!AE21)</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQ5ThIRML8-S9czd3JEMxpMlnMn9UAMwdeiBw&amp;s</v>
       </c>
       <c r="AE20" t="str">
-        <f>Palmon!AF21</f>
+        <f>IF(Palmon!AF21="","",Palmon!AF21)</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTQp9fQrKVHd_zzyuSxM8QSOjlZsRbJ0lwxrg&amp;s</v>
       </c>
       <c r="AF20" t="str">
@@ -13971,11 +13971,11 @@
         <v>0</v>
       </c>
       <c r="AD21" t="str">
-        <f>Palmon!AE22</f>
+        <f>IF(Palmon!AE22="","",Palmon!AE22)</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQlW5YoM4c6bArAuIb7UxI-VfUI9GmBp85Qig&amp;s</v>
       </c>
       <c r="AE21" t="str">
-        <f>Palmon!AF22</f>
+        <f>IF(Palmon!AF22="","",Palmon!AF22)</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRXczs_Bjhslhr7Mf2HENU6MTyGpz0RJEMjNA&amp;s</v>
       </c>
       <c r="AF21" t="str">
@@ -14117,11 +14117,11 @@
         <v>0</v>
       </c>
       <c r="AD22" t="str">
-        <f>Palmon!AE23</f>
+        <f>IF(Palmon!AE23="","",Palmon!AE23)</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcS2Z4TkKenIldVD1AQ7o1ftBU6pG9zKRz-FKA&amp;s</v>
       </c>
       <c r="AE22" t="str">
-        <f>Palmon!AF23</f>
+        <f>IF(Palmon!AF23="","",Palmon!AF23)</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQt6lIf0Em_f_DT0VurOVsujswJCEmGOpJk4N6txfed&amp;s</v>
       </c>
       <c r="AF22" t="str">
@@ -14263,12 +14263,12 @@
         <v>0</v>
       </c>
       <c r="AD23" t="str">
-        <f>Palmon!AE24</f>
+        <f>IF(Palmon!AE24="","",Palmon!AE24)</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSPFSxpzP3XhhfdRhxvv_Oi86DkexX6yjZrRA&amp;s</v>
       </c>
-      <c r="AE23">
-        <f>Palmon!AF24</f>
-        <v>0</v>
+      <c r="AE23" t="str">
+        <f>IF(Palmon!AF24="","",Palmon!AF24)</f>
+        <v/>
       </c>
       <c r="AF23" t="str">
         <f>Palmon!AG24</f>
@@ -14409,11 +14409,11 @@
         <v>0</v>
       </c>
       <c r="AD24" t="str">
-        <f>Palmon!AE25</f>
+        <f>IF(Palmon!AE25="","",Palmon!AE25)</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcToQuTLjFC_oynclPIY9tWM7qAaMIPbmzTn2Q&amp;s</v>
       </c>
       <c r="AE24" t="str">
-        <f>Palmon!AF25</f>
+        <f>IF(Palmon!AF25="","",Palmon!AF25)</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcS0uWep-9VXcdMd6qSpdASqYR42mG4SmBsCjw&amp;s</v>
       </c>
       <c r="AF24" t="str">
@@ -14555,11 +14555,11 @@
         <v>0</v>
       </c>
       <c r="AD25" t="str">
-        <f>Palmon!AE26</f>
+        <f>IF(Palmon!AE26="","",Palmon!AE26)</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSWhzppoZXwh-zBnWIY3GFkIp0x0kc0hAzG0A&amp;s</v>
       </c>
       <c r="AE25" t="str">
-        <f>Palmon!AF26</f>
+        <f>IF(Palmon!AF26="","",Palmon!AF26)</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AF25" t="str">
@@ -14701,11 +14701,11 @@
         <v>0</v>
       </c>
       <c r="AD26" t="str">
-        <f>Palmon!AE27</f>
+        <f>IF(Palmon!AE27="","",Palmon!AE27)</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQ02wmDjsAMofj1ObwwNW6Vhl_QQ-LUodGIKA&amp;s</v>
       </c>
       <c r="AE26" t="str">
-        <f>Palmon!AF27</f>
+        <f>IF(Palmon!AF27="","",Palmon!AF27)</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AF26" t="str">
@@ -14847,11 +14847,11 @@
         <v>0</v>
       </c>
       <c r="AD27" t="str">
-        <f>Palmon!AE28</f>
+        <f>IF(Palmon!AE28="","",Palmon!AE28)</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcT29K673YTBvt_EofrppvnWB4sgt43DEq1pTw&amp;s</v>
       </c>
       <c r="AE27" t="str">
-        <f>Palmon!AF28</f>
+        <f>IF(Palmon!AF28="","",Palmon!AF28)</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AF27" t="str">
@@ -14993,12 +14993,12 @@
         <v>0</v>
       </c>
       <c r="AD28" t="str">
-        <f>Palmon!AE29</f>
+        <f>IF(Palmon!AE29="","",Palmon!AE29)</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRV1HdRcNPUS4HjDBZ2YOXgaMW_I8FgZEP5xg&amp;s</v>
       </c>
-      <c r="AE28">
-        <f>Palmon!AF29</f>
-        <v>0</v>
+      <c r="AE28" t="str">
+        <f>IF(Palmon!AF29="","",Palmon!AF29)</f>
+        <v/>
       </c>
       <c r="AF28" t="str">
         <f>Palmon!AG29</f>
@@ -15139,11 +15139,11 @@
         <v>0</v>
       </c>
       <c r="AD29" t="str">
-        <f>Palmon!AE30</f>
+        <f>IF(Palmon!AE30="","",Palmon!AE30)</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRh7P3oaH_Kq0fni1aOxe3TmDgHULu_Z-UWUg&amp;s</v>
       </c>
       <c r="AE29" t="str">
-        <f>Palmon!AF30</f>
+        <f>IF(Palmon!AF30="","",Palmon!AF30)</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSQA67-vNrm701vphmHvRKGkJTx2O2gyTi00Q&amp;s</v>
       </c>
       <c r="AF29" t="str">
@@ -15285,11 +15285,11 @@
         <v>0</v>
       </c>
       <c r="AD30" t="str">
-        <f>Palmon!AE31</f>
+        <f>IF(Palmon!AE31="","",Palmon!AE31)</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQxjczIZhaTQV2VukHWlKoJMQ30DrUIwatAEw&amp;s</v>
       </c>
       <c r="AE30" t="str">
-        <f>Palmon!AF31</f>
+        <f>IF(Palmon!AF31="","",Palmon!AF31)</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AF30" t="str">
@@ -15431,11 +15431,11 @@
         <v>0</v>
       </c>
       <c r="AD31" t="str">
-        <f>Palmon!AE32</f>
+        <f>IF(Palmon!AE32="","",Palmon!AE32)</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRNSg29kZ5t51s7m9SpGygJKsQow67zLt08qg&amp;s</v>
       </c>
       <c r="AE31" t="str">
-        <f>Palmon!AF32</f>
+        <f>IF(Palmon!AF32="","",Palmon!AF32)</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQoXkXemCK02vmhKICXcvjchtQ-qvcAc5zyrA&amp;s</v>
       </c>
       <c r="AF31" t="str">
@@ -15577,11 +15577,11 @@
         <v>0</v>
       </c>
       <c r="AD32" t="str">
-        <f>Palmon!AE33</f>
+        <f>IF(Palmon!AE33="","",Palmon!AE33)</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRR4T5jdtF_LaheoRmg2FLSWS4DS4QhqCFaAg&amp;s</v>
       </c>
       <c r="AE32" t="str">
-        <f>Palmon!AF33</f>
+        <f>IF(Palmon!AF33="","",Palmon!AF33)</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AF32" t="str">
@@ -15723,11 +15723,11 @@
         <v>0</v>
       </c>
       <c r="AD33" t="str">
-        <f>Palmon!AE34</f>
+        <f>IF(Palmon!AE34="","",Palmon!AE34)</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTrE4qGrnpy2BMETqUKNyATj-OrXMdX4IeXcQ&amp;s</v>
       </c>
       <c r="AE33" t="str">
-        <f>Palmon!AF34</f>
+        <f>IF(Palmon!AF34="","",Palmon!AF34)</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSRbCy1ARx2qd0P1rLvdoRvfNqa4pUV20r12A&amp;s</v>
       </c>
       <c r="AF33" t="str">
@@ -15868,12 +15868,12 @@
         <f>Palmon!AD35</f>
         <v>0</v>
       </c>
-      <c r="AD34">
-        <f>Palmon!AE35</f>
-        <v>0</v>
+      <c r="AD34" t="str">
+        <f>IF(Palmon!AE35="","",Palmon!AE35)</f>
+        <v/>
       </c>
       <c r="AE34" t="str">
-        <f>Palmon!AF35</f>
+        <f>IF(Palmon!AF35="","",Palmon!AF35)</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AF34" t="str">
@@ -16015,12 +16015,12 @@
         <v>0</v>
       </c>
       <c r="AD35" t="str">
-        <f>Palmon!AE36</f>
+        <f>IF(Palmon!AE36="","",Palmon!AE36)</f>
         <v>https://scontent-cdg4-2.xx.fbcdn.net/v/t39.30808-6/649210457_122193691484516338_487581885207006414_n.jpg?_nc_cat=109&amp;ccb=1-7&amp;_nc_sid=13d280&amp;_nc_ohc=wC2lV9slkY0Q7kNvwFsmsEi&amp;_nc_oc=AdoKFb_1lsq4UKznFnmvtUqFji4Fy3cRlYhvboqzO_RsdrIGc0H1ylJ_YUjH-ZC78Mo&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-2.xx&amp;_nc_gid=Djk5o2l4ZrQNgbZ5SKGinA&amp;_nc_ss=7a30f&amp;oh=00_AfyKhBvM3HYsSpbWT_gcFpYi9I2AfF0V35uyBreinYCQwQ&amp;oe=69C8204C</v>
       </c>
-      <c r="AE35">
-        <f>Palmon!AF36</f>
-        <v>0</v>
+      <c r="AE35" t="str">
+        <f>IF(Palmon!AF36="","",Palmon!AF36)</f>
+        <v/>
       </c>
       <c r="AF35">
         <f>Palmon!AG36</f>
@@ -16161,12 +16161,12 @@
         <v>0</v>
       </c>
       <c r="AD36" t="str">
-        <f>Palmon!AE37</f>
+        <f>IF(Palmon!AE37="","",Palmon!AE37)</f>
         <v>https://scontent-cdg4-2.xx.fbcdn.net/v/t39.30808-6/649210457_122193691484516338_487581885207006414_n.jpg?_nc_cat=109&amp;ccb=1-7&amp;_nc_sid=13d280&amp;_nc_ohc=wC2lV9slkY0Q7kNvwFsmsEi&amp;_nc_oc=AdoKFb_1lsq4UKznFnmvtUqFji4Fy3cRlYhvboqzO_RsdrIGc0H1ylJ_YUjH-ZC78Mo&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-2.xx&amp;_nc_gid=Djk5o2l4ZrQNgbZ5SKGinA&amp;_nc_ss=7a30f&amp;oh=00_AfyKhBvM3HYsSpbWT_gcFpYi9I2AfF0V35uyBreinYCQwQ&amp;oe=69C8204C</v>
       </c>
-      <c r="AE36">
-        <f>Palmon!AF37</f>
-        <v>0</v>
+      <c r="AE36" t="str">
+        <f>IF(Palmon!AF37="","",Palmon!AF37)</f>
+        <v/>
       </c>
       <c r="AF36">
         <f>Palmon!AG37</f>
@@ -16307,11 +16307,11 @@
         <v>0</v>
       </c>
       <c r="AD37" t="str">
-        <f>Palmon!AE38</f>
+        <f>IF(Palmon!AE38="","",Palmon!AE38)</f>
         <v>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQCf63iS9oq-SMn3DO74UTS2j_zSrzNVTRMOQ&amp;s</v>
       </c>
       <c r="AE37" t="str">
-        <f>Palmon!AF38</f>
+        <f>IF(Palmon!AF38="","",Palmon!AF38)</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AF37" t="str">
@@ -16452,12 +16452,12 @@
         <f>Palmon!AD39</f>
         <v>0</v>
       </c>
-      <c r="AD38">
-        <f>Palmon!AE39</f>
-        <v>0</v>
+      <c r="AD38" t="str">
+        <f>IF(Palmon!AE39="","",Palmon!AE39)</f>
+        <v/>
       </c>
       <c r="AE38" t="str">
-        <f>Palmon!AF39</f>
+        <f>IF(Palmon!AF39="","",Palmon!AF39)</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AF38" t="str">
@@ -16598,12 +16598,12 @@
         <f>Palmon!AD40</f>
         <v>0</v>
       </c>
-      <c r="AD39">
-        <f>Palmon!AE40</f>
-        <v>0</v>
+      <c r="AD39" t="str">
+        <f>IF(Palmon!AE40="","",Palmon!AE40)</f>
+        <v/>
       </c>
       <c r="AE39" t="str">
-        <f>Palmon!AF40</f>
+        <f>IF(Palmon!AF40="","",Palmon!AF40)</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AF39" t="str">
@@ -16744,12 +16744,12 @@
         <f>Palmon!AD41</f>
         <v>0</v>
       </c>
-      <c r="AD40">
-        <f>Palmon!AE41</f>
-        <v>0</v>
+      <c r="AD40" t="str">
+        <f>IF(Palmon!AE41="","",Palmon!AE41)</f>
+        <v/>
       </c>
       <c r="AE40" t="str">
-        <f>Palmon!AF41</f>
+        <f>IF(Palmon!AF41="","",Palmon!AF41)</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AF40" t="str">
@@ -16890,12 +16890,12 @@
         <f>Palmon!AD42</f>
         <v>0</v>
       </c>
-      <c r="AD41">
-        <f>Palmon!AE42</f>
-        <v>0</v>
+      <c r="AD41" t="str">
+        <f>IF(Palmon!AE42="","",Palmon!AE42)</f>
+        <v/>
       </c>
       <c r="AE41" t="str">
-        <f>Palmon!AF42</f>
+        <f>IF(Palmon!AF42="","",Palmon!AF42)</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AF41" t="str">
@@ -17036,12 +17036,12 @@
         <f>Palmon!AD43</f>
         <v>0</v>
       </c>
-      <c r="AD42">
-        <f>Palmon!AE43</f>
-        <v>0</v>
+      <c r="AD42" t="str">
+        <f>IF(Palmon!AE43="","",Palmon!AE43)</f>
+        <v/>
       </c>
       <c r="AE42" t="str">
-        <f>Palmon!AF43</f>
+        <f>IF(Palmon!AF43="","",Palmon!AF43)</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AF42" t="str">
@@ -17182,12 +17182,12 @@
         <f>Palmon!AD44</f>
         <v>0</v>
       </c>
-      <c r="AD43">
-        <f>Palmon!AE44</f>
-        <v>0</v>
+      <c r="AD43" t="str">
+        <f>IF(Palmon!AE44="","",Palmon!AE44)</f>
+        <v/>
       </c>
       <c r="AE43" t="str">
-        <f>Palmon!AF44</f>
+        <f>IF(Palmon!AF44="","",Palmon!AF44)</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AF43" t="str">
@@ -17328,12 +17328,12 @@
         <f>Palmon!AD45</f>
         <v>0</v>
       </c>
-      <c r="AD44">
-        <f>Palmon!AE45</f>
-        <v>0</v>
+      <c r="AD44" t="str">
+        <f>IF(Palmon!AE45="","",Palmon!AE45)</f>
+        <v/>
       </c>
       <c r="AE44" t="str">
-        <f>Palmon!AF45</f>
+        <f>IF(Palmon!AF45="","",Palmon!AF45)</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AF44" t="str">
@@ -17474,12 +17474,12 @@
         <f>Palmon!AD46</f>
         <v>0</v>
       </c>
-      <c r="AD45">
-        <f>Palmon!AE46</f>
-        <v>0</v>
+      <c r="AD45" t="str">
+        <f>IF(Palmon!AE46="","",Palmon!AE46)</f>
+        <v/>
       </c>
       <c r="AE45" t="str">
-        <f>Palmon!AF46</f>
+        <f>IF(Palmon!AF46="","",Palmon!AF46)</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AF45" t="str">

--- a/data/PS - Estimation (version 1).xlsx
+++ b/data/PS - Estimation (version 1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xvjm020\Documents\Personnel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C639114-F005-4191-9F4B-591C8425A082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{954A2804-E0F2-4186-BCAA-BBC887C95201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{9D83D047-1CAD-4BF9-942E-B289F790400E}"/>
   </bookViews>
@@ -38614,7 +38614,7 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="225">
-        <v>7.3571428571428497</v>
+        <v>8</v>
       </c>
       <c r="B29" s="250" t="s">
         <v>273</v>
@@ -38645,7 +38645,7 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="225">
-        <v>7.5476190476190403</v>
+        <v>8</v>
       </c>
       <c r="B30" s="250" t="s">
         <v>273</v>
@@ -38676,7 +38676,7 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="225">
-        <v>7.7380952380952301</v>
+        <v>8</v>
       </c>
       <c r="B31" s="250" t="s">
         <v>273</v>
@@ -38707,7 +38707,7 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="225">
-        <v>7.9285714285714199</v>
+        <v>8</v>
       </c>
       <c r="B32" s="250" t="s">
         <v>273</v>
@@ -38738,7 +38738,7 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="225">
-        <v>8.1190476190476204</v>
+        <v>9</v>
       </c>
       <c r="B33" s="250" t="s">
         <v>274</v>
@@ -38769,7 +38769,7 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="225">
-        <v>8.3095238095238102</v>
+        <v>9</v>
       </c>
       <c r="B34" s="250" t="s">
         <v>274</v>
@@ -38800,7 +38800,7 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="225">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="B35" s="250" t="s">
         <v>274</v>
@@ -38831,7 +38831,7 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="225">
-        <v>8.6904761904761898</v>
+        <v>9</v>
       </c>
       <c r="B36" s="250" t="s">
         <v>274</v>
@@ -38862,7 +38862,7 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="225">
-        <v>8.8809523809523796</v>
+        <v>10</v>
       </c>
       <c r="B37" s="250" t="s">
         <v>275</v>
@@ -38893,7 +38893,7 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="225">
-        <v>9.0714285714285694</v>
+        <v>10</v>
       </c>
       <c r="B38" s="250" t="s">
         <v>275</v>
@@ -38924,7 +38924,7 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="225">
-        <v>9.2619047619047592</v>
+        <v>10</v>
       </c>
       <c r="B39" s="250" t="s">
         <v>275</v>
@@ -38955,7 +38955,7 @@
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="225">
-        <v>9.4523809523809508</v>
+        <v>10</v>
       </c>
       <c r="B40" s="250" t="s">
         <v>275</v>
@@ -38986,7 +38986,7 @@
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="225">
-        <v>9.6428571428571406</v>
+        <v>11</v>
       </c>
       <c r="B41" s="250" t="s">
         <v>276</v>
@@ -39017,7 +39017,7 @@
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="225">
-        <v>9.8333333333333304</v>
+        <v>11</v>
       </c>
       <c r="B42" s="250" t="s">
         <v>276</v>
@@ -39048,7 +39048,7 @@
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="225">
-        <v>10.023809523809501</v>
+        <v>11</v>
       </c>
       <c r="B43" s="250" t="s">
         <v>276</v>
@@ -39079,7 +39079,7 @@
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="225">
-        <v>10.214285714285699</v>
+        <v>11</v>
       </c>
       <c r="B44" s="250" t="s">
         <v>276</v>

--- a/data/PS - Estimation (version 1).xlsx
+++ b/data/PS - Estimation (version 1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xvjm020\Documents\Personnel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43A65372-2394-4137-AEB7-5CEBF401809F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDDB9F42-0C1C-4753-A82B-1AB4FF63830B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9D83D047-1CAD-4BF9-942E-B289F790400E}"/>
   </bookViews>
@@ -2471,7 +2471,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="300">
+  <cellXfs count="299">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2969,6 +2969,13 @@
     <xf numFmtId="3" fontId="1" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3102,16 +3109,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5518,51 +5515,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="263" t="s">
+      <c r="B1" s="266" t="s">
         <v>107</v>
       </c>
-      <c r="C1" s="264"/>
-      <c r="D1" s="264"/>
-      <c r="E1" s="264"/>
-      <c r="F1" s="264"/>
-      <c r="G1" s="264"/>
-      <c r="H1" s="264"/>
-      <c r="I1" s="265"/>
-      <c r="J1" s="260" t="s">
+      <c r="C1" s="267"/>
+      <c r="D1" s="267"/>
+      <c r="E1" s="267"/>
+      <c r="F1" s="267"/>
+      <c r="G1" s="267"/>
+      <c r="H1" s="267"/>
+      <c r="I1" s="268"/>
+      <c r="J1" s="263" t="s">
         <v>89</v>
       </c>
-      <c r="K1" s="261"/>
-      <c r="L1" s="261"/>
-      <c r="M1" s="261"/>
-      <c r="N1" s="262"/>
-      <c r="P1" s="268" t="s">
+      <c r="K1" s="264"/>
+      <c r="L1" s="264"/>
+      <c r="M1" s="264"/>
+      <c r="N1" s="265"/>
+      <c r="P1" s="271" t="s">
         <v>17</v>
       </c>
-      <c r="Q1" s="269"/>
-      <c r="R1" s="269"/>
-      <c r="S1" s="269"/>
-      <c r="T1" s="269"/>
-      <c r="U1" s="269"/>
-      <c r="V1" s="270"/>
-      <c r="X1" s="266" t="s">
+      <c r="Q1" s="272"/>
+      <c r="R1" s="272"/>
+      <c r="S1" s="272"/>
+      <c r="T1" s="272"/>
+      <c r="U1" s="272"/>
+      <c r="V1" s="273"/>
+      <c r="X1" s="269" t="s">
         <v>79</v>
       </c>
-      <c r="Y1" s="267"/>
-      <c r="AA1" s="258" t="s">
+      <c r="Y1" s="270"/>
+      <c r="AA1" s="261" t="s">
         <v>93</v>
       </c>
-      <c r="AB1" s="258"/>
-      <c r="AC1" s="259"/>
-      <c r="AE1" s="251" t="s">
+      <c r="AB1" s="261"/>
+      <c r="AC1" s="262"/>
+      <c r="AE1" s="254" t="s">
         <v>143</v>
       </c>
-      <c r="AF1" s="252"/>
-      <c r="AG1" s="253"/>
-      <c r="AI1" s="251" t="s">
+      <c r="AF1" s="255"/>
+      <c r="AG1" s="256"/>
+      <c r="AI1" s="254" t="s">
         <v>103</v>
       </c>
-      <c r="AJ1" s="252"/>
-      <c r="AK1" s="253"/>
+      <c r="AJ1" s="255"/>
+      <c r="AK1" s="256"/>
     </row>
     <row r="2" spans="1:37" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B2" s="23" t="s">
@@ -6530,7 +6527,7 @@
       </c>
       <c r="AB10" s="63">
         <f>RANK($AA10,$AA$3:$AA$47)+COUNTIF($AA$3:$AA10,AA10)-1</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AC10" s="61" t="str" cm="1">
         <f t="array" ref="AC10">IFERROR(_xlfn.IFS($AB10&lt;8,1,$AB10&lt;15,2,$AB10&lt;21,3),"")</f>
@@ -7128,7 +7125,7 @@
         <v>98</v>
       </c>
       <c r="E16" s="63">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="F16" s="125" cm="1">
         <f t="array" ref="F16">IsUpgradable(E16)</f>
@@ -7191,7 +7188,7 @@
       </c>
       <c r="X16" s="13" cm="1">
         <f t="array" ref="X16">LevelUpgradeCost($E16)</f>
-        <v>3390620000</v>
+        <v>2831420000</v>
       </c>
       <c r="Y16" s="61">
         <f t="shared" si="4"/>
@@ -7199,11 +7196,11 @@
       </c>
       <c r="AA16" s="110">
         <f t="shared" si="5"/>
-        <v>2430</v>
+        <v>2440</v>
       </c>
       <c r="AB16" s="63">
         <f>RANK($AA16,$AA$3:$AA$47)+COUNTIF($AA$3:$AA16,AA16)-1</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AC16" s="61" t="str" cm="1">
         <f t="array" ref="AC16">IFERROR(_xlfn.IFS($AB16&lt;8,1,$AB16&lt;15,2,$AB16&lt;21,3),"")</f>
@@ -10718,7 +10715,7 @@
       <c r="I49" s="5"/>
       <c r="X49" s="5">
         <f>SUMPRODUCT(X3:X47,Y3:Y47)</f>
-        <v>96807467400</v>
+        <v>96248267400</v>
       </c>
     </row>
     <row r="50" spans="2:24" ht="12" customHeight="1" x14ac:dyDescent="0.2">
@@ -10745,10 +10742,10 @@
       <c r="I52" s="5"/>
     </row>
     <row r="53" spans="2:24" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="256" t="s">
+      <c r="B53" s="259" t="s">
         <v>48</v>
       </c>
-      <c r="C53" s="257"/>
+      <c r="C53" s="260"/>
       <c r="D53" s="142"/>
       <c r="I53" s="5"/>
     </row>
@@ -10829,7 +10826,7 @@
       </c>
       <c r="Q58" s="1">
         <f>SUMIF($C$3:$C$47,"=" &amp; $P58,$E$3:$E$47)</f>
-        <v>1631</v>
+        <v>1641</v>
       </c>
       <c r="R58" s="1">
         <f>COUNTIFS($C$3:$C$47,"=" &amp; $P58,$E$3:$E$47,"&gt;0")</f>
@@ -10837,15 +10834,15 @@
       </c>
       <c r="S58" s="1">
         <f>Q58/R58</f>
-        <v>203.875</v>
+        <v>205.125</v>
       </c>
       <c r="X58"/>
     </row>
     <row r="59" spans="2:24" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="254" t="s">
+      <c r="B59" s="257" t="s">
         <v>203</v>
       </c>
-      <c r="C59" s="255"/>
+      <c r="C59" s="258"/>
       <c r="D59" s="142"/>
       <c r="I59" s="5"/>
       <c r="P59" s="1" t="s">
@@ -11098,7 +11095,7 @@
     <mergeCell ref="X1:Y1"/>
     <mergeCell ref="P1:V1"/>
   </mergeCells>
-  <conditionalFormatting sqref="B52:C52 B58:C58 C60:C62 B63:C82 B3:C49">
+  <conditionalFormatting sqref="B3:C49 B52:C52 B58:C58 C60:C62 B63:C82">
     <cfRule type="expression" dxfId="77" priority="108">
       <formula>$C3="Fire"</formula>
     </cfRule>
@@ -11112,7 +11109,7 @@
       <formula>$C3="Wood"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D58:D82 D3:D54">
+  <conditionalFormatting sqref="D3:D54 D58:D82">
     <cfRule type="cellIs" dxfId="73" priority="76" operator="equal">
       <formula>"Attack"</formula>
     </cfRule>
@@ -11573,7 +11570,7 @@
       </c>
       <c r="F9" t="str">
         <f>Palmon!B10 &amp; "," &amp; Palmon!C10 &amp; "," &amp; Palmon!D10 &amp; "," &amp; Palmon!E10 &amp; "," &amp; Palmon!G10 &amp; "," &amp; SUBSTITUTE(Palmon!H10,",",".") &amp; "," &amp; Palmon!I10 &amp; "," &amp; SUBSTITUTE(Palmon!P10,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q10,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R10,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S10,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T10,",",".") &amp; "," &amp; Palmon!J10 &amp; "," &amp; Palmon!K10 &amp; "," &amp; Palmon!L10 &amp; "," &amp; Palmon!M10 &amp; "," &amp; Palmon!N10 &amp; "," &amp; SUBSTITUTE(Palmon!U10,",",".") &amp; "," &amp; Palmon!V10 &amp; "," &amp; Palmon!X10 &amp; "," &amp; Palmon!Y10 &amp; "," &amp; Palmon!AA10 &amp; "," &amp; Palmon!AB10 &amp; "," &amp; Palmon!AC10 &amp; "," &amp; Palmon!AE10 &amp; "," &amp; Palmon!AF10 &amp; "," &amp; Palmon!AI10 &amp; "," &amp; Palmon!AJ10</f>
-        <v>Limudroid,Electricity,Attack,230,2,2.2,4,1,1,0.4,0,0,1,1,5,,,0.117948717948718,856,3390620000,1,2430,23,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQzaI21taP2V17MKjiPAeulm4V9qfST4umPdg&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRMlruQNUenhVk-fAEq9d3Wi8zw--0GbkLGJrX1CuQ1&amp;s,Bunodroid,</v>
+        <v>Limudroid,Electricity,Attack,230,2,2.2,4,1,1,0.4,0,0,1,1,5,,,0.117948717948718,856,3390620000,1,2430,24,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQzaI21taP2V17MKjiPAeulm4V9qfST4umPdg&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRMlruQNUenhVk-fAEq9d3Wi8zw--0GbkLGJrX1CuQ1&amp;s,Bunodroid,</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -11729,7 +11726,7 @@
       </c>
       <c r="F15" t="str">
         <f>Palmon!B16 &amp; "," &amp; Palmon!C16 &amp; "," &amp; Palmon!D16 &amp; "," &amp; Palmon!E16 &amp; "," &amp; Palmon!G16 &amp; "," &amp; SUBSTITUTE(Palmon!H16,",",".") &amp; "," &amp; Palmon!I16 &amp; "," &amp; SUBSTITUTE(Palmon!P16,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q16,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R16,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S16,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T16,",",".") &amp; "," &amp; Palmon!J16 &amp; "," &amp; Palmon!K16 &amp; "," &amp; Palmon!L16 &amp; "," &amp; Palmon!M16 &amp; "," &amp; Palmon!N16 &amp; "," &amp; SUBSTITUTE(Palmon!U16,",",".") &amp; "," &amp; Palmon!V16 &amp; "," &amp; Palmon!X16 &amp; "," &amp; Palmon!Y16 &amp; "," &amp; Palmon!AA16 &amp; "," &amp; Palmon!AB16 &amp; "," &amp; Palmon!AC16 &amp; "," &amp; Palmon!AE16 &amp; "," &amp; Palmon!AF16 &amp; "," &amp; Palmon!AI16 &amp; "," &amp; Palmon!AJ16</f>
-        <v>Statchew,Wood,Defend,230,2,2.2,10,1,1,0.4,0,0,15,5,9,,,0.117948717948718,850,3390620000,1,2430,24,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSC1rp-0lIuUyVvSi8kN_vJnr_Ln4mF4lh4zg&amp;s, ,Anubeast,</v>
+        <v>Statchew,Wood,Defend,240,2,2.2,10,1,1,0.4,0,0,15,5,9,,,0.117948717948718,850,2831420000,1,2440,23,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSC1rp-0lIuUyVvSi8kN_vJnr_Ln4mF4lh4zg&amp;s, ,Anubeast,</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -16398,7 +16395,7 @@
       </c>
       <c r="AA9">
         <f>Palmon!AB10</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB9" t="str">
         <f>Palmon!AC10</f>
@@ -17182,7 +17179,7 @@
       </c>
       <c r="D15">
         <f>Palmon!E16</f>
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="E15">
         <f>Palmon!F16</f>
@@ -17258,7 +17255,7 @@
       </c>
       <c r="W15">
         <f>Palmon!X16</f>
-        <v>3390620000</v>
+        <v>2831420000</v>
       </c>
       <c r="X15">
         <f>Palmon!Y16</f>
@@ -17270,11 +17267,11 @@
       </c>
       <c r="Z15">
         <f>Palmon!AA16</f>
-        <v>2430</v>
+        <v>2440</v>
       </c>
       <c r="AA15">
         <f>Palmon!AB16</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AB15" t="str">
         <f>Palmon!AC16</f>
@@ -21859,24 +21856,24 @@
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="271" t="s">
+      <c r="E2" s="274" t="s">
         <v>91</v>
       </c>
-      <c r="F2" s="272"/>
-      <c r="G2" s="272"/>
-      <c r="H2" s="272"/>
-      <c r="I2" s="272"/>
-      <c r="J2" s="273"/>
+      <c r="F2" s="275"/>
+      <c r="G2" s="275"/>
+      <c r="H2" s="275"/>
+      <c r="I2" s="275"/>
+      <c r="J2" s="276"/>
       <c r="L2" s="1"/>
-      <c r="M2" s="271" t="s">
+      <c r="M2" s="274" t="s">
         <v>109</v>
       </c>
-      <c r="N2" s="272"/>
-      <c r="O2" s="272"/>
-      <c r="P2" s="272"/>
-      <c r="Q2" s="272"/>
-      <c r="R2" s="272"/>
-      <c r="S2" s="273"/>
+      <c r="N2" s="275"/>
+      <c r="O2" s="275"/>
+      <c r="P2" s="275"/>
+      <c r="Q2" s="275"/>
+      <c r="R2" s="275"/>
+      <c r="S2" s="276"/>
     </row>
     <row r="3" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="str" cm="1">
@@ -22328,14 +22325,14 @@
       </c>
       <c r="J12" s="40"/>
       <c r="L12" s="1"/>
-      <c r="M12" s="271" t="str">
+      <c r="M12" s="274" t="str">
         <f>TCD!E2 &amp; " per Type"</f>
         <v>Palmon upgrade costs per Type</v>
       </c>
-      <c r="N12" s="272"/>
-      <c r="O12" s="272"/>
-      <c r="P12" s="272"/>
-      <c r="Q12" s="273"/>
+      <c r="N12" s="275"/>
+      <c r="O12" s="275"/>
+      <c r="P12" s="275"/>
+      <c r="Q12" s="276"/>
       <c r="R12" s="1"/>
     </row>
     <row r="13" spans="2:23" x14ac:dyDescent="0.25">
@@ -22704,7 +22701,7 @@
         <v>Wood</v>
       </c>
       <c r="V19" s="194">
-        <v>232.85714285714286</v>
+        <v>234.28571428571428</v>
       </c>
       <c r="W19" s="195" cm="1">
         <f t="array" ref="W19">COUNTA(_xlfn._xlws.FILTER(C6:C45,C6:C45=$U19,""))</f>
@@ -22758,7 +22755,7 @@
       <c r="R20" s="1"/>
       <c r="V20" s="197">
         <f>AVERAGE(V16:V19)</f>
-        <v>236.54761904761907</v>
+        <v>236.90476190476193</v>
       </c>
       <c r="W20" s="196">
         <f>SUM(W16:W19)</f>
@@ -22826,15 +22823,15 @@
       </c>
       <c r="J22" s="40"/>
       <c r="L22" s="1"/>
-      <c r="M22" s="271" t="s">
+      <c r="M22" s="274" t="s">
         <v>90</v>
       </c>
-      <c r="N22" s="272"/>
-      <c r="O22" s="272"/>
-      <c r="P22" s="272"/>
-      <c r="Q22" s="272"/>
-      <c r="R22" s="272"/>
-      <c r="S22" s="273"/>
+      <c r="N22" s="275"/>
+      <c r="O22" s="275"/>
+      <c r="P22" s="275"/>
+      <c r="Q22" s="275"/>
+      <c r="R22" s="275"/>
+      <c r="S22" s="276"/>
     </row>
     <row r="23" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B23" s="36" t="str">
@@ -23290,11 +23287,11 @@
       </c>
       <c r="J32" s="40"/>
       <c r="L32" s="1"/>
-      <c r="M32" s="271" t="s">
+      <c r="M32" s="274" t="s">
         <v>95</v>
       </c>
-      <c r="N32" s="272"/>
-      <c r="O32" s="273"/>
+      <c r="N32" s="275"/>
+      <c r="O32" s="276"/>
       <c r="P32" s="1"/>
       <c r="Q32" s="1"/>
       <c r="R32" s="1"/>
@@ -23607,11 +23604,11 @@
       <c r="H40" s="33"/>
       <c r="I40" s="33"/>
       <c r="J40" s="40"/>
-      <c r="L40" s="271" t="s">
+      <c r="L40" s="274" t="s">
         <v>94</v>
       </c>
-      <c r="M40" s="272"/>
-      <c r="N40" s="273"/>
+      <c r="M40" s="275"/>
+      <c r="N40" s="276"/>
       <c r="O40" s="1"/>
       <c r="P40" s="1"/>
       <c r="Q40" s="1"/>
@@ -24321,7 +24318,7 @@
     </row>
     <row r="68" spans="7:20" s="1" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="G68" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H68" s="1" t="str">
         <v/>
@@ -24330,7 +24327,7 @@
         <v>Limudroid</v>
       </c>
       <c r="M68" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N68" s="1" t="str">
         <v/>
@@ -24554,7 +24551,7 @@
         <v/>
       </c>
       <c r="H78" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L78" s="1" t="str">
         <v>Statchew</v>
@@ -24563,7 +24560,7 @@
         <v/>
       </c>
       <c r="N78" s="1">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P78" s="1" t="str">
         <v/>
@@ -24892,12 +24889,12 @@
     </row>
     <row r="2" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="B2" s="283" t="s">
+      <c r="B2" s="286" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="284"/>
-      <c r="D2" s="284"/>
-      <c r="E2" s="284"/>
+      <c r="C2" s="287"/>
+      <c r="D2" s="287"/>
+      <c r="E2" s="287"/>
       <c r="F2" s="58" t="s">
         <v>19</v>
       </c>
@@ -24905,12 +24902,12 @@
         <f>VLOOKUP($G$7,PalmonList,8,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H2" s="274" t="e" vm="1">
+      <c r="H2" s="277" t="e" vm="1">
         <f>IFERROR(_xlfn.IMAGE(VLOOKUP($G$7,PalmonList,30,FALSE),$G$7,0),"")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I2" s="275"/>
-      <c r="J2" s="276"/>
+      <c r="I2" s="278"/>
+      <c r="J2" s="279"/>
     </row>
     <row r="3" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
@@ -24933,9 +24930,9 @@
         <f>VLOOKUP($G$7,PalmonList,7,FALSE)</f>
         <v>5</v>
       </c>
-      <c r="H3" s="277"/>
-      <c r="I3" s="278"/>
-      <c r="J3" s="279"/>
+      <c r="H3" s="280"/>
+      <c r="I3" s="281"/>
+      <c r="J3" s="282"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -24958,9 +24955,9 @@
         <v>1</v>
       </c>
       <c r="G4" s="226"/>
-      <c r="H4" s="277"/>
-      <c r="I4" s="278"/>
-      <c r="J4" s="279"/>
+      <c r="H4" s="280"/>
+      <c r="I4" s="281"/>
+      <c r="J4" s="282"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -24983,9 +24980,9 @@
         <v>1</v>
       </c>
       <c r="G5" s="226"/>
-      <c r="H5" s="277"/>
-      <c r="I5" s="278"/>
-      <c r="J5" s="279"/>
+      <c r="H5" s="280"/>
+      <c r="I5" s="281"/>
+      <c r="J5" s="282"/>
     </row>
     <row r="6" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
@@ -25008,9 +25005,9 @@
         <v>1</v>
       </c>
       <c r="G6" s="226"/>
-      <c r="H6" s="277"/>
-      <c r="I6" s="278"/>
-      <c r="J6" s="279"/>
+      <c r="H6" s="280"/>
+      <c r="I6" s="281"/>
+      <c r="J6" s="282"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -25035,9 +25032,9 @@
       <c r="G7" s="227" t="s">
         <v>139</v>
       </c>
-      <c r="H7" s="277"/>
-      <c r="I7" s="278"/>
-      <c r="J7" s="279"/>
+      <c r="H7" s="280"/>
+      <c r="I7" s="281"/>
+      <c r="J7" s="282"/>
     </row>
     <row r="8" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -25062,9 +25059,9 @@
       <c r="G8" s="230" t="s">
         <v>22</v>
       </c>
-      <c r="H8" s="277"/>
-      <c r="I8" s="278"/>
-      <c r="J8" s="279"/>
+      <c r="H8" s="280"/>
+      <c r="I8" s="281"/>
+      <c r="J8" s="282"/>
     </row>
     <row r="9" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -25088,9 +25085,9 @@
         <f>SUMPRODUCT($F$4:$F$8,$D$4:$D$8)/$D$9</f>
         <v>1</v>
       </c>
-      <c r="H9" s="280"/>
-      <c r="I9" s="281"/>
-      <c r="J9" s="282"/>
+      <c r="H9" s="283"/>
+      <c r="I9" s="284"/>
+      <c r="J9" s="285"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
@@ -25173,28 +25170,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="287" t="s">
+      <c r="A1" s="290" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="288"/>
-      <c r="C1" s="288"/>
-      <c r="D1" s="288"/>
-      <c r="E1" s="288"/>
-      <c r="F1" s="289"/>
-      <c r="H1" s="287" t="s">
+      <c r="B1" s="291"/>
+      <c r="C1" s="291"/>
+      <c r="D1" s="291"/>
+      <c r="E1" s="291"/>
+      <c r="F1" s="292"/>
+      <c r="H1" s="290" t="s">
         <v>89</v>
       </c>
-      <c r="I1" s="288"/>
-      <c r="J1" s="288"/>
-      <c r="K1" s="288"/>
-      <c r="L1" s="289"/>
-      <c r="N1" s="287" t="s">
+      <c r="I1" s="291"/>
+      <c r="J1" s="291"/>
+      <c r="K1" s="291"/>
+      <c r="L1" s="292"/>
+      <c r="N1" s="290" t="s">
         <v>103</v>
       </c>
-      <c r="O1" s="288"/>
-      <c r="P1" s="288"/>
-      <c r="Q1" s="288"/>
-      <c r="R1" s="289"/>
+      <c r="O1" s="291"/>
+      <c r="P1" s="291"/>
+      <c r="Q1" s="291"/>
+      <c r="R1" s="292"/>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A2" s="54" t="s">
@@ -25731,13 +25728,13 @@
       <c r="U8" s="1" t="str">
         <v>Bufonobi</v>
       </c>
-      <c r="Z8" s="290" t="s">
+      <c r="Z8" s="293" t="s">
         <v>30</v>
       </c>
-      <c r="AA8" s="291"/>
-      <c r="AB8" s="291"/>
-      <c r="AC8" s="291"/>
-      <c r="AD8" s="292"/>
+      <c r="AA8" s="294"/>
+      <c r="AB8" s="294"/>
+      <c r="AC8" s="294"/>
+      <c r="AD8" s="295"/>
     </row>
     <row r="9" spans="1:32" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
@@ -25896,10 +25893,10 @@
         <f>1/60</f>
         <v>1.6666666666666666E-2</v>
       </c>
-      <c r="AE10" s="285" t="s">
+      <c r="AE10" s="288" t="s">
         <v>32</v>
       </c>
-      <c r="AF10" s="286"/>
+      <c r="AF10" s="289"/>
     </row>
     <row r="11" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
@@ -37615,35 +37612,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="254" t="s">
+      <c r="A1" s="257" t="s">
         <v>203</v>
       </c>
-      <c r="B1" s="255"/>
-      <c r="D1" s="293" t="s">
+      <c r="B1" s="258"/>
+      <c r="D1" s="296" t="s">
         <v>240</v>
       </c>
-      <c r="E1" s="294"/>
-      <c r="F1" s="294"/>
-      <c r="H1" s="293" t="s">
+      <c r="E1" s="297"/>
+      <c r="F1" s="297"/>
+      <c r="H1" s="296" t="s">
         <v>240</v>
       </c>
-      <c r="I1" s="294"/>
-      <c r="J1" s="294"/>
-      <c r="K1" s="294"/>
-      <c r="L1" s="294"/>
-      <c r="M1" s="294"/>
-      <c r="N1" s="294"/>
-      <c r="O1" s="294"/>
-      <c r="P1" s="294"/>
-      <c r="Q1" s="294"/>
-      <c r="Z1" s="254" t="s">
+      <c r="I1" s="297"/>
+      <c r="J1" s="297"/>
+      <c r="K1" s="297"/>
+      <c r="L1" s="297"/>
+      <c r="M1" s="297"/>
+      <c r="N1" s="297"/>
+      <c r="O1" s="297"/>
+      <c r="P1" s="297"/>
+      <c r="Q1" s="297"/>
+      <c r="Z1" s="257" t="s">
         <v>257</v>
       </c>
-      <c r="AA1" s="255"/>
-      <c r="AC1" s="254" t="s">
+      <c r="AA1" s="258"/>
+      <c r="AC1" s="257" t="s">
         <v>262</v>
       </c>
-      <c r="AD1" s="255"/>
+      <c r="AD1" s="258"/>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="240" t="s">
@@ -38226,26 +38223,26 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="7" width="15.28515625" customWidth="1"/>
-    <col min="8" max="9" width="15.28515625" style="298" customWidth="1"/>
-    <col min="11" max="11" width="11.42578125" style="297"/>
+    <col min="8" max="9" width="15.28515625" style="253" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" style="252"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="254" t="s">
+      <c r="A1" s="257" t="s">
         <v>262</v>
       </c>
-      <c r="B1" s="295"/>
-      <c r="C1" s="295"/>
-      <c r="D1" s="255"/>
-      <c r="F1" s="293" t="s">
+      <c r="B1" s="298"/>
+      <c r="C1" s="298"/>
+      <c r="D1" s="258"/>
+      <c r="F1" s="296" t="s">
         <v>277</v>
       </c>
-      <c r="G1" s="299"/>
-      <c r="H1" s="299"/>
-      <c r="I1" s="299"/>
-      <c r="J1" s="299"/>
-      <c r="K1" s="299"/>
-      <c r="L1" s="299"/>
+      <c r="G1" s="297"/>
+      <c r="H1" s="297"/>
+      <c r="I1" s="297"/>
+      <c r="J1" s="297"/>
+      <c r="K1" s="297"/>
+      <c r="L1" s="297"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="223" t="s">
@@ -38275,10 +38272,10 @@
       <c r="J2" s="247" t="s">
         <v>79</v>
       </c>
-      <c r="K2" s="296" t="s">
+      <c r="K2" s="251" t="s">
         <v>279</v>
       </c>
-      <c r="L2" s="296" t="s">
+      <c r="L2" s="251" t="s">
         <v>387</v>
       </c>
     </row>

--- a/data/PS - Estimation (version 1).xlsx
+++ b/data/PS - Estimation (version 1).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xvjm020\Documents\Personnel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDDB9F42-0C1C-4753-A82B-1AB4FF63830B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B222438A-2567-49C6-8EEC-EA8CCF656B7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9D83D047-1CAD-4BF9-942E-B289F790400E}"/>
   </bookViews>
@@ -4791,7 +4791,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp2.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="22" fmlaLink="$C$50" max="30" min="1" page="10" val="27"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="22" fmlaLink="$C$50" max="30" min="1" page="10" val="28"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5669,9 +5669,9 @@
       <c r="E3" s="63">
         <v>270</v>
       </c>
-      <c r="F3" s="125" t="str" cm="1">
+      <c r="F3" s="125" cm="1">
         <f t="array" ref="F3">IsUpgradable(E3)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G3" s="127">
         <f t="shared" ref="G3:G27" si="0">INT(H3)</f>
@@ -5687,7 +5687,7 @@
         <v>30</v>
       </c>
       <c r="K3" s="7">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="L3" s="7">
         <v>30</v>
@@ -5730,11 +5730,11 @@
       </c>
       <c r="X3" s="13" cm="1">
         <f t="array" ref="X3">LevelUpgradeCost($E3)</f>
-        <v>135120000</v>
-      </c>
-      <c r="Y3" s="61" t="str">
+        <v>1515640000</v>
+      </c>
+      <c r="Y3" s="61">
         <f>F3</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AA3" s="110">
         <f>$H3*1000+$E3</f>
@@ -5742,7 +5742,7 @@
       </c>
       <c r="AB3" s="110">
         <f>RANK($AA3,$AA$3:$AA$47)+COUNTIF($AA$3:$AA3,AA3)-1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC3" s="61" cm="1">
         <f t="array" ref="AC3">IFERROR(_xlfn.IFS($AB3&lt;8,1,$AB3&lt;15,2,$AB3&lt;21,3),"")</f>
@@ -5783,9 +5783,9 @@
       <c r="E4" s="63">
         <v>270</v>
       </c>
-      <c r="F4" s="125" t="str" cm="1">
+      <c r="F4" s="125" cm="1">
         <f t="array" ref="F4">IsUpgradable(E4)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G4" s="127">
         <f t="shared" si="0"/>
@@ -5844,11 +5844,11 @@
       </c>
       <c r="X4" s="13" cm="1">
         <f t="array" ref="X4">LevelUpgradeCost($E4)</f>
-        <v>135120000</v>
-      </c>
-      <c r="Y4" s="61" t="str">
+        <v>1515640000</v>
+      </c>
+      <c r="Y4" s="61">
         <f t="shared" ref="Y4:Y47" si="4">F4</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AA4" s="110">
         <f t="shared" ref="AA4:AA47" si="5">$H4*1000+$E4</f>
@@ -5856,7 +5856,7 @@
       </c>
       <c r="AB4" s="63">
         <f>RANK($AA4,$AA$3:$AA$47)+COUNTIF($AA$3:$AA4,AA4)-1</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC4" s="61" cm="1">
         <f t="array" ref="AC4">IFERROR(_xlfn.IFS($AB4&lt;8,1,$AB4&lt;15,2,$AB4&lt;21,3),"")</f>
@@ -5893,9 +5893,9 @@
       <c r="E5" s="63">
         <v>270</v>
       </c>
-      <c r="F5" s="125" t="str" cm="1">
+      <c r="F5" s="125" cm="1">
         <f t="array" ref="F5">IsUpgradable(E5)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G5" s="127">
         <f t="shared" si="0"/>
@@ -5954,11 +5954,11 @@
       </c>
       <c r="X5" s="13" cm="1">
         <f t="array" ref="X5">LevelUpgradeCost($E5)</f>
-        <v>135120000</v>
-      </c>
-      <c r="Y5" s="61" t="str">
+        <v>1515640000</v>
+      </c>
+      <c r="Y5" s="61">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AA5" s="110">
         <f t="shared" si="5"/>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="AB5" s="63">
         <f>RANK($AA5,$AA$3:$AA$47)+COUNTIF($AA$3:$AA5,AA5)-1</f>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AC5" s="61" cm="1">
         <f t="array" ref="AC5">IFERROR(_xlfn.IFS($AB5&lt;8,1,$AB5&lt;15,2,$AB5&lt;21,3),"")</f>
@@ -6066,7 +6066,7 @@
       </c>
       <c r="X6" s="13" cm="1">
         <f t="array" ref="X6">LevelUpgradeCost($E6)</f>
-        <v>2123020000</v>
+        <v>3503540000</v>
       </c>
       <c r="Y6" s="61">
         <f t="shared" si="4"/>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="AB6" s="63">
         <f>RANK($AA6,$AA$3:$AA$47)+COUNTIF($AA$3:$AA6,AA6)-1</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC6" s="61" cm="1">
         <f t="array" ref="AC6">IFERROR(_xlfn.IFS($AB6&lt;8,1,$AB6&lt;15,2,$AB6&lt;21,3),"")</f>
@@ -6118,9 +6118,9 @@
       <c r="E7" s="63">
         <v>270</v>
       </c>
-      <c r="F7" s="125" t="str" cm="1">
+      <c r="F7" s="125" cm="1">
         <f t="array" ref="F7">IsUpgradable(E7)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G7" s="127">
         <f t="shared" ref="G7" si="7">INT(H7)</f>
@@ -6179,11 +6179,11 @@
       </c>
       <c r="X7" s="13" cm="1">
         <f t="array" ref="X7">LevelUpgradeCost($E7)</f>
-        <v>135120000</v>
-      </c>
-      <c r="Y7" s="61" t="str">
+        <v>1515640000</v>
+      </c>
+      <c r="Y7" s="61">
         <f t="shared" ref="Y7" si="9">F7</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AA7" s="110">
         <f t="shared" si="5"/>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="AB7" s="63">
         <f>RANK($AA7,$AA$3:$AA$47)+COUNTIF($AA$3:$AA7,AA7)-1</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC7" s="61" cm="1">
         <f t="array" ref="AC7">IFERROR(_xlfn.IFS($AB7&lt;8,1,$AB7&lt;15,2,$AB7&lt;21,3),"")</f>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="X8" s="13" cm="1">
         <f t="array" ref="X8">LevelUpgradeCost($E8)</f>
-        <v>5044093700</v>
+        <v>6424613700</v>
       </c>
       <c r="Y8" s="61">
         <f t="shared" si="4"/>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="X9" s="13" cm="1">
         <f t="array" ref="X9">LevelUpgradeCost($E9)</f>
-        <v>2831420000</v>
+        <v>4211940000</v>
       </c>
       <c r="Y9" s="61">
         <f t="shared" si="4"/>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="AB9" s="63">
         <f>RANK($AA9,$AA$3:$AA$47)+COUNTIF($AA$3:$AA9,AA9)-1</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AC9" s="61" cm="1">
         <f t="array" ref="AC9">IFERROR(_xlfn.IFS($AB9&lt;8,1,$AB9&lt;15,2,$AB9&lt;21,3),"")</f>
@@ -6515,7 +6515,7 @@
       </c>
       <c r="X10" s="13" cm="1">
         <f t="array" ref="X10">LevelUpgradeCost($E10)</f>
-        <v>3390620000</v>
+        <v>4771140000</v>
       </c>
       <c r="Y10" s="61">
         <f t="shared" si="4"/>
@@ -6527,7 +6527,7 @@
       </c>
       <c r="AB10" s="63">
         <f>RANK($AA10,$AA$3:$AA$47)+COUNTIF($AA$3:$AA10,AA10)-1</f>
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AC10" s="61" t="str" cm="1">
         <f t="array" ref="AC10">IFERROR(_xlfn.IFS($AB10&lt;8,1,$AB10&lt;15,2,$AB10&lt;21,3),"")</f>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="X11" s="13" cm="1">
         <f t="array" ref="X11">LevelUpgradeCost($E11)</f>
-        <v>2123020000</v>
+        <v>3503540000</v>
       </c>
       <c r="Y11" s="61">
         <f t="shared" si="4"/>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="AB11" s="63">
         <f>RANK($AA11,$AA$3:$AA$47)+COUNTIF($AA$3:$AA11,AA11)-1</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AC11" s="61" cm="1">
         <f t="array" ref="AC11">IFERROR(_xlfn.IFS($AB11&lt;8,1,$AB11&lt;15,2,$AB11&lt;21,3),"")</f>
@@ -6676,7 +6676,7 @@
         <v>98</v>
       </c>
       <c r="E12" s="63">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="F12" s="125" cm="1">
         <f t="array" ref="F12">IsUpgradable(E12)</f>
@@ -6687,7 +6687,7 @@
         <v>4</v>
       </c>
       <c r="H12" s="198">
-        <v>4</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="I12" s="123">
         <v>14</v>
@@ -6727,19 +6727,19 @@
       </c>
       <c r="T12" s="9">
         <f>IFERROR(CHOOSE(IF($H12&gt;=Details!$B$8,1,2),Details!$D$8,IF($H12&gt;Details!$B$8-1,IF($H12&lt;1,Details!$G$5,MOD($H12,Details!$B$8-1))*10*Details!$C$8,""))/Details!$D$8,0)</f>
-        <v>0</v>
+        <v>0.19999999999999929</v>
       </c>
       <c r="U12" s="9" cm="1">
         <f t="array" ref="U12">SUMPRODUCT(TRANSPOSE(Details!$D$4:$D$8),$P12:$T12)/Details!$D$9</f>
-        <v>0.48717948717948717</v>
+        <v>0.58974358974358942</v>
       </c>
       <c r="V12" s="13" cm="1">
         <f t="array" ref="V12">Details!$D$9-SUMPRODUCT(TRANSPOSE(Details!$D$4:$D$8),$P12:$T12)-$I12</f>
-        <v>486</v>
+        <v>386.00000000000034</v>
       </c>
       <c r="X12" s="13" cm="1">
         <f t="array" ref="X12">LevelUpgradeCost($E12)</f>
-        <v>3390620000</v>
+        <v>3503540000</v>
       </c>
       <c r="Y12" s="61">
         <f t="shared" si="4"/>
@@ -6747,11 +6747,11 @@
       </c>
       <c r="AA12" s="110">
         <f t="shared" si="5"/>
-        <v>4230</v>
+        <v>4350</v>
       </c>
       <c r="AB12" s="63">
         <f>RANK($AA12,$AA$3:$AA$47)+COUNTIF($AA$3:$AA12,AA12)-1</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC12" s="61" cm="1">
         <f t="array" ref="AC12">IFERROR(_xlfn.IFS($AB12&lt;8,1,$AB12&lt;15,2,$AB12&lt;21,3),"")</f>
@@ -6788,7 +6788,7 @@
         <v>98</v>
       </c>
       <c r="E13" s="63">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="F13" s="125" cm="1">
         <f t="array" ref="F13">IsUpgradable(E13)</f>
@@ -6799,7 +6799,7 @@
         <v>2</v>
       </c>
       <c r="H13" s="198">
-        <v>2.2999999999999998</v>
+        <v>2.4</v>
       </c>
       <c r="I13" s="123">
         <v>8</v>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="R13" s="9">
         <f>IFERROR(CHOOSE(IF($H13&gt;=Details!$B$6,1,2),Details!$D$6,IF($H13&gt;Details!$B$6-1,IF($H13&lt;1,Details!$G$5,MOD($H13,Details!$B$6-1))*10*Details!$C$6,""))/Details!$D$6,0)</f>
-        <v>0.59999999999999964</v>
+        <v>0.79999999999999982</v>
       </c>
       <c r="S13" s="9">
         <f>IFERROR(CHOOSE(IF($H13&gt;=Details!$B$7,1,2),Details!$D$7,IF($H13&gt;Details!$B$7-1,IF($H13&lt;1,Details!$G$5,MOD($H13,Details!$B$7-1))*10*Details!$C$7,""))/Details!$D$7,0)</f>
@@ -6843,15 +6843,15 @@
       </c>
       <c r="U13" s="9" cm="1">
         <f t="array" ref="U13">SUMPRODUCT(TRANSPOSE(Details!$D$4:$D$8),$P13:$T13)/Details!$D$9</f>
-        <v>0.13846153846153844</v>
+        <v>0.15897435897435896</v>
       </c>
       <c r="V13" s="13" cm="1">
         <f t="array" ref="V13">Details!$D$9-SUMPRODUCT(TRANSPOSE(Details!$D$4:$D$8),$P13:$T13)-$I13</f>
-        <v>832</v>
+        <v>812</v>
       </c>
       <c r="X13" s="13" cm="1">
         <f t="array" ref="X13">LevelUpgradeCost($E13)</f>
-        <v>3390620000</v>
+        <v>4211940000</v>
       </c>
       <c r="Y13" s="61">
         <f t="shared" si="4"/>
@@ -6859,15 +6859,15 @@
       </c>
       <c r="AA13" s="110">
         <f t="shared" si="5"/>
-        <v>2530</v>
+        <v>2640</v>
       </c>
       <c r="AB13" s="63">
         <f>RANK($AA13,$AA$3:$AA$47)+COUNTIF($AA$3:$AA13,AA13)-1</f>
-        <v>20</v>
-      </c>
-      <c r="AC13" s="61" cm="1">
+        <v>22</v>
+      </c>
+      <c r="AC13" s="61" t="str" cm="1">
         <f t="array" ref="AC13">IFERROR(_xlfn.IFS($AB13&lt;8,1,$AB13&lt;15,2,$AB13&lt;21,3),"")</f>
-        <v>3</v>
+        <v/>
       </c>
       <c r="AE13" s="63" t="s">
         <v>160</v>
@@ -6903,9 +6903,9 @@
       <c r="E14" s="63">
         <v>270</v>
       </c>
-      <c r="F14" s="125" t="str" cm="1">
+      <c r="F14" s="125" cm="1">
         <f t="array" ref="F14">IsUpgradable(E14)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G14" s="127">
         <f t="shared" si="0"/>
@@ -6964,11 +6964,11 @@
       </c>
       <c r="X14" s="13" cm="1">
         <f t="array" ref="X14">LevelUpgradeCost($E14)</f>
-        <v>135120000</v>
-      </c>
-      <c r="Y14" s="61" t="str">
+        <v>1515640000</v>
+      </c>
+      <c r="Y14" s="61">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AA14" s="110">
         <f t="shared" si="5"/>
@@ -6976,7 +6976,7 @@
       </c>
       <c r="AB14" s="63">
         <f>RANK($AA14,$AA$3:$AA$47)+COUNTIF($AA$3:$AA14,AA14)-1</f>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AC14" s="61" cm="1">
         <f t="array" ref="AC14">IFERROR(_xlfn.IFS($AB14&lt;8,1,$AB14&lt;15,2,$AB14&lt;21,3),"")</f>
@@ -7014,7 +7014,7 @@
         <v>97</v>
       </c>
       <c r="E15" s="63">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="F15" s="125" cm="1">
         <f t="array" ref="F15">IsUpgradable(E15)</f>
@@ -7077,7 +7077,7 @@
       </c>
       <c r="X15" s="13" cm="1">
         <f t="array" ref="X15">LevelUpgradeCost($E15)</f>
-        <v>1235520000</v>
+        <v>1515640000</v>
       </c>
       <c r="Y15" s="61">
         <f t="shared" si="4"/>
@@ -7085,7 +7085,7 @@
       </c>
       <c r="AA15" s="110">
         <f t="shared" si="5"/>
-        <v>5260</v>
+        <v>5270</v>
       </c>
       <c r="AB15" s="63">
         <f>RANK($AA15,$AA$3:$AA$47)+COUNTIF($AA$3:$AA15,AA15)-1</f>
@@ -7125,7 +7125,7 @@
         <v>98</v>
       </c>
       <c r="E16" s="63">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="F16" s="125" cm="1">
         <f t="array" ref="F16">IsUpgradable(E16)</f>
@@ -7133,10 +7133,10 @@
       </c>
       <c r="G16" s="127">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H16" s="198">
-        <v>2.2000000000000002</v>
+        <v>3</v>
       </c>
       <c r="I16" s="123">
         <v>10</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="R16" s="9">
         <f>IFERROR(CHOOSE(IF($H16&gt;=Details!$B$6,1,2),Details!$D$6,IF($H16&gt;Details!$B$6-1,IF($H16&lt;1,Details!$G$5,MOD($H16,Details!$B$6-1))*10*Details!$C$6,""))/Details!$D$6,0)</f>
-        <v>0.40000000000000036</v>
+        <v>1</v>
       </c>
       <c r="S16" s="9">
         <f>IFERROR(CHOOSE(IF($H16&gt;=Details!$B$7,1,2),Details!$D$7,IF($H16&gt;Details!$B$7-1,IF($H16&lt;1,Details!$G$5,MOD($H16,Details!$B$7-1))*10*Details!$C$7,""))/Details!$D$7,0)</f>
@@ -7180,15 +7180,15 @@
       </c>
       <c r="U16" s="9" cm="1">
         <f t="array" ref="U16">SUMPRODUCT(TRANSPOSE(Details!$D$4:$D$8),$P16:$T16)/Details!$D$9</f>
-        <v>0.11794871794871797</v>
+        <v>0.17948717948717949</v>
       </c>
       <c r="V16" s="13" cm="1">
         <f t="array" ref="V16">Details!$D$9-SUMPRODUCT(TRANSPOSE(Details!$D$4:$D$8),$P16:$T16)-$I16</f>
-        <v>850</v>
+        <v>790</v>
       </c>
       <c r="X16" s="13" cm="1">
         <f t="array" ref="X16">LevelUpgradeCost($E16)</f>
-        <v>2831420000</v>
+        <v>3503540000</v>
       </c>
       <c r="Y16" s="61">
         <f t="shared" si="4"/>
@@ -7196,15 +7196,15 @@
       </c>
       <c r="AA16" s="110">
         <f t="shared" si="5"/>
-        <v>2440</v>
+        <v>3250</v>
       </c>
       <c r="AB16" s="63">
         <f>RANK($AA16,$AA$3:$AA$47)+COUNTIF($AA$3:$AA16,AA16)-1</f>
-        <v>23</v>
-      </c>
-      <c r="AC16" s="61" t="str" cm="1">
+        <v>19</v>
+      </c>
+      <c r="AC16" s="61" cm="1">
         <f t="array" ref="AC16">IFERROR(_xlfn.IFS($AB16&lt;8,1,$AB16&lt;15,2,$AB16&lt;21,3),"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AE16" s="63" t="s">
         <v>159</v>
@@ -7238,7 +7238,7 @@
         <v>97</v>
       </c>
       <c r="E17" s="63">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="F17" s="125" cm="1">
         <f t="array" ref="F17">IsUpgradable(E17)</f>
@@ -7246,10 +7246,10 @@
       </c>
       <c r="G17" s="127">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H17" s="198">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I17" s="123">
         <v>0</v>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="M17" s="7" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Max</v>
       </c>
       <c r="N17" s="19" t="str">
         <f t="shared" si="2"/>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="S17" s="9">
         <f>IFERROR(CHOOSE(IF($H17&gt;=Details!$B$7,1,2),Details!$D$7,IF($H17&gt;Details!$B$7-1,IF($H17&lt;1,Details!$G$5,MOD($H17,Details!$B$7-1))*10*Details!$C$7,""))/Details!$D$7,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T17" s="9">
         <f>IFERROR(CHOOSE(IF($H17&gt;=Details!$B$8,1,2),Details!$D$8,IF($H17&gt;Details!$B$8-1,IF($H17&lt;1,Details!$G$5,MOD($H17,Details!$B$8-1))*10*Details!$C$8,""))/Details!$D$8,0)</f>
@@ -7293,15 +7293,15 @@
       </c>
       <c r="U17" s="9" cm="1">
         <f t="array" ref="U17">SUMPRODUCT(TRANSPOSE(Details!$D$4:$D$8),$P17:$T17)/Details!$D$9</f>
-        <v>0.17948717948717949</v>
+        <v>0.48717948717948717</v>
       </c>
       <c r="V17" s="13" cm="1">
         <f t="array" ref="V17">Details!$D$9-SUMPRODUCT(TRANSPOSE(Details!$D$4:$D$8),$P17:$T17)-$I17</f>
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="X17" s="13" cm="1">
         <f t="array" ref="X17">LevelUpgradeCost($E17)</f>
-        <v>4161420000</v>
+        <v>3503540000</v>
       </c>
       <c r="Y17" s="61">
         <f t="shared" si="4"/>
@@ -7309,11 +7309,11 @@
       </c>
       <c r="AA17" s="110">
         <f t="shared" si="5"/>
-        <v>3210</v>
+        <v>4250</v>
       </c>
       <c r="AB17" s="63">
         <f>RANK($AA17,$AA$3:$AA$47)+COUNTIF($AA$3:$AA17,AA17)-1</f>
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AC17" s="61" cm="1">
         <f t="array" ref="AC17">IFERROR(_xlfn.IFS($AB17&lt;8,1,$AB17&lt;15,2,$AB17&lt;21,3),"")</f>
@@ -7350,7 +7350,7 @@
         <v>98</v>
       </c>
       <c r="E18" s="63">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="F18" s="125" cm="1">
         <f t="array" ref="F18">IsUpgradable(E18)</f>
@@ -7358,10 +7358,10 @@
       </c>
       <c r="G18" s="127">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H18" s="198">
-        <v>2.2000000000000002</v>
+        <v>3.1</v>
       </c>
       <c r="I18" s="123">
         <v>0</v>
@@ -7393,11 +7393,11 @@
       </c>
       <c r="R18" s="9">
         <f>IFERROR(CHOOSE(IF($H18&gt;=Details!$B$6,1,2),Details!$D$6,IF($H18&gt;Details!$B$6-1,IF($H18&lt;1,Details!$G$5,MOD($H18,Details!$B$6-1))*10*Details!$C$6,""))/Details!$D$6,0)</f>
-        <v>0.40000000000000036</v>
+        <v>1</v>
       </c>
       <c r="S18" s="9">
         <f>IFERROR(CHOOSE(IF($H18&gt;=Details!$B$7,1,2),Details!$D$7,IF($H18&gt;Details!$B$7-1,IF($H18&lt;1,Details!$G$5,MOD($H18,Details!$B$7-1))*10*Details!$C$7,""))/Details!$D$7,0)</f>
-        <v>0</v>
+        <v>0.20000000000000018</v>
       </c>
       <c r="T18" s="9">
         <f>IFERROR(CHOOSE(IF($H18&gt;=Details!$B$8,1,2),Details!$D$8,IF($H18&gt;Details!$B$8-1,IF($H18&lt;1,Details!$G$5,MOD($H18,Details!$B$8-1))*10*Details!$C$8,""))/Details!$D$8,0)</f>
@@ -7405,15 +7405,15 @@
       </c>
       <c r="U18" s="9" cm="1">
         <f t="array" ref="U18">SUMPRODUCT(TRANSPOSE(Details!$D$4:$D$8),$P18:$T18)/Details!$D$9</f>
-        <v>0.11794871794871797</v>
+        <v>0.24102564102564109</v>
       </c>
       <c r="V18" s="13" cm="1">
         <f t="array" ref="V18">Details!$D$9-SUMPRODUCT(TRANSPOSE(Details!$D$4:$D$8),$P18:$T18)-$I18</f>
-        <v>860</v>
+        <v>740</v>
       </c>
       <c r="X18" s="13" cm="1">
         <f t="array" ref="X18">LevelUpgradeCost($E18)</f>
-        <v>4161420000</v>
+        <v>4771140000</v>
       </c>
       <c r="Y18" s="61">
         <f t="shared" si="4"/>
@@ -7421,15 +7421,15 @@
       </c>
       <c r="AA18" s="110">
         <f t="shared" si="5"/>
-        <v>2410</v>
+        <v>3330</v>
       </c>
       <c r="AB18" s="63">
         <f>RANK($AA18,$AA$3:$AA$47)+COUNTIF($AA$3:$AA18,AA18)-1</f>
-        <v>25</v>
-      </c>
-      <c r="AC18" s="61" t="str" cm="1">
+        <v>17</v>
+      </c>
+      <c r="AC18" s="61" cm="1">
         <f t="array" ref="AC18">IFERROR(_xlfn.IFS($AB18&lt;8,1,$AB18&lt;15,2,$AB18&lt;21,3),"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AE18" s="63" t="s">
         <v>146</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="X19" s="13" cm="1">
         <f t="array" ref="X19">LevelUpgradeCost($E19)</f>
-        <v>2123020000</v>
+        <v>3503540000</v>
       </c>
       <c r="Y19" s="61">
         <f t="shared" si="4"/>
@@ -7537,7 +7537,7 @@
       </c>
       <c r="AB19" s="63">
         <f>RANK($AA19,$AA$3:$AA$47)+COUNTIF($AA$3:$AA19,AA19)-1</f>
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AC19" s="61" cm="1">
         <f t="array" ref="AC19">IFERROR(_xlfn.IFS($AB19&lt;8,1,$AB19&lt;15,2,$AB19&lt;21,3),"")</f>
@@ -7576,9 +7576,9 @@
       <c r="E20" s="63">
         <v>270</v>
       </c>
-      <c r="F20" s="125" t="str" cm="1">
+      <c r="F20" s="125" cm="1">
         <f t="array" ref="F20">IsUpgradable(E20)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G20" s="127">
         <f t="shared" si="0"/>
@@ -7637,11 +7637,11 @@
       </c>
       <c r="X20" s="13" cm="1">
         <f t="array" ref="X20">LevelUpgradeCost($E20)</f>
-        <v>135120000</v>
-      </c>
-      <c r="Y20" s="61" t="str">
+        <v>1515640000</v>
+      </c>
+      <c r="Y20" s="61">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AA20" s="110">
         <f t="shared" si="5"/>
@@ -7649,7 +7649,7 @@
       </c>
       <c r="AB20" s="63">
         <f>RANK($AA20,$AA$3:$AA$47)+COUNTIF($AA$3:$AA20,AA20)-1</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC20" s="61" cm="1">
         <f t="array" ref="AC20">IFERROR(_xlfn.IFS($AB20&lt;8,1,$AB20&lt;15,2,$AB20&lt;21,3),"")</f>
@@ -7757,7 +7757,7 @@
       </c>
       <c r="X21" s="13" cm="1">
         <f t="array" ref="X21">LevelUpgradeCost($E21)</f>
-        <v>4415720000</v>
+        <v>5796240000</v>
       </c>
       <c r="Y21" s="61">
         <f t="shared" si="4"/>
@@ -7769,7 +7769,7 @@
       </c>
       <c r="AB21" s="63">
         <f>RANK($AA21,$AA$3:$AA$47)+COUNTIF($AA$3:$AA21,AA21)-1</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AC21" s="61" t="str" cm="1">
         <f t="array" ref="AC21">IFERROR(_xlfn.IFS($AB21&lt;8,1,$AB21&lt;15,2,$AB21&lt;21,3),"")</f>
@@ -7817,7 +7817,7 @@
         <v>2</v>
       </c>
       <c r="H22" s="198">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="I22" s="123">
         <v>1</v>
@@ -7849,7 +7849,7 @@
       </c>
       <c r="R22" s="9">
         <f>IFERROR(CHOOSE(IF($H22&gt;=Details!$B$6,1,2),Details!$D$6,IF($H22&gt;Details!$B$6-1,IF($H22&lt;1,Details!$G$5,MOD($H22,Details!$B$6-1))*10*Details!$C$6,""))/Details!$D$6,0)</f>
-        <v>0.40000000000000036</v>
+        <v>0.79999999999999982</v>
       </c>
       <c r="S22" s="9">
         <f>IFERROR(CHOOSE(IF($H22&gt;=Details!$B$7,1,2),Details!$D$7,IF($H22&gt;Details!$B$7-1,IF($H22&lt;1,Details!$G$5,MOD($H22,Details!$B$7-1))*10*Details!$C$7,""))/Details!$D$7,0)</f>
@@ -7861,15 +7861,15 @@
       </c>
       <c r="U22" s="9" cm="1">
         <f t="array" ref="U22">SUMPRODUCT(TRANSPOSE(Details!$D$4:$D$8),$P22:$T22)/Details!$D$9</f>
-        <v>0.11794871794871797</v>
+        <v>0.15897435897435896</v>
       </c>
       <c r="V22" s="13" cm="1">
         <f t="array" ref="V22">Details!$D$9-SUMPRODUCT(TRANSPOSE(Details!$D$4:$D$8),$P22:$T22)-$I22</f>
-        <v>859</v>
+        <v>819</v>
       </c>
       <c r="X22" s="13" cm="1">
         <f t="array" ref="X22">LevelUpgradeCost($E22)</f>
-        <v>4161420000</v>
+        <v>5541940000</v>
       </c>
       <c r="Y22" s="61">
         <f t="shared" si="4"/>
@@ -7877,11 +7877,11 @@
       </c>
       <c r="AA22" s="110">
         <f t="shared" si="5"/>
-        <v>2410</v>
+        <v>2610</v>
       </c>
       <c r="AB22" s="63">
         <f>RANK($AA22,$AA$3:$AA$47)+COUNTIF($AA$3:$AA22,AA22)-1</f>
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AC22" s="61" t="str" cm="1">
         <f t="array" ref="AC22">IFERROR(_xlfn.IFS($AB22&lt;8,1,$AB22&lt;15,2,$AB22&lt;21,3),"")</f>
@@ -7981,7 +7981,7 @@
       </c>
       <c r="X23" s="13" cm="1">
         <f t="array" ref="X23">LevelUpgradeCost($E23)</f>
-        <v>4919220000</v>
+        <v>6299740000</v>
       </c>
       <c r="Y23" s="61">
         <f t="shared" si="4"/>
@@ -7993,7 +7993,7 @@
       </c>
       <c r="AB23" s="63">
         <f>RANK($AA23,$AA$3:$AA$47)+COUNTIF($AA$3:$AA23,AA23)-1</f>
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AC23" s="61" t="str" cm="1">
         <f t="array" ref="AC23">IFERROR(_xlfn.IFS($AB23&lt;8,1,$AB23&lt;15,2,$AB23&lt;21,3),"")</f>
@@ -8032,7 +8032,7 @@
         <v>97</v>
       </c>
       <c r="E24" s="63">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="F24" s="125" cm="1">
         <f t="array" ref="F24">IsUpgradable(E24)</f>
@@ -8095,7 +8095,7 @@
       </c>
       <c r="X24" s="13" cm="1">
         <f t="array" ref="X24">LevelUpgradeCost($E24)</f>
-        <v>3826220000</v>
+        <v>4771140000</v>
       </c>
       <c r="Y24" s="61">
         <f t="shared" si="4"/>
@@ -8103,11 +8103,11 @@
       </c>
       <c r="AA24" s="110">
         <f t="shared" si="5"/>
-        <v>2220</v>
+        <v>2230</v>
       </c>
       <c r="AB24" s="63">
         <f>RANK($AA24,$AA$3:$AA$47)+COUNTIF($AA$3:$AA24,AA24)-1</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AC24" s="61" t="str" cm="1">
         <f t="array" ref="AC24">IFERROR(_xlfn.IFS($AB24&lt;8,1,$AB24&lt;15,2,$AB24&lt;21,3),"")</f>
@@ -8155,7 +8155,7 @@
         <v>2</v>
       </c>
       <c r="H25" s="198">
-        <v>2</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="I25" s="123">
         <v>0</v>
@@ -8187,7 +8187,7 @@
       </c>
       <c r="R25" s="9">
         <f>IFERROR(CHOOSE(IF($H25&gt;=Details!$B$6,1,2),Details!$D$6,IF($H25&gt;Details!$B$6-1,IF($H25&lt;1,Details!$G$5,MOD($H25,Details!$B$6-1))*10*Details!$C$6,""))/Details!$D$6,0)</f>
-        <v>0</v>
+        <v>0.59999999999999964</v>
       </c>
       <c r="S25" s="9">
         <f>IFERROR(CHOOSE(IF($H25&gt;=Details!$B$7,1,2),Details!$D$7,IF($H25&gt;Details!$B$7-1,IF($H25&lt;1,Details!$G$5,MOD($H25,Details!$B$7-1))*10*Details!$C$7,""))/Details!$D$7,0)</f>
@@ -8199,15 +8199,15 @@
       </c>
       <c r="U25" s="9" cm="1">
         <f t="array" ref="U25">SUMPRODUCT(TRANSPOSE(Details!$D$4:$D$8),$P25:$T25)/Details!$D$9</f>
-        <v>7.6923076923076927E-2</v>
+        <v>0.13846153846153844</v>
       </c>
       <c r="V25" s="13" cm="1">
         <f t="array" ref="V25">Details!$D$9-SUMPRODUCT(TRANSPOSE(Details!$D$4:$D$8),$P25:$T25)-$I25</f>
-        <v>900</v>
+        <v>840</v>
       </c>
       <c r="X25" s="13" cm="1">
         <f t="array" ref="X25">LevelUpgradeCost($E25)</f>
-        <v>4415720000</v>
+        <v>5796240000</v>
       </c>
       <c r="Y25" s="61">
         <f t="shared" si="4"/>
@@ -8215,11 +8215,11 @@
       </c>
       <c r="AA25" s="110">
         <f t="shared" si="5"/>
-        <v>2200</v>
+        <v>2500</v>
       </c>
       <c r="AB25" s="63">
         <f>RANK($AA25,$AA$3:$AA$47)+COUNTIF($AA$3:$AA25,AA25)-1</f>
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="AC25" s="61" t="str" cm="1">
         <f t="array" ref="AC25">IFERROR(_xlfn.IFS($AB25&lt;8,1,$AB25&lt;15,2,$AB25&lt;21,3),"")</f>
@@ -8265,7 +8265,7 @@
         <v>2</v>
       </c>
       <c r="H26" s="198">
-        <v>2.1</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="I26" s="123">
         <v>11</v>
@@ -8297,7 +8297,7 @@
       </c>
       <c r="R26" s="9">
         <f>IFERROR(CHOOSE(IF($H26&gt;=Details!$B$6,1,2),Details!$D$6,IF($H26&gt;Details!$B$6-1,IF($H26&lt;1,Details!$G$5,MOD($H26,Details!$B$6-1))*10*Details!$C$6,""))/Details!$D$6,0)</f>
-        <v>0.20000000000000018</v>
+        <v>0.40000000000000036</v>
       </c>
       <c r="S26" s="9">
         <f>IFERROR(CHOOSE(IF($H26&gt;=Details!$B$7,1,2),Details!$D$7,IF($H26&gt;Details!$B$7-1,IF($H26&lt;1,Details!$G$5,MOD($H26,Details!$B$7-1))*10*Details!$C$7,""))/Details!$D$7,0)</f>
@@ -8309,15 +8309,15 @@
       </c>
       <c r="U26" s="9" cm="1">
         <f t="array" ref="U26">SUMPRODUCT(TRANSPOSE(Details!$D$4:$D$8),$P26:$T26)/Details!$D$9</f>
-        <v>9.7435897435897451E-2</v>
+        <v>0.11794871794871797</v>
       </c>
       <c r="V26" s="13" cm="1">
         <f t="array" ref="V26">Details!$D$9-SUMPRODUCT(TRANSPOSE(Details!$D$4:$D$8),$P26:$T26)-$I26</f>
-        <v>869</v>
+        <v>849</v>
       </c>
       <c r="X26" s="13" cm="1">
         <f t="array" ref="X26">LevelUpgradeCost($E26)</f>
-        <v>4415720000</v>
+        <v>5796240000</v>
       </c>
       <c r="Y26" s="61">
         <f t="shared" si="4"/>
@@ -8325,11 +8325,11 @@
       </c>
       <c r="AA26" s="110">
         <f t="shared" si="5"/>
-        <v>2300</v>
+        <v>2400</v>
       </c>
       <c r="AB26" s="63">
         <f>RANK($AA26,$AA$3:$AA$47)+COUNTIF($AA$3:$AA26,AA26)-1</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AC26" s="61" t="str" cm="1">
         <f t="array" ref="AC26">IFERROR(_xlfn.IFS($AB26&lt;8,1,$AB26&lt;15,2,$AB26&lt;21,3),"")</f>
@@ -8366,7 +8366,7 @@
         <v>97</v>
       </c>
       <c r="E27" s="63">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="F27" s="125" cm="1">
         <f t="array" ref="F27">IsUpgradable(E27)</f>
@@ -8429,7 +8429,7 @@
       </c>
       <c r="X27" s="13" cm="1">
         <f t="array" ref="X27">LevelUpgradeCost($E27)</f>
-        <v>4161420000</v>
+        <v>4771140000</v>
       </c>
       <c r="Y27" s="61">
         <f t="shared" si="4"/>
@@ -8437,15 +8437,15 @@
       </c>
       <c r="AA27" s="110">
         <f t="shared" si="5"/>
-        <v>2610</v>
+        <v>2630</v>
       </c>
       <c r="AB27" s="63">
         <f>RANK($AA27,$AA$3:$AA$47)+COUNTIF($AA$3:$AA27,AA27)-1</f>
-        <v>19</v>
-      </c>
-      <c r="AC27" s="61" cm="1">
+        <v>23</v>
+      </c>
+      <c r="AC27" s="61" t="str" cm="1">
         <f t="array" ref="AC27">IFERROR(_xlfn.IFS($AB27&lt;8,1,$AB27&lt;15,2,$AB27&lt;21,3),"")</f>
-        <v>3</v>
+        <v/>
       </c>
       <c r="AE27" s="63" t="s">
         <v>148</v>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="X28" s="13" cm="1">
         <f t="array" ref="X28">LevelUpgradeCost($E28)</f>
-        <v>1235520000</v>
+        <v>2616040000</v>
       </c>
       <c r="Y28" s="61">
         <f t="shared" si="4"/>
@@ -8554,7 +8554,7 @@
       </c>
       <c r="AB28" s="63">
         <f>RANK($AA28,$AA$3:$AA$47)+COUNTIF($AA$3:$AA28,AA28)-1</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC28" s="61" cm="1">
         <f t="array" ref="AC28">IFERROR(_xlfn.IFS($AB28&lt;8,1,$AB28&lt;15,2,$AB28&lt;21,3),"")</f>
@@ -8590,7 +8590,7 @@
         <v>97</v>
       </c>
       <c r="E29" s="153">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="F29" s="125" cm="1">
         <f t="array" ref="F29">IsUpgradable(E29)</f>
@@ -8598,10 +8598,10 @@
       </c>
       <c r="G29" s="127">
         <f>INT(H29)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H29" s="199">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="I29" s="156">
         <v>10</v>
@@ -8613,15 +8613,15 @@
         <v>1</v>
       </c>
       <c r="L29" s="157">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M29" s="7" t="str">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="N29" s="19" t="str">
+        <v>Max</v>
+      </c>
+      <c r="N29" s="19">
         <f t="shared" si="11"/>
-        <v/>
+        <v>10</v>
       </c>
       <c r="P29" s="9">
         <f>IFERROR(CHOOSE(IF($H29&gt;=Details!$B$4,1,2),Details!$D$4,IF($H29&gt;Details!$B$4-1,IF($H29&lt;1,$H29,MOD($H29,Details!$B$4-1))*10*Details!$C$4,""))/Details!$D$4,0)</f>
@@ -8637,23 +8637,23 @@
       </c>
       <c r="S29" s="9">
         <f>IFERROR(CHOOSE(IF($H29&gt;=Details!$B$7,1,2),Details!$D$7,IF($H29&gt;Details!$B$7-1,IF($H29&lt;1,Details!$G$5,MOD($H29,Details!$B$7-1))*10*Details!$C$7,""))/Details!$D$7,0)</f>
-        <v>0.40000000000000036</v>
+        <v>1</v>
       </c>
       <c r="T29" s="9">
         <f>IFERROR(CHOOSE(IF($H29&gt;=Details!$B$8,1,2),Details!$D$8,IF($H29&gt;Details!$B$8-1,IF($H29&lt;1,Details!$G$5,MOD($H29,Details!$B$8-1))*10*Details!$C$8,""))/Details!$D$8,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U29" s="9" cm="1">
         <f t="array" ref="U29">SUMPRODUCT(TRANSPOSE(Details!$D$4:$D$8),$P29:$T29)/Details!$D$9</f>
-        <v>0.30256410256410265</v>
+        <v>1</v>
       </c>
       <c r="V29" s="13" cm="1">
         <f t="array" ref="V29">Details!$D$9-SUMPRODUCT(TRANSPOSE(Details!$D$4:$D$8),$P29:$T29)-$I29</f>
-        <v>669.99999999999989</v>
+        <v>-10</v>
       </c>
       <c r="X29" s="13" cm="1">
         <f t="array" ref="X29">LevelUpgradeCost($E29)</f>
-        <v>4161420000</v>
+        <v>4771140000</v>
       </c>
       <c r="Y29" s="61">
         <f t="shared" si="4"/>
@@ -8661,11 +8661,11 @@
       </c>
       <c r="AA29" s="110">
         <f t="shared" si="5"/>
-        <v>3410</v>
+        <v>5230</v>
       </c>
       <c r="AB29" s="63">
         <f>RANK($AA29,$AA$3:$AA$47)+COUNTIF($AA$3:$AA29,AA29)-1</f>
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AC29" s="61" cm="1">
         <f t="array" ref="AC29">IFERROR(_xlfn.IFS($AB29&lt;8,1,$AB29&lt;15,2,$AB29&lt;21,3),"")</f>
@@ -8701,7 +8701,7 @@
         <v>98</v>
       </c>
       <c r="E30" s="63">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="F30" s="125" cm="1">
         <f t="array" ref="F30">IsUpgradable(E30)</f>
@@ -8712,7 +8712,7 @@
         <v>4</v>
       </c>
       <c r="H30" s="198">
-        <v>4</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="I30" s="123">
         <v>30</v>
@@ -8752,19 +8752,19 @@
       </c>
       <c r="T30" s="9">
         <f>IFERROR(CHOOSE(IF($H30&gt;=Details!$B$8,1,2),Details!$D$8,IF($H30&gt;Details!$B$8-1,IF($H30&lt;1,Details!$G$5,MOD($H30,Details!$B$8-1))*10*Details!$C$8,""))/Details!$D$8,0)</f>
-        <v>0</v>
+        <v>0.19999999999999929</v>
       </c>
       <c r="U30" s="9" cm="1">
         <f t="array" ref="U30">SUMPRODUCT(TRANSPOSE(Details!$D$4:$D$8),$P30:$T30)/Details!$D$9</f>
-        <v>0.48717948717948717</v>
+        <v>0.58974358974358942</v>
       </c>
       <c r="V30" s="13" cm="1">
         <f t="array" ref="V30">Details!$D$9-SUMPRODUCT(TRANSPOSE(Details!$D$4:$D$8),$P30:$T30)-$I30</f>
-        <v>470</v>
+        <v>370.00000000000034</v>
       </c>
       <c r="X30" s="13" cm="1">
         <f t="array" ref="X30">LevelUpgradeCost($E30)</f>
-        <v>4605720000</v>
+        <v>5796240000</v>
       </c>
       <c r="Y30" s="61">
         <f t="shared" ref="Y30" si="13">F30</f>
@@ -8772,11 +8772,11 @@
       </c>
       <c r="AA30" s="110">
         <f t="shared" si="5"/>
-        <v>4190</v>
+        <v>4300</v>
       </c>
       <c r="AB30" s="63">
         <f>RANK($AA30,$AA$3:$AA$47)+COUNTIF($AA$3:$AA30,AA30)-1</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AC30" s="61" cm="1">
         <f t="array" ref="AC30">IFERROR(_xlfn.IFS($AB30&lt;8,1,$AB30&lt;15,2,$AB30&lt;21,3),"")</f>
@@ -8809,7 +8809,7 @@
         <v>97</v>
       </c>
       <c r="E31" s="153">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="F31" s="154" cm="1">
         <f t="array" ref="F31">IsUpgradable(E31)</f>
@@ -8817,10 +8817,10 @@
       </c>
       <c r="G31" s="155">
         <f>INT(H31)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H31" s="199">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="I31" s="156">
         <v>10</v>
@@ -8852,7 +8852,7 @@
       </c>
       <c r="R31" s="158">
         <f>IFERROR(CHOOSE(IF($H31&gt;=Details!$B$6,1,2),Details!$D$6,IF($H31&gt;Details!$B$6-1,IF($H31&lt;1,Details!$G$5,MOD($H31,Details!$B$6-1))*10*Details!$C$6,""))/Details!$D$6,0)</f>
-        <v>0.20000000000000018</v>
+        <v>1</v>
       </c>
       <c r="S31" s="158">
         <f>IFERROR(CHOOSE(IF($H31&gt;=Details!$B$7,1,2),Details!$D$7,IF($H31&gt;Details!$B$7-1,IF($H31&lt;1,Details!$G$5,MOD($H31,Details!$B$7-1))*10*Details!$C$7,""))/Details!$D$7,0)</f>
@@ -8864,15 +8864,15 @@
       </c>
       <c r="U31" s="158" cm="1">
         <f t="array" ref="U31">SUMPRODUCT(TRANSPOSE(Details!$D$4:$D$8),$P31:$T31)/Details!$D$9</f>
-        <v>9.7435897435897451E-2</v>
+        <v>0.17948717948717949</v>
       </c>
       <c r="V31" s="159" cm="1">
         <f t="array" ref="V31">Details!$D$9-SUMPRODUCT(TRANSPOSE(Details!$D$4:$D$8),$P31:$T31)-$I31</f>
-        <v>870</v>
+        <v>790</v>
       </c>
       <c r="X31" s="159" cm="1">
         <f t="array" ref="X31">LevelUpgradeCost($E31)</f>
-        <v>4161420000</v>
+        <v>4211940000</v>
       </c>
       <c r="Y31" s="160">
         <f t="shared" si="4"/>
@@ -8880,11 +8880,11 @@
       </c>
       <c r="AA31" s="202">
         <f t="shared" si="5"/>
-        <v>2310</v>
+        <v>3240</v>
       </c>
       <c r="AB31" s="153">
         <f>RANK($AA31,$AA$3:$AA$47)+COUNTIF($AA$3:$AA31,AA31)-1</f>
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AC31" s="160" t="str" cm="1">
         <f t="array" ref="AC31">IFERROR(_xlfn.IFS($AB31&lt;8,1,$AB31&lt;15,2,$AB31&lt;21,3),"")</f>
@@ -8977,7 +8977,7 @@
       <c r="W32" s="140"/>
       <c r="X32" s="60" cm="1">
         <f t="array" ref="X32">LevelUpgradeCost($E32)</f>
-        <v>5044093700</v>
+        <v>6424613700</v>
       </c>
       <c r="Y32" s="180" t="str">
         <f t="shared" si="4"/>
@@ -9028,7 +9028,7 @@
         <v>97</v>
       </c>
       <c r="E33" s="63">
-        <v>140</v>
+        <v>270</v>
       </c>
       <c r="F33" s="125" cm="1">
         <f t="array" ref="F33">IsUpgradable(E33)</f>
@@ -9092,7 +9092,7 @@
       </c>
       <c r="X33" s="13" cm="1">
         <f t="array" ref="X33">LevelUpgradeCost($E33)</f>
-        <v>4999220000</v>
+        <v>1515640000</v>
       </c>
       <c r="Y33" s="61">
         <f t="shared" si="4"/>
@@ -9100,11 +9100,11 @@
       </c>
       <c r="AA33" s="110">
         <f t="shared" si="5"/>
-        <v>5140</v>
+        <v>5270</v>
       </c>
       <c r="AB33" s="63">
         <f>RANK($AA33,$AA$3:$AA$47)+COUNTIF($AA$3:$AA33,AA33)-1</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC33" s="61" cm="1">
         <f t="array" ref="AC33">IFERROR(_xlfn.IFS($AB33&lt;8,1,$AB33&lt;15,2,$AB33&lt;21,3),"")</f>
@@ -9195,7 +9195,7 @@
       </c>
       <c r="X34" s="13" cm="1">
         <f t="array" ref="X34">LevelUpgradeCost($E34)</f>
-        <v>5044093700</v>
+        <v>6424613700</v>
       </c>
       <c r="Y34" s="61" t="str">
         <f t="shared" si="4"/>
@@ -9245,7 +9245,7 @@
         <v>97</v>
       </c>
       <c r="E35" s="64">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="F35" s="126" t="str" cm="1">
         <f t="array" ref="F35">IsUpgradable(E35)</f>
@@ -9310,7 +9310,7 @@
       <c r="W35" s="141"/>
       <c r="X35" s="22" cm="1">
         <f t="array" ref="X35">LevelUpgradeCost($E35)</f>
-        <v>135120000</v>
+        <v>164440000</v>
       </c>
       <c r="Y35" s="62" t="str">
         <f t="shared" si="4"/>
@@ -9319,11 +9319,11 @@
       <c r="Z35" s="141"/>
       <c r="AA35" s="112">
         <f t="shared" si="5"/>
-        <v>5270</v>
+        <v>5280</v>
       </c>
       <c r="AB35" s="64">
         <f>RANK($AA35,$AA$3:$AA$47)+COUNTIF($AA$3:$AA35,AA35)-1</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AC35" s="62" cm="1">
         <f t="array" ref="AC35">IFERROR(_xlfn.IFS($AB35&lt;8,1,$AB35&lt;15,2,$AB35&lt;21,3),"")</f>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="X36" s="168" cm="1">
         <f t="array" ref="X36">LevelUpgradeCost($E36)</f>
-        <v>5044093700</v>
+        <v>6424613700</v>
       </c>
       <c r="Y36" s="169" t="str">
         <f t="shared" si="4"/>
@@ -9512,7 +9512,7 @@
       </c>
       <c r="X37" s="168" cm="1">
         <f t="array" ref="X37">LevelUpgradeCost($E37)</f>
-        <v>5044093700</v>
+        <v>6424613700</v>
       </c>
       <c r="Y37" s="169" t="str">
         <f t="shared" si="4"/>
@@ -9607,7 +9607,7 @@
       </c>
       <c r="X38" s="168" cm="1">
         <f t="array" ref="X38">LevelUpgradeCost($E38)</f>
-        <v>5044093700</v>
+        <v>6424613700</v>
       </c>
       <c r="Y38" s="169" t="str">
         <f t="shared" ref="Y38" si="20">F38</f>
@@ -9714,7 +9714,7 @@
       </c>
       <c r="X39" s="13" cm="1">
         <f t="array" ref="X39">LevelUpgradeCost($E39)</f>
-        <v>5044093700</v>
+        <v>6424613700</v>
       </c>
       <c r="Y39" s="61">
         <f t="shared" ref="Y39" si="23">F39</f>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="X40" s="13" cm="1">
         <f t="array" ref="X40">LevelUpgradeCost($E40)</f>
-        <v>5044093700</v>
+        <v>6424613700</v>
       </c>
       <c r="Y40" s="61" t="str">
         <f t="shared" si="4"/>
@@ -9918,7 +9918,7 @@
       </c>
       <c r="X41" s="13" cm="1">
         <f t="array" ref="X41">LevelUpgradeCost($E41)</f>
-        <v>5044093700</v>
+        <v>6424613700</v>
       </c>
       <c r="Y41" s="61" t="str">
         <f t="shared" si="4"/>
@@ -10018,7 +10018,7 @@
       </c>
       <c r="X42" s="13" cm="1">
         <f t="array" ref="X42">LevelUpgradeCost($E42)</f>
-        <v>5044093700</v>
+        <v>6424613700</v>
       </c>
       <c r="Y42" s="61" t="str">
         <f t="shared" si="4"/>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="X43" s="13" cm="1">
         <f t="array" ref="X43">LevelUpgradeCost($E43)</f>
-        <v>5044093700</v>
+        <v>6424613700</v>
       </c>
       <c r="Y43" s="61" t="str">
         <f t="shared" si="4"/>
@@ -10218,7 +10218,7 @@
       </c>
       <c r="X44" s="13" cm="1">
         <f t="array" ref="X44">LevelUpgradeCost($E44)</f>
-        <v>5044093700</v>
+        <v>6424613700</v>
       </c>
       <c r="Y44" s="61" t="str">
         <f t="shared" si="4"/>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="X45" s="13" cm="1">
         <f t="array" ref="X45">LevelUpgradeCost($E45)</f>
-        <v>5044093700</v>
+        <v>6424613700</v>
       </c>
       <c r="Y45" s="61" t="str">
         <f t="shared" si="4"/>
@@ -10418,7 +10418,7 @@
       </c>
       <c r="X46" s="13" cm="1">
         <f t="array" ref="X46">LevelUpgradeCost($E46)</f>
-        <v>5044093700</v>
+        <v>6424613700</v>
       </c>
       <c r="Y46" s="61" t="str">
         <f t="shared" si="4"/>
@@ -10528,7 +10528,7 @@
       </c>
       <c r="X47" s="22" cm="1">
         <f t="array" ref="X47">LevelUpgradeCost($E47)</f>
-        <v>4919220000</v>
+        <v>6299740000</v>
       </c>
       <c r="Y47" s="62">
         <f t="shared" si="4"/>
@@ -10540,7 +10540,7 @@
       </c>
       <c r="AB47" s="64">
         <f>RANK($AA47,$AA$3:$AA$47)+COUNTIF($AA$3:$AA47,AA47)-1</f>
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AC47" s="62" t="str" cm="1">
         <f t="array" ref="AC47">IFERROR(_xlfn.IFS($AB47&lt;8,1,$AB47&lt;15,2,$AB47&lt;21,3),"")</f>
@@ -10708,14 +10708,14 @@
       <c r="D49" s="142"/>
       <c r="E49" s="1">
         <f>COUNTIF(E3:E47,"&gt;0")-COUNTIF(E3:E47,"="&amp;HallLevel*10)</f>
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F49" s="142"/>
       <c r="G49" s="142"/>
       <c r="I49" s="5"/>
       <c r="X49" s="5">
         <f>SUMPRODUCT(X3:X47,Y3:Y47)</f>
-        <v>96248267400</v>
+        <v>126429527400</v>
       </c>
     </row>
     <row r="50" spans="2:24" ht="12" customHeight="1" x14ac:dyDescent="0.2">
@@ -10723,7 +10723,7 @@
         <v>80</v>
       </c>
       <c r="C50" s="25">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D50" s="142"/>
     </row>
@@ -10785,11 +10785,11 @@
       </c>
       <c r="C56" s="207" cm="1">
         <f t="array" ref="C56">LevelUpgradeCost(C54)</f>
-        <v>4968220000</v>
+        <v>6348740000</v>
       </c>
       <c r="D56" s="234" t="str" cm="1">
         <f t="array" ref="D56">CostScreen(C56)</f>
-        <v>4,97B</v>
+        <v>6,35B</v>
       </c>
       <c r="E56" s="61">
         <f>SUMIF(Tableaux!$A$3:$A$302,"&lt;" &amp; Palmon!$C$55,Tableaux!$C$3:$C$302)</f>
@@ -10826,7 +10826,7 @@
       </c>
       <c r="Q58" s="1">
         <f>SUMIF($C$3:$C$47,"=" &amp; $P58,$E$3:$E$47)</f>
-        <v>1641</v>
+        <v>1701</v>
       </c>
       <c r="R58" s="1">
         <f>COUNTIFS($C$3:$C$47,"=" &amp; $P58,$E$3:$E$47,"&gt;0")</f>
@@ -10834,7 +10834,7 @@
       </c>
       <c r="S58" s="1">
         <f>Q58/R58</f>
-        <v>205.125</v>
+        <v>212.625</v>
       </c>
       <c r="X58"/>
     </row>
@@ -10850,7 +10850,7 @@
       </c>
       <c r="Q59" s="1">
         <f t="shared" ref="Q59:Q61" si="25">SUMIF($C$3:$C$47,"=" &amp; $P59,$E$3:$E$47)</f>
-        <v>2041</v>
+        <v>2061</v>
       </c>
       <c r="R59" s="1">
         <f t="shared" ref="R59:R61" si="26">COUNTIFS($C$3:$C$47,"=" &amp; $P59,$E$3:$E$47,"&gt;0")</f>
@@ -10858,7 +10858,7 @@
       </c>
       <c r="S59" s="1">
         <f t="shared" ref="S59:S61" si="27">Q59/R59</f>
-        <v>204.1</v>
+        <v>206.1</v>
       </c>
       <c r="X59"/>
     </row>
@@ -10876,7 +10876,7 @@
       </c>
       <c r="Q60" s="1">
         <f t="shared" si="25"/>
-        <v>1900</v>
+        <v>1930</v>
       </c>
       <c r="R60" s="1">
         <f t="shared" si="26"/>
@@ -10884,7 +10884,7 @@
       </c>
       <c r="S60" s="1">
         <f t="shared" si="27"/>
-        <v>237.5</v>
+        <v>241.25</v>
       </c>
       <c r="X60"/>
     </row>
@@ -10902,7 +10902,7 @@
       </c>
       <c r="Q61" s="1">
         <f t="shared" si="25"/>
-        <v>1480</v>
+        <v>1710</v>
       </c>
       <c r="R61" s="1">
         <f t="shared" si="26"/>
@@ -10910,7 +10910,7 @@
       </c>
       <c r="S61" s="1">
         <f t="shared" si="27"/>
-        <v>211.42857142857142</v>
+        <v>244.28571428571428</v>
       </c>
       <c r="X61"/>
     </row>
@@ -11414,7 +11414,7 @@
       </c>
       <c r="F3" t="str">
         <f>Palmon!B3 &amp; "," &amp; Palmon!C3 &amp; "," &amp; Palmon!D3 &amp; "," &amp; Palmon!E3 &amp; "," &amp; Palmon!G3 &amp; "," &amp; SUBSTITUTE(Palmon!H3,",",".") &amp; "," &amp; Palmon!I3 &amp; "," &amp; SUBSTITUTE(Palmon!P3,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q3,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R3,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S3,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T3,",",".") &amp; "," &amp; Palmon!J3 &amp; "," &amp; Palmon!K3 &amp; "," &amp; Palmon!L3 &amp; "," &amp; Palmon!M3 &amp; "," &amp; Palmon!N3 &amp; "," &amp; SUBSTITUTE(Palmon!U3,",",".") &amp; "," &amp; Palmon!V3 &amp; "," &amp; Palmon!X3 &amp; "," &amp; Palmon!Y3 &amp; "," &amp; Palmon!AA3 &amp; "," &amp; Palmon!AB3 &amp; "," &amp; Palmon!AC3 &amp; "," &amp; Palmon!AE3 &amp; "," &amp; Palmon!AF3 &amp; "," &amp; Palmon!AI3 &amp; "," &amp; Palmon!AJ3</f>
-        <v>Bufonobi,Water,Attack,270,5,5,0,1,1,1,1,1,30,20,30,Max,10,1,0,135120000,,5270,1,1,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRXczs_Bjhslhr7Mf2HENU6MTyGpz0RJEMjNA&amp;s, ,,Shadowkaeru</v>
+        <v>Bufonobi,Water,Attack,270,5,5,0,1,1,1,1,1,30,30,30,Max,10,1,0,1515640000,1,5270,2,1,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRXczs_Bjhslhr7Mf2HENU6MTyGpz0RJEMjNA&amp;s, ,,Shadowkaeru</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -11440,7 +11440,7 @@
       </c>
       <c r="F4" t="str">
         <f>Palmon!B4 &amp; "," &amp; Palmon!C4 &amp; "," &amp; Palmon!D4 &amp; "," &amp; Palmon!E4 &amp; "," &amp; Palmon!G4 &amp; "," &amp; SUBSTITUTE(Palmon!H4,",",".") &amp; "," &amp; Palmon!I4 &amp; "," &amp; SUBSTITUTE(Palmon!P4,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q4,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R4,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S4,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T4,",",".") &amp; "," &amp; Palmon!J4 &amp; "," &amp; Palmon!K4 &amp; "," &amp; Palmon!L4 &amp; "," &amp; Palmon!M4 &amp; "," &amp; Palmon!N4 &amp; "," &amp; SUBSTITUTE(Palmon!U4,",",".") &amp; "," &amp; Palmon!V4 &amp; "," &amp; Palmon!X4 &amp; "," &amp; Palmon!Y4 &amp; "," &amp; Palmon!AA4 &amp; "," &amp; Palmon!AB4 &amp; "," &amp; Palmon!AC4 &amp; "," &amp; Palmon!AE4 &amp; "," &amp; Palmon!AF4 &amp; "," &amp; Palmon!AI4 &amp; "," &amp; Palmon!AJ4</f>
-        <v>Vulpyrean,Fire,Attack,270,5,5,0,1,1,1,1,1,20,20,20,Max,10,1,0,135120000,,5270,2,1,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSDZWuq2tiKYc0zKRxpHXrLSMZ1GsY_6wEIYw&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRGF27Z8fOuiwM1qjDFQVY262gS_QKIJamMNg&amp;s,,</v>
+        <v>Vulpyrean,Fire,Attack,270,5,5,0,1,1,1,1,1,20,20,20,Max,10,1,0,1515640000,1,5270,3,1,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSDZWuq2tiKYc0zKRxpHXrLSMZ1GsY_6wEIYw&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRGF27Z8fOuiwM1qjDFQVY262gS_QKIJamMNg&amp;s,,</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -11466,7 +11466,7 @@
       </c>
       <c r="F5" t="str">
         <f>Palmon!B5 &amp; "," &amp; Palmon!C5 &amp; "," &amp; Palmon!D5 &amp; "," &amp; Palmon!E5 &amp; "," &amp; Palmon!G5 &amp; "," &amp; SUBSTITUTE(Palmon!H5,",",".") &amp; "," &amp; Palmon!I5 &amp; "," &amp; SUBSTITUTE(Palmon!P5,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q5,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R5,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S5,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T5,",",".") &amp; "," &amp; Palmon!J5 &amp; "," &amp; Palmon!K5 &amp; "," &amp; Palmon!L5 &amp; "," &amp; Palmon!M5 &amp; "," &amp; Palmon!N5 &amp; "," &amp; SUBSTITUTE(Palmon!U5,",",".") &amp; "," &amp; Palmon!V5 &amp; "," &amp; Palmon!X5 &amp; "," &amp; Palmon!Y5 &amp; "," &amp; Palmon!AA5 &amp; "," &amp; Palmon!AB5 &amp; "," &amp; Palmon!AC5 &amp; "," &amp; Palmon!AE5 &amp; "," &amp; Palmon!AF5 &amp; "," &amp; Palmon!AI5 &amp; "," &amp; Palmon!AJ5</f>
-        <v>Hoofrit,Fire,Attack,270,4,4,11,1,1,1,1,0,15,15,15,Max,,0.487179487179487,489,135120000,,4270,10,2,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRwfHFWjB1bN67FJNyjjWvBJwviWJ3Tada0Yg&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSkOv6mOI5FaIAjcVgErYDwVaivkH3WdUQIzw&amp;s,Flaries,</v>
+        <v>Hoofrit,Fire,Attack,270,4,4,11,1,1,1,1,0,15,15,15,Max,,0.487179487179487,489,1515640000,1,4270,13,2,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRwfHFWjB1bN67FJNyjjWvBJwviWJ3Tada0Yg&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSkOv6mOI5FaIAjcVgErYDwVaivkH3WdUQIzw&amp;s,Flaries,</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -11492,7 +11492,7 @@
       </c>
       <c r="F6" t="str">
         <f>Palmon!B6 &amp; "," &amp; Palmon!C6 &amp; "," &amp; Palmon!D6 &amp; "," &amp; Palmon!E6 &amp; "," &amp; Palmon!G6 &amp; "," &amp; SUBSTITUTE(Palmon!H6,",",".") &amp; "," &amp; Palmon!I6 &amp; "," &amp; SUBSTITUTE(Palmon!P6,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q6,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R6,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S6,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T6,",",".") &amp; "," &amp; Palmon!J6 &amp; "," &amp; Palmon!K6 &amp; "," &amp; Palmon!L6 &amp; "," &amp; Palmon!M6 &amp; "," &amp; Palmon!N6 &amp; "," &amp; SUBSTITUTE(Palmon!U6,",",".") &amp; "," &amp; Palmon!V6 &amp; "," &amp; Palmon!X6 &amp; "," &amp; Palmon!Y6 &amp; "," &amp; Palmon!AA6 &amp; "," &amp; Palmon!AB6 &amp; "," &amp; Palmon!AC6 &amp; "," &amp; Palmon!AE6 &amp; "," &amp; Palmon!AF6 &amp; "," &amp; Palmon!AI6 &amp; "," &amp; Palmon!AJ6</f>
-        <v>Ghillant,Wood,Defend,250,4,4.1,0,1,1,1,1,0.199999999999999,5,5,5,Max,,0.589743589743589,400,2123020000,1,4350,9,2,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQOwDXppnwkCtCXXAqUiiNMhf6T-lane54jPg&amp;s, ,Chefeuillier,</v>
+        <v>Ghillant,Wood,Defend,250,4,4.1,0,1,1,1,1,0.199999999999999,5,5,5,Max,,0.589743589743589,400,3503540000,1,4350,10,2,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQOwDXppnwkCtCXXAqUiiNMhf6T-lane54jPg&amp;s, ,Chefeuillier,</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -11518,7 +11518,7 @@
       </c>
       <c r="F7" t="str">
         <f>Palmon!B8 &amp; "," &amp; Palmon!C8 &amp; "," &amp; Palmon!D8 &amp; "," &amp; Palmon!E8 &amp; "," &amp; Palmon!G8 &amp; "," &amp; SUBSTITUTE(Palmon!H8,",",".") &amp; "," &amp; Palmon!I8 &amp; "," &amp; SUBSTITUTE(Palmon!P8,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q8,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R8,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S8,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T8,",",".") &amp; "," &amp; Palmon!J8 &amp; "," &amp; Palmon!K8 &amp; "," &amp; Palmon!L8 &amp; "," &amp; Palmon!M8 &amp; "," &amp; Palmon!N8 &amp; "," &amp; SUBSTITUTE(Palmon!U8,",",".") &amp; "," &amp; Palmon!V8 &amp; "," &amp; Palmon!X8 &amp; "," &amp; Palmon!Y8 &amp; "," &amp; Palmon!AA8 &amp; "," &amp; Palmon!AB8 &amp; "," &amp; Palmon!AC8 &amp; "," &amp; Palmon!AE8 &amp; "," &amp; Palmon!AF8 &amp; "," &amp; Palmon!AI8 &amp; "," &amp; Palmon!AJ8</f>
-        <v>Gnashley,Water,Defend,1,1,1,0,1,0,0,0,0,1,1,1,,,0.0256410256410256,950,5044093700,1,1001,32,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQtrOr7ePo-_tg085QaHk6NorM32ywE44672A&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTII6bAUVzdPfr_45Db3bGwDuIVxhe-n4dSSgHRGJaEpg&amp;s,Gnashfin,</v>
+        <v>Gnashley,Water,Defend,1,1,1,0,1,0,0,0,0,1,1,1,,,0.0256410256410256,950,6424613700,1,1001,32,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQtrOr7ePo-_tg085QaHk6NorM32ywE44672A&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTII6bAUVzdPfr_45Db3bGwDuIVxhe-n4dSSgHRGJaEpg&amp;s,Gnashfin,</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -11544,7 +11544,7 @@
       </c>
       <c r="F8" t="str">
         <f>Palmon!B9 &amp; "," &amp; Palmon!C9 &amp; "," &amp; Palmon!D9 &amp; "," &amp; Palmon!E9 &amp; "," &amp; Palmon!G9 &amp; "," &amp; SUBSTITUTE(Palmon!H9,",",".") &amp; "," &amp; Palmon!I9 &amp; "," &amp; SUBSTITUTE(Palmon!P9,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q9,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R9,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S9,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T9,",",".") &amp; "," &amp; Palmon!J9 &amp; "," &amp; Palmon!K9 &amp; "," &amp; Palmon!L9 &amp; "," &amp; Palmon!M9 &amp; "," &amp; Palmon!N9 &amp; "," &amp; SUBSTITUTE(Palmon!U9,",",".") &amp; "," &amp; Palmon!V9 &amp; "," &amp; Palmon!X9 &amp; "," &amp; Palmon!Y9 &amp; "," &amp; Palmon!AA9 &amp; "," &amp; Palmon!AB9 &amp; "," &amp; Palmon!AC9 &amp; "," &amp; Palmon!AE9 &amp; "," &amp; Palmon!AF9 &amp; "," &amp; Palmon!AI9 &amp; "," &amp; Palmon!AJ9</f>
-        <v>Magmolin,Fire,Defend,240,3,3.1,61,1,1,1,0.2,0,10,5,15,,,0.241025641025641,679,2831420000,1,3340,15,3,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRebc6KbOAxblleg_L3rr2K13bt-Yyzq1bAaw&amp;s, ,Obsidrake,</v>
+        <v>Magmolin,Fire,Defend,240,3,3.1,61,1,1,1,0.2,0,10,5,15,,,0.241025641025641,679,4211940000,1,3340,16,3,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRebc6KbOAxblleg_L3rr2K13bt-Yyzq1bAaw&amp;s, ,Obsidrake,</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -11570,7 +11570,7 @@
       </c>
       <c r="F9" t="str">
         <f>Palmon!B10 &amp; "," &amp; Palmon!C10 &amp; "," &amp; Palmon!D10 &amp; "," &amp; Palmon!E10 &amp; "," &amp; Palmon!G10 &amp; "," &amp; SUBSTITUTE(Palmon!H10,",",".") &amp; "," &amp; Palmon!I10 &amp; "," &amp; SUBSTITUTE(Palmon!P10,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q10,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R10,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S10,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T10,",",".") &amp; "," &amp; Palmon!J10 &amp; "," &amp; Palmon!K10 &amp; "," &amp; Palmon!L10 &amp; "," &amp; Palmon!M10 &amp; "," &amp; Palmon!N10 &amp; "," &amp; SUBSTITUTE(Palmon!U10,",",".") &amp; "," &amp; Palmon!V10 &amp; "," &amp; Palmon!X10 &amp; "," &amp; Palmon!Y10 &amp; "," &amp; Palmon!AA10 &amp; "," &amp; Palmon!AB10 &amp; "," &amp; Palmon!AC10 &amp; "," &amp; Palmon!AE10 &amp; "," &amp; Palmon!AF10 &amp; "," &amp; Palmon!AI10 &amp; "," &amp; Palmon!AJ10</f>
-        <v>Limudroid,Electricity,Attack,230,2,2.2,4,1,1,0.4,0,0,1,1,5,,,0.117948717948718,856,3390620000,1,2430,24,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQzaI21taP2V17MKjiPAeulm4V9qfST4umPdg&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRMlruQNUenhVk-fAEq9d3Wi8zw--0GbkLGJrX1CuQ1&amp;s,Bunodroid,</v>
+        <v>Limudroid,Electricity,Attack,230,2,2.2,4,1,1,0.4,0,0,1,1,5,,,0.117948717948718,856,4771140000,1,2430,28,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQzaI21taP2V17MKjiPAeulm4V9qfST4umPdg&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRMlruQNUenhVk-fAEq9d3Wi8zw--0GbkLGJrX1CuQ1&amp;s,Bunodroid,</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -11596,7 +11596,7 @@
       </c>
       <c r="F10" t="str">
         <f>Palmon!B11 &amp; "," &amp; Palmon!C11 &amp; "," &amp; Palmon!D11 &amp; "," &amp; Palmon!E11 &amp; "," &amp; Palmon!G11 &amp; "," &amp; SUBSTITUTE(Palmon!H11,",",".") &amp; "," &amp; Palmon!I11 &amp; "," &amp; SUBSTITUTE(Palmon!P11,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q11,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R11,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S11,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T11,",",".") &amp; "," &amp; Palmon!J11 &amp; "," &amp; Palmon!K11 &amp; "," &amp; Palmon!L11 &amp; "," &amp; Palmon!M11 &amp; "," &amp; Palmon!N11 &amp; "," &amp; SUBSTITUTE(Palmon!U11,",",".") &amp; "," &amp; Palmon!V11 &amp; "," &amp; Palmon!X11 &amp; "," &amp; Palmon!Y11 &amp; "," &amp; Palmon!AA11 &amp; "," &amp; Palmon!AB11 &amp; "," &amp; Palmon!AC11 &amp; "," &amp; Palmon!AE11 &amp; "," &amp; Palmon!AF11 &amp; "," &amp; Palmon!AI11 &amp; "," &amp; Palmon!AJ11</f>
-        <v>Barkplug,Electricity,Defend,250,3,3,0,1,1,1,0,0,14,5,10,,,0.179487179487179,800,2123020000,1,3250,16,3,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSf59xsunrPEuFvdtBi-IRVMcrdBfW_vNshLA&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRUDpuK5BvjXDFqgMZvlxYadsaFFQDKOQrNCAHymiAy_w&amp;s,Wattweiler,</v>
+        <v>Barkplug,Electricity,Defend,250,3,3,0,1,1,1,0,0,14,5,10,,,0.179487179487179,800,3503540000,1,3250,18,3,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSf59xsunrPEuFvdtBi-IRVMcrdBfW_vNshLA&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRUDpuK5BvjXDFqgMZvlxYadsaFFQDKOQrNCAHymiAy_w&amp;s,Wattweiler,</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -11622,7 +11622,7 @@
       </c>
       <c r="F11" t="str">
         <f>Palmon!B12 &amp; "," &amp; Palmon!C12 &amp; "," &amp; Palmon!D12 &amp; "," &amp; Palmon!E12 &amp; "," &amp; Palmon!G12 &amp; "," &amp; SUBSTITUTE(Palmon!H12,",",".") &amp; "," &amp; Palmon!I12 &amp; "," &amp; SUBSTITUTE(Palmon!P12,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q12,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R12,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S12,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T12,",",".") &amp; "," &amp; Palmon!J12 &amp; "," &amp; Palmon!K12 &amp; "," &amp; Palmon!L12 &amp; "," &amp; Palmon!M12 &amp; "," &amp; Palmon!N12 &amp; "," &amp; SUBSTITUTE(Palmon!U12,",",".") &amp; "," &amp; Palmon!V12 &amp; "," &amp; Palmon!X12 &amp; "," &amp; Palmon!Y12 &amp; "," &amp; Palmon!AA12 &amp; "," &amp; Palmon!AB12 &amp; "," &amp; Palmon!AC12 &amp; "," &amp; Palmon!AE12 &amp; "," &amp; Palmon!AF12 &amp; "," &amp; Palmon!AI12 &amp; "," &amp; Palmon!AJ12</f>
-        <v>Abuzzinian,Electricity,Defend,230,4,4,14,1,1,1,1,0,1,1,1,Max,,0.487179487179487,486,3390620000,1,4230,12,2,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcT-r6BZKxjf-kMlCmzHjhnUHjvmCaOn5DxiYw&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcR23XO-FCNYoHOIhLnxge8AzFmdP8mD1D-mzQ&amp;s,Servolt,</v>
+        <v>Abuzzinian,Electricity,Defend,250,4,4.1,14,1,1,1,1,0.199999999999999,1,1,1,Max,,0.589743589743589,386,3503540000,1,4350,11,2,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcT-r6BZKxjf-kMlCmzHjhnUHjvmCaOn5DxiYw&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcR23XO-FCNYoHOIhLnxge8AzFmdP8mD1D-mzQ&amp;s,Servolt,</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -11648,7 +11648,7 @@
       </c>
       <c r="F12" t="str">
         <f>Palmon!B13 &amp; "," &amp; Palmon!C13 &amp; "," &amp; Palmon!D13 &amp; "," &amp; Palmon!E13 &amp; "," &amp; Palmon!G13 &amp; "," &amp; SUBSTITUTE(Palmon!H13,",",".") &amp; "," &amp; Palmon!I13 &amp; "," &amp; SUBSTITUTE(Palmon!P13,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q13,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R13,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S13,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T13,",",".") &amp; "," &amp; Palmon!J13 &amp; "," &amp; Palmon!K13 &amp; "," &amp; Palmon!L13 &amp; "," &amp; Palmon!M13 &amp; "," &amp; Palmon!N13 &amp; "," &amp; SUBSTITUTE(Palmon!U13,",",".") &amp; "," &amp; Palmon!V13 &amp; "," &amp; Palmon!X13 &amp; "," &amp; Palmon!Y13 &amp; "," &amp; Palmon!AA13 &amp; "," &amp; Palmon!AB13 &amp; "," &amp; Palmon!AC13 &amp; "," &amp; Palmon!AE13 &amp; "," &amp; Palmon!AF13 &amp; "," &amp; Palmon!AI13 &amp; "," &amp; Palmon!AJ13</f>
-        <v>Escarffier,Fire,Defend,230,2,2.3,8,1,1,0.6,0,0,5,5,5,,,0.138461538461538,832,3390620000,1,2530,20,3,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcST2CrUIPAlFNBLPgZn0Tu93KelabHVVAbNLQ&amp;s, ,Essaucier,</v>
+        <v>Escarffier,Fire,Defend,240,2,2.4,8,1,1,0.8,0,0,5,5,5,,,0.158974358974359,812,4211940000,1,2640,22,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcST2CrUIPAlFNBLPgZn0Tu93KelabHVVAbNLQ&amp;s, ,Essaucier,</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -11674,7 +11674,7 @@
       </c>
       <c r="F13" t="str">
         <f>Palmon!B14 &amp; "," &amp; Palmon!C14 &amp; "," &amp; Palmon!D14 &amp; "," &amp; Palmon!E14 &amp; "," &amp; Palmon!G14 &amp; "," &amp; SUBSTITUTE(Palmon!H14,",",".") &amp; "," &amp; Palmon!I14 &amp; "," &amp; SUBSTITUTE(Palmon!P14,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q14,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R14,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S14,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T14,",",".") &amp; "," &amp; Palmon!J14 &amp; "," &amp; Palmon!K14 &amp; "," &amp; Palmon!L14 &amp; "," &amp; Palmon!M14 &amp; "," &amp; Palmon!N14 &amp; "," &amp; SUBSTITUTE(Palmon!U14,",",".") &amp; "," &amp; Palmon!V14 &amp; "," &amp; Palmon!X14 &amp; "," &amp; Palmon!Y14 &amp; "," &amp; Palmon!AA14 &amp; "," &amp; Palmon!AB14 &amp; "," &amp; Palmon!AC14 &amp; "," &amp; Palmon!AE14 &amp; "," &amp; Palmon!AF14 &amp; "," &amp; Palmon!AI14 &amp; "," &amp; Palmon!AJ14</f>
-        <v>Lucidina,Water,Attack,270,4,4,0,1,1,1,1,0,5,5,15,Max,,0.487179487179487,500,135120000,,4270,11,2,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcR9A_xtftnwTH1zCnLIOcgmJKNZtFnB-e8QOw&amp;s, ,Oneirina,</v>
+        <v>Lucidina,Water,Attack,270,4,4,0,1,1,1,1,0,5,5,15,Max,,0.487179487179487,500,1515640000,1,4270,14,2,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcR9A_xtftnwTH1zCnLIOcgmJKNZtFnB-e8QOw&amp;s, ,Oneirina,</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -11700,7 +11700,7 @@
       </c>
       <c r="F14" t="str">
         <f>Palmon!B15 &amp; "," &amp; Palmon!C15 &amp; "," &amp; Palmon!D15 &amp; "," &amp; Palmon!E15 &amp; "," &amp; Palmon!G15 &amp; "," &amp; SUBSTITUTE(Palmon!H15,",",".") &amp; "," &amp; Palmon!I15 &amp; "," &amp; SUBSTITUTE(Palmon!P15,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q15,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R15,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S15,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T15,",",".") &amp; "," &amp; Palmon!J15 &amp; "," &amp; Palmon!K15 &amp; "," &amp; Palmon!L15 &amp; "," &amp; Palmon!M15 &amp; "," &amp; Palmon!N15 &amp; "," &amp; SUBSTITUTE(Palmon!U15,",",".") &amp; "," &amp; Palmon!V15 &amp; "," &amp; Palmon!X15 &amp; "," &amp; Palmon!Y15 &amp; "," &amp; Palmon!AA15 &amp; "," &amp; Palmon!AB15 &amp; "," &amp; Palmon!AC15 &amp; "," &amp; Palmon!AE15 &amp; "," &amp; Palmon!AF15 &amp; "," &amp; Palmon!AI15 &amp; "," &amp; Palmon!AJ15</f>
-        <v>Fleurizard,Wood,Attack,260,5,5,0,1,1,1,1,1,1,1,1,Max,10,1,0,1235520000,1,5260,5,1,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQCf63iS9oq-SMn3DO74UTS2j_zSrzNVTRMOQ&amp;s, ,,</v>
+        <v>Fleurizard,Wood,Attack,270,5,5,0,1,1,1,1,1,1,1,1,Max,10,1,0,1515640000,1,5270,5,1,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQCf63iS9oq-SMn3DO74UTS2j_zSrzNVTRMOQ&amp;s, ,,</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -11726,7 +11726,7 @@
       </c>
       <c r="F15" t="str">
         <f>Palmon!B16 &amp; "," &amp; Palmon!C16 &amp; "," &amp; Palmon!D16 &amp; "," &amp; Palmon!E16 &amp; "," &amp; Palmon!G16 &amp; "," &amp; SUBSTITUTE(Palmon!H16,",",".") &amp; "," &amp; Palmon!I16 &amp; "," &amp; SUBSTITUTE(Palmon!P16,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q16,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R16,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S16,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T16,",",".") &amp; "," &amp; Palmon!J16 &amp; "," &amp; Palmon!K16 &amp; "," &amp; Palmon!L16 &amp; "," &amp; Palmon!M16 &amp; "," &amp; Palmon!N16 &amp; "," &amp; SUBSTITUTE(Palmon!U16,",",".") &amp; "," &amp; Palmon!V16 &amp; "," &amp; Palmon!X16 &amp; "," &amp; Palmon!Y16 &amp; "," &amp; Palmon!AA16 &amp; "," &amp; Palmon!AB16 &amp; "," &amp; Palmon!AC16 &amp; "," &amp; Palmon!AE16 &amp; "," &amp; Palmon!AF16 &amp; "," &amp; Palmon!AI16 &amp; "," &amp; Palmon!AJ16</f>
-        <v>Statchew,Wood,Defend,240,2,2.2,10,1,1,0.4,0,0,15,5,9,,,0.117948717948718,850,2831420000,1,2440,23,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSC1rp-0lIuUyVvSi8kN_vJnr_Ln4mF4lh4zg&amp;s, ,Anubeast,</v>
+        <v>Statchew,Wood,Defend,250,3,3,10,1,1,1,0,0,15,5,9,,,0.179487179487179,790,3503540000,1,3250,19,3,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSC1rp-0lIuUyVvSi8kN_vJnr_Ln4mF4lh4zg&amp;s, ,Anubeast,</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -11752,7 +11752,7 @@
       </c>
       <c r="F16" t="str">
         <f>Palmon!B17 &amp; "," &amp; Palmon!C17 &amp; "," &amp; Palmon!D17 &amp; "," &amp; Palmon!E17 &amp; "," &amp; Palmon!G17 &amp; "," &amp; SUBSTITUTE(Palmon!H17,",",".") &amp; "," &amp; Palmon!I17 &amp; "," &amp; SUBSTITUTE(Palmon!P17,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q17,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R17,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S17,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T17,",",".") &amp; "," &amp; Palmon!J17 &amp; "," &amp; Palmon!K17 &amp; "," &amp; Palmon!L17 &amp; "," &amp; Palmon!M17 &amp; "," &amp; Palmon!N17 &amp; "," &amp; SUBSTITUTE(Palmon!U17,",",".") &amp; "," &amp; Palmon!V17 &amp; "," &amp; Palmon!X17 &amp; "," &amp; Palmon!Y17 &amp; "," &amp; Palmon!AA17 &amp; "," &amp; Palmon!AB17 &amp; "," &amp; Palmon!AC17 &amp; "," &amp; Palmon!AE17 &amp; "," &amp; Palmon!AF17 &amp; "," &amp; Palmon!AI17 &amp; "," &amp; Palmon!AJ17</f>
-        <v>Battereina,Electricity,Attack,210,3,3,0,1,1,1,0,0,1,1,1,,,0.179487179487179,800,4161420000,1,3210,18,3,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQaumzt62POzCPWE5kNVnUA5j6pKVetbogSOJqvW2HU&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTun-SMpIMKagR2SMRlAysEcjxhO7sD6Nq3IQ&amp;s,Ampereina,</v>
+        <v>Battereina,Electricity,Attack,250,4,4,0,1,1,1,1,0,1,1,1,Max,,0.487179487179487,500,3503540000,1,4250,15,3,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQaumzt62POzCPWE5kNVnUA5j6pKVetbogSOJqvW2HU&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTun-SMpIMKagR2SMRlAysEcjxhO7sD6Nq3IQ&amp;s,Ampereina,</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="F17" t="str">
         <f>Palmon!B18 &amp; "," &amp; Palmon!C18 &amp; "," &amp; Palmon!D18 &amp; "," &amp; Palmon!E18 &amp; "," &amp; Palmon!G18 &amp; "," &amp; SUBSTITUTE(Palmon!H18,",",".") &amp; "," &amp; Palmon!I18 &amp; "," &amp; SUBSTITUTE(Palmon!P18,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q18,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R18,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S18,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T18,",",".") &amp; "," &amp; Palmon!J18 &amp; "," &amp; Palmon!K18 &amp; "," &amp; Palmon!L18 &amp; "," &amp; Palmon!M18 &amp; "," &amp; Palmon!N18 &amp; "," &amp; SUBSTITUTE(Palmon!U18,",",".") &amp; "," &amp; Palmon!V18 &amp; "," &amp; Palmon!X18 &amp; "," &amp; Palmon!Y18 &amp; "," &amp; Palmon!AA18 &amp; "," &amp; Palmon!AB18 &amp; "," &amp; Palmon!AC18 &amp; "," &amp; Palmon!AE18 &amp; "," &amp; Palmon!AF18 &amp; "," &amp; Palmon!AI18 &amp; "," &amp; Palmon!AJ18</f>
-        <v>Fulgairy,Electricity,Defend,210,2,2.2,0,1,1,0.4,0,0,5,5,10,,,0.117948717948718,860,4161420000,1,2410,25,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRvhKm8Syu_29_yraif6I_ybijQhVUhvDmMNg&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSNLJe_mmX76tcOcm93Zzrq-x4btMmg4l1csw&amp;s,Keraunosaur,</v>
+        <v>Fulgairy,Electricity,Defend,230,3,3.1,0,1,1,1,0.2,0,5,5,10,,,0.241025641025641,740,4771140000,1,3330,17,3,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRvhKm8Syu_29_yraif6I_ybijQhVUhvDmMNg&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSNLJe_mmX76tcOcm93Zzrq-x4btMmg4l1csw&amp;s,Keraunosaur,</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -11804,7 +11804,7 @@
       </c>
       <c r="F18" t="str">
         <f>Palmon!B19 &amp; "," &amp; Palmon!C19 &amp; "," &amp; Palmon!D19 &amp; "," &amp; Palmon!E19 &amp; "," &amp; Palmon!G19 &amp; "," &amp; SUBSTITUTE(Palmon!H19,",",".") &amp; "," &amp; Palmon!I19 &amp; "," &amp; SUBSTITUTE(Palmon!P19,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q19,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R19,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S19,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T19,",",".") &amp; "," &amp; Palmon!J19 &amp; "," &amp; Palmon!K19 &amp; "," &amp; Palmon!L19 &amp; "," &amp; Palmon!M19 &amp; "," &amp; Palmon!N19 &amp; "," &amp; SUBSTITUTE(Palmon!U19,",",".") &amp; "," &amp; Palmon!V19 &amp; "," &amp; Palmon!X19 &amp; "," &amp; Palmon!Y19 &amp; "," &amp; Palmon!AA19 &amp; "," &amp; Palmon!AB19 &amp; "," &amp; Palmon!AC19 &amp; "," &amp; Palmon!AE19 &amp; "," &amp; Palmon!AF19 &amp; "," &amp; Palmon!AI19 &amp; "," &amp; Palmon!AJ19</f>
-        <v>Blazeal,Fire,Attack,250,3,3,10,1,1,1,0,0,15,10,15,,,0.179487179487179,790,2123020000,1,3250,17,3,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRsDMtJC3uCFkue3lLpIZqf7OpQgR7XoKOS8g&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTc2Arfa7L5NJadx_WdnWjGTYRLP6bgvNMsDUbraRNI&amp;s,Wildfuror,</v>
+        <v>Blazeal,Fire,Attack,250,3,3,10,1,1,1,0,0,15,10,15,,,0.179487179487179,790,3503540000,1,3250,20,3,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRsDMtJC3uCFkue3lLpIZqf7OpQgR7XoKOS8g&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTc2Arfa7L5NJadx_WdnWjGTYRLP6bgvNMsDUbraRNI&amp;s,Wildfuror,</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -11830,7 +11830,7 @@
       </c>
       <c r="F19" t="str">
         <f>Palmon!B20 &amp; "," &amp; Palmon!C20 &amp; "," &amp; Palmon!D20 &amp; "," &amp; Palmon!E20 &amp; "," &amp; Palmon!G20 &amp; "," &amp; SUBSTITUTE(Palmon!H20,",",".") &amp; "," &amp; Palmon!I20 &amp; "," &amp; SUBSTITUTE(Palmon!P20,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q20,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R20,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S20,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T20,",",".") &amp; "," &amp; Palmon!J20 &amp; "," &amp; Palmon!K20 &amp; "," &amp; Palmon!L20 &amp; "," &amp; Palmon!M20 &amp; "," &amp; Palmon!N20 &amp; "," &amp; SUBSTITUTE(Palmon!U20,",",".") &amp; "," &amp; Palmon!V20 &amp; "," &amp; Palmon!X20 &amp; "," &amp; Palmon!Y20 &amp; "," &amp; Palmon!AA20 &amp; "," &amp; Palmon!AB20 &amp; "," &amp; Palmon!AC20 &amp; "," &amp; Palmon!AE20 &amp; "," &amp; Palmon!AF20 &amp; "," &amp; Palmon!AI20 &amp; "," &amp; Palmon!AJ20</f>
-        <v>Pipistrigoi,Fire,Attack,270,4,4.1,13,1,1,1,1,0.199999999999999,15,15,15,Max,,0.589743589743589,387,135120000,,4370,8,2,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSSdARGNHB_mPJlsb0v4ULv5HaXw2movjzNTNSrkzsi&amp;s, ,Azurostrigoi,</v>
+        <v>Pipistrigoi,Fire,Attack,270,4,4.1,13,1,1,1,1,0.199999999999999,15,15,15,Max,,0.589743589743589,387,1515640000,1,4370,9,2,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSSdARGNHB_mPJlsb0v4ULv5HaXw2movjzNTNSrkzsi&amp;s, ,Azurostrigoi,</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="F20" t="str">
         <f>Palmon!B21 &amp; "," &amp; Palmon!C21 &amp; "," &amp; Palmon!D21 &amp; "," &amp; Palmon!E21 &amp; "," &amp; Palmon!G21 &amp; "," &amp; SUBSTITUTE(Palmon!H21,",",".") &amp; "," &amp; Palmon!I21 &amp; "," &amp; SUBSTITUTE(Palmon!P21,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q21,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R21,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S21,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T21,",",".") &amp; "," &amp; Palmon!J21 &amp; "," &amp; Palmon!K21 &amp; "," &amp; Palmon!L21 &amp; "," &amp; Palmon!M21 &amp; "," &amp; Palmon!N21 &amp; "," &amp; SUBSTITUTE(Palmon!U21,",",".") &amp; "," &amp; Palmon!V21 &amp; "," &amp; Palmon!X21 &amp; "," &amp; Palmon!Y21 &amp; "," &amp; Palmon!AA21 &amp; "," &amp; Palmon!AB21 &amp; "," &amp; Palmon!AC21 &amp; "," &amp; Palmon!AE21 &amp; "," &amp; Palmon!AF21 &amp; "," &amp; Palmon!AI21 &amp; "," &amp; Palmon!AJ21</f>
-        <v>Fingenue,Water,Attack,200,2,2,13,1,1,0,0,0,5,1,5,,,0.0769230769230769,887,4415720000,1,2200,30,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQMvgcplGCQCmIPq5ypILKf8v4mBVwxsMgKdg&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQK8ZtDU3nBBFFGN2vhlNn2ACJuBBoGsnFHZC7On4Gb&amp;s,Finnabelle,</v>
+        <v>Fingenue,Water,Attack,200,2,2,13,1,1,0,0,0,5,1,5,,,0.0769230769230769,887,5796240000,1,2200,31,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQMvgcplGCQCmIPq5ypILKf8v4mBVwxsMgKdg&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQK8ZtDU3nBBFFGN2vhlNn2ACJuBBoGsnFHZC7On4Gb&amp;s,Finnabelle,</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -11882,7 +11882,7 @@
       </c>
       <c r="F21" t="str">
         <f>Palmon!B22 &amp; "," &amp; Palmon!C22 &amp; "," &amp; Palmon!D22 &amp; "," &amp; Palmon!E22 &amp; "," &amp; Palmon!G22 &amp; "," &amp; SUBSTITUTE(Palmon!H22,",",".") &amp; "," &amp; Palmon!I22 &amp; "," &amp; SUBSTITUTE(Palmon!P22,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q22,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R22,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S22,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T22,",",".") &amp; "," &amp; Palmon!J22 &amp; "," &amp; Palmon!K22 &amp; "," &amp; Palmon!L22 &amp; "," &amp; Palmon!M22 &amp; "," &amp; Palmon!N22 &amp; "," &amp; SUBSTITUTE(Palmon!U22,",",".") &amp; "," &amp; Palmon!V22 &amp; "," &amp; Palmon!X22 &amp; "," &amp; Palmon!Y22 &amp; "," &amp; Palmon!AA22 &amp; "," &amp; Palmon!AB22 &amp; "," &amp; Palmon!AC22 &amp; "," &amp; Palmon!AE22 &amp; "," &amp; Palmon!AF22 &amp; "," &amp; Palmon!AI22 &amp; "," &amp; Palmon!AJ22</f>
-        <v>Dolphriend,Water,Defend,210,2,2.2,1,1,1,0.4,0,0,1,1,1,,,0.117948717948718,859,4161420000,1,2410,26,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQ5ThIRML8-S9czd3JEMxpMlnMn9UAMwdeiBw&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTQp9fQrKVHd_zzyuSxM8QSOjlZsRbJ0lwxrg&amp;s,Adolphonis,</v>
+        <v>Dolphriend,Water,Defend,210,2,2.4,1,1,1,0.8,0,0,1,1,1,,,0.158974358974359,819,5541940000,1,2610,24,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQ5ThIRML8-S9czd3JEMxpMlnMn9UAMwdeiBw&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTQp9fQrKVHd_zzyuSxM8QSOjlZsRbJ0lwxrg&amp;s,Adolphonis,</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -11908,7 +11908,7 @@
       </c>
       <c r="F22" t="str">
         <f>Palmon!B23 &amp; "," &amp; Palmon!C23 &amp; "," &amp; Palmon!D23 &amp; "," &amp; Palmon!E23 &amp; "," &amp; Palmon!G23 &amp; "," &amp; SUBSTITUTE(Palmon!H23,",",".") &amp; "," &amp; Palmon!I23 &amp; "," &amp; SUBSTITUTE(Palmon!P23,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q23,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R23,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S23,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T23,",",".") &amp; "," &amp; Palmon!J23 &amp; "," &amp; Palmon!K23 &amp; "," &amp; Palmon!L23 &amp; "," &amp; Palmon!M23 &amp; "," &amp; Palmon!N23 &amp; "," &amp; SUBSTITUTE(Palmon!U23,",",".") &amp; "," &amp; Palmon!V23 &amp; "," &amp; Palmon!X23 &amp; "," &amp; Palmon!Y23 &amp; "," &amp; Palmon!AA23 &amp; "," &amp; Palmon!AB23 &amp; "," &amp; Palmon!AC23 &amp; "," &amp; Palmon!AE23 &amp; "," &amp; Palmon!AF23 &amp; "," &amp; Palmon!AI23 &amp; "," &amp; Palmon!AJ23</f>
-        <v>Ninjump,Water,Attack,160,2,2.3,10,1,1,0.6,0,0,1,1,1,,,0.138461538461538,830,4919220000,1,2460,21,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQlW5YoM4c6bArAuIb7UxI-VfUI9GmBp85Qig&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRXczs_Bjhslhr7Mf2HENU6MTyGpz0RJEMjNA&amp;s,Bufonobi,Shadowkaeru</v>
+        <v>Ninjump,Water,Attack,160,2,2.3,10,1,1,0.6,0,0,1,1,1,,,0.138461538461538,830,6299740000,1,2460,26,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQlW5YoM4c6bArAuIb7UxI-VfUI9GmBp85Qig&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRXczs_Bjhslhr7Mf2HENU6MTyGpz0RJEMjNA&amp;s,Bufonobi,Shadowkaeru</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="F23" t="str">
         <f>Palmon!B24 &amp; "," &amp; Palmon!C24 &amp; "," &amp; Palmon!D24 &amp; "," &amp; Palmon!E24 &amp; "," &amp; Palmon!G24 &amp; "," &amp; SUBSTITUTE(Palmon!H24,",",".") &amp; "," &amp; Palmon!I24 &amp; "," &amp; SUBSTITUTE(Palmon!P24,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q24,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R24,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S24,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T24,",",".") &amp; "," &amp; Palmon!J24 &amp; "," &amp; Palmon!K24 &amp; "," &amp; Palmon!L24 &amp; "," &amp; Palmon!M24 &amp; "," &amp; Palmon!N24 &amp; "," &amp; SUBSTITUTE(Palmon!U24,",",".") &amp; "," &amp; Palmon!V24 &amp; "," &amp; Palmon!X24 &amp; "," &amp; Palmon!Y24 &amp; "," &amp; Palmon!AA24 &amp; "," &amp; Palmon!AB24 &amp; "," &amp; Palmon!AC24 &amp; "," &amp; Palmon!AE24 &amp; "," &amp; Palmon!AF24 &amp; "," &amp; Palmon!AI24 &amp; "," &amp; Palmon!AJ24</f>
-        <v>Surveilynx,Wood,Attack,220,2,2,0,1,1,0,0,0,10,10,10,,,0.0769230769230769,900,3826220000,1,2220,29,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcS2Z4TkKenIldVD1AQ7o1ftBU6pG9zKRz-FKA&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQt6lIf0Em_f_DT0VurOVsujswJCEmGOpJk4N6txfed&amp;s,Camouflynx,</v>
+        <v>Surveilynx,Wood,Attack,230,2,2,0,1,1,0,0,0,10,10,10,,,0.0769230769230769,900,4771140000,1,2230,30,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcS2Z4TkKenIldVD1AQ7o1ftBU6pG9zKRz-FKA&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQt6lIf0Em_f_DT0VurOVsujswJCEmGOpJk4N6txfed&amp;s,Camouflynx,</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -11960,7 +11960,7 @@
       </c>
       <c r="F24" t="str">
         <f>Palmon!B25 &amp; "," &amp; Palmon!C25 &amp; "," &amp; Palmon!D25 &amp; "," &amp; Palmon!E25 &amp; "," &amp; Palmon!G25 &amp; "," &amp; SUBSTITUTE(Palmon!H25,",",".") &amp; "," &amp; Palmon!I25 &amp; "," &amp; SUBSTITUTE(Palmon!P25,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q25,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R25,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S25,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T25,",",".") &amp; "," &amp; Palmon!J25 &amp; "," &amp; Palmon!K25 &amp; "," &amp; Palmon!L25 &amp; "," &amp; Palmon!M25 &amp; "," &amp; Palmon!N25 &amp; "," &amp; SUBSTITUTE(Palmon!U25,",",".") &amp; "," &amp; Palmon!V25 &amp; "," &amp; Palmon!X25 &amp; "," &amp; Palmon!Y25 &amp; "," &amp; Palmon!AA25 &amp; "," &amp; Palmon!AB25 &amp; "," &amp; Palmon!AC25 &amp; "," &amp; Palmon!AE25 &amp; "," &amp; Palmon!AF25 &amp; "," &amp; Palmon!AI25 &amp; "," &amp; Palmon!AJ25</f>
-        <v>Salamantis,Wood,Attack,200,2,2,0,1,1,0,0,0,1,1,1,,,0.0769230769230769,900,4415720000,1,2200,31,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSPFSxpzP3XhhfdRhxvv_Oi86DkexX6yjZrRA&amp;s,,Silvaurus,</v>
+        <v>Salamantis,Wood,Attack,200,2,2.3,0,1,1,0.6,0,0,1,1,1,,,0.138461538461538,840,5796240000,1,2500,25,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSPFSxpzP3XhhfdRhxvv_Oi86DkexX6yjZrRA&amp;s,,Silvaurus,</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -11986,7 +11986,7 @@
       </c>
       <c r="F25" t="str">
         <f>Palmon!B26 &amp; "," &amp; Palmon!C26 &amp; "," &amp; Palmon!D26 &amp; "," &amp; Palmon!E26 &amp; "," &amp; Palmon!G26 &amp; "," &amp; SUBSTITUTE(Palmon!H26,",",".") &amp; "," &amp; Palmon!I26 &amp; "," &amp; SUBSTITUTE(Palmon!P26,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q26,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R26,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S26,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T26,",",".") &amp; "," &amp; Palmon!J26 &amp; "," &amp; Palmon!K26 &amp; "," &amp; Palmon!L26 &amp; "," &amp; Palmon!M26 &amp; "," &amp; Palmon!N26 &amp; "," &amp; SUBSTITUTE(Palmon!U26,",",".") &amp; "," &amp; Palmon!V26 &amp; "," &amp; Palmon!X26 &amp; "," &amp; Palmon!Y26 &amp; "," &amp; Palmon!AA26 &amp; "," &amp; Palmon!AB26 &amp; "," &amp; Palmon!AC26 &amp; "," &amp; Palmon!AE26 &amp; "," &amp; Palmon!AF26 &amp; "," &amp; Palmon!AI26 &amp; "," &amp; Palmon!AJ26</f>
-        <v>Regalion,Water,Defend,200,2,2.1,11,1,1,0.2,0,0,10,10,10,,,0.0974358974358975,869,4415720000,1,2300,28,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcToQuTLjFC_oynclPIY9tWM7qAaMIPbmzTn2Q&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcS0uWep-9VXcdMd6qSpdASqYR42mG4SmBsCjw&amp;s,Lionarch,</v>
+        <v>Regalion,Water,Defend,200,2,2.2,11,1,1,0.4,0,0,10,10,10,,,0.117948717948718,849,5796240000,1,2400,29,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcToQuTLjFC_oynclPIY9tWM7qAaMIPbmzTn2Q&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcS0uWep-9VXcdMd6qSpdASqYR42mG4SmBsCjw&amp;s,Lionarch,</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -12012,7 +12012,7 @@
       </c>
       <c r="F26" t="str">
         <f>Palmon!B27 &amp; "," &amp; Palmon!C27 &amp; "," &amp; Palmon!D27 &amp; "," &amp; Palmon!E27 &amp; "," &amp; Palmon!G27 &amp; "," &amp; SUBSTITUTE(Palmon!H27,",",".") &amp; "," &amp; Palmon!I27 &amp; "," &amp; SUBSTITUTE(Palmon!P27,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q27,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R27,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S27,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T27,",",".") &amp; "," &amp; Palmon!J27 &amp; "," &amp; Palmon!K27 &amp; "," &amp; Palmon!L27 &amp; "," &amp; Palmon!M27 &amp; "," &amp; Palmon!N27 &amp; "," &amp; SUBSTITUTE(Palmon!U27,",",".") &amp; "," &amp; Palmon!V27 &amp; "," &amp; Palmon!X27 &amp; "," &amp; Palmon!Y27 &amp; "," &amp; Palmon!AA27 &amp; "," &amp; Palmon!AB27 &amp; "," &amp; Palmon!AC27 &amp; "," &amp; Palmon!AE27 &amp; "," &amp; Palmon!AF27 &amp; "," &amp; Palmon!AI27 &amp; "," &amp; Palmon!AJ27</f>
-        <v>Mantleray,Electricity,Attack,210,2,2.4,3,1,1,0.8,0,0,4,1,1,,,0.158974358974359,817,4161420000,1,2610,19,3,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSWhzppoZXwh-zBnWIY3GFkIp0x0kc0hAzG0A&amp;s, ,Sorceray,</v>
+        <v>Mantleray,Electricity,Attack,230,2,2.4,3,1,1,0.8,0,0,4,1,1,,,0.158974358974359,817,4771140000,1,2630,23,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSWhzppoZXwh-zBnWIY3GFkIp0x0kc0hAzG0A&amp;s, ,Sorceray,</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -12038,7 +12038,7 @@
       </c>
       <c r="F27" t="str">
         <f>Palmon!B28 &amp; "," &amp; Palmon!C28 &amp; "," &amp; Palmon!D28 &amp; "," &amp; Palmon!E28 &amp; "," &amp; Palmon!G28 &amp; "," &amp; SUBSTITUTE(Palmon!H28,",",".") &amp; "," &amp; Palmon!I28 &amp; "," &amp; SUBSTITUTE(Palmon!P28,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q28,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R28,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S28,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T28,",",".") &amp; "," &amp; Palmon!J28 &amp; "," &amp; Palmon!K28 &amp; "," &amp; Palmon!L28 &amp; "," &amp; Palmon!M28 &amp; "," &amp; Palmon!N28 &amp; "," &amp; SUBSTITUTE(Palmon!U28,",",".") &amp; "," &amp; Palmon!V28 &amp; "," &amp; Palmon!X28 &amp; "," &amp; Palmon!Y28 &amp; "," &amp; Palmon!AA28 &amp; "," &amp; Palmon!AB28 &amp; "," &amp; Palmon!AC28 &amp; "," &amp; Palmon!AE28 &amp; "," &amp; Palmon!AF28 &amp; "," &amp; Palmon!AI28 &amp; "," &amp; Palmon!AJ28</f>
-        <v>Oleana,Wood,Attack,260,5,5,128,1,1,1,1,1,1,1,1,Max,10,1,-128,1235520000,1,5260,6,1,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQ02wmDjsAMofj1ObwwNW6Vhl_QQ-LUodGIKA&amp;s, ,,</v>
+        <v>Oleana,Wood,Attack,260,5,5,128,1,1,1,1,1,1,1,1,Max,10,1,-128,2616040000,1,5260,7,1,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQ02wmDjsAMofj1ObwwNW6Vhl_QQ-LUodGIKA&amp;s, ,,</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -12064,7 +12064,7 @@
       </c>
       <c r="F28" t="str">
         <f>Palmon!B29 &amp; "," &amp; Palmon!C29 &amp; "," &amp; Palmon!D29 &amp; "," &amp; Palmon!E29 &amp; "," &amp; Palmon!G29 &amp; "," &amp; SUBSTITUTE(Palmon!H29,",",".") &amp; "," &amp; Palmon!I29 &amp; "," &amp; SUBSTITUTE(Palmon!P29,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q29,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R29,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S29,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T29,",",".") &amp; "," &amp; Palmon!J29 &amp; "," &amp; Palmon!K29 &amp; "," &amp; Palmon!L29 &amp; "," &amp; Palmon!M29 &amp; "," &amp; Palmon!N29 &amp; "," &amp; SUBSTITUTE(Palmon!U29,",",".") &amp; "," &amp; Palmon!V29 &amp; "," &amp; Palmon!X29 &amp; "," &amp; Palmon!Y29 &amp; "," &amp; Palmon!AA29 &amp; "," &amp; Palmon!AB29 &amp; "," &amp; Palmon!AC29 &amp; "," &amp; Palmon!AE29 &amp; "," &amp; Palmon!AF29 &amp; "," &amp; Palmon!AI29 &amp; "," &amp; Palmon!AJ29</f>
-        <v>Spookaboo,Fire,Attack,210,3,3.2,10,1,1,1,0.4,0,1,1,20,,,0.302564102564103,670,4161420000,1,3410,14,2,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcT29K673YTBvt_EofrppvnWB4sgt43DEq1pTw&amp;s, ,,</v>
+        <v>Spookaboo,Fire,Attack,230,5,5,10,1,1,1,1,1,1,1,30,Max,10,1,-10,4771140000,1,5230,8,2,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcT29K673YTBvt_EofrppvnWB4sgt43DEq1pTw&amp;s, ,,</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -12090,7 +12090,7 @@
       </c>
       <c r="F29" t="str">
         <f>Palmon!B30 &amp; "," &amp; Palmon!C30 &amp; "," &amp; Palmon!D30 &amp; "," &amp; Palmon!E30 &amp; "," &amp; Palmon!G30 &amp; "," &amp; SUBSTITUTE(Palmon!H30,",",".") &amp; "," &amp; Palmon!I30 &amp; "," &amp; SUBSTITUTE(Palmon!P30,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q30,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R30,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S30,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T30,",",".") &amp; "," &amp; Palmon!J30 &amp; "," &amp; Palmon!K30 &amp; "," &amp; Palmon!L30 &amp; "," &amp; Palmon!M30 &amp; "," &amp; Palmon!N30 &amp; "," &amp; SUBSTITUTE(Palmon!U30,",",".") &amp; "," &amp; Palmon!V30 &amp; "," &amp; Palmon!X30 &amp; "," &amp; Palmon!Y30 &amp; "," &amp; Palmon!AA30 &amp; "," &amp; Palmon!AB30 &amp; "," &amp; Palmon!AC30 &amp; "," &amp; Palmon!AE30 &amp; "," &amp; Palmon!AF30 &amp; "," &amp; Palmon!AI30 &amp; "," &amp; Palmon!AJ30</f>
-        <v>Kungpaw,Water,Defend,190,4,4,30,1,1,1,1,0,1,1,1,Max,,0.487179487179487,470,4605720000,1,4190,13,2,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRV1HdRcNPUS4HjDBZ2YOXgaMW_I8FgZEP5xg&amp;s,,,</v>
+        <v>Kungpaw,Water,Defend,200,4,4.1,30,1,1,1,1,0.199999999999999,1,1,1,Max,,0.589743589743589,370,5796240000,1,4300,12,2,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRV1HdRcNPUS4HjDBZ2YOXgaMW_I8FgZEP5xg&amp;s,,,</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -12116,7 +12116,7 @@
       </c>
       <c r="F30" t="str">
         <f>Palmon!B31 &amp; "," &amp; Palmon!C31 &amp; "," &amp; Palmon!D31 &amp; "," &amp; Palmon!E31 &amp; "," &amp; Palmon!G31 &amp; "," &amp; SUBSTITUTE(Palmon!H31,",",".") &amp; "," &amp; Palmon!I31 &amp; "," &amp; SUBSTITUTE(Palmon!P31,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q31,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R31,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S31,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T31,",",".") &amp; "," &amp; Palmon!J31 &amp; "," &amp; Palmon!K31 &amp; "," &amp; Palmon!L31 &amp; "," &amp; Palmon!M31 &amp; "," &amp; Palmon!N31 &amp; "," &amp; SUBSTITUTE(Palmon!U31,",",".") &amp; "," &amp; Palmon!V31 &amp; "," &amp; Palmon!X31 &amp; "," &amp; Palmon!Y31 &amp; "," &amp; Palmon!AA31 &amp; "," &amp; Palmon!AB31 &amp; "," &amp; Palmon!AC31 &amp; "," &amp; Palmon!AE31 &amp; "," &amp; Palmon!AF31 &amp; "," &amp; Palmon!AI31 &amp; "," &amp; Palmon!AJ31</f>
-        <v>Baboom,Wood,Attack,210,2,2.1,10,1,1,0.2,0,0,5,1,1,,,0.0974358974358975,870,4161420000,1,2310,27,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRh7P3oaH_Kq0fni1aOxe3TmDgHULu_Z-UWUg&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSQA67-vNrm701vphmHvRKGkJTx2O2gyTi00Q&amp;s,Rumbkey,</v>
+        <v>Baboom,Wood,Attack,240,3,3,10,1,1,1,0,0,5,1,1,,,0.179487179487179,790,4211940000,1,3240,21,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRh7P3oaH_Kq0fni1aOxe3TmDgHULu_Z-UWUg&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSQA67-vNrm701vphmHvRKGkJTx2O2gyTi00Q&amp;s,Rumbkey,</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -12142,7 +12142,7 @@
       </c>
       <c r="F31" t="str">
         <f>Palmon!B32 &amp; "," &amp; Palmon!C32 &amp; "," &amp; Palmon!D32 &amp; "," &amp; Palmon!E32 &amp; "," &amp; Palmon!G32 &amp; "," &amp; SUBSTITUTE(Palmon!H32,",",".") &amp; "," &amp; Palmon!I32 &amp; "," &amp; SUBSTITUTE(Palmon!P32,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q32,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R32,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S32,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T32,",",".") &amp; "," &amp; Palmon!J32 &amp; "," &amp; Palmon!K32 &amp; "," &amp; Palmon!L32 &amp; "," &amp; Palmon!M32 &amp; "," &amp; Palmon!N32 &amp; "," &amp; SUBSTITUTE(Palmon!U32,",",".") &amp; "," &amp; Palmon!V32 &amp; "," &amp; Palmon!X32 &amp; "," &amp; Palmon!Y32 &amp; "," &amp; Palmon!AA32 &amp; "," &amp; Palmon!AB32 &amp; "," &amp; Palmon!AC32 &amp; "," &amp; Palmon!AE32 &amp; "," &amp; Palmon!AF32 &amp; "," &amp; Palmon!AI32 &amp; "," &amp; Palmon!AJ32</f>
-        <v>Pyregeist,Fire,Defend,,0,,,0,0,0,0,0,,,,,,0,975,5044093700,,0,34,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQxjczIZhaTQV2VukHWlKoJMQ30DrUIwatAEw&amp;s, ,Embergeist,</v>
+        <v>Pyregeist,Fire,Defend,,0,,,0,0,0,0,0,,,,,,0,975,6424613700,,0,34,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQxjczIZhaTQV2VukHWlKoJMQ30DrUIwatAEw&amp;s, ,Embergeist,</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -12168,7 +12168,7 @@
       </c>
       <c r="F32" t="str">
         <f>Palmon!B33 &amp; "," &amp; Palmon!C33 &amp; "," &amp; Palmon!D33 &amp; "," &amp; Palmon!E33 &amp; "," &amp; Palmon!G33 &amp; "," &amp; SUBSTITUTE(Palmon!H33,",",".") &amp; "," &amp; Palmon!I33 &amp; "," &amp; SUBSTITUTE(Palmon!P33,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q33,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R33,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S33,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T33,",",".") &amp; "," &amp; Palmon!J33 &amp; "," &amp; Palmon!K33 &amp; "," &amp; Palmon!L33 &amp; "," &amp; Palmon!M33 &amp; "," &amp; Palmon!N33 &amp; "," &amp; SUBSTITUTE(Palmon!U33,",",".") &amp; "," &amp; Palmon!V33 &amp; "," &amp; Palmon!X33 &amp; "," &amp; Palmon!Y33 &amp; "," &amp; Palmon!AA33 &amp; "," &amp; Palmon!AB33 &amp; "," &amp; Palmon!AC33 &amp; "," &amp; Palmon!AE33 &amp; "," &amp; Palmon!AF33 &amp; "," &amp; Palmon!AI33 &amp; "," &amp; Palmon!AJ33</f>
-        <v>Thundertooth,Electricity,Attack,140,5,5,0,1,1,1,1,1,1,1,1,Max,10,1,0,4999220000,1,5140,7,1,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRNSg29kZ5t51s7m9SpGygJKsQow67zLt08qg&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQoXkXemCK02vmhKICXcvjchtQ-qvcAc5zyrA&amp;s,Thundermane,</v>
+        <v>Thundertooth,Electricity,Attack,270,5,5,0,1,1,1,1,1,1,1,1,Max,10,1,0,1515640000,1,5270,6,1,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRNSg29kZ5t51s7m9SpGygJKsQow67zLt08qg&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQoXkXemCK02vmhKICXcvjchtQ-qvcAc5zyrA&amp;s,Thundermane,</v>
       </c>
     </row>
     <row r="33" spans="3:6" x14ac:dyDescent="0.25">
@@ -12186,7 +12186,7 @@
       </c>
       <c r="F33" t="str">
         <f>Palmon!B34 &amp; "," &amp; Palmon!C34 &amp; "," &amp; Palmon!D34 &amp; "," &amp; Palmon!E34 &amp; "," &amp; Palmon!G34 &amp; "," &amp; SUBSTITUTE(Palmon!H34,",",".") &amp; "," &amp; Palmon!I34 &amp; "," &amp; SUBSTITUTE(Palmon!P34,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q34,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R34,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S34,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T34,",",".") &amp; "," &amp; Palmon!J34 &amp; "," &amp; Palmon!K34 &amp; "," &amp; Palmon!L34 &amp; "," &amp; Palmon!M34 &amp; "," &amp; Palmon!N34 &amp; "," &amp; SUBSTITUTE(Palmon!U34,",",".") &amp; "," &amp; Palmon!V34 &amp; "," &amp; Palmon!X34 &amp; "," &amp; Palmon!Y34 &amp; "," &amp; Palmon!AA34 &amp; "," &amp; Palmon!AB34 &amp; "," &amp; Palmon!AC34 &amp; "," &amp; Palmon!AE34 &amp; "," &amp; Palmon!AF34 &amp; "," &amp; Palmon!AI34 &amp; "," &amp; Palmon!AJ34</f>
-        <v>Mammolith,Wood,Defend,,0,,,0,0,0,0,0,,,,,,0,975,5044093700,,0,35,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRR4T5jdtF_LaheoRmg2FLSWS4DS4QhqCFaAg&amp;s, ,Prismalith,</v>
+        <v>Mammolith,Wood,Defend,,0,,,0,0,0,0,0,,,,,,0,975,6424613700,,0,35,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRR4T5jdtF_LaheoRmg2FLSWS4DS4QhqCFaAg&amp;s, ,Prismalith,</v>
       </c>
     </row>
     <row r="34" spans="3:6" x14ac:dyDescent="0.25">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="F34" t="str">
         <f>Palmon!B35 &amp; "," &amp; Palmon!C35 &amp; "," &amp; Palmon!D35 &amp; "," &amp; Palmon!E35 &amp; "," &amp; Palmon!G35 &amp; "," &amp; SUBSTITUTE(Palmon!H35,",",".") &amp; "," &amp; Palmon!I35 &amp; "," &amp; SUBSTITUTE(Palmon!P35,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q35,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R35,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S35,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T35,",",".") &amp; "," &amp; Palmon!J35 &amp; "," &amp; Palmon!K35 &amp; "," &amp; Palmon!L35 &amp; "," &amp; Palmon!M35 &amp; "," &amp; Palmon!N35 &amp; "," &amp; SUBSTITUTE(Palmon!U35,",",".") &amp; "," &amp; Palmon!V35 &amp; "," &amp; Palmon!X35 &amp; "," &amp; Palmon!Y35 &amp; "," &amp; Palmon!AA35 &amp; "," &amp; Palmon!AB35 &amp; "," &amp; Palmon!AC35 &amp; "," &amp; Palmon!AE35 &amp; "," &amp; Palmon!AF35 &amp; "," &amp; Palmon!AI35 &amp; "," &amp; Palmon!AJ35</f>
-        <v>Glacewing,Water,Attack,270,5,5,0,1,1,1,1,1,30,30,30,Max,10,1,0,135120000,,5270,4,1,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTrE4qGrnpy2BMETqUKNyATj-OrXMdX4IeXcQ&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSRbCy1ARx2qd0P1rLvdoRvfNqa4pUV20r12A&amp;s,Cryovern,</v>
+        <v>Glacewing,Water,Attack,280,5,5,0,1,1,1,1,1,30,30,30,Max,10,1,0,164440000,,5280,1,1,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTrE4qGrnpy2BMETqUKNyATj-OrXMdX4IeXcQ&amp;s,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSRbCy1ARx2qd0P1rLvdoRvfNqa4pUV20r12A&amp;s,Cryovern,</v>
       </c>
     </row>
     <row r="35" spans="3:6" x14ac:dyDescent="0.25">
@@ -12222,7 +12222,7 @@
       </c>
       <c r="F35" t="str">
         <f>Palmon!B36 &amp; "," &amp; Palmon!C36 &amp; "," &amp; Palmon!D36 &amp; "," &amp; Palmon!E36 &amp; "," &amp; Palmon!G36 &amp; "," &amp; SUBSTITUTE(Palmon!H36,",",".") &amp; "," &amp; Palmon!I36 &amp; "," &amp; SUBSTITUTE(Palmon!P36,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q36,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R36,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S36,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T36,",",".") &amp; "," &amp; Palmon!J36 &amp; "," &amp; Palmon!K36 &amp; "," &amp; Palmon!L36 &amp; "," &amp; Palmon!M36 &amp; "," &amp; Palmon!N36 &amp; "," &amp; SUBSTITUTE(Palmon!U36,",",".") &amp; "," &amp; Palmon!V36 &amp; "," &amp; Palmon!X36 &amp; "," &amp; Palmon!Y36 &amp; "," &amp; Palmon!AA36 &amp; "," &amp; Palmon!AB36 &amp; "," &amp; Palmon!AC36 &amp; "," &amp; Palmon!AE36 &amp; "," &amp; Palmon!AF36 &amp; "," &amp; Palmon!AI36 &amp; "," &amp; Palmon!AJ36</f>
-        <v>Shadowkaeru,Water,Attack,,0,,,0,0,0,0,0,,,,,,0,975,5044093700,,0,36,,, ,,</v>
+        <v>Shadowkaeru,Water,Attack,,0,,,0,0,0,0,0,,,,,,0,975,6424613700,,0,36,,, ,,</v>
       </c>
     </row>
     <row r="36" spans="3:6" x14ac:dyDescent="0.25">
@@ -12240,7 +12240,7 @@
       </c>
       <c r="F36" t="str">
         <f>Palmon!B40 &amp; "," &amp; Palmon!C40 &amp; "," &amp; Palmon!D40 &amp; "," &amp; Palmon!E40 &amp; "," &amp; Palmon!G40 &amp; "," &amp; SUBSTITUTE(Palmon!H40,",",".") &amp; "," &amp; Palmon!I40 &amp; "," &amp; SUBSTITUTE(Palmon!P40,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q40,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R40,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S40,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T40,",",".") &amp; "," &amp; Palmon!J40 &amp; "," &amp; Palmon!K40 &amp; "," &amp; Palmon!L40 &amp; "," &amp; Palmon!M40 &amp; "," &amp; Palmon!N40 &amp; "," &amp; SUBSTITUTE(Palmon!U40,",",".") &amp; "," &amp; Palmon!V40 &amp; "," &amp; Palmon!X40 &amp; "," &amp; Palmon!Y40 &amp; "," &amp; Palmon!AA40 &amp; "," &amp; Palmon!AB40 &amp; "," &amp; Palmon!AC40 &amp; "," &amp; Palmon!AE40 &amp; "," &amp; Palmon!AF40 &amp; "," &amp; Palmon!AI40 &amp; "," &amp; Palmon!AJ40</f>
-        <v>Mystiray,Electricity,Attack,,0,,,0,0,0,0,0,,,,,,0,975,5044093700,,0,39,,, ,,</v>
+        <v>Mystiray,Electricity,Attack,,0,,,0,0,0,0,0,,,,,,0,975,6424613700,,0,39,,, ,,</v>
       </c>
     </row>
     <row r="37" spans="3:6" x14ac:dyDescent="0.25">
@@ -12258,7 +12258,7 @@
       </c>
       <c r="F37" t="str">
         <f>Palmon!B41 &amp; "," &amp; Palmon!C41 &amp; "," &amp; Palmon!D41 &amp; "," &amp; Palmon!E41 &amp; "," &amp; Palmon!G41 &amp; "," &amp; SUBSTITUTE(Palmon!H41,",",".") &amp; "," &amp; Palmon!I41 &amp; "," &amp; SUBSTITUTE(Palmon!P41,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q41,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R41,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S41,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T41,",",".") &amp; "," &amp; Palmon!J41 &amp; "," &amp; Palmon!K41 &amp; "," &amp; Palmon!L41 &amp; "," &amp; Palmon!M41 &amp; "," &amp; Palmon!N41 &amp; "," &amp; SUBSTITUTE(Palmon!U41,",",".") &amp; "," &amp; Palmon!V41 &amp; "," &amp; Palmon!X41 &amp; "," &amp; Palmon!Y41 &amp; "," &amp; Palmon!AA41 &amp; "," &amp; Palmon!AB41 &amp; "," &amp; Palmon!AC41 &amp; "," &amp; Palmon!AE41 &amp; "," &amp; Palmon!AF41 &amp; "," &amp; Palmon!AI41 &amp; "," &amp; Palmon!AJ41</f>
-        <v>Predalynx,Wood,Attack,,0,,,0,0,0,0,0,,,,,,0,975,5044093700,,0,40,,, ,,</v>
+        <v>Predalynx,Wood,Attack,,0,,,0,0,0,0,0,,,,,,0,975,6424613700,,0,40,,, ,,</v>
       </c>
     </row>
     <row r="38" spans="3:6" x14ac:dyDescent="0.25">
@@ -12276,7 +12276,7 @@
       </c>
       <c r="F38" t="str">
         <f>Palmon!B42 &amp; "," &amp; Palmon!C42 &amp; "," &amp; Palmon!D42 &amp; "," &amp; Palmon!E42 &amp; "," &amp; Palmon!G42 &amp; "," &amp; SUBSTITUTE(Palmon!H42,",",".") &amp; "," &amp; Palmon!I42 &amp; "," &amp; SUBSTITUTE(Palmon!P42,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q42,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R42,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S42,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T42,",",".") &amp; "," &amp; Palmon!J42 &amp; "," &amp; Palmon!K42 &amp; "," &amp; Palmon!L42 &amp; "," &amp; Palmon!M42 &amp; "," &amp; Palmon!N42 &amp; "," &amp; SUBSTITUTE(Palmon!U42,",",".") &amp; "," &amp; Palmon!V42 &amp; "," &amp; Palmon!X42 &amp; "," &amp; Palmon!Y42 &amp; "," &amp; Palmon!AA42 &amp; "," &amp; Palmon!AB42 &amp; "," &amp; Palmon!AC42 &amp; "," &amp; Palmon!AE42 &amp; "," &amp; Palmon!AF42 &amp; "," &amp; Palmon!AI42 &amp; "," &amp; Palmon!AJ42</f>
-        <v>Solhorn,Fire,Attack,,0,,,0,0,0,0,0,,,,,,0,975,5044093700,,0,41,,, ,,</v>
+        <v>Solhorn,Fire,Attack,,0,,,0,0,0,0,0,,,,,,0,975,6424613700,,0,41,,, ,,</v>
       </c>
     </row>
     <row r="39" spans="3:6" x14ac:dyDescent="0.25">
@@ -12294,7 +12294,7 @@
       </c>
       <c r="F39" t="str">
         <f>Palmon!B43 &amp; "," &amp; Palmon!C43 &amp; "," &amp; Palmon!D43 &amp; "," &amp; Palmon!E43 &amp; "," &amp; Palmon!G43 &amp; "," &amp; SUBSTITUTE(Palmon!H43,",",".") &amp; "," &amp; Palmon!I43 &amp; "," &amp; SUBSTITUTE(Palmon!P43,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q43,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R43,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S43,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T43,",",".") &amp; "," &amp; Palmon!J43 &amp; "," &amp; Palmon!K43 &amp; "," &amp; Palmon!L43 &amp; "," &amp; Palmon!M43 &amp; "," &amp; Palmon!N43 &amp; "," &amp; SUBSTITUTE(Palmon!U43,",",".") &amp; "," &amp; Palmon!V43 &amp; "," &amp; Palmon!X43 &amp; "," &amp; Palmon!Y43 &amp; "," &amp; Palmon!AA43 &amp; "," &amp; Palmon!AB43 &amp; "," &amp; Palmon!AC43 &amp; "," &amp; Palmon!AE43 &amp; "," &amp; Palmon!AF43 &amp; "," &amp; Palmon!AI43 &amp; "," &amp; Palmon!AJ43</f>
-        <v>Leviadolph,Water,Attack,,0,,,0,0,0,0,0,,,,,,0,975,5044093700,,0,42,,, ,,</v>
+        <v>Leviadolph,Water,Attack,,0,,,0,0,0,0,0,,,,,,0,975,6424613700,,0,42,,, ,,</v>
       </c>
     </row>
     <row r="40" spans="3:6" x14ac:dyDescent="0.25">
@@ -12312,7 +12312,7 @@
       </c>
       <c r="F40" t="str">
         <f>Palmon!B44 &amp; "," &amp; Palmon!C44 &amp; "," &amp; Palmon!D44 &amp; "," &amp; Palmon!E44 &amp; "," &amp; Palmon!G44 &amp; "," &amp; SUBSTITUTE(Palmon!H44,",",".") &amp; "," &amp; Palmon!I44 &amp; "," &amp; SUBSTITUTE(Palmon!P44,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q44,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R44,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S44,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T44,",",".") &amp; "," &amp; Palmon!J44 &amp; "," &amp; Palmon!K44 &amp; "," &amp; Palmon!L44 &amp; "," &amp; Palmon!M44 &amp; "," &amp; Palmon!N44 &amp; "," &amp; SUBSTITUTE(Palmon!U44,",",".") &amp; "," &amp; Palmon!V44 &amp; "," &amp; Palmon!X44 &amp; "," &amp; Palmon!Y44 &amp; "," &amp; Palmon!AA44 &amp; "," &amp; Palmon!AB44 &amp; "," &amp; Palmon!AC44 &amp; "," &amp; Palmon!AE44 &amp; "," &amp; Palmon!AF44 &amp; "," &amp; Palmon!AI44 &amp; "," &amp; Palmon!AJ44</f>
-        <v>Voltfang,Electricity,Attack,,0,,,0,0,0,0,0,,,,,,0,975,5044093700,,0,43,,, ,,</v>
+        <v>Voltfang,Electricity,Attack,,0,,,0,0,0,0,0,,,,,,0,975,6424613700,,0,43,,, ,,</v>
       </c>
     </row>
     <row r="41" spans="3:6" x14ac:dyDescent="0.25">
@@ -12330,7 +12330,7 @@
       </c>
       <c r="F41" t="str">
         <f>Palmon!B45 &amp; "," &amp; Palmon!C45 &amp; "," &amp; Palmon!D45 &amp; "," &amp; Palmon!E45 &amp; "," &amp; Palmon!G45 &amp; "," &amp; SUBSTITUTE(Palmon!H45,",",".") &amp; "," &amp; Palmon!I45 &amp; "," &amp; SUBSTITUTE(Palmon!P45,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q45,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R45,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S45,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T45,",",".") &amp; "," &amp; Palmon!J45 &amp; "," &amp; Palmon!K45 &amp; "," &amp; Palmon!L45 &amp; "," &amp; Palmon!M45 &amp; "," &amp; Palmon!N45 &amp; "," &amp; SUBSTITUTE(Palmon!U45,",",".") &amp; "," &amp; Palmon!V45 &amp; "," &amp; Palmon!X45 &amp; "," &amp; Palmon!Y45 &amp; "," &amp; Palmon!AA45 &amp; "," &amp; Palmon!AB45 &amp; "," &amp; Palmon!AC45 &amp; "," &amp; Palmon!AE45 &amp; "," &amp; Palmon!AF45 &amp; "," &amp; Palmon!AI45 &amp; "," &amp; Palmon!AJ45</f>
-        <v>Leafgarde,Wood,Attack,,0,,,0,0,0,0,0,,,,,,0,975,5044093700,,0,44,,, ,,</v>
+        <v>Leafgarde,Wood,Attack,,0,,,0,0,0,0,0,,,,,,0,975,6424613700,,0,44,,, ,,</v>
       </c>
     </row>
     <row r="42" spans="3:6" x14ac:dyDescent="0.25">
@@ -12348,7 +12348,7 @@
       </c>
       <c r="F42" t="str">
         <f>Palmon!B46 &amp; "," &amp; Palmon!C46 &amp; "," &amp; Palmon!D46 &amp; "," &amp; Palmon!E46 &amp; "," &amp; Palmon!G46 &amp; "," &amp; SUBSTITUTE(Palmon!H46,",",".") &amp; "," &amp; Palmon!I46 &amp; "," &amp; SUBSTITUTE(Palmon!P46,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q46,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R46,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S46,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T46,",",".") &amp; "," &amp; Palmon!J46 &amp; "," &amp; Palmon!K46 &amp; "," &amp; Palmon!L46 &amp; "," &amp; Palmon!M46 &amp; "," &amp; Palmon!N46 &amp; "," &amp; SUBSTITUTE(Palmon!U46,",",".") &amp; "," &amp; Palmon!V46 &amp; "," &amp; Palmon!X46 &amp; "," &amp; Palmon!Y46 &amp; "," &amp; Palmon!AA46 &amp; "," &amp; Palmon!AB46 &amp; "," &amp; Palmon!AC46 &amp; "," &amp; Palmon!AE46 &amp; "," &amp; Palmon!AF46 &amp; "," &amp; Palmon!AI46 &amp; "," &amp; Palmon!AJ46</f>
-        <v>Inferdrake,Fire,Attack,,0,,,0,0,0,0,0,,,,,,0,975,5044093700,,0,45,,, ,,</v>
+        <v>Inferdrake,Fire,Attack,,0,,,0,0,0,0,0,,,,,,0,975,6424613700,,0,45,,, ,,</v>
       </c>
     </row>
     <row r="43" spans="3:6" x14ac:dyDescent="0.25">
@@ -12366,7 +12366,7 @@
       </c>
       <c r="F43" t="str">
         <f>Palmon!B47 &amp; "," &amp; Palmon!C47 &amp; "," &amp; Palmon!D47 &amp; "," &amp; Palmon!E47 &amp; "," &amp; Palmon!G47 &amp; "," &amp; SUBSTITUTE(Palmon!H47,",",".") &amp; "," &amp; Palmon!I47 &amp; "," &amp; SUBSTITUTE(Palmon!P47,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!Q47,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!R47,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!S47,",",".") &amp; "," &amp; SUBSTITUTE(Palmon!T47,",",".") &amp; "," &amp; Palmon!J47 &amp; "," &amp; Palmon!K47 &amp; "," &amp; Palmon!L47 &amp; "," &amp; Palmon!M47 &amp; "," &amp; Palmon!N47 &amp; "," &amp; SUBSTITUTE(Palmon!U47,",",".") &amp; "," &amp; Palmon!V47 &amp; "," &amp; Palmon!X47 &amp; "," &amp; Palmon!Y47 &amp; "," &amp; Palmon!AA47 &amp; "," &amp; Palmon!AB47 &amp; "," &amp; Palmon!AC47 &amp; "," &amp; Palmon!AE47 &amp; "," &amp; Palmon!AF47 &amp; "," &amp; Palmon!AI47 &amp; "," &amp; Palmon!AJ47</f>
-        <v>Revontulet,Fire,Attack,160,2,2.3,0,1,1,0.6,0,0,1,1,1,,,0.138461538461538,840,4919220000,1,2460,22,,, ,Vulpyrean,</v>
+        <v>Revontulet,Fire,Attack,160,2,2.3,0,1,1,0.6,0,0,1,1,1,,,0.138461538461538,840,6299740000,1,2460,27,,, ,Vulpyrean,</v>
       </c>
     </row>
     <row r="44" spans="3:6" x14ac:dyDescent="0.25">
@@ -14666,7 +14666,7 @@
       </c>
       <c r="D273" t="str">
         <f>Tableaux!A273 &amp; "," &amp; Tableaux!B273 &amp; "," &amp; Tableaux!C273</f>
-        <v>270,271,135120000</v>
+        <v>270,271,123200000</v>
       </c>
     </row>
     <row r="274" spans="3:4" x14ac:dyDescent="0.25">
@@ -14676,7 +14676,7 @@
       </c>
       <c r="D274" t="str">
         <f>Tableaux!A274 &amp; "," &amp; Tableaux!B274 &amp; "," &amp; Tableaux!C274</f>
-        <v>271,272,135120000</v>
+        <v>271,272,125700000</v>
       </c>
     </row>
     <row r="275" spans="3:4" x14ac:dyDescent="0.25">
@@ -14686,7 +14686,7 @@
       </c>
       <c r="D275" t="str">
         <f>Tableaux!A275 &amp; "," &amp; Tableaux!B275 &amp; "," &amp; Tableaux!C275</f>
-        <v>272,273,135120000</v>
+        <v>272,273,128300000</v>
       </c>
     </row>
     <row r="276" spans="3:4" x14ac:dyDescent="0.25">
@@ -14696,7 +14696,7 @@
       </c>
       <c r="D276" t="str">
         <f>Tableaux!A276 &amp; "," &amp; Tableaux!B276 &amp; "," &amp; Tableaux!C276</f>
-        <v>273,274,135120000</v>
+        <v>273,274,130900000</v>
       </c>
     </row>
     <row r="277" spans="3:4" x14ac:dyDescent="0.25">
@@ -14706,7 +14706,7 @@
       </c>
       <c r="D277" t="str">
         <f>Tableaux!A277 &amp; "," &amp; Tableaux!B277 &amp; "," &amp; Tableaux!C277</f>
-        <v>274,275,135120000</v>
+        <v>274,275,133600000</v>
       </c>
     </row>
     <row r="278" spans="3:4" x14ac:dyDescent="0.25">
@@ -14716,7 +14716,7 @@
       </c>
       <c r="D278" t="str">
         <f>Tableaux!A278 &amp; "," &amp; Tableaux!B278 &amp; "," &amp; Tableaux!C278</f>
-        <v>275,276,135120000</v>
+        <v>275,276,136300000</v>
       </c>
     </row>
     <row r="279" spans="3:4" x14ac:dyDescent="0.25">
@@ -14726,7 +14726,7 @@
       </c>
       <c r="D279" t="str">
         <f>Tableaux!A279 &amp; "," &amp; Tableaux!B279 &amp; "," &amp; Tableaux!C279</f>
-        <v>276,277,135120000</v>
+        <v>276,277,139100000</v>
       </c>
     </row>
     <row r="280" spans="3:4" x14ac:dyDescent="0.25">
@@ -14736,7 +14736,7 @@
       </c>
       <c r="D280" t="str">
         <f>Tableaux!A280 &amp; "," &amp; Tableaux!B280 &amp; "," &amp; Tableaux!C280</f>
-        <v>277,278,135120000</v>
+        <v>277,278,141800000</v>
       </c>
     </row>
     <row r="281" spans="3:4" x14ac:dyDescent="0.25">
@@ -14746,7 +14746,7 @@
       </c>
       <c r="D281" t="str">
         <f>Tableaux!A281 &amp; "," &amp; Tableaux!B281 &amp; "," &amp; Tableaux!C281</f>
-        <v>278,279,135120000</v>
+        <v>278,279,144700000</v>
       </c>
     </row>
     <row r="282" spans="3:4" x14ac:dyDescent="0.25">
@@ -14756,7 +14756,7 @@
       </c>
       <c r="D282" t="str">
         <f>Tableaux!A282 &amp; "," &amp; Tableaux!B282 &amp; "," &amp; Tableaux!C282</f>
-        <v>279,280,135120000</v>
+        <v>279,280,147600000</v>
       </c>
     </row>
     <row r="283" spans="3:4" x14ac:dyDescent="0.25">
@@ -14983,7 +14983,7 @@
     <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="str" cm="1">
         <f t="array" ref="A3">_xlfn.CONCAT(_xlfn.LAMBDA(_xlpm.cell,_xlpm.cell &amp; ",")(Palmon!B3:'Palmon'!AJ3))</f>
-        <v>Bufonobi,Water,Attack,270,,5,5,0,30,20,30,Max,10,,1,1,1,1,1,1,0,,135120000,,,5270,1,1,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRXczs_Bjhslhr7Mf2HENU6MTyGpz0RJEMjNA&amp;s, , ,,,Shadowkaeru,</v>
+        <v>Bufonobi,Water,Attack,270,1,5,5,0,30,30,30,Max,10,,1,1,1,1,1,1,0,,1515640000,1,,5270,2,1,,https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRXczs_Bjhslhr7Mf2HENU6MTyGpz0RJEMjNA&amp;s, , ,,,Shadowkaeru,</v>
       </c>
     </row>
     <row r="4" spans="1:35" x14ac:dyDescent="0.25">
@@ -15283,9 +15283,9 @@
         <f>Palmon!E3</f>
         <v>270</v>
       </c>
-      <c r="E2" t="str">
+      <c r="E2">
         <f>Palmon!F3</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F2">
         <f>Palmon!G3</f>
@@ -15305,7 +15305,7 @@
       </c>
       <c r="J2">
         <f>Palmon!K3</f>
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K2">
         <f>Palmon!L3</f>
@@ -15357,11 +15357,11 @@
       </c>
       <c r="W2">
         <f>Palmon!X3</f>
-        <v>135120000</v>
-      </c>
-      <c r="X2" t="str">
+        <v>1515640000</v>
+      </c>
+      <c r="X2">
         <f>Palmon!Y3</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="Y2">
         <f>Palmon!Z3</f>
@@ -15373,7 +15373,7 @@
       </c>
       <c r="AA2">
         <f>Palmon!AB3</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB2">
         <f>Palmon!AC3</f>
@@ -15429,9 +15429,9 @@
         <f>Palmon!E4</f>
         <v>270</v>
       </c>
-      <c r="E3" t="str">
+      <c r="E3">
         <f>Palmon!F4</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F3">
         <f>Palmon!G4</f>
@@ -15503,11 +15503,11 @@
       </c>
       <c r="W3">
         <f>Palmon!X4</f>
-        <v>135120000</v>
-      </c>
-      <c r="X3" t="str">
+        <v>1515640000</v>
+      </c>
+      <c r="X3">
         <f>Palmon!Y4</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="Y3">
         <f>Palmon!Z4</f>
@@ -15519,7 +15519,7 @@
       </c>
       <c r="AA3">
         <f>Palmon!AB4</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB3">
         <f>Palmon!AC4</f>
@@ -15575,9 +15575,9 @@
         <f>Palmon!E5</f>
         <v>270</v>
       </c>
-      <c r="E4" t="str">
+      <c r="E4">
         <f>Palmon!F5</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F4">
         <f>Palmon!G5</f>
@@ -15649,11 +15649,11 @@
       </c>
       <c r="W4">
         <f>Palmon!X5</f>
-        <v>135120000</v>
-      </c>
-      <c r="X4" t="str">
+        <v>1515640000</v>
+      </c>
+      <c r="X4">
         <f>Palmon!Y5</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="Y4">
         <f>Palmon!Z5</f>
@@ -15665,7 +15665,7 @@
       </c>
       <c r="AA4">
         <f>Palmon!AB5</f>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AB4">
         <f>Palmon!AC5</f>
@@ -15795,7 +15795,7 @@
       </c>
       <c r="W5">
         <f>Palmon!X6</f>
-        <v>2123020000</v>
+        <v>3503540000</v>
       </c>
       <c r="X5">
         <f>Palmon!Y6</f>
@@ -15811,7 +15811,7 @@
       </c>
       <c r="AA5">
         <f>Palmon!AB6</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB5">
         <f>Palmon!AC6</f>
@@ -15867,9 +15867,9 @@
         <f>Palmon!E7</f>
         <v>270</v>
       </c>
-      <c r="E6" t="str">
+      <c r="E6">
         <f>Palmon!F7</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F6">
         <f>Palmon!G7</f>
@@ -15941,11 +15941,11 @@
       </c>
       <c r="W6">
         <f>Palmon!X7</f>
-        <v>135120000</v>
-      </c>
-      <c r="X6" t="str">
+        <v>1515640000</v>
+      </c>
+      <c r="X6">
         <f>Palmon!Y7</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="Y6">
         <f>Palmon!Z7</f>
@@ -15957,7 +15957,7 @@
       </c>
       <c r="AA6">
         <f>Palmon!AB7</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB6">
         <f>Palmon!AC7</f>
@@ -16087,7 +16087,7 @@
       </c>
       <c r="W7">
         <f>Palmon!X8</f>
-        <v>5044093700</v>
+        <v>6424613700</v>
       </c>
       <c r="X7">
         <f>Palmon!Y8</f>
@@ -16233,7 +16233,7 @@
       </c>
       <c r="W8">
         <f>Palmon!X9</f>
-        <v>2831420000</v>
+        <v>4211940000</v>
       </c>
       <c r="X8">
         <f>Palmon!Y9</f>
@@ -16249,7 +16249,7 @@
       </c>
       <c r="AA8">
         <f>Palmon!AB9</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB8">
         <f>Palmon!AC9</f>
@@ -16379,7 +16379,7 @@
       </c>
       <c r="W9">
         <f>Palmon!X10</f>
-        <v>3390620000</v>
+        <v>4771140000</v>
       </c>
       <c r="X9">
         <f>Palmon!Y10</f>
@@ -16395,7 +16395,7 @@
       </c>
       <c r="AA9">
         <f>Palmon!AB10</f>
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AB9" t="str">
         <f>Palmon!AC10</f>
@@ -16525,7 +16525,7 @@
       </c>
       <c r="W10">
         <f>Palmon!X11</f>
-        <v>2123020000</v>
+        <v>3503540000</v>
       </c>
       <c r="X10">
         <f>Palmon!Y11</f>
@@ -16541,7 +16541,7 @@
       </c>
       <c r="AA10">
         <f>Palmon!AB11</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AB10">
         <f>Palmon!AC11</f>
@@ -16595,7 +16595,7 @@
       </c>
       <c r="D11">
         <f>Palmon!E12</f>
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="E11">
         <f>Palmon!F12</f>
@@ -16607,7 +16607,7 @@
       </c>
       <c r="G11">
         <f>Palmon!H12</f>
-        <v>4</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="H11">
         <f>Palmon!I12</f>
@@ -16655,15 +16655,15 @@
       </c>
       <c r="S11">
         <f>Palmon!T12</f>
-        <v>0</v>
+        <v>0.19999999999999929</v>
       </c>
       <c r="T11">
         <f>Palmon!U12</f>
-        <v>0.48717948717948717</v>
+        <v>0.58974358974358942</v>
       </c>
       <c r="U11">
         <f>Palmon!V12</f>
-        <v>486</v>
+        <v>386.00000000000034</v>
       </c>
       <c r="V11">
         <f>Palmon!W12</f>
@@ -16671,7 +16671,7 @@
       </c>
       <c r="W11">
         <f>Palmon!X12</f>
-        <v>3390620000</v>
+        <v>3503540000</v>
       </c>
       <c r="X11">
         <f>Palmon!Y12</f>
@@ -16683,11 +16683,11 @@
       </c>
       <c r="Z11">
         <f>Palmon!AA12</f>
-        <v>4230</v>
+        <v>4350</v>
       </c>
       <c r="AA11">
         <f>Palmon!AB12</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AB11">
         <f>Palmon!AC12</f>
@@ -16741,7 +16741,7 @@
       </c>
       <c r="D12">
         <f>Palmon!E13</f>
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="E12">
         <f>Palmon!F13</f>
@@ -16753,7 +16753,7 @@
       </c>
       <c r="G12">
         <f>Palmon!H13</f>
-        <v>2.2999999999999998</v>
+        <v>2.4</v>
       </c>
       <c r="H12">
         <f>Palmon!I13</f>
@@ -16793,7 +16793,7 @@
       </c>
       <c r="Q12">
         <f>Palmon!R13</f>
-        <v>0.59999999999999964</v>
+        <v>0.79999999999999982</v>
       </c>
       <c r="R12">
         <f>Palmon!S13</f>
@@ -16805,11 +16805,11 @@
       </c>
       <c r="T12">
         <f>Palmon!U13</f>
-        <v>0.13846153846153844</v>
+        <v>0.15897435897435896</v>
       </c>
       <c r="U12">
         <f>Palmon!V13</f>
-        <v>832</v>
+        <v>812</v>
       </c>
       <c r="V12">
         <f>Palmon!W13</f>
@@ -16817,7 +16817,7 @@
       </c>
       <c r="W12">
         <f>Palmon!X13</f>
-        <v>3390620000</v>
+        <v>4211940000</v>
       </c>
       <c r="X12">
         <f>Palmon!Y13</f>
@@ -16829,15 +16829,15 @@
       </c>
       <c r="Z12">
         <f>Palmon!AA13</f>
-        <v>2530</v>
+        <v>2640</v>
       </c>
       <c r="AA12">
         <f>Palmon!AB13</f>
-        <v>20</v>
-      </c>
-      <c r="AB12">
+        <v>22</v>
+      </c>
+      <c r="AB12" t="str">
         <f>Palmon!AC13</f>
-        <v>3</v>
+        <v/>
       </c>
       <c r="AC12">
         <f>Palmon!AD13</f>
@@ -16889,9 +16889,9 @@
         <f>Palmon!E14</f>
         <v>270</v>
       </c>
-      <c r="E13" t="str">
+      <c r="E13">
         <f>Palmon!F14</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F13">
         <f>Palmon!G14</f>
@@ -16963,11 +16963,11 @@
       </c>
       <c r="W13">
         <f>Palmon!X14</f>
-        <v>135120000</v>
-      </c>
-      <c r="X13" t="str">
+        <v>1515640000</v>
+      </c>
+      <c r="X13">
         <f>Palmon!Y14</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="Y13">
         <f>Palmon!Z14</f>
@@ -16979,7 +16979,7 @@
       </c>
       <c r="AA13">
         <f>Palmon!AB14</f>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AB13">
         <f>Palmon!AC14</f>
@@ -17033,7 +17033,7 @@
       </c>
       <c r="D14">
         <f>Palmon!E15</f>
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="E14">
         <f>Palmon!F15</f>
@@ -17109,7 +17109,7 @@
       </c>
       <c r="W14">
         <f>Palmon!X15</f>
-        <v>1235520000</v>
+        <v>1515640000</v>
       </c>
       <c r="X14">
         <f>Palmon!Y15</f>
@@ -17121,7 +17121,7 @@
       </c>
       <c r="Z14">
         <f>Palmon!AA15</f>
-        <v>5260</v>
+        <v>5270</v>
       </c>
       <c r="AA14">
         <f>Palmon!AB15</f>
@@ -17179,7 +17179,7 @@
       </c>
       <c r="D15">
         <f>Palmon!E16</f>
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="E15">
         <f>Palmon!F16</f>
@@ -17187,11 +17187,11 @@
       </c>
       <c r="F15">
         <f>Palmon!G16</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15">
         <f>Palmon!H16</f>
-        <v>2.2000000000000002</v>
+        <v>3</v>
       </c>
       <c r="H15">
         <f>Palmon!I16</f>
@@ -17231,7 +17231,7 @@
       </c>
       <c r="Q15">
         <f>Palmon!R16</f>
-        <v>0.40000000000000036</v>
+        <v>1</v>
       </c>
       <c r="R15">
         <f>Palmon!S16</f>
@@ -17243,11 +17243,11 @@
       </c>
       <c r="T15">
         <f>Palmon!U16</f>
-        <v>0.11794871794871797</v>
+        <v>0.17948717948717949</v>
       </c>
       <c r="U15">
         <f>Palmon!V16</f>
-        <v>850</v>
+        <v>790</v>
       </c>
       <c r="V15">
         <f>Palmon!W16</f>
@@ -17255,7 +17255,7 @@
       </c>
       <c r="W15">
         <f>Palmon!X16</f>
-        <v>2831420000</v>
+        <v>3503540000</v>
       </c>
       <c r="X15">
         <f>Palmon!Y16</f>
@@ -17267,15 +17267,15 @@
       </c>
       <c r="Z15">
         <f>Palmon!AA16</f>
-        <v>2440</v>
+        <v>3250</v>
       </c>
       <c r="AA15">
         <f>Palmon!AB16</f>
-        <v>23</v>
-      </c>
-      <c r="AB15" t="str">
+        <v>19</v>
+      </c>
+      <c r="AB15">
         <f>Palmon!AC16</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AC15">
         <f>Palmon!AD16</f>
@@ -17325,7 +17325,7 @@
       </c>
       <c r="D16">
         <f>Palmon!E17</f>
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="E16">
         <f>Palmon!F17</f>
@@ -17333,11 +17333,11 @@
       </c>
       <c r="F16">
         <f>Palmon!G17</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G16">
         <f>Palmon!H17</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H16">
         <f>Palmon!I17</f>
@@ -17357,7 +17357,7 @@
       </c>
       <c r="L16" t="str">
         <f>Palmon!M17</f>
-        <v/>
+        <v>Max</v>
       </c>
       <c r="M16" t="str">
         <f>Palmon!N17</f>
@@ -17381,7 +17381,7 @@
       </c>
       <c r="R16">
         <f>Palmon!S17</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16">
         <f>Palmon!T17</f>
@@ -17389,11 +17389,11 @@
       </c>
       <c r="T16">
         <f>Palmon!U17</f>
-        <v>0.17948717948717949</v>
+        <v>0.48717948717948717</v>
       </c>
       <c r="U16">
         <f>Palmon!V17</f>
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="V16">
         <f>Palmon!W17</f>
@@ -17401,7 +17401,7 @@
       </c>
       <c r="W16">
         <f>Palmon!X17</f>
-        <v>4161420000</v>
+        <v>3503540000</v>
       </c>
       <c r="X16">
         <f>Palmon!Y17</f>
@@ -17413,11 +17413,11 @@
       </c>
       <c r="Z16">
         <f>Palmon!AA17</f>
-        <v>3210</v>
+        <v>4250</v>
       </c>
       <c r="AA16">
         <f>Palmon!AB17</f>
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AB16">
         <f>Palmon!AC17</f>
@@ -17471,7 +17471,7 @@
       </c>
       <c r="D17">
         <f>Palmon!E18</f>
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="E17">
         <f>Palmon!F18</f>
@@ -17479,11 +17479,11 @@
       </c>
       <c r="F17">
         <f>Palmon!G18</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G17">
         <f>Palmon!H18</f>
-        <v>2.2000000000000002</v>
+        <v>3.1</v>
       </c>
       <c r="H17">
         <f>Palmon!I18</f>
@@ -17523,11 +17523,11 @@
       </c>
       <c r="Q17">
         <f>Palmon!R18</f>
-        <v>0.40000000000000036</v>
+        <v>1</v>
       </c>
       <c r="R17">
         <f>Palmon!S18</f>
-        <v>0</v>
+        <v>0.20000000000000018</v>
       </c>
       <c r="S17">
         <f>Palmon!T18</f>
@@ -17535,11 +17535,11 @@
       </c>
       <c r="T17">
         <f>Palmon!U18</f>
-        <v>0.11794871794871797</v>
+        <v>0.24102564102564109</v>
       </c>
       <c r="U17">
         <f>Palmon!V18</f>
-        <v>860</v>
+        <v>740</v>
       </c>
       <c r="V17">
         <f>Palmon!W18</f>
@@ -17547,7 +17547,7 @@
       </c>
       <c r="W17">
         <f>Palmon!X18</f>
-        <v>4161420000</v>
+        <v>4771140000</v>
       </c>
       <c r="X17">
         <f>Palmon!Y18</f>
@@ -17559,15 +17559,15 @@
       </c>
       <c r="Z17">
         <f>Palmon!AA18</f>
-        <v>2410</v>
+        <v>3330</v>
       </c>
       <c r="AA17">
         <f>Palmon!AB18</f>
-        <v>25</v>
-      </c>
-      <c r="AB17" t="str">
+        <v>17</v>
+      </c>
+      <c r="AB17">
         <f>Palmon!AC18</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AC17">
         <f>Palmon!AD18</f>
@@ -17693,7 +17693,7 @@
       </c>
       <c r="W18">
         <f>Palmon!X19</f>
-        <v>2123020000</v>
+        <v>3503540000</v>
       </c>
       <c r="X18">
         <f>Palmon!Y19</f>
@@ -17709,7 +17709,7 @@
       </c>
       <c r="AA18">
         <f>Palmon!AB19</f>
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AB18">
         <f>Palmon!AC19</f>
@@ -17765,9 +17765,9 @@
         <f>Palmon!E20</f>
         <v>270</v>
       </c>
-      <c r="E19" t="str">
+      <c r="E19">
         <f>Palmon!F20</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F19">
         <f>Palmon!G20</f>
@@ -17839,11 +17839,11 @@
       </c>
       <c r="W19">
         <f>Palmon!X20</f>
-        <v>135120000</v>
-      </c>
-      <c r="X19" t="str">
+        <v>1515640000</v>
+      </c>
+      <c r="X19">
         <f>Palmon!Y20</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="Y19">
         <f>Palmon!Z20</f>
@@ -17855,7 +17855,7 @@
       </c>
       <c r="AA19">
         <f>Palmon!AB20</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB19">
         <f>Palmon!AC20</f>
@@ -17985,7 +17985,7 @@
       </c>
       <c r="W20">
         <f>Palmon!X21</f>
-        <v>4415720000</v>
+        <v>5796240000</v>
       </c>
       <c r="X20">
         <f>Palmon!Y21</f>
@@ -18001,7 +18001,7 @@
       </c>
       <c r="AA20">
         <f>Palmon!AB21</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AB20" t="str">
         <f>Palmon!AC21</f>
@@ -18067,7 +18067,7 @@
       </c>
       <c r="G21">
         <f>Palmon!H22</f>
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="H21">
         <f>Palmon!I22</f>
@@ -18107,7 +18107,7 @@
       </c>
       <c r="Q21">
         <f>Palmon!R22</f>
-        <v>0.40000000000000036</v>
+        <v>0.79999999999999982</v>
       </c>
       <c r="R21">
         <f>Palmon!S22</f>
@@ -18119,11 +18119,11 @@
       </c>
       <c r="T21">
         <f>Palmon!U22</f>
-        <v>0.11794871794871797</v>
+        <v>0.15897435897435896</v>
       </c>
       <c r="U21">
         <f>Palmon!V22</f>
-        <v>859</v>
+        <v>819</v>
       </c>
       <c r="V21">
         <f>Palmon!W22</f>
@@ -18131,7 +18131,7 @@
       </c>
       <c r="W21">
         <f>Palmon!X22</f>
-        <v>4161420000</v>
+        <v>5541940000</v>
       </c>
       <c r="X21">
         <f>Palmon!Y22</f>
@@ -18143,11 +18143,11 @@
       </c>
       <c r="Z21">
         <f>Palmon!AA22</f>
-        <v>2410</v>
+        <v>2610</v>
       </c>
       <c r="AA21">
         <f>Palmon!AB22</f>
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AB21" t="str">
         <f>Palmon!AC22</f>
@@ -18277,7 +18277,7 @@
       </c>
       <c r="W22">
         <f>Palmon!X23</f>
-        <v>4919220000</v>
+        <v>6299740000</v>
       </c>
       <c r="X22">
         <f>Palmon!Y23</f>
@@ -18293,7 +18293,7 @@
       </c>
       <c r="AA22">
         <f>Palmon!AB23</f>
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AB22" t="str">
         <f>Palmon!AC23</f>
@@ -18347,7 +18347,7 @@
       </c>
       <c r="D23">
         <f>Palmon!E24</f>
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="E23">
         <f>Palmon!F24</f>
@@ -18423,7 +18423,7 @@
       </c>
       <c r="W23">
         <f>Palmon!X24</f>
-        <v>3826220000</v>
+        <v>4771140000</v>
       </c>
       <c r="X23">
         <f>Palmon!Y24</f>
@@ -18435,11 +18435,11 @@
       </c>
       <c r="Z23">
         <f>Palmon!AA24</f>
-        <v>2220</v>
+        <v>2230</v>
       </c>
       <c r="AA23">
         <f>Palmon!AB24</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AB23" t="str">
         <f>Palmon!AC24</f>
@@ -18505,7 +18505,7 @@
       </c>
       <c r="G24">
         <f>Palmon!H25</f>
-        <v>2</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="H24">
         <f>Palmon!I25</f>
@@ -18545,7 +18545,7 @@
       </c>
       <c r="Q24">
         <f>Palmon!R25</f>
-        <v>0</v>
+        <v>0.59999999999999964</v>
       </c>
       <c r="R24">
         <f>Palmon!S25</f>
@@ -18557,11 +18557,11 @@
       </c>
       <c r="T24">
         <f>Palmon!U25</f>
-        <v>7.6923076923076927E-2</v>
+        <v>0.13846153846153844</v>
       </c>
       <c r="U24">
         <f>Palmon!V25</f>
-        <v>900</v>
+        <v>840</v>
       </c>
       <c r="V24">
         <f>Palmon!W25</f>
@@ -18569,7 +18569,7 @@
       </c>
       <c r="W24">
         <f>Palmon!X25</f>
-        <v>4415720000</v>
+        <v>5796240000</v>
       </c>
       <c r="X24">
         <f>Palmon!Y25</f>
@@ -18581,11 +18581,11 @@
       </c>
       <c r="Z24">
         <f>Palmon!AA25</f>
-        <v>2200</v>
+        <v>2500</v>
       </c>
       <c r="AA24">
         <f>Palmon!AB25</f>
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="AB24" t="str">
         <f>Palmon!AC25</f>
@@ -18651,7 +18651,7 @@
       </c>
       <c r="G25">
         <f>Palmon!H26</f>
-        <v>2.1</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="H25">
         <f>Palmon!I26</f>
@@ -18691,7 +18691,7 @@
       </c>
       <c r="Q25">
         <f>Palmon!R26</f>
-        <v>0.20000000000000018</v>
+        <v>0.40000000000000036</v>
       </c>
       <c r="R25">
         <f>Palmon!S26</f>
@@ -18703,11 +18703,11 @@
       </c>
       <c r="T25">
         <f>Palmon!U26</f>
-        <v>9.7435897435897451E-2</v>
+        <v>0.11794871794871797</v>
       </c>
       <c r="U25">
         <f>Palmon!V26</f>
-        <v>869</v>
+        <v>849</v>
       </c>
       <c r="V25">
         <f>Palmon!W26</f>
@@ -18715,7 +18715,7 @@
       </c>
       <c r="W25">
         <f>Palmon!X26</f>
-        <v>4415720000</v>
+        <v>5796240000</v>
       </c>
       <c r="X25">
         <f>Palmon!Y26</f>
@@ -18727,11 +18727,11 @@
       </c>
       <c r="Z25">
         <f>Palmon!AA26</f>
-        <v>2300</v>
+        <v>2400</v>
       </c>
       <c r="AA25">
         <f>Palmon!AB26</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AB25" t="str">
         <f>Palmon!AC26</f>
@@ -18785,7 +18785,7 @@
       </c>
       <c r="D26">
         <f>Palmon!E27</f>
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="E26">
         <f>Palmon!F27</f>
@@ -18861,7 +18861,7 @@
       </c>
       <c r="W26">
         <f>Palmon!X27</f>
-        <v>4161420000</v>
+        <v>4771140000</v>
       </c>
       <c r="X26">
         <f>Palmon!Y27</f>
@@ -18873,15 +18873,15 @@
       </c>
       <c r="Z26">
         <f>Palmon!AA27</f>
-        <v>2610</v>
+        <v>2630</v>
       </c>
       <c r="AA26">
         <f>Palmon!AB27</f>
-        <v>19</v>
-      </c>
-      <c r="AB26">
+        <v>23</v>
+      </c>
+      <c r="AB26" t="str">
         <f>Palmon!AC27</f>
-        <v>3</v>
+        <v/>
       </c>
       <c r="AC26">
         <f>Palmon!AD27</f>
@@ -19007,7 +19007,7 @@
       </c>
       <c r="W27">
         <f>Palmon!X28</f>
-        <v>1235520000</v>
+        <v>2616040000</v>
       </c>
       <c r="X27">
         <f>Palmon!Y28</f>
@@ -19023,7 +19023,7 @@
       </c>
       <c r="AA27">
         <f>Palmon!AB28</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB27">
         <f>Palmon!AC28</f>
@@ -19077,7 +19077,7 @@
       </c>
       <c r="D28">
         <f>Palmon!E29</f>
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="E28">
         <f>Palmon!F29</f>
@@ -19085,11 +19085,11 @@
       </c>
       <c r="F28">
         <f>Palmon!G29</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G28">
         <f>Palmon!H29</f>
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="H28">
         <f>Palmon!I29</f>
@@ -19105,15 +19105,15 @@
       </c>
       <c r="K28">
         <f>Palmon!L29</f>
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="L28" t="str">
         <f>Palmon!M29</f>
-        <v/>
-      </c>
-      <c r="M28" t="str">
+        <v>Max</v>
+      </c>
+      <c r="M28">
         <f>Palmon!N29</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="N28">
         <f>Palmon!O29</f>
@@ -19133,19 +19133,19 @@
       </c>
       <c r="R28">
         <f>Palmon!S29</f>
-        <v>0.40000000000000036</v>
+        <v>1</v>
       </c>
       <c r="S28">
         <f>Palmon!T29</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T28">
         <f>Palmon!U29</f>
-        <v>0.30256410256410265</v>
+        <v>1</v>
       </c>
       <c r="U28">
         <f>Palmon!V29</f>
-        <v>669.99999999999989</v>
+        <v>-10</v>
       </c>
       <c r="V28">
         <f>Palmon!W29</f>
@@ -19153,7 +19153,7 @@
       </c>
       <c r="W28">
         <f>Palmon!X29</f>
-        <v>4161420000</v>
+        <v>4771140000</v>
       </c>
       <c r="X28">
         <f>Palmon!Y29</f>
@@ -19165,11 +19165,11 @@
       </c>
       <c r="Z28">
         <f>Palmon!AA29</f>
-        <v>3410</v>
+        <v>5230</v>
       </c>
       <c r="AA28">
         <f>Palmon!AB29</f>
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AB28">
         <f>Palmon!AC29</f>
@@ -19223,7 +19223,7 @@
       </c>
       <c r="D29">
         <f>Palmon!E30</f>
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="E29">
         <f>Palmon!F30</f>
@@ -19235,7 +19235,7 @@
       </c>
       <c r="G29">
         <f>Palmon!H30</f>
-        <v>4</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="H29">
         <f>Palmon!I30</f>
@@ -19283,15 +19283,15 @@
       </c>
       <c r="S29">
         <f>Palmon!T30</f>
-        <v>0</v>
+        <v>0.19999999999999929</v>
       </c>
       <c r="T29">
         <f>Palmon!U30</f>
-        <v>0.48717948717948717</v>
+        <v>0.58974358974358942</v>
       </c>
       <c r="U29">
         <f>Palmon!V30</f>
-        <v>470</v>
+        <v>370.00000000000034</v>
       </c>
       <c r="V29">
         <f>Palmon!W30</f>
@@ -19299,7 +19299,7 @@
       </c>
       <c r="W29">
         <f>Palmon!X30</f>
-        <v>4605720000</v>
+        <v>5796240000</v>
       </c>
       <c r="X29">
         <f>Palmon!Y30</f>
@@ -19311,11 +19311,11 @@
       </c>
       <c r="Z29">
         <f>Palmon!AA30</f>
-        <v>4190</v>
+        <v>4300</v>
       </c>
       <c r="AA29">
         <f>Palmon!AB30</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AB29">
         <f>Palmon!AC30</f>
@@ -19369,7 +19369,7 @@
       </c>
       <c r="D30">
         <f>Palmon!E31</f>
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="E30">
         <f>Palmon!F31</f>
@@ -19377,11 +19377,11 @@
       </c>
       <c r="F30">
         <f>Palmon!G31</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G30">
         <f>Palmon!H31</f>
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="H30">
         <f>Palmon!I31</f>
@@ -19421,7 +19421,7 @@
       </c>
       <c r="Q30">
         <f>Palmon!R31</f>
-        <v>0.20000000000000018</v>
+        <v>1</v>
       </c>
       <c r="R30">
         <f>Palmon!S31</f>
@@ -19433,11 +19433,11 @@
       </c>
       <c r="T30">
         <f>Palmon!U31</f>
-        <v>9.7435897435897451E-2</v>
+        <v>0.17948717948717949</v>
       </c>
       <c r="U30">
         <f>Palmon!V31</f>
-        <v>870</v>
+        <v>790</v>
       </c>
       <c r="V30">
         <f>Palmon!W31</f>
@@ -19445,7 +19445,7 @@
       </c>
       <c r="W30">
         <f>Palmon!X31</f>
-        <v>4161420000</v>
+        <v>4211940000</v>
       </c>
       <c r="X30">
         <f>Palmon!Y31</f>
@@ -19457,11 +19457,11 @@
       </c>
       <c r="Z30">
         <f>Palmon!AA31</f>
-        <v>2310</v>
+        <v>3240</v>
       </c>
       <c r="AA30">
         <f>Palmon!AB31</f>
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AB30" t="str">
         <f>Palmon!AC31</f>
@@ -19591,7 +19591,7 @@
       </c>
       <c r="W31">
         <f>Palmon!X32</f>
-        <v>5044093700</v>
+        <v>6424613700</v>
       </c>
       <c r="X31" t="str">
         <f>Palmon!Y32</f>
@@ -19661,7 +19661,7 @@
       </c>
       <c r="D32">
         <f>Palmon!E33</f>
-        <v>140</v>
+        <v>270</v>
       </c>
       <c r="E32">
         <f>Palmon!F33</f>
@@ -19737,7 +19737,7 @@
       </c>
       <c r="W32">
         <f>Palmon!X33</f>
-        <v>4999220000</v>
+        <v>1515640000</v>
       </c>
       <c r="X32">
         <f>Palmon!Y33</f>
@@ -19749,11 +19749,11 @@
       </c>
       <c r="Z32">
         <f>Palmon!AA33</f>
-        <v>5140</v>
+        <v>5270</v>
       </c>
       <c r="AA32">
         <f>Palmon!AB33</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB32">
         <f>Palmon!AC33</f>
@@ -19883,7 +19883,7 @@
       </c>
       <c r="W33">
         <f>Palmon!X34</f>
-        <v>5044093700</v>
+        <v>6424613700</v>
       </c>
       <c r="X33" t="str">
         <f>Palmon!Y34</f>
@@ -19953,7 +19953,7 @@
       </c>
       <c r="D34">
         <f>Palmon!E35</f>
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="E34" t="str">
         <f>Palmon!F35</f>
@@ -20029,7 +20029,7 @@
       </c>
       <c r="W34">
         <f>Palmon!X35</f>
-        <v>135120000</v>
+        <v>164440000</v>
       </c>
       <c r="X34" t="str">
         <f>Palmon!Y35</f>
@@ -20041,11 +20041,11 @@
       </c>
       <c r="Z34">
         <f>Palmon!AA35</f>
-        <v>5270</v>
+        <v>5280</v>
       </c>
       <c r="AA34">
         <f>Palmon!AB35</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AB34">
         <f>Palmon!AC35</f>
@@ -20175,7 +20175,7 @@
       </c>
       <c r="W35">
         <f>Palmon!X36</f>
-        <v>5044093700</v>
+        <v>6424613700</v>
       </c>
       <c r="X35" t="str">
         <f>Palmon!Y36</f>
@@ -20321,7 +20321,7 @@
       </c>
       <c r="W36">
         <f>Palmon!X37</f>
-        <v>5044093700</v>
+        <v>6424613700</v>
       </c>
       <c r="X36" t="str">
         <f>Palmon!Y37</f>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="W37">
         <f>Palmon!X38</f>
-        <v>5044093700</v>
+        <v>6424613700</v>
       </c>
       <c r="X37" t="str">
         <f>Palmon!Y38</f>
@@ -20613,7 +20613,7 @@
       </c>
       <c r="W38">
         <f>Palmon!X39</f>
-        <v>5044093700</v>
+        <v>6424613700</v>
       </c>
       <c r="X38">
         <f>Palmon!Y39</f>
@@ -20759,7 +20759,7 @@
       </c>
       <c r="W39">
         <f>Palmon!X40</f>
-        <v>5044093700</v>
+        <v>6424613700</v>
       </c>
       <c r="X39" t="str">
         <f>Palmon!Y40</f>
@@ -20905,7 +20905,7 @@
       </c>
       <c r="W40">
         <f>Palmon!X41</f>
-        <v>5044093700</v>
+        <v>6424613700</v>
       </c>
       <c r="X40" t="str">
         <f>Palmon!Y41</f>
@@ -21051,7 +21051,7 @@
       </c>
       <c r="W41">
         <f>Palmon!X42</f>
-        <v>5044093700</v>
+        <v>6424613700</v>
       </c>
       <c r="X41" t="str">
         <f>Palmon!Y42</f>
@@ -21197,7 +21197,7 @@
       </c>
       <c r="W42">
         <f>Palmon!X43</f>
-        <v>5044093700</v>
+        <v>6424613700</v>
       </c>
       <c r="X42" t="str">
         <f>Palmon!Y43</f>
@@ -21343,7 +21343,7 @@
       </c>
       <c r="W43">
         <f>Palmon!X44</f>
-        <v>5044093700</v>
+        <v>6424613700</v>
       </c>
       <c r="X43" t="str">
         <f>Palmon!Y44</f>
@@ -21489,7 +21489,7 @@
       </c>
       <c r="W44">
         <f>Palmon!X45</f>
-        <v>5044093700</v>
+        <v>6424613700</v>
       </c>
       <c r="X44" t="str">
         <f>Palmon!Y45</f>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="W45">
         <f>Palmon!X46</f>
-        <v>5044093700</v>
+        <v>6424613700</v>
       </c>
       <c r="X45" t="str">
         <f>Palmon!Y46</f>
@@ -21781,7 +21781,7 @@
       </c>
       <c r="W46">
         <f>Palmon!X47</f>
-        <v>4919220000</v>
+        <v>6299740000</v>
       </c>
       <c r="X46">
         <f>Palmon!Y47</f>
@@ -21797,7 +21797,7 @@
       </c>
       <c r="AA46">
         <f>Palmon!AB47</f>
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AB46" t="str">
         <f>Palmon!AC47</f>
@@ -22050,7 +22050,7 @@
         <v/>
       </c>
       <c r="H6" s="33">
-        <v>486</v>
+        <v>386.00000000000034</v>
       </c>
       <c r="I6" s="33" t="str">
         <v/>
@@ -22094,11 +22094,11 @@
       <c r="E7" s="39" t="str">
         <v/>
       </c>
-      <c r="F7" s="33">
-        <v>69.999999999999986</v>
-      </c>
-      <c r="G7" s="33" t="str">
-        <v/>
+      <c r="F7" s="33" t="str">
+        <v/>
+      </c>
+      <c r="G7" s="33">
+        <v>290</v>
       </c>
       <c r="H7" s="33" t="str">
         <v/>
@@ -22199,11 +22199,11 @@
       <c r="F9" s="33" t="str">
         <v/>
       </c>
-      <c r="G9" s="33">
-        <v>300</v>
-      </c>
-      <c r="H9" s="33" t="str">
-        <v/>
+      <c r="G9" s="33" t="str">
+        <v/>
+      </c>
+      <c r="H9" s="33">
+        <v>500</v>
       </c>
       <c r="I9" s="33" t="str">
         <v/>
@@ -22312,7 +22312,7 @@
         <v/>
       </c>
       <c r="F12" s="33">
-        <v>58.999999999999972</v>
+        <v>19</v>
       </c>
       <c r="G12" s="33" t="str">
         <v/>
@@ -22349,7 +22349,7 @@
         <v/>
       </c>
       <c r="F13" s="33">
-        <v>32.000000000000028</v>
+        <v>12</v>
       </c>
       <c r="G13" s="33" t="str">
         <v/>
@@ -22497,11 +22497,11 @@
       <c r="E16" s="39" t="str">
         <v/>
       </c>
-      <c r="F16" s="33">
-        <v>59.999999999999972</v>
-      </c>
-      <c r="G16" s="33" t="str">
-        <v/>
+      <c r="F16" s="33" t="str">
+        <v/>
+      </c>
+      <c r="G16" s="33">
+        <v>239.99999999999994</v>
       </c>
       <c r="H16" s="33" t="str">
         <v/>
@@ -22517,23 +22517,23 @@
         <v/>
       </c>
       <c r="N16" s="33">
-        <v>59.999999999999972</v>
+        <v>55.999999999999972</v>
       </c>
       <c r="O16" s="33">
         <v>300</v>
       </c>
       <c r="P16" s="47">
-        <v>486</v>
+        <v>500</v>
       </c>
       <c r="Q16" s="40">
-        <v>486</v>
+        <v>500</v>
       </c>
       <c r="R16" s="1"/>
       <c r="U16" s="46" t="str">
         <v>Electricity</v>
       </c>
       <c r="V16" s="192">
-        <v>223.33333333333334</v>
+        <v>244.28571428571428</v>
       </c>
       <c r="W16" s="40" cm="1">
         <f t="array" ref="W16">COUNTA(_xlfn._xlws.FILTER(C3:C42,C3:C42=$U16,""))</f>
@@ -22573,7 +22573,7 @@
         <v/>
       </c>
       <c r="N17" s="33">
-        <v>32.000000000000028</v>
+        <v>12</v>
       </c>
       <c r="O17" s="33">
         <v>290</v>
@@ -22589,7 +22589,7 @@
         <v>Fire</v>
       </c>
       <c r="V17" s="192">
-        <v>248.57142857142858</v>
+        <v>252.85714285714286</v>
       </c>
       <c r="W17" s="40" cm="1">
         <f t="array" ref="W17">COUNTA(_xlfn._xlws.FILTER(C4:C43,C4:C43=$U17,""))</f>
@@ -22645,7 +22645,7 @@
         <v>Water</v>
       </c>
       <c r="V18" s="192">
-        <v>241.42857142857142</v>
+        <v>237.5</v>
       </c>
       <c r="W18" s="40" cm="1">
         <f t="array" ref="W18">COUNTA(_xlfn._xlws.FILTER(C5:C44,C5:C44=$U18,""))</f>
@@ -22687,8 +22687,8 @@
       <c r="N19" s="33">
         <v>100</v>
       </c>
-      <c r="O19" s="33" t="str">
-        <v/>
+      <c r="O19" s="33">
+        <v>290</v>
       </c>
       <c r="P19" s="47">
         <v>400.00000000000034</v>
@@ -22701,7 +22701,7 @@
         <v>Wood</v>
       </c>
       <c r="V19" s="194">
-        <v>234.28571428571428</v>
+        <v>242.85714285714286</v>
       </c>
       <c r="W19" s="195" cm="1">
         <f t="array" ref="W19">COUNTA(_xlfn._xlws.FILTER(C6:C45,C6:C45=$U19,""))</f>
@@ -22755,7 +22755,7 @@
       <c r="R20" s="1"/>
       <c r="V20" s="197">
         <f>AVERAGE(V16:V19)</f>
-        <v>236.90476190476193</v>
+        <v>244.375</v>
       </c>
       <c r="W20" s="196">
         <f>SUM(W16:W19)</f>
@@ -22816,7 +22816,7 @@
         <v/>
       </c>
       <c r="H22" s="33">
-        <v>470</v>
+        <v>370.00000000000034</v>
       </c>
       <c r="I22" s="33" t="str">
         <v/>
@@ -23014,13 +23014,13 @@
         <v/>
       </c>
       <c r="N26" s="33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O26" s="33">
         <v>2</v>
       </c>
       <c r="P26" s="33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q26" s="47" t="str">
         <v/>
@@ -23066,13 +23066,13 @@
         <v>1</v>
       </c>
       <c r="O27" s="33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P27" s="33">
         <v>2</v>
       </c>
       <c r="Q27" s="47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R27" s="40">
         <v>7</v>
@@ -23161,10 +23161,10 @@
         <v/>
       </c>
       <c r="N29" s="33">
-        <v>4</v>
-      </c>
-      <c r="O29" s="33" t="str">
-        <v/>
+        <v>2</v>
+      </c>
+      <c r="O29" s="33">
+        <v>2</v>
       </c>
       <c r="P29" s="33">
         <v>1</v>
@@ -23191,7 +23191,7 @@
         <v/>
       </c>
       <c r="F30" s="33">
-        <v>68.999999999999986</v>
+        <v>48.999999999999972</v>
       </c>
       <c r="G30" s="33" t="str">
         <v/>
@@ -23210,16 +23210,16 @@
         <v>1</v>
       </c>
       <c r="N30" s="86">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="O30" s="86">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P30" s="86">
+        <v>7</v>
+      </c>
+      <c r="Q30" s="87">
         <v>6</v>
-      </c>
-      <c r="Q30" s="87">
-        <v>5</v>
       </c>
       <c r="R30" s="88">
         <v>29</v>
@@ -23274,7 +23274,7 @@
         <v/>
       </c>
       <c r="F32" s="33">
-        <v>100</v>
+        <v>40.000000000000028</v>
       </c>
       <c r="G32" s="33" t="str">
         <v/>
@@ -23312,14 +23312,14 @@
       <c r="F33" s="33" t="str">
         <v/>
       </c>
-      <c r="G33" s="33">
-        <v>169.99999999999989</v>
+      <c r="G33" s="33" t="str">
+        <v/>
       </c>
       <c r="H33" s="33" t="str">
         <v/>
       </c>
-      <c r="I33" s="33" t="str">
-        <v/>
+      <c r="I33" s="33">
+        <v>0</v>
       </c>
       <c r="J33" s="40"/>
       <c r="L33" s="1" t="str" cm="1">
@@ -23360,11 +23360,11 @@
       <c r="E34" s="39" t="str">
         <v/>
       </c>
-      <c r="F34" s="33">
-        <v>49.999999999999972</v>
-      </c>
-      <c r="G34" s="33" t="str">
-        <v/>
+      <c r="F34" s="33" t="str">
+        <v/>
+      </c>
+      <c r="G34" s="33">
+        <v>290</v>
       </c>
       <c r="H34" s="33" t="str">
         <v/>
@@ -23432,7 +23432,7 @@
         <v>3</v>
       </c>
       <c r="O35" s="40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P35" s="1"/>
       <c r="Q35" s="217" t="str">
@@ -23529,8 +23529,8 @@
       <c r="N37" s="33">
         <v>1</v>
       </c>
-      <c r="O37" s="40" t="str">
-        <v/>
+      <c r="O37" s="40">
+        <v>1</v>
       </c>
       <c r="P37" s="1"/>
       <c r="Q37" s="217" t="str">
@@ -23661,21 +23661,21 @@
       <c r="J42" s="40"/>
       <c r="L42" s="73" t="str" cm="1">
         <f t="array" ref="L42:N48">_xlfn.MAKEARRAY(7,3,_xlfn.LAMBDA(_xlpm.row,_xlpm.col,VLOOKUP(_xlpm.row+(7*(_xlpm.col-1)),_xlfn.CHOOSECOLS(PalmonList,27,1),2,FALSE)))</f>
-        <v>Bufonobi</v>
+        <v>Glacewing</v>
       </c>
       <c r="M42" s="74" t="str">
-        <v>Pipistrigoi</v>
+        <v>Spookaboo</v>
       </c>
       <c r="N42" s="75" t="str">
-        <v>Magmolin</v>
+        <v>Battereina</v>
       </c>
       <c r="O42" s="1"/>
       <c r="P42" s="1" t="str" cm="1">
         <f t="array" ref="P42:Q48">_xlfn.MAKEARRAY(7,2,_xlfn.LAMBDA(_xlpm.row,_xlpm.col,VLOOKUP(_xlpm.row+(7*(_xlpm.col-1)),_xlfn.CHOOSECOLS(PalmonList,27,1,3),2,FALSE)))</f>
-        <v>Bufonobi</v>
+        <v>Glacewing</v>
       </c>
       <c r="Q42" s="1" t="str">
-        <v>Pipistrigoi</v>
+        <v>Spookaboo</v>
       </c>
       <c r="R42" s="1"/>
       <c r="T42"/>
@@ -23694,20 +23694,20 @@
       <c r="I43" s="33"/>
       <c r="J43" s="40"/>
       <c r="L43" s="76" t="str">
-        <v>Vulpyrean</v>
+        <v>Bufonobi</v>
       </c>
       <c r="M43" s="77" t="str">
-        <v>Ghillant</v>
+        <v>Pipistrigoi</v>
       </c>
       <c r="N43" s="78" t="str">
-        <v>Barkplug</v>
+        <v>Magmolin</v>
       </c>
       <c r="O43" s="1"/>
       <c r="P43" s="1" t="str">
-        <v>Vulpyrean</v>
+        <v>Bufonobi</v>
       </c>
       <c r="Q43" s="1" t="str">
-        <v>Ghillant</v>
+        <v>Pipistrigoi</v>
       </c>
       <c r="R43" s="1"/>
       <c r="T43"/>
@@ -23726,20 +23726,20 @@
       <c r="I44" s="33"/>
       <c r="J44" s="40"/>
       <c r="L44" s="76" t="str">
-        <v>Gnashfin</v>
+        <v>Vulpyrean</v>
       </c>
       <c r="M44" s="77" t="str">
-        <v>Hoofrit</v>
+        <v>Ghillant</v>
       </c>
       <c r="N44" s="78" t="str">
-        <v>Blazeal</v>
+        <v>Fulgairy</v>
       </c>
       <c r="O44" s="1"/>
       <c r="P44" s="1" t="str">
-        <v>Gnashfin</v>
+        <v>Vulpyrean</v>
       </c>
       <c r="Q44" s="1" t="str">
-        <v>Hoofrit</v>
+        <v>Ghillant</v>
       </c>
       <c r="R44" s="1"/>
       <c r="T44"/>
@@ -23758,20 +23758,20 @@
       <c r="I45" s="33"/>
       <c r="J45" s="40"/>
       <c r="L45" s="76" t="str">
-        <v>Glacewing</v>
+        <v>Gnashfin</v>
       </c>
       <c r="M45" s="77" t="str">
-        <v>Lucidina</v>
+        <v>Abuzzinian</v>
       </c>
       <c r="N45" s="78" t="str">
-        <v>Battereina</v>
+        <v>Barkplug</v>
       </c>
       <c r="O45" s="1"/>
       <c r="P45" s="1" t="str">
-        <v>Glacewing</v>
+        <v>Gnashfin</v>
       </c>
       <c r="Q45" s="1" t="str">
-        <v>Lucidina</v>
+        <v>Abuzzinian</v>
       </c>
       <c r="R45" s="1"/>
       <c r="T45"/>
@@ -23784,17 +23784,17 @@
         <v>Fleurizard</v>
       </c>
       <c r="M46" s="77" t="str">
-        <v>Abuzzinian</v>
+        <v>Kungpaw</v>
       </c>
       <c r="N46" s="78" t="str">
-        <v>Mantleray</v>
+        <v>Statchew</v>
       </c>
       <c r="O46" s="1"/>
       <c r="P46" s="1" t="str">
         <v>Fleurizard</v>
       </c>
       <c r="Q46" s="1" t="str">
-        <v>Abuzzinian</v>
+        <v>Kungpaw</v>
       </c>
       <c r="R46" s="1"/>
       <c r="T46"/>
@@ -23804,20 +23804,20 @@
     </row>
     <row r="47" spans="2:23" x14ac:dyDescent="0.25">
       <c r="L47" s="76" t="str">
-        <v>Oleana</v>
+        <v>Thundertooth</v>
       </c>
       <c r="M47" s="77" t="str">
-        <v>Kungpaw</v>
+        <v>Hoofrit</v>
       </c>
       <c r="N47" s="78" t="str">
-        <v>Escarffier</v>
+        <v>Blazeal</v>
       </c>
       <c r="O47" s="1"/>
       <c r="P47" s="1" t="str">
-        <v>Oleana</v>
+        <v>Thundertooth</v>
       </c>
       <c r="Q47" s="1" t="str">
-        <v>Kungpaw</v>
+        <v>Hoofrit</v>
       </c>
       <c r="R47" s="1"/>
       <c r="T47"/>
@@ -23827,20 +23827,20 @@
     </row>
     <row r="48" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L48" s="81" t="str">
-        <v>Thundertooth</v>
+        <v>Oleana</v>
       </c>
       <c r="M48" s="82" t="str">
-        <v>Spookaboo</v>
+        <v>Lucidina</v>
       </c>
       <c r="N48" s="83" t="str">
-        <v>Ninjump</v>
+        <v>Baboom</v>
       </c>
       <c r="O48" s="1"/>
       <c r="P48" s="1" t="str">
-        <v>Thundertooth</v>
+        <v>Oleana</v>
       </c>
       <c r="Q48" s="1" t="str">
-        <v>Spookaboo</v>
+        <v>Lucidina</v>
       </c>
       <c r="R48" s="1"/>
       <c r="T48"/>
@@ -23907,7 +23907,7 @@
         <v/>
       </c>
       <c r="H52" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L52" s="1" t="str">
         <v>Abuzzinian</v>
@@ -23916,7 +23916,7 @@
         <v/>
       </c>
       <c r="N52" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P52" s="1" t="str" cm="1">
         <f t="array" ref="P52:P78">_xlfn.LAMBDA(_xlpm.row,IFERROR(_xlfn.RANK.EQ(_xlpm.row,M$52:M$78,1),""))(M$52:M$78)</f>
@@ -23937,7 +23937,7 @@
     </row>
     <row r="53" spans="7:20" s="1" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="G53" s="1">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H53" s="1" t="str">
         <v/>
@@ -23946,13 +23946,13 @@
         <v>Baboom</v>
       </c>
       <c r="M53" s="1">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="N53" s="1" t="str">
         <v/>
       </c>
       <c r="P53" s="1">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Q53" s="1" t="str">
         <v/>
@@ -23969,7 +23969,7 @@
         <v/>
       </c>
       <c r="H54" s="1">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L54" s="1" t="str">
         <v>Barkplug</v>
@@ -23978,24 +23978,24 @@
         <v/>
       </c>
       <c r="N54" s="1">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="P54" s="1" t="str">
         <v/>
       </c>
       <c r="Q54" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S54" s="1" t="str">
         <v>Hoofrit</v>
       </c>
       <c r="T54" s="1" t="str">
-        <v>Escarffier</v>
+        <v>Fulgairy</v>
       </c>
     </row>
     <row r="55" spans="7:20" s="1" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="G55" s="1">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H55" s="1" t="str">
         <v/>
@@ -24004,13 +24004,13 @@
         <v>Battereina</v>
       </c>
       <c r="M55" s="1">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="N55" s="1" t="str">
         <v/>
       </c>
       <c r="P55" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q55" s="1" t="str">
         <v/>
@@ -24024,7 +24024,7 @@
     </row>
     <row r="56" spans="7:20" s="1" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="G56" s="1">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H56" s="1" t="str">
         <v/>
@@ -24033,13 +24033,13 @@
         <v>Blazeal</v>
       </c>
       <c r="M56" s="1">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N56" s="1" t="str">
         <v/>
       </c>
       <c r="P56" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q56" s="1" t="str">
         <v/>
@@ -24062,7 +24062,7 @@
         <v>Bufonobi</v>
       </c>
       <c r="M57" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N57" s="1" t="str">
         <v/>
@@ -24085,7 +24085,7 @@
         <v/>
       </c>
       <c r="H58" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L58" s="1" t="str">
         <v>Dolphriend</v>
@@ -24094,7 +24094,7 @@
         <v/>
       </c>
       <c r="N58" s="1">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="P58" s="1" t="str">
         <v/>
@@ -24114,7 +24114,7 @@
         <v/>
       </c>
       <c r="H59" s="1">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L59" s="1" t="str">
         <v>Escarffier</v>
@@ -24123,18 +24123,18 @@
         <v/>
       </c>
       <c r="N59" s="1">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="P59" s="1" t="str">
         <v/>
       </c>
       <c r="Q59" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60" spans="7:20" s="1" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="G60" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H60" s="1" t="str">
         <v/>
@@ -24143,13 +24143,13 @@
         <v>Fingenue</v>
       </c>
       <c r="M60" s="1">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N60" s="1" t="str">
         <v/>
       </c>
       <c r="P60" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q60" s="1" t="str">
         <v/>
@@ -24183,7 +24183,7 @@
         <v/>
       </c>
       <c r="H62" s="1">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="L62" s="1" t="str">
         <v>Fulgairy</v>
@@ -24192,13 +24192,13 @@
         <v/>
       </c>
       <c r="N62" s="1">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="P62" s="1" t="str">
         <v/>
       </c>
       <c r="Q62" s="1">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63" spans="7:20" s="1" customFormat="1" ht="12" x14ac:dyDescent="0.2">
@@ -24206,7 +24206,7 @@
         <v/>
       </c>
       <c r="H63" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L63" s="1" t="str">
         <v>Ghillant</v>
@@ -24215,7 +24215,7 @@
         <v/>
       </c>
       <c r="N63" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P63" s="1" t="str">
         <v/>
@@ -24238,7 +24238,7 @@
         <v/>
       </c>
       <c r="N64" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P64" s="1" t="str">
         <v/>
@@ -24272,7 +24272,7 @@
     </row>
     <row r="66" spans="7:20" s="1" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="G66" s="1">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H66" s="1" t="str">
         <v/>
@@ -24281,13 +24281,13 @@
         <v>Hoofrit</v>
       </c>
       <c r="M66" s="1">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="N66" s="1" t="str">
         <v/>
       </c>
       <c r="P66" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q66" s="1" t="str">
         <v/>
@@ -24298,7 +24298,7 @@
         <v/>
       </c>
       <c r="H67" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L67" s="1" t="str">
         <v>Kungpaw</v>
@@ -24307,7 +24307,7 @@
         <v/>
       </c>
       <c r="N67" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P67" s="1" t="str">
         <v/>
@@ -24318,7 +24318,7 @@
     </row>
     <row r="68" spans="7:20" s="1" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="G68" s="1">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H68" s="1" t="str">
         <v/>
@@ -24327,13 +24327,13 @@
         <v>Limudroid</v>
       </c>
       <c r="M68" s="1">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="N68" s="1" t="str">
         <v/>
       </c>
       <c r="P68" s="1">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q68" s="1" t="str">
         <v/>
@@ -24341,7 +24341,7 @@
     </row>
     <row r="69" spans="7:20" s="1" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="G69" s="1">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H69" s="1" t="str">
         <v/>
@@ -24350,13 +24350,13 @@
         <v>Lucidina</v>
       </c>
       <c r="M69" s="1">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="N69" s="1" t="str">
         <v/>
       </c>
       <c r="P69" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q69" s="1" t="str">
         <v/>
@@ -24367,7 +24367,7 @@
         <v/>
       </c>
       <c r="H70" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L70" s="1" t="str">
         <v>Magmolin</v>
@@ -24376,7 +24376,7 @@
         <v/>
       </c>
       <c r="N70" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P70" s="1" t="str">
         <v/>
@@ -24387,7 +24387,7 @@
     </row>
     <row r="71" spans="7:20" s="1" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="G71" s="1">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H71" s="1" t="str">
         <v/>
@@ -24396,13 +24396,13 @@
         <v>Mantleray</v>
       </c>
       <c r="M71" s="1">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="N71" s="1" t="str">
         <v/>
       </c>
       <c r="P71" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q71" s="1" t="str">
         <v/>
@@ -24410,7 +24410,7 @@
     </row>
     <row r="72" spans="7:20" s="1" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="G72" s="1">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H72" s="1" t="str">
         <v/>
@@ -24419,13 +24419,13 @@
         <v>Ninjump</v>
       </c>
       <c r="M72" s="1">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N72" s="1" t="str">
         <v/>
       </c>
       <c r="P72" s="1">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q72" s="1" t="str">
         <v/>
@@ -24442,7 +24442,7 @@
         <v>Oleana</v>
       </c>
       <c r="M73" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N73" s="1" t="str">
         <v/>
@@ -24456,7 +24456,7 @@
     </row>
     <row r="74" spans="7:20" s="1" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="G74" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H74" s="1" t="str">
         <v/>
@@ -24465,13 +24465,13 @@
         <v>Pipistrigoi</v>
       </c>
       <c r="M74" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N74" s="1" t="str">
         <v/>
       </c>
       <c r="P74" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q74" s="1" t="str">
         <v/>
@@ -24482,7 +24482,7 @@
         <v/>
       </c>
       <c r="H75" s="1">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L75" s="1" t="str">
         <v>Regalion</v>
@@ -24491,7 +24491,7 @@
         <v/>
       </c>
       <c r="N75" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P75" s="1" t="str">
         <v/>
@@ -24502,7 +24502,7 @@
     </row>
     <row r="76" spans="7:20" s="1" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="G76" s="1">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H76" s="1" t="str">
         <v/>
@@ -24511,13 +24511,13 @@
         <v>Salamantis</v>
       </c>
       <c r="M76" s="1">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="N76" s="1" t="str">
         <v/>
       </c>
       <c r="P76" s="1">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Q76" s="1" t="str">
         <v/>
@@ -24525,7 +24525,7 @@
     </row>
     <row r="77" spans="7:20" s="1" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="G77" s="1">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H77" s="1" t="str">
         <v/>
@@ -24534,13 +24534,13 @@
         <v>Spookaboo</v>
       </c>
       <c r="M77" s="1">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="N77" s="1" t="str">
         <v/>
       </c>
       <c r="P77" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Q77" s="1" t="str">
         <v/>
@@ -24551,7 +24551,7 @@
         <v/>
       </c>
       <c r="H78" s="1">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="L78" s="1" t="str">
         <v>Statchew</v>
@@ -24560,7 +24560,7 @@
         <v/>
       </c>
       <c r="N78" s="1">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="P78" s="1" t="str">
         <v/>
@@ -24574,7 +24574,7 @@
         <v>Surveilynx</v>
       </c>
       <c r="M79" s="1">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N79" s="1" t="str">
         <v/>
@@ -24589,7 +24589,7 @@
         <v>Vulpyrean</v>
       </c>
       <c r="M80" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N80" s="1" t="str">
         <v/>
@@ -36281,7 +36281,7 @@
         <v>85.7</v>
       </c>
       <c r="I256" s="1">
-        <f t="shared" ref="I256:I272" si="33">H256*1000000</f>
+        <f t="shared" ref="I256:I282" si="33">H256*1000000</f>
         <v>85700000</v>
       </c>
     </row>
@@ -36820,19 +36820,26 @@
         <v>271</v>
       </c>
       <c r="C273" s="4">
-        <v>135120000</v>
+        <v>123200000</v>
       </c>
       <c r="D273" s="4">
         <f t="shared" si="36"/>
-        <v>14420000</v>
+        <v>2500000</v>
       </c>
       <c r="E273" s="4">
         <f t="shared" si="37"/>
-        <v>5044093700</v>
+        <v>5032173700</v>
       </c>
       <c r="F273" s="3" t="str" cm="1">
         <f t="array" ref="F273">CostScreen($C273)</f>
-        <v>135,12M</v>
+        <v>123,2M</v>
+      </c>
+      <c r="H273" s="1">
+        <v>123.2</v>
+      </c>
+      <c r="I273" s="1">
+        <f t="shared" si="33"/>
+        <v>123200000</v>
       </c>
     </row>
     <row r="274" spans="1:11" x14ac:dyDescent="0.2">
@@ -36845,19 +36852,26 @@
         <v>272</v>
       </c>
       <c r="C274" s="4">
-        <v>135120000</v>
+        <v>125700000</v>
       </c>
       <c r="D274" s="4">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>2500000</v>
       </c>
       <c r="E274" s="4">
         <f t="shared" si="37"/>
-        <v>5179213700</v>
+        <v>5157873700</v>
       </c>
       <c r="F274" s="3" t="str" cm="1">
         <f t="array" ref="F274">CostScreen($C274)</f>
-        <v>135,12M</v>
+        <v>125,7M</v>
+      </c>
+      <c r="H274" s="1">
+        <v>125.7</v>
+      </c>
+      <c r="I274" s="1">
+        <f t="shared" si="33"/>
+        <v>125700000</v>
       </c>
     </row>
     <row r="275" spans="1:11" x14ac:dyDescent="0.2">
@@ -36870,19 +36884,26 @@
         <v>273</v>
       </c>
       <c r="C275" s="4">
-        <v>135120000</v>
+        <v>128300000.00000001</v>
       </c>
       <c r="D275" s="4">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>2600000.0000000149</v>
       </c>
       <c r="E275" s="4">
         <f t="shared" si="37"/>
-        <v>5314333700</v>
+        <v>5286173700</v>
       </c>
       <c r="F275" s="3" t="str" cm="1">
         <f t="array" ref="F275">CostScreen($C275)</f>
-        <v>135,12M</v>
+        <v>128,3M</v>
+      </c>
+      <c r="H275" s="1">
+        <v>128.30000000000001</v>
+      </c>
+      <c r="I275" s="1">
+        <f t="shared" si="33"/>
+        <v>128300000.00000001</v>
       </c>
     </row>
     <row r="276" spans="1:11" x14ac:dyDescent="0.2">
@@ -36895,19 +36916,26 @@
         <v>274</v>
       </c>
       <c r="C276" s="4">
-        <v>135120000</v>
+        <v>130900000</v>
       </c>
       <c r="D276" s="4">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>2599999.9999999851</v>
       </c>
       <c r="E276" s="4">
         <f t="shared" si="37"/>
-        <v>5449453700</v>
+        <v>5417073700</v>
       </c>
       <c r="F276" s="3" t="str" cm="1">
         <f t="array" ref="F276">CostScreen($C276)</f>
-        <v>135,12M</v>
+        <v>130,9M</v>
+      </c>
+      <c r="H276" s="1">
+        <v>130.9</v>
+      </c>
+      <c r="I276" s="1">
+        <f t="shared" si="33"/>
+        <v>130900000</v>
       </c>
     </row>
     <row r="277" spans="1:11" x14ac:dyDescent="0.2">
@@ -36920,19 +36948,26 @@
         <v>275</v>
       </c>
       <c r="C277" s="4">
-        <v>135120000</v>
+        <v>133600000</v>
       </c>
       <c r="D277" s="4">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>2700000</v>
       </c>
       <c r="E277" s="4">
         <f t="shared" si="37"/>
-        <v>5584573700</v>
+        <v>5550673700</v>
       </c>
       <c r="F277" s="3" t="str" cm="1">
         <f t="array" ref="F277">CostScreen($C277)</f>
-        <v>135,12M</v>
+        <v>133,6M</v>
+      </c>
+      <c r="H277" s="1">
+        <v>133.6</v>
+      </c>
+      <c r="I277" s="1">
+        <f t="shared" si="33"/>
+        <v>133600000</v>
       </c>
     </row>
     <row r="278" spans="1:11" x14ac:dyDescent="0.2">
@@ -36945,19 +36980,26 @@
         <v>276</v>
       </c>
       <c r="C278" s="4">
-        <v>135120000</v>
+        <v>136300000</v>
       </c>
       <c r="D278" s="4">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>2700000</v>
       </c>
       <c r="E278" s="4">
         <f t="shared" si="37"/>
-        <v>5719693700</v>
+        <v>5686973700</v>
       </c>
       <c r="F278" s="3" t="str" cm="1">
         <f t="array" ref="F278">CostScreen($C278)</f>
-        <v>135,12M</v>
+        <v>136,3M</v>
+      </c>
+      <c r="H278" s="1">
+        <v>136.30000000000001</v>
+      </c>
+      <c r="I278" s="1">
+        <f t="shared" si="33"/>
+        <v>136300000</v>
       </c>
     </row>
     <row r="279" spans="1:11" x14ac:dyDescent="0.2">
@@ -36970,19 +37012,26 @@
         <v>277</v>
       </c>
       <c r="C279" s="4">
-        <v>135120000</v>
+        <v>139100000</v>
       </c>
       <c r="D279" s="4">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>2800000</v>
       </c>
       <c r="E279" s="4">
         <f t="shared" si="37"/>
-        <v>5854813700</v>
+        <v>5826073700</v>
       </c>
       <c r="F279" s="3" t="str" cm="1">
         <f t="array" ref="F279">CostScreen($C279)</f>
-        <v>135,12M</v>
+        <v>139,1M</v>
+      </c>
+      <c r="H279" s="1">
+        <v>139.1</v>
+      </c>
+      <c r="I279" s="1">
+        <f t="shared" si="33"/>
+        <v>139100000</v>
       </c>
     </row>
     <row r="280" spans="1:11" x14ac:dyDescent="0.2">
@@ -36995,19 +37044,26 @@
         <v>278</v>
       </c>
       <c r="C280" s="4">
-        <v>135120000</v>
+        <v>141800000</v>
       </c>
       <c r="D280" s="4">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>2700000</v>
       </c>
       <c r="E280" s="4">
         <f t="shared" si="37"/>
-        <v>5989933700</v>
+        <v>5967873700</v>
       </c>
       <c r="F280" s="3" t="str" cm="1">
         <f t="array" ref="F280">CostScreen($C280)</f>
-        <v>135,12M</v>
+        <v>141,8M</v>
+      </c>
+      <c r="H280" s="1">
+        <v>141.80000000000001</v>
+      </c>
+      <c r="I280" s="1">
+        <f t="shared" si="33"/>
+        <v>141800000</v>
       </c>
     </row>
     <row r="281" spans="1:11" x14ac:dyDescent="0.2">
@@ -37020,19 +37076,26 @@
         <v>279</v>
       </c>
       <c r="C281" s="4">
-        <v>135120000</v>
+        <v>144700000</v>
       </c>
       <c r="D281" s="4">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>2900000</v>
       </c>
       <c r="E281" s="4">
         <f t="shared" si="37"/>
-        <v>6125053700</v>
+        <v>6112573700</v>
       </c>
       <c r="F281" s="3" t="str" cm="1">
         <f t="array" ref="F281">CostScreen($C281)</f>
-        <v>135,12M</v>
+        <v>144,7M</v>
+      </c>
+      <c r="H281" s="1">
+        <v>144.69999999999999</v>
+      </c>
+      <c r="I281" s="1">
+        <f t="shared" si="33"/>
+        <v>144700000</v>
       </c>
     </row>
     <row r="282" spans="1:11" x14ac:dyDescent="0.2">
@@ -37045,11 +37108,11 @@
         <v>280</v>
       </c>
       <c r="C282" s="4">
-        <v>135120000</v>
+        <v>147600000</v>
       </c>
       <c r="D282" s="4">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>2900000</v>
       </c>
       <c r="E282" s="4">
         <f t="shared" si="37"/>
@@ -37057,7 +37120,14 @@
       </c>
       <c r="F282" s="3" t="str" cm="1">
         <f t="array" ref="F282">CostScreen($C282)</f>
-        <v>135,12M</v>
+        <v>147,6M</v>
+      </c>
+      <c r="H282" s="1">
+        <v>147.6</v>
+      </c>
+      <c r="I282" s="1">
+        <f t="shared" si="33"/>
+        <v>147600000</v>
       </c>
       <c r="J282" s="1">
         <f>K282/10</f>
@@ -37081,7 +37151,7 @@
       </c>
       <c r="D283" s="4">
         <f t="shared" si="36"/>
-        <v>29320000</v>
+        <v>16840000</v>
       </c>
       <c r="E283" s="4">
         <f t="shared" si="37"/>
@@ -37922,11 +37992,11 @@
         <v>4</v>
       </c>
       <c r="E6" s="4">
-        <v>1000</v>
+        <v>2500</v>
       </c>
       <c r="F6" s="4">
         <f t="shared" si="0"/>
-        <v>5000</v>
+        <v>12500</v>
       </c>
       <c r="H6" s="245" t="s">
         <v>250</v>
@@ -37938,16 +38008,16 @@
         <v>150</v>
       </c>
       <c r="K6" s="246">
-        <v>2.2000000000000002</v>
+        <v>3</v>
       </c>
       <c r="L6" s="4">
         <v>5</v>
       </c>
       <c r="M6" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N6" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O6" s="4">
         <v>0</v>
@@ -37979,11 +38049,11 @@
         <v>5</v>
       </c>
       <c r="E7" s="4">
-        <v>1200</v>
+        <v>5000</v>
       </c>
       <c r="F7" s="4">
         <f t="shared" si="0"/>
-        <v>6000</v>
+        <v>25000</v>
       </c>
       <c r="H7" s="245" t="s">
         <v>251</v>
@@ -37992,7 +38062,7 @@
         <v>55</v>
       </c>
       <c r="J7" s="4">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="K7" s="246">
         <v>0</v>
